--- a/artfynd/A 46357-2025 artfynd.xlsx
+++ b/artfynd/A 46357-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129298751</v>
+        <v>129298851</v>
       </c>
       <c r="B2" t="n">
-        <v>57725</v>
+        <v>91554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487263</v>
+        <v>487144</v>
       </c>
       <c r="R2" t="n">
-        <v>7038949</v>
+        <v>7039078</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129298818</v>
+        <v>129298751</v>
       </c>
       <c r="B3" t="n">
         <v>57725</v>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487389</v>
+        <v>487263</v>
       </c>
       <c r="R3" t="n">
-        <v>7038925</v>
+        <v>7038949</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +874,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129298819</v>
+        <v>129298786</v>
       </c>
       <c r="B4" t="n">
         <v>57725</v>
@@ -914,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487346</v>
+        <v>487006</v>
       </c>
       <c r="R4" t="n">
-        <v>7038911</v>
+        <v>7039175</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129298844</v>
+        <v>129298818</v>
       </c>
       <c r="B5" t="n">
-        <v>78052</v>
+        <v>57725</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>487374</v>
+        <v>487389</v>
       </c>
       <c r="R5" t="n">
-        <v>7039027</v>
+        <v>7038925</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1052,6 +1047,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129298827</v>
+        <v>129298819</v>
       </c>
       <c r="B6" t="n">
-        <v>57885</v>
+        <v>57725</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>487352</v>
+        <v>487346</v>
       </c>
       <c r="R6" t="n">
-        <v>7038906</v>
+        <v>7038911</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129298851</v>
+        <v>129298827</v>
       </c>
       <c r="B7" t="n">
-        <v>91547</v>
+        <v>57885</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>487144</v>
+        <v>487352</v>
       </c>
       <c r="R7" t="n">
-        <v>7039078</v>
+        <v>7038906</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1251,6 +1251,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,10 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129298786</v>
+        <v>129298844</v>
       </c>
       <c r="B8" t="n">
-        <v>57725</v>
+        <v>78052</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1293,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>487006</v>
+        <v>487374</v>
       </c>
       <c r="R8" t="n">
-        <v>7039175</v>
+        <v>7039027</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1348,11 +1353,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129298838</v>
+        <v>129298742</v>
       </c>
       <c r="B9" t="n">
-        <v>80144</v>
+        <v>91540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1390,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>487035</v>
+        <v>487129</v>
       </c>
       <c r="R9" t="n">
-        <v>7039161</v>
+        <v>7039097</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129298759</v>
+        <v>129298838</v>
       </c>
       <c r="B10" t="n">
-        <v>57725</v>
+        <v>80144</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,21 +1487,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>487171</v>
+        <v>487035</v>
       </c>
       <c r="R10" t="n">
-        <v>7039000</v>
+        <v>7039161</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1547,11 +1547,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,10 +1573,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129298742</v>
+        <v>129298812</v>
       </c>
       <c r="B11" t="n">
-        <v>91533</v>
+        <v>57725</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,21 +1584,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1613,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>487129</v>
+        <v>487362</v>
       </c>
       <c r="R11" t="n">
-        <v>7039097</v>
+        <v>7039030</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,6 +1644,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1675,7 +1675,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129298812</v>
+        <v>129298759</v>
       </c>
       <c r="B12" t="n">
         <v>57725</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>487362</v>
+        <v>487171</v>
       </c>
       <c r="R12" t="n">
-        <v>7039030</v>
+        <v>7039000</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1777,7 +1777,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129298799</v>
+        <v>129298761</v>
       </c>
       <c r="B13" t="n">
         <v>57725</v>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>487230</v>
+        <v>487137</v>
       </c>
       <c r="R13" t="n">
-        <v>7039041</v>
+        <v>7039024</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129298761</v>
+        <v>129298755</v>
       </c>
       <c r="B14" t="n">
         <v>57725</v>
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>487137</v>
+        <v>487206</v>
       </c>
       <c r="R14" t="n">
-        <v>7039024</v>
+        <v>7038982</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1981,7 +1981,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129298755</v>
+        <v>129298799</v>
       </c>
       <c r="B15" t="n">
         <v>57725</v>
@@ -2016,10 +2016,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>487206</v>
+        <v>487230</v>
       </c>
       <c r="R15" t="n">
-        <v>7038982</v>
+        <v>7039041</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129298787</v>
+        <v>129298857</v>
       </c>
       <c r="B16" t="n">
-        <v>57725</v>
+        <v>82997</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2094,21 +2094,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486999</v>
+        <v>487340</v>
       </c>
       <c r="R16" t="n">
-        <v>7039162</v>
+        <v>7039016</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2154,11 +2154,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2185,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129298857</v>
+        <v>129298855</v>
       </c>
       <c r="B17" t="n">
-        <v>83007</v>
+        <v>79039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2196,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2220,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>487340</v>
+        <v>487542</v>
       </c>
       <c r="R17" t="n">
-        <v>7039016</v>
+        <v>7038985</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2282,10 +2277,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129298855</v>
+        <v>129298777</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2293,21 +2288,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2317,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>487542</v>
+        <v>486860</v>
       </c>
       <c r="R18" t="n">
-        <v>7038985</v>
+        <v>7039254</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2353,6 +2348,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2379,7 +2379,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129298777</v>
+        <v>129298787</v>
       </c>
       <c r="B19" t="n">
         <v>57725</v>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486860</v>
+        <v>486999</v>
       </c>
       <c r="R19" t="n">
-        <v>7039254</v>
+        <v>7039162</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2481,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129298845</v>
+        <v>129298775</v>
       </c>
       <c r="B20" t="n">
-        <v>78052</v>
+        <v>57725</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>487526</v>
+        <v>486860</v>
       </c>
       <c r="R20" t="n">
-        <v>7039006</v>
+        <v>7039244</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2552,6 +2552,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2578,7 +2583,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129298780</v>
+        <v>129298808</v>
       </c>
       <c r="B21" t="n">
         <v>57725</v>
@@ -2613,10 +2618,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486859</v>
+        <v>487344</v>
       </c>
       <c r="R21" t="n">
-        <v>7039262</v>
+        <v>7039018</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2653,7 +2658,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2680,10 +2685,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129298837</v>
+        <v>129298780</v>
       </c>
       <c r="B22" t="n">
-        <v>80144</v>
+        <v>57725</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2691,21 +2696,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2715,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>487004</v>
+        <v>486859</v>
       </c>
       <c r="R22" t="n">
-        <v>7039214</v>
+        <v>7039262</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2751,6 +2756,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2777,10 +2787,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129298775</v>
+        <v>129298852</v>
       </c>
       <c r="B23" t="n">
-        <v>57725</v>
+        <v>91554</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2788,21 +2798,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2812,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486860</v>
+        <v>487127</v>
       </c>
       <c r="R23" t="n">
-        <v>7039244</v>
+        <v>7039070</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2848,11 +2858,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2879,10 +2884,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129298740</v>
+        <v>129298837</v>
       </c>
       <c r="B24" t="n">
-        <v>91533</v>
+        <v>80144</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2890,21 +2895,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2914,10 +2919,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>487145</v>
+        <v>487004</v>
       </c>
       <c r="R24" t="n">
-        <v>7039179</v>
+        <v>7039214</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2976,45 +2981,57 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129298852</v>
+        <v>129298830</v>
       </c>
       <c r="B25" t="n">
-        <v>91547</v>
+        <v>57566</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1204</v>
+        <v>102621</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>487127</v>
+        <v>487123</v>
       </c>
       <c r="R25" t="n">
-        <v>7039070</v>
+        <v>7039173</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3073,57 +3090,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129298830</v>
+        <v>129298740</v>
       </c>
       <c r="B26" t="n">
-        <v>57566</v>
+        <v>91540</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102621</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>487123</v>
+        <v>487145</v>
       </c>
       <c r="R26" t="n">
-        <v>7039173</v>
+        <v>7039179</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3182,10 +3187,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129298808</v>
+        <v>129298845</v>
       </c>
       <c r="B27" t="n">
-        <v>57725</v>
+        <v>78052</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3193,21 +3198,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3217,10 +3222,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>487344</v>
+        <v>487526</v>
       </c>
       <c r="R27" t="n">
-        <v>7039018</v>
+        <v>7039006</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3253,11 +3258,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3284,10 +3284,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129298823</v>
+        <v>129298843</v>
       </c>
       <c r="B28" t="n">
-        <v>57725</v>
+        <v>80144</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3295,21 +3295,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3319,10 +3319,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>487363</v>
+        <v>487391</v>
       </c>
       <c r="R28" t="n">
-        <v>7038902</v>
+        <v>7038927</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3355,11 +3355,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3386,7 +3381,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129298778</v>
+        <v>129298793</v>
       </c>
       <c r="B29" t="n">
         <v>57725</v>
@@ -3421,10 +3416,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486871</v>
+        <v>487183</v>
       </c>
       <c r="R29" t="n">
-        <v>7039260</v>
+        <v>7039216</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3488,10 +3483,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129298843</v>
+        <v>129298823</v>
       </c>
       <c r="B30" t="n">
-        <v>80144</v>
+        <v>57725</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3499,21 +3494,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3523,10 +3518,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>487391</v>
+        <v>487363</v>
       </c>
       <c r="R30" t="n">
-        <v>7038927</v>
+        <v>7038902</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3559,6 +3554,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3687,27 +3687,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129298846</v>
+        <v>129298770</v>
       </c>
       <c r="B32" t="n">
-        <v>57829</v>
+        <v>57725</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486976</v>
+        <v>486972</v>
       </c>
       <c r="R32" t="n">
-        <v>7039216</v>
+        <v>7039122</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3758,6 +3758,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3784,7 +3789,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129298770</v>
+        <v>129298778</v>
       </c>
       <c r="B33" t="n">
         <v>57725</v>
@@ -3819,10 +3824,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486972</v>
+        <v>486871</v>
       </c>
       <c r="R33" t="n">
-        <v>7039122</v>
+        <v>7039260</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3886,27 +3891,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129298793</v>
+        <v>129298846</v>
       </c>
       <c r="B34" t="n">
-        <v>57725</v>
+        <v>57829</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3921,7 +3926,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>487183</v>
+        <v>486976</v>
       </c>
       <c r="R34" t="n">
         <v>7039216</v>
@@ -3957,11 +3962,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4192,7 +4192,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129298804</v>
+        <v>129298769</v>
       </c>
       <c r="B37" t="n">
         <v>57725</v>
@@ -4227,10 +4227,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>487288</v>
+        <v>487109</v>
       </c>
       <c r="R37" t="n">
-        <v>7039002</v>
+        <v>7039040</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129298769</v>
+        <v>129298804</v>
       </c>
       <c r="B38" t="n">
         <v>57725</v>
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>487109</v>
+        <v>487288</v>
       </c>
       <c r="R38" t="n">
-        <v>7039040</v>
+        <v>7039002</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4498,10 +4498,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129298805</v>
+        <v>129298833</v>
       </c>
       <c r="B40" t="n">
-        <v>57725</v>
+        <v>80145</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4509,21 +4509,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>487346</v>
+        <v>487265</v>
       </c>
       <c r="R40" t="n">
-        <v>7039012</v>
+        <v>7038997</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4569,11 +4569,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4600,10 +4595,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129298802</v>
+        <v>129298854</v>
       </c>
       <c r="B41" t="n">
-        <v>57725</v>
+        <v>91558</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4611,21 +4606,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4635,10 +4630,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>487302</v>
+        <v>487522</v>
       </c>
       <c r="R41" t="n">
-        <v>7039045</v>
+        <v>7038997</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4671,11 +4666,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4702,7 +4692,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129298783</v>
+        <v>129298805</v>
       </c>
       <c r="B42" t="n">
         <v>57725</v>
@@ -4737,10 +4727,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>487024</v>
+        <v>487346</v>
       </c>
       <c r="R42" t="n">
-        <v>7039203</v>
+        <v>7039012</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4804,10 +4794,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129298840</v>
+        <v>129298809</v>
       </c>
       <c r="B43" t="n">
-        <v>80144</v>
+        <v>57725</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4815,21 +4805,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4839,7 +4829,7 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>487314</v>
+        <v>487348</v>
       </c>
       <c r="R43" t="n">
         <v>7039005</v>
@@ -4875,6 +4865,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4901,7 +4896,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129298795</v>
+        <v>129298802</v>
       </c>
       <c r="B44" t="n">
         <v>57725</v>
@@ -4936,10 +4931,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>487100</v>
+        <v>487302</v>
       </c>
       <c r="R44" t="n">
-        <v>7039085</v>
+        <v>7039045</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5003,10 +4998,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129298833</v>
+        <v>129298795</v>
       </c>
       <c r="B45" t="n">
-        <v>80145</v>
+        <v>57725</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5014,21 +5009,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5038,10 +5033,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>487265</v>
+        <v>487100</v>
       </c>
       <c r="R45" t="n">
-        <v>7038997</v>
+        <v>7039085</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5074,6 +5069,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5100,10 +5100,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129298854</v>
+        <v>129298748</v>
       </c>
       <c r="B46" t="n">
-        <v>91551</v>
+        <v>57725</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5111,21 +5111,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>487522</v>
+        <v>487301</v>
       </c>
       <c r="R46" t="n">
-        <v>7038997</v>
+        <v>7038925</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5171,6 +5171,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5197,7 +5202,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129298748</v>
+        <v>129298783</v>
       </c>
       <c r="B47" t="n">
         <v>57725</v>
@@ -5232,10 +5237,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>487301</v>
+        <v>487024</v>
       </c>
       <c r="R47" t="n">
-        <v>7038925</v>
+        <v>7039203</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5299,10 +5304,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129298809</v>
+        <v>129298840</v>
       </c>
       <c r="B48" t="n">
-        <v>57725</v>
+        <v>80144</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5310,21 +5315,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5334,7 +5339,7 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>487348</v>
+        <v>487314</v>
       </c>
       <c r="R48" t="n">
         <v>7039005</v>
@@ -5370,11 +5375,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5401,10 +5401,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129298810</v>
+        <v>129298856</v>
       </c>
       <c r="B49" t="n">
-        <v>57725</v>
+        <v>82871</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5412,21 +5412,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5436,10 +5436,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>487355</v>
+        <v>487541</v>
       </c>
       <c r="R49" t="n">
-        <v>7039005</v>
+        <v>7038983</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5472,11 +5472,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5503,10 +5498,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129298798</v>
+        <v>129298738</v>
       </c>
       <c r="B50" t="n">
-        <v>57725</v>
+        <v>96922</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5514,21 +5509,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5538,10 +5533,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>487131</v>
+        <v>487311</v>
       </c>
       <c r="R50" t="n">
-        <v>7039049</v>
+        <v>7039063</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5574,11 +5569,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5605,10 +5595,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129298738</v>
+        <v>129298842</v>
       </c>
       <c r="B51" t="n">
-        <v>96915</v>
+        <v>80144</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5616,21 +5606,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5640,10 +5630,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>487311</v>
+        <v>487393</v>
       </c>
       <c r="R51" t="n">
-        <v>7039063</v>
+        <v>7038908</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5702,10 +5692,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129298856</v>
+        <v>129298798</v>
       </c>
       <c r="B52" t="n">
-        <v>82902</v>
+        <v>57725</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5713,21 +5703,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5737,10 +5727,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>487541</v>
+        <v>487131</v>
       </c>
       <c r="R52" t="n">
-        <v>7038983</v>
+        <v>7039049</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5773,6 +5763,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5799,10 +5794,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129298842</v>
+        <v>129298810</v>
       </c>
       <c r="B53" t="n">
-        <v>80144</v>
+        <v>57725</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5810,21 +5805,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5834,10 +5829,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>487393</v>
+        <v>487355</v>
       </c>
       <c r="R53" t="n">
-        <v>7038908</v>
+        <v>7039005</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5870,6 +5865,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5896,10 +5896,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129298779</v>
+        <v>129298825</v>
       </c>
       <c r="B54" t="n">
-        <v>57725</v>
+        <v>57885</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5907,21 +5907,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5931,10 +5931,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486866</v>
+        <v>487247</v>
       </c>
       <c r="R54" t="n">
-        <v>7039259</v>
+        <v>7039020</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5998,7 +5998,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129298749</v>
+        <v>129298779</v>
       </c>
       <c r="B55" t="n">
         <v>57725</v>
@@ -6033,10 +6033,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>487275</v>
+        <v>486866</v>
       </c>
       <c r="R55" t="n">
-        <v>7038947</v>
+        <v>7039259</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6100,10 +6100,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129298825</v>
+        <v>129298749</v>
       </c>
       <c r="B56" t="n">
-        <v>57885</v>
+        <v>57725</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6111,21 +6111,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6135,10 +6135,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>487247</v>
+        <v>487275</v>
       </c>
       <c r="R56" t="n">
-        <v>7039020</v>
+        <v>7038947</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6202,7 +6202,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129298813</v>
+        <v>129298767</v>
       </c>
       <c r="B57" t="n">
         <v>57725</v>
@@ -6237,10 +6237,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>487367</v>
+        <v>487123</v>
       </c>
       <c r="R57" t="n">
-        <v>7038998</v>
+        <v>7039031</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6304,7 +6304,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129298774</v>
+        <v>129298776</v>
       </c>
       <c r="B58" t="n">
         <v>57725</v>
@@ -6339,10 +6339,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>486866</v>
+        <v>486855</v>
       </c>
       <c r="R58" t="n">
-        <v>7039249</v>
+        <v>7039252</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6406,7 +6406,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129298776</v>
+        <v>129298816</v>
       </c>
       <c r="B59" t="n">
         <v>57725</v>
@@ -6441,10 +6441,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>486855</v>
+        <v>487389</v>
       </c>
       <c r="R59" t="n">
-        <v>7039252</v>
+        <v>7038985</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6508,10 +6508,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129298826</v>
+        <v>129298813</v>
       </c>
       <c r="B60" t="n">
-        <v>57885</v>
+        <v>57725</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6519,21 +6519,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6543,10 +6543,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>487457</v>
+        <v>487367</v>
       </c>
       <c r="R60" t="n">
-        <v>7038967</v>
+        <v>7038998</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6610,7 +6610,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129298816</v>
+        <v>129298820</v>
       </c>
       <c r="B61" t="n">
         <v>57725</v>
@@ -6645,10 +6645,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>487389</v>
+        <v>487354</v>
       </c>
       <c r="R61" t="n">
-        <v>7038985</v>
+        <v>7038894</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6712,7 +6712,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129298767</v>
+        <v>129298774</v>
       </c>
       <c r="B62" t="n">
         <v>57725</v>
@@ -6747,10 +6747,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>487123</v>
+        <v>486866</v>
       </c>
       <c r="R62" t="n">
-        <v>7039031</v>
+        <v>7039249</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6916,10 +6916,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129298820</v>
+        <v>129298826</v>
       </c>
       <c r="B64" t="n">
-        <v>57725</v>
+        <v>57885</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6927,21 +6927,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6951,10 +6951,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>487354</v>
+        <v>487457</v>
       </c>
       <c r="R64" t="n">
-        <v>7038894</v>
+        <v>7038967</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7018,10 +7018,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129298811</v>
+        <v>129298853</v>
       </c>
       <c r="B65" t="n">
-        <v>57725</v>
+        <v>91558</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7029,21 +7029,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>487357</v>
+        <v>487415</v>
       </c>
       <c r="R65" t="n">
-        <v>7039009</v>
+        <v>7038971</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7089,11 +7089,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7123,7 +7118,7 @@
         <v>129298741</v>
       </c>
       <c r="B66" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7217,10 +7212,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129298853</v>
+        <v>129298811</v>
       </c>
       <c r="B67" t="n">
-        <v>91551</v>
+        <v>57725</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7228,21 +7223,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7252,10 +7247,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>487415</v>
+        <v>487357</v>
       </c>
       <c r="R67" t="n">
-        <v>7038971</v>
+        <v>7039009</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7288,6 +7283,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7314,32 +7314,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129298821</v>
+        <v>129298831</v>
       </c>
       <c r="B68" t="n">
-        <v>57725</v>
+        <v>82996</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7349,10 +7349,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>487368</v>
+        <v>487307</v>
       </c>
       <c r="R68" t="n">
-        <v>7038892</v>
+        <v>7039016</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7385,11 +7385,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7416,32 +7411,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129298839</v>
+        <v>129298828</v>
       </c>
       <c r="B69" t="n">
-        <v>80144</v>
+        <v>80173</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7454,7 +7449,7 @@
         <v>487269</v>
       </c>
       <c r="R69" t="n">
-        <v>7039001</v>
+        <v>7039004</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7513,32 +7508,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129298828</v>
+        <v>129298839</v>
       </c>
       <c r="B70" t="n">
-        <v>80173</v>
+        <v>80144</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7551,7 +7546,7 @@
         <v>487269</v>
       </c>
       <c r="R70" t="n">
-        <v>7039004</v>
+        <v>7039001</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7610,10 +7605,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129298800</v>
+        <v>129298737</v>
       </c>
       <c r="B71" t="n">
-        <v>57725</v>
+        <v>83005</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7621,50 +7616,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>487288</v>
+        <v>487523</v>
       </c>
       <c r="R71" t="n">
-        <v>7039015</v>
+        <v>7039001</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7697,11 +7676,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Födosökande hane</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7728,7 +7702,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129298803</v>
+        <v>129298797</v>
       </c>
       <c r="B72" t="n">
         <v>57725</v>
@@ -7763,7 +7737,7 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>487303</v>
+        <v>487134</v>
       </c>
       <c r="R72" t="n">
         <v>7039037</v>
@@ -7830,7 +7804,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129298797</v>
+        <v>129298803</v>
       </c>
       <c r="B73" t="n">
         <v>57725</v>
@@ -7865,7 +7839,7 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>487134</v>
+        <v>487303</v>
       </c>
       <c r="R73" t="n">
         <v>7039037</v>
@@ -7932,10 +7906,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129298737</v>
+        <v>129298822</v>
       </c>
       <c r="B74" t="n">
-        <v>83015</v>
+        <v>57725</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7943,21 +7917,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7967,10 +7941,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>487523</v>
+        <v>487373</v>
       </c>
       <c r="R74" t="n">
-        <v>7039001</v>
+        <v>7038897</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8003,6 +7977,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8029,32 +8008,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129298831</v>
+        <v>129298817</v>
       </c>
       <c r="B75" t="n">
-        <v>83006</v>
+        <v>57725</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8064,10 +8043,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>487307</v>
+        <v>487460</v>
       </c>
       <c r="R75" t="n">
-        <v>7039016</v>
+        <v>7038984</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8100,6 +8079,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8126,7 +8110,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129298822</v>
+        <v>129298800</v>
       </c>
       <c r="B76" t="n">
         <v>57725</v>
@@ -8154,17 +8138,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>487373</v>
+        <v>487288</v>
       </c>
       <c r="R76" t="n">
-        <v>7038897</v>
+        <v>7039015</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8201,7 +8201,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Födosökande hane</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8228,7 +8228,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129298817</v>
+        <v>129298821</v>
       </c>
       <c r="B77" t="n">
         <v>57725</v>
@@ -8263,10 +8263,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>487460</v>
+        <v>487368</v>
       </c>
       <c r="R77" t="n">
-        <v>7038984</v>
+        <v>7038892</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8330,7 +8330,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129298757</v>
+        <v>129298781</v>
       </c>
       <c r="B78" t="n">
         <v>57725</v>
@@ -8365,10 +8365,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>487188</v>
+        <v>486864</v>
       </c>
       <c r="R78" t="n">
-        <v>7038992</v>
+        <v>7039272</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8432,7 +8432,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129298781</v>
+        <v>129298785</v>
       </c>
       <c r="B79" t="n">
         <v>57725</v>
@@ -8467,10 +8467,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>486864</v>
+        <v>487007</v>
       </c>
       <c r="R79" t="n">
-        <v>7039272</v>
+        <v>7039210</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8636,7 +8636,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129298784</v>
+        <v>129298757</v>
       </c>
       <c r="B81" t="n">
         <v>57725</v>
@@ -8671,10 +8671,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>487011</v>
+        <v>487188</v>
       </c>
       <c r="R81" t="n">
-        <v>7039207</v>
+        <v>7038992</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8738,7 +8738,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129298785</v>
+        <v>129298784</v>
       </c>
       <c r="B82" t="n">
         <v>57725</v>
@@ -8773,10 +8773,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>487007</v>
+        <v>487011</v>
       </c>
       <c r="R82" t="n">
-        <v>7039210</v>
+        <v>7039207</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8813,7 +8813,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8840,10 +8840,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129298772</v>
+        <v>129298841</v>
       </c>
       <c r="B83" t="n">
-        <v>57725</v>
+        <v>80144</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8851,21 +8851,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8875,10 +8875,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>486849</v>
+        <v>487515</v>
       </c>
       <c r="R83" t="n">
-        <v>7039185</v>
+        <v>7038993</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8911,11 +8911,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8942,10 +8937,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129298841</v>
+        <v>129298771</v>
       </c>
       <c r="B84" t="n">
-        <v>80144</v>
+        <v>57725</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8953,21 +8948,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8977,10 +8972,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>487515</v>
+        <v>486885</v>
       </c>
       <c r="R84" t="n">
-        <v>7038993</v>
+        <v>7039172</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9013,6 +9008,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9039,45 +9039,61 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129298746</v>
+        <v>129298847</v>
       </c>
       <c r="B85" t="n">
-        <v>57725</v>
+        <v>57585</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>100136</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>487316</v>
+        <v>486999</v>
       </c>
       <c r="R85" t="n">
-        <v>7038914</v>
+        <v>7039199</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9114,7 +9130,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Jagades av en nötskrika</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9447,7 +9463,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129298771</v>
+        <v>129298772</v>
       </c>
       <c r="B89" t="n">
         <v>57725</v>
@@ -9482,10 +9498,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>486885</v>
+        <v>486849</v>
       </c>
       <c r="R89" t="n">
-        <v>7039172</v>
+        <v>7039185</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9549,61 +9565,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129298847</v>
+        <v>129298746</v>
       </c>
       <c r="B90" t="n">
-        <v>57585</v>
+        <v>57725</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100136</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>486999</v>
+        <v>487316</v>
       </c>
       <c r="R90" t="n">
-        <v>7039199</v>
+        <v>7038914</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9640,7 +9640,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Jagades av en nötskrika</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9667,10 +9667,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129298836</v>
+        <v>129298752</v>
       </c>
       <c r="B91" t="n">
-        <v>80144</v>
+        <v>57725</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9678,21 +9678,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9702,10 +9702,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>486899</v>
+        <v>487246</v>
       </c>
       <c r="R91" t="n">
-        <v>7039370</v>
+        <v>7038958</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9738,6 +9738,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9764,7 +9769,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129298752</v>
+        <v>129298768</v>
       </c>
       <c r="B92" t="n">
         <v>57725</v>
@@ -9799,10 +9804,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>487246</v>
+        <v>487123</v>
       </c>
       <c r="R92" t="n">
-        <v>7038958</v>
+        <v>7039032</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9869,7 +9874,7 @@
         <v>129298743</v>
       </c>
       <c r="B93" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9963,10 +9968,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129298768</v>
+        <v>129298836</v>
       </c>
       <c r="B94" t="n">
-        <v>57725</v>
+        <v>80144</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9974,21 +9979,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9998,10 +10003,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>487123</v>
+        <v>486899</v>
       </c>
       <c r="R94" t="n">
-        <v>7039032</v>
+        <v>7039370</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10034,11 +10039,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10167,32 +10167,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129298739</v>
+        <v>129298791</v>
       </c>
       <c r="B96" t="n">
-        <v>91497</v>
+        <v>57725</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10202,10 +10202,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>487384</v>
+        <v>487112</v>
       </c>
       <c r="R96" t="n">
-        <v>7038973</v>
+        <v>7039182</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10238,6 +10238,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10264,7 +10269,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129298791</v>
+        <v>129298754</v>
       </c>
       <c r="B97" t="n">
         <v>57725</v>
@@ -10299,10 +10304,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>487112</v>
+        <v>487222</v>
       </c>
       <c r="R97" t="n">
-        <v>7039182</v>
+        <v>7038974</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10339,7 +10344,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10366,32 +10371,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129298754</v>
+        <v>129298739</v>
       </c>
       <c r="B98" t="n">
-        <v>57725</v>
+        <v>91504</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10401,10 +10406,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>487222</v>
+        <v>487384</v>
       </c>
       <c r="R98" t="n">
-        <v>7038974</v>
+        <v>7038973</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10437,11 +10442,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10683,32 +10683,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129298806</v>
+        <v>129298832</v>
       </c>
       <c r="B101" t="n">
-        <v>57725</v>
+        <v>82996</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10718,10 +10718,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>487339</v>
+        <v>487393</v>
       </c>
       <c r="R101" t="n">
-        <v>7039009</v>
+        <v>7038976</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10754,11 +10754,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10785,10 +10780,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129298782</v>
+        <v>129298858</v>
       </c>
       <c r="B102" t="n">
-        <v>57725</v>
+        <v>82997</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10796,21 +10791,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10820,10 +10815,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>486857</v>
+        <v>487408</v>
       </c>
       <c r="R102" t="n">
-        <v>7039276</v>
+        <v>7038959</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10856,11 +10851,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10887,10 +10877,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129298858</v>
+        <v>129298806</v>
       </c>
       <c r="B103" t="n">
-        <v>83007</v>
+        <v>57725</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10898,21 +10888,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10922,10 +10912,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>487408</v>
+        <v>487339</v>
       </c>
       <c r="R103" t="n">
-        <v>7038959</v>
+        <v>7039009</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10958,6 +10948,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10984,7 +10979,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129298788</v>
+        <v>129298782</v>
       </c>
       <c r="B104" t="n">
         <v>57725</v>
@@ -11019,10 +11014,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>487039</v>
+        <v>486857</v>
       </c>
       <c r="R104" t="n">
-        <v>7039164</v>
+        <v>7039276</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11059,7 +11054,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11188,32 +11183,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129298832</v>
+        <v>129298815</v>
       </c>
       <c r="B106" t="n">
-        <v>83006</v>
+        <v>57725</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11223,10 +11218,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>487393</v>
+        <v>487375</v>
       </c>
       <c r="R106" t="n">
-        <v>7038976</v>
+        <v>7038981</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11259,6 +11254,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11285,7 +11285,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129298815</v>
+        <v>129298788</v>
       </c>
       <c r="B107" t="n">
         <v>57725</v>
@@ -11320,10 +11320,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>487375</v>
+        <v>487039</v>
       </c>
       <c r="R107" t="n">
-        <v>7038981</v>
+        <v>7039164</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11387,7 +11387,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129298760</v>
+        <v>129298766</v>
       </c>
       <c r="B108" t="n">
         <v>57725</v>
@@ -11422,10 +11422,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>487141</v>
+        <v>487124</v>
       </c>
       <c r="R108" t="n">
-        <v>7039023</v>
+        <v>7039030</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11591,7 +11591,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129298766</v>
+        <v>129298760</v>
       </c>
       <c r="B110" t="n">
         <v>57725</v>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>487124</v>
+        <v>487141</v>
       </c>
       <c r="R110" t="n">
-        <v>7039030</v>
+        <v>7039023</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11666,7 +11666,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 46357-2025 artfynd.xlsx
+++ b/artfynd/A 46357-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129298851</v>
       </c>
       <c r="B2" t="n">
-        <v>91554</v>
+        <v>91556</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129298751</v>
       </c>
       <c r="B3" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129298786</v>
       </c>
       <c r="B4" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>129298818</v>
       </c>
       <c r="B5" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>129298819</v>
       </c>
       <c r="B6" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>129298827</v>
       </c>
       <c r="B7" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>129298844</v>
       </c>
       <c r="B8" t="n">
-        <v>78052</v>
+        <v>78054</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>129298742</v>
       </c>
       <c r="B9" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129298838</v>
+        <v>129298812</v>
       </c>
       <c r="B10" t="n">
-        <v>80144</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,21 +1487,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>487035</v>
+        <v>487362</v>
       </c>
       <c r="R10" t="n">
-        <v>7039161</v>
+        <v>7039030</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1547,6 +1547,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1573,10 +1578,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129298812</v>
+        <v>129298759</v>
       </c>
       <c r="B11" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1608,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>487362</v>
+        <v>487171</v>
       </c>
       <c r="R11" t="n">
-        <v>7039030</v>
+        <v>7039000</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1675,10 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129298759</v>
+        <v>129298838</v>
       </c>
       <c r="B12" t="n">
-        <v>57725</v>
+        <v>80146</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1686,21 +1691,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1710,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>487171</v>
+        <v>487035</v>
       </c>
       <c r="R12" t="n">
-        <v>7039000</v>
+        <v>7039161</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1746,11 +1751,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1777,10 +1777,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129298761</v>
+        <v>129298755</v>
       </c>
       <c r="B13" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>487137</v>
+        <v>487206</v>
       </c>
       <c r="R13" t="n">
-        <v>7039024</v>
+        <v>7038982</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1879,10 +1879,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129298755</v>
+        <v>129298799</v>
       </c>
       <c r="B14" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>487206</v>
+        <v>487230</v>
       </c>
       <c r="R14" t="n">
-        <v>7038982</v>
+        <v>7039041</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1981,10 +1981,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129298799</v>
+        <v>129298761</v>
       </c>
       <c r="B15" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2016,10 +2016,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>487230</v>
+        <v>487137</v>
       </c>
       <c r="R15" t="n">
-        <v>7039041</v>
+        <v>7039024</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129298857</v>
+        <v>129298787</v>
       </c>
       <c r="B16" t="n">
-        <v>82997</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2094,21 +2094,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>487340</v>
+        <v>486999</v>
       </c>
       <c r="R16" t="n">
-        <v>7039016</v>
+        <v>7039162</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2154,6 +2154,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2180,10 +2185,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129298855</v>
+        <v>129298857</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>82999</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2196,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>487542</v>
+        <v>487340</v>
       </c>
       <c r="R17" t="n">
-        <v>7038985</v>
+        <v>7039016</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2277,10 +2282,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129298777</v>
+        <v>129298855</v>
       </c>
       <c r="B18" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,21 +2293,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2312,10 +2317,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486860</v>
+        <v>487542</v>
       </c>
       <c r="R18" t="n">
-        <v>7039254</v>
+        <v>7038985</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2348,11 +2353,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2379,10 +2379,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129298787</v>
+        <v>129298777</v>
       </c>
       <c r="B19" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486999</v>
+        <v>486860</v>
       </c>
       <c r="R19" t="n">
-        <v>7039162</v>
+        <v>7039254</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2484,7 +2484,7 @@
         <v>129298775</v>
       </c>
       <c r="B20" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>129298808</v>
       </c>
       <c r="B21" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>129298780</v>
       </c>
       <c r="B22" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2787,10 +2787,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129298852</v>
+        <v>129298740</v>
       </c>
       <c r="B23" t="n">
-        <v>91554</v>
+        <v>91542</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2798,21 +2798,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>487127</v>
+        <v>487145</v>
       </c>
       <c r="R23" t="n">
-        <v>7039070</v>
+        <v>7039179</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2884,10 +2884,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129298837</v>
+        <v>129298852</v>
       </c>
       <c r="B24" t="n">
-        <v>80144</v>
+        <v>91556</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2895,21 +2895,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2919,10 +2919,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>487004</v>
+        <v>487127</v>
       </c>
       <c r="R24" t="n">
-        <v>7039214</v>
+        <v>7039070</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2981,57 +2981,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129298830</v>
+        <v>129298837</v>
       </c>
       <c r="B25" t="n">
-        <v>57566</v>
+        <v>80146</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102621</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>487123</v>
+        <v>487004</v>
       </c>
       <c r="R25" t="n">
-        <v>7039173</v>
+        <v>7039214</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3090,45 +3078,57 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129298740</v>
+        <v>129298830</v>
       </c>
       <c r="B26" t="n">
-        <v>91540</v>
+        <v>57568</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>102621</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>487145</v>
+        <v>487123</v>
       </c>
       <c r="R26" t="n">
-        <v>7039179</v>
+        <v>7039173</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3190,7 +3190,7 @@
         <v>129298845</v>
       </c>
       <c r="B27" t="n">
-        <v>78052</v>
+        <v>78054</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3284,10 +3284,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129298843</v>
+        <v>129298765</v>
       </c>
       <c r="B28" t="n">
-        <v>80144</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3295,21 +3295,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3319,10 +3319,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>487391</v>
+        <v>487122</v>
       </c>
       <c r="R28" t="n">
-        <v>7038927</v>
+        <v>7039034</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3355,6 +3355,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3381,10 +3386,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129298793</v>
+        <v>129298770</v>
       </c>
       <c r="B29" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3416,10 +3421,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>487183</v>
+        <v>486972</v>
       </c>
       <c r="R29" t="n">
-        <v>7039216</v>
+        <v>7039122</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3483,10 +3488,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129298823</v>
+        <v>129298778</v>
       </c>
       <c r="B30" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3518,10 +3523,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>487363</v>
+        <v>486871</v>
       </c>
       <c r="R30" t="n">
-        <v>7038902</v>
+        <v>7039260</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3585,10 +3590,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129298765</v>
+        <v>129298793</v>
       </c>
       <c r="B31" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3620,10 +3625,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>487122</v>
+        <v>487183</v>
       </c>
       <c r="R31" t="n">
-        <v>7039034</v>
+        <v>7039216</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3687,10 +3692,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129298770</v>
+        <v>129298823</v>
       </c>
       <c r="B32" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3722,10 +3727,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486972</v>
+        <v>487363</v>
       </c>
       <c r="R32" t="n">
-        <v>7039122</v>
+        <v>7038902</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3789,10 +3794,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129298778</v>
+        <v>129298843</v>
       </c>
       <c r="B33" t="n">
-        <v>57725</v>
+        <v>80146</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3800,21 +3805,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3824,10 +3829,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486871</v>
+        <v>487391</v>
       </c>
       <c r="R33" t="n">
-        <v>7039260</v>
+        <v>7038927</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3860,11 +3865,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3894,7 +3894,7 @@
         <v>129298846</v>
       </c>
       <c r="B34" t="n">
-        <v>57829</v>
+        <v>57831</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>129298792</v>
       </c>
       <c r="B35" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>129298750</v>
       </c>
       <c r="B36" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v>129298769</v>
       </c>
       <c r="B37" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>129298804</v>
       </c>
       <c r="B38" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>129298794</v>
       </c>
       <c r="B39" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4498,10 +4498,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129298833</v>
+        <v>129298840</v>
       </c>
       <c r="B40" t="n">
-        <v>80145</v>
+        <v>80146</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4509,21 +4509,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>487265</v>
+        <v>487314</v>
       </c>
       <c r="R40" t="n">
-        <v>7038997</v>
+        <v>7039005</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4598,7 +4598,7 @@
         <v>129298854</v>
       </c>
       <c r="B41" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>129298805</v>
       </c>
       <c r="B42" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4794,10 +4794,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129298809</v>
+        <v>129298795</v>
       </c>
       <c r="B43" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>487348</v>
+        <v>487100</v>
       </c>
       <c r="R43" t="n">
-        <v>7039005</v>
+        <v>7039085</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4896,10 +4896,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129298802</v>
+        <v>129298833</v>
       </c>
       <c r="B44" t="n">
-        <v>57725</v>
+        <v>80147</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4907,21 +4907,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4931,10 +4931,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>487302</v>
+        <v>487265</v>
       </c>
       <c r="R44" t="n">
-        <v>7039045</v>
+        <v>7038997</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4967,11 +4967,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4998,10 +4993,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129298795</v>
+        <v>129298809</v>
       </c>
       <c r="B45" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5033,10 +5028,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>487100</v>
+        <v>487348</v>
       </c>
       <c r="R45" t="n">
-        <v>7039085</v>
+        <v>7039005</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5100,10 +5095,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129298748</v>
+        <v>129298802</v>
       </c>
       <c r="B46" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5135,10 +5130,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>487301</v>
+        <v>487302</v>
       </c>
       <c r="R46" t="n">
-        <v>7038925</v>
+        <v>7039045</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5202,10 +5197,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129298783</v>
+        <v>129298748</v>
       </c>
       <c r="B47" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5237,10 +5232,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>487024</v>
+        <v>487301</v>
       </c>
       <c r="R47" t="n">
-        <v>7039203</v>
+        <v>7038925</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5304,10 +5299,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129298840</v>
+        <v>129298783</v>
       </c>
       <c r="B48" t="n">
-        <v>80144</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5315,21 +5310,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5339,10 +5334,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>487314</v>
+        <v>487024</v>
       </c>
       <c r="R48" t="n">
-        <v>7039005</v>
+        <v>7039203</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5375,6 +5370,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5401,10 +5401,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129298856</v>
+        <v>129298738</v>
       </c>
       <c r="B49" t="n">
-        <v>82871</v>
+        <v>96924</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5412,21 +5412,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>53</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5436,10 +5436,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>487541</v>
+        <v>487311</v>
       </c>
       <c r="R49" t="n">
-        <v>7038983</v>
+        <v>7039063</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5498,10 +5498,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129298738</v>
+        <v>129298856</v>
       </c>
       <c r="B50" t="n">
-        <v>96922</v>
+        <v>82873</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5509,21 +5509,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>1312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>487311</v>
+        <v>487541</v>
       </c>
       <c r="R50" t="n">
-        <v>7039063</v>
+        <v>7038983</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5598,7 +5598,7 @@
         <v>129298842</v>
       </c>
       <c r="B51" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>129298798</v>
       </c>
       <c r="B52" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>129298810</v>
       </c>
       <c r="B53" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129298825</v>
+        <v>129298779</v>
       </c>
       <c r="B54" t="n">
-        <v>57885</v>
+        <v>57727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5907,21 +5907,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5931,10 +5931,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>487247</v>
+        <v>486866</v>
       </c>
       <c r="R54" t="n">
-        <v>7039020</v>
+        <v>7039259</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5998,10 +5998,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129298779</v>
+        <v>129298749</v>
       </c>
       <c r="B55" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6033,10 +6033,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486866</v>
+        <v>487275</v>
       </c>
       <c r="R55" t="n">
-        <v>7039259</v>
+        <v>7038947</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6100,10 +6100,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129298749</v>
+        <v>129298825</v>
       </c>
       <c r="B56" t="n">
-        <v>57725</v>
+        <v>57887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6111,21 +6111,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6135,10 +6135,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>487275</v>
+        <v>487247</v>
       </c>
       <c r="R56" t="n">
-        <v>7038947</v>
+        <v>7039020</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6205,7 +6205,7 @@
         <v>129298767</v>
       </c>
       <c r="B57" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>129298776</v>
       </c>
       <c r="B58" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6406,10 +6406,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129298816</v>
+        <v>129298774</v>
       </c>
       <c r="B59" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6441,10 +6441,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>487389</v>
+        <v>486866</v>
       </c>
       <c r="R59" t="n">
-        <v>7038985</v>
+        <v>7039249</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6508,10 +6508,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129298813</v>
+        <v>129298773</v>
       </c>
       <c r="B60" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6543,10 +6543,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>487367</v>
+        <v>486807</v>
       </c>
       <c r="R60" t="n">
-        <v>7038998</v>
+        <v>7039220</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6610,10 +6610,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129298820</v>
+        <v>129298816</v>
       </c>
       <c r="B61" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6645,10 +6645,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>487354</v>
+        <v>487389</v>
       </c>
       <c r="R61" t="n">
-        <v>7038894</v>
+        <v>7038985</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6712,10 +6712,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129298774</v>
+        <v>129298813</v>
       </c>
       <c r="B62" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6747,10 +6747,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>486866</v>
+        <v>487367</v>
       </c>
       <c r="R62" t="n">
-        <v>7039249</v>
+        <v>7038998</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6814,10 +6814,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129298773</v>
+        <v>129298820</v>
       </c>
       <c r="B63" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6849,10 +6849,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>486807</v>
+        <v>487354</v>
       </c>
       <c r="R63" t="n">
-        <v>7039220</v>
+        <v>7038894</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6889,7 +6889,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6919,7 +6919,7 @@
         <v>129298826</v>
       </c>
       <c r="B64" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>129298853</v>
       </c>
       <c r="B65" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7115,10 +7115,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129298741</v>
+        <v>129298811</v>
       </c>
       <c r="B66" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7126,21 +7126,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>487185</v>
+        <v>487357</v>
       </c>
       <c r="R66" t="n">
-        <v>7039203</v>
+        <v>7039009</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7186,6 +7186,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7212,10 +7217,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129298811</v>
+        <v>129298741</v>
       </c>
       <c r="B67" t="n">
-        <v>57725</v>
+        <v>91542</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7223,21 +7228,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7247,10 +7252,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>487357</v>
+        <v>487185</v>
       </c>
       <c r="R67" t="n">
-        <v>7039009</v>
+        <v>7039203</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7283,11 +7288,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7317,7 +7317,7 @@
         <v>129298831</v>
       </c>
       <c r="B68" t="n">
-        <v>82996</v>
+        <v>82998</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7411,32 +7411,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129298828</v>
+        <v>129298737</v>
       </c>
       <c r="B69" t="n">
-        <v>80173</v>
+        <v>83007</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>487269</v>
+        <v>487523</v>
       </c>
       <c r="R69" t="n">
-        <v>7039004</v>
+        <v>7039001</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7511,7 +7511,7 @@
         <v>129298839</v>
       </c>
       <c r="B70" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7605,32 +7605,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129298737</v>
+        <v>129298828</v>
       </c>
       <c r="B71" t="n">
-        <v>83005</v>
+        <v>80175</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7640,10 +7640,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>487523</v>
+        <v>487269</v>
       </c>
       <c r="R71" t="n">
-        <v>7039001</v>
+        <v>7039004</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7705,7 +7705,7 @@
         <v>129298797</v>
       </c>
       <c r="B72" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>129298803</v>
       </c>
       <c r="B73" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
         <v>129298822</v>
       </c>
       <c r="B74" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>129298817</v>
       </c>
       <c r="B75" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>129298800</v>
       </c>
       <c r="B76" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>129298821</v>
       </c>
       <c r="B77" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8330,10 +8330,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129298781</v>
+        <v>129298753</v>
       </c>
       <c r="B78" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8365,10 +8365,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>486864</v>
+        <v>487240</v>
       </c>
       <c r="R78" t="n">
-        <v>7039272</v>
+        <v>7038959</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8432,10 +8432,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129298785</v>
+        <v>129298781</v>
       </c>
       <c r="B79" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8467,10 +8467,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>487007</v>
+        <v>486864</v>
       </c>
       <c r="R79" t="n">
-        <v>7039210</v>
+        <v>7039272</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8534,10 +8534,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129298753</v>
+        <v>129298785</v>
       </c>
       <c r="B80" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8569,10 +8569,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>487240</v>
+        <v>487007</v>
       </c>
       <c r="R80" t="n">
-        <v>7038959</v>
+        <v>7039210</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8609,7 +8609,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8639,7 +8639,7 @@
         <v>129298757</v>
       </c>
       <c r="B81" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>129298784</v>
       </c>
       <c r="B82" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         <v>129298841</v>
       </c>
       <c r="B83" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>129298771</v>
       </c>
       <c r="B84" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>129298847</v>
       </c>
       <c r="B85" t="n">
-        <v>57585</v>
+        <v>57587</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>129298789</v>
       </c>
       <c r="B86" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9259,10 +9259,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129298801</v>
+        <v>129298772</v>
       </c>
       <c r="B87" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9294,10 +9294,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>487268</v>
+        <v>486849</v>
       </c>
       <c r="R87" t="n">
-        <v>7039003</v>
+        <v>7039185</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9361,10 +9361,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129298814</v>
+        <v>129298801</v>
       </c>
       <c r="B88" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9396,10 +9396,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>487366</v>
+        <v>487268</v>
       </c>
       <c r="R88" t="n">
-        <v>7038997</v>
+        <v>7039003</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9436,7 +9436,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9463,10 +9463,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129298772</v>
+        <v>129298814</v>
       </c>
       <c r="B89" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9498,10 +9498,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>486849</v>
+        <v>487366</v>
       </c>
       <c r="R89" t="n">
-        <v>7039185</v>
+        <v>7038997</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9538,7 +9538,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9568,7 +9568,7 @@
         <v>129298746</v>
       </c>
       <c r="B90" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9667,10 +9667,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129298752</v>
+        <v>129298743</v>
       </c>
       <c r="B91" t="n">
-        <v>57725</v>
+        <v>91542</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9678,21 +9678,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9702,10 +9702,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>487246</v>
+        <v>487331</v>
       </c>
       <c r="R91" t="n">
-        <v>7038958</v>
+        <v>7039023</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9738,11 +9738,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9769,10 +9764,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129298768</v>
+        <v>129298836</v>
       </c>
       <c r="B92" t="n">
-        <v>57725</v>
+        <v>80146</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9780,21 +9775,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9804,10 +9799,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>487123</v>
+        <v>486899</v>
       </c>
       <c r="R92" t="n">
-        <v>7039032</v>
+        <v>7039370</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9840,11 +9835,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9871,10 +9861,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129298743</v>
+        <v>129298768</v>
       </c>
       <c r="B93" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9882,21 +9872,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9906,10 +9896,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>487331</v>
+        <v>487123</v>
       </c>
       <c r="R93" t="n">
-        <v>7039023</v>
+        <v>7039032</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9942,6 +9932,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9968,10 +9963,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129298836</v>
+        <v>129298752</v>
       </c>
       <c r="B94" t="n">
-        <v>80144</v>
+        <v>57727</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9979,21 +9974,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10003,10 +9998,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>486899</v>
+        <v>487246</v>
       </c>
       <c r="R94" t="n">
-        <v>7039370</v>
+        <v>7038958</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10039,6 +10034,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10065,32 +10065,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129298745</v>
+        <v>129298739</v>
       </c>
       <c r="B95" t="n">
-        <v>57725</v>
+        <v>91506</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10100,10 +10100,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>486881</v>
+        <v>487384</v>
       </c>
       <c r="R95" t="n">
-        <v>7039175</v>
+        <v>7038973</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10136,11 +10136,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10170,7 +10165,7 @@
         <v>129298791</v>
       </c>
       <c r="B96" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10272,7 +10267,7 @@
         <v>129298754</v>
       </c>
       <c r="B97" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10371,32 +10366,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129298739</v>
+        <v>129298745</v>
       </c>
       <c r="B98" t="n">
-        <v>91504</v>
+        <v>57727</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10406,10 +10401,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>487384</v>
+        <v>486881</v>
       </c>
       <c r="R98" t="n">
-        <v>7038973</v>
+        <v>7039175</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10442,6 +10437,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10471,7 +10471,7 @@
         <v>129298829</v>
       </c>
       <c r="B99" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>129298807</v>
       </c>
       <c r="B100" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>129298832</v>
       </c>
       <c r="B101" t="n">
-        <v>82996</v>
+        <v>82998</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>129298858</v>
       </c>
       <c r="B102" t="n">
-        <v>82997</v>
+        <v>82999</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>129298806</v>
       </c>
       <c r="B103" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>129298782</v>
       </c>
       <c r="B104" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>129298758</v>
       </c>
       <c r="B105" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>129298815</v>
       </c>
       <c r="B106" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>129298788</v>
       </c>
       <c r="B107" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>129298766</v>
       </c>
       <c r="B108" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
         <v>129298796</v>
       </c>
       <c r="B109" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>129298760</v>
       </c>
       <c r="B110" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>129298790</v>
       </c>
       <c r="B111" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 46357-2025 artfynd.xlsx
+++ b/artfynd/A 46357-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129298751</v>
+        <v>129298827</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487263</v>
+        <v>487352</v>
       </c>
       <c r="R3" t="n">
-        <v>7038949</v>
+        <v>7038906</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,7 +847,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129298786</v>
+        <v>129298844</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>78054</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487006</v>
+        <v>487374</v>
       </c>
       <c r="R4" t="n">
-        <v>7039175</v>
+        <v>7039027</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,7 +971,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129298818</v>
+        <v>129298751</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1011,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>487389</v>
+        <v>487263</v>
       </c>
       <c r="R5" t="n">
-        <v>7038925</v>
+        <v>7038949</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,7 +1073,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129298819</v>
+        <v>129298786</v>
       </c>
       <c r="B6" t="n">
         <v>57727</v>
@@ -1113,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>487346</v>
+        <v>487006</v>
       </c>
       <c r="R6" t="n">
-        <v>7038911</v>
+        <v>7039175</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129298827</v>
+        <v>129298818</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>487352</v>
+        <v>487389</v>
       </c>
       <c r="R7" t="n">
-        <v>7038906</v>
+        <v>7038925</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,7 +1250,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1282,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129298844</v>
+        <v>129298819</v>
       </c>
       <c r="B8" t="n">
-        <v>78054</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1293,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1317,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>487374</v>
+        <v>487346</v>
       </c>
       <c r="R8" t="n">
-        <v>7039027</v>
+        <v>7038911</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1353,6 +1348,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129298742</v>
+        <v>129298812</v>
       </c>
       <c r="B9" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1390,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>487129</v>
+        <v>487362</v>
       </c>
       <c r="R9" t="n">
-        <v>7039097</v>
+        <v>7039030</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1450,6 +1450,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1476,7 +1481,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129298812</v>
+        <v>129298759</v>
       </c>
       <c r="B10" t="n">
         <v>57727</v>
@@ -1511,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>487362</v>
+        <v>487171</v>
       </c>
       <c r="R10" t="n">
-        <v>7039030</v>
+        <v>7039000</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1578,10 +1583,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129298759</v>
+        <v>129298742</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>91542</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,21 +1594,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1613,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>487171</v>
+        <v>487129</v>
       </c>
       <c r="R11" t="n">
-        <v>7039000</v>
+        <v>7039097</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,11 +1654,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1777,7 +1777,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129298755</v>
+        <v>129298761</v>
       </c>
       <c r="B13" t="n">
         <v>57727</v>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>487206</v>
+        <v>487137</v>
       </c>
       <c r="R13" t="n">
-        <v>7038982</v>
+        <v>7039024</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129298799</v>
+        <v>129298755</v>
       </c>
       <c r="B14" t="n">
         <v>57727</v>
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>487230</v>
+        <v>487206</v>
       </c>
       <c r="R14" t="n">
-        <v>7039041</v>
+        <v>7038982</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1981,7 +1981,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129298761</v>
+        <v>129298799</v>
       </c>
       <c r="B15" t="n">
         <v>57727</v>
@@ -2016,10 +2016,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>487137</v>
+        <v>487230</v>
       </c>
       <c r="R15" t="n">
-        <v>7039024</v>
+        <v>7039041</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129298787</v>
+        <v>129298855</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2094,21 +2094,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486999</v>
+        <v>487542</v>
       </c>
       <c r="R16" t="n">
-        <v>7039162</v>
+        <v>7038985</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2154,11 +2154,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2185,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129298857</v>
+        <v>129298777</v>
       </c>
       <c r="B17" t="n">
-        <v>82999</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2196,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2220,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>487340</v>
+        <v>486860</v>
       </c>
       <c r="R17" t="n">
-        <v>7039016</v>
+        <v>7039254</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2256,6 +2251,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2282,10 +2282,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129298855</v>
+        <v>129298787</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2293,21 +2293,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>487542</v>
+        <v>486999</v>
       </c>
       <c r="R18" t="n">
-        <v>7038985</v>
+        <v>7039162</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2353,6 +2353,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2379,10 +2384,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129298777</v>
+        <v>129298857</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>82999</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2390,21 +2395,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2414,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486860</v>
+        <v>487340</v>
       </c>
       <c r="R19" t="n">
-        <v>7039254</v>
+        <v>7039016</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2450,11 +2455,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2481,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129298775</v>
+        <v>129298740</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>91542</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486860</v>
+        <v>487145</v>
       </c>
       <c r="R20" t="n">
-        <v>7039244</v>
+        <v>7039179</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2552,11 +2552,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2583,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129298808</v>
+        <v>129298852</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>91556</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2594,21 +2589,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2618,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>487344</v>
+        <v>487127</v>
       </c>
       <c r="R21" t="n">
-        <v>7039018</v>
+        <v>7039070</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2654,11 +2649,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2685,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129298780</v>
+        <v>129298837</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2696,21 +2686,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2720,10 +2710,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486859</v>
+        <v>487004</v>
       </c>
       <c r="R22" t="n">
-        <v>7039262</v>
+        <v>7039214</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2756,11 +2746,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2787,45 +2772,57 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129298740</v>
+        <v>129298830</v>
       </c>
       <c r="B23" t="n">
-        <v>91542</v>
+        <v>57568</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>102621</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>487145</v>
+        <v>487123</v>
       </c>
       <c r="R23" t="n">
-        <v>7039179</v>
+        <v>7039173</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2884,10 +2881,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129298852</v>
+        <v>129298775</v>
       </c>
       <c r="B24" t="n">
-        <v>91556</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2895,21 +2892,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2919,10 +2916,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>487127</v>
+        <v>486860</v>
       </c>
       <c r="R24" t="n">
-        <v>7039070</v>
+        <v>7039244</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2955,6 +2952,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2981,10 +2983,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129298837</v>
+        <v>129298808</v>
       </c>
       <c r="B25" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2992,21 +2994,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3016,10 +3018,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>487004</v>
+        <v>487344</v>
       </c>
       <c r="R25" t="n">
-        <v>7039214</v>
+        <v>7039018</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3052,6 +3054,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3078,27 +3085,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129298830</v>
+        <v>129298780</v>
       </c>
       <c r="B26" t="n">
-        <v>57568</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3106,29 +3113,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>487123</v>
+        <v>486859</v>
       </c>
       <c r="R26" t="n">
-        <v>7039173</v>
+        <v>7039262</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3161,6 +3156,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3590,10 +3590,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129298793</v>
+        <v>129298843</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3601,21 +3601,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>487183</v>
+        <v>487391</v>
       </c>
       <c r="R31" t="n">
-        <v>7039216</v>
+        <v>7038927</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3661,11 +3661,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3692,7 +3687,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129298823</v>
+        <v>129298793</v>
       </c>
       <c r="B32" t="n">
         <v>57727</v>
@@ -3727,10 +3722,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>487363</v>
+        <v>487183</v>
       </c>
       <c r="R32" t="n">
-        <v>7038902</v>
+        <v>7039216</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3794,10 +3789,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129298843</v>
+        <v>129298823</v>
       </c>
       <c r="B33" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3805,21 +3800,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3829,10 +3824,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>487391</v>
+        <v>487363</v>
       </c>
       <c r="R33" t="n">
-        <v>7038927</v>
+        <v>7038902</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3865,6 +3860,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4498,10 +4498,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129298840</v>
+        <v>129298833</v>
       </c>
       <c r="B40" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4509,21 +4509,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>487314</v>
+        <v>487265</v>
       </c>
       <c r="R40" t="n">
-        <v>7039005</v>
+        <v>7038997</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4692,10 +4692,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129298805</v>
+        <v>129298840</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4703,21 +4703,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>487346</v>
+        <v>487314</v>
       </c>
       <c r="R42" t="n">
-        <v>7039012</v>
+        <v>7039005</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4763,11 +4763,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4794,7 +4789,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129298795</v>
+        <v>129298805</v>
       </c>
       <c r="B43" t="n">
         <v>57727</v>
@@ -4829,10 +4824,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>487100</v>
+        <v>487346</v>
       </c>
       <c r="R43" t="n">
-        <v>7039085</v>
+        <v>7039012</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4896,10 +4891,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129298833</v>
+        <v>129298809</v>
       </c>
       <c r="B44" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4907,21 +4902,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4931,10 +4926,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>487265</v>
+        <v>487348</v>
       </c>
       <c r="R44" t="n">
-        <v>7038997</v>
+        <v>7039005</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4967,6 +4962,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4993,7 +4993,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129298809</v>
+        <v>129298802</v>
       </c>
       <c r="B45" t="n">
         <v>57727</v>
@@ -5028,10 +5028,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>487348</v>
+        <v>487302</v>
       </c>
       <c r="R45" t="n">
-        <v>7039005</v>
+        <v>7039045</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5095,7 +5095,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129298802</v>
+        <v>129298795</v>
       </c>
       <c r="B46" t="n">
         <v>57727</v>
@@ -5130,10 +5130,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>487302</v>
+        <v>487100</v>
       </c>
       <c r="R46" t="n">
-        <v>7039045</v>
+        <v>7039085</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5401,10 +5401,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129298738</v>
+        <v>129298856</v>
       </c>
       <c r="B49" t="n">
-        <v>96924</v>
+        <v>82873</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5412,21 +5412,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>53</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5436,10 +5436,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>487311</v>
+        <v>487541</v>
       </c>
       <c r="R49" t="n">
-        <v>7039063</v>
+        <v>7038983</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5498,10 +5498,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129298856</v>
+        <v>129298738</v>
       </c>
       <c r="B50" t="n">
-        <v>82873</v>
+        <v>96924</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5509,21 +5509,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>53</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>487541</v>
+        <v>487311</v>
       </c>
       <c r="R50" t="n">
-        <v>7038983</v>
+        <v>7039063</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6406,7 +6406,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129298774</v>
+        <v>129298816</v>
       </c>
       <c r="B59" t="n">
         <v>57727</v>
@@ -6441,10 +6441,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>486866</v>
+        <v>487389</v>
       </c>
       <c r="R59" t="n">
-        <v>7039249</v>
+        <v>7038985</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6508,7 +6508,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129298773</v>
+        <v>129298813</v>
       </c>
       <c r="B60" t="n">
         <v>57727</v>
@@ -6543,10 +6543,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>486807</v>
+        <v>487367</v>
       </c>
       <c r="R60" t="n">
-        <v>7039220</v>
+        <v>7038998</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6610,7 +6610,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129298816</v>
+        <v>129298820</v>
       </c>
       <c r="B61" t="n">
         <v>57727</v>
@@ -6645,10 +6645,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>487389</v>
+        <v>487354</v>
       </c>
       <c r="R61" t="n">
-        <v>7038985</v>
+        <v>7038894</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6712,7 +6712,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129298813</v>
+        <v>129298774</v>
       </c>
       <c r="B62" t="n">
         <v>57727</v>
@@ -6747,10 +6747,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>487367</v>
+        <v>486866</v>
       </c>
       <c r="R62" t="n">
-        <v>7038998</v>
+        <v>7039249</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6814,7 +6814,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129298820</v>
+        <v>129298773</v>
       </c>
       <c r="B63" t="n">
         <v>57727</v>
@@ -6849,10 +6849,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>487354</v>
+        <v>486807</v>
       </c>
       <c r="R63" t="n">
-        <v>7038894</v>
+        <v>7039220</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6889,7 +6889,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7314,32 +7314,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129298831</v>
+        <v>129298737</v>
       </c>
       <c r="B68" t="n">
-        <v>82998</v>
+        <v>83007</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>492</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7349,10 +7349,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>487307</v>
+        <v>487523</v>
       </c>
       <c r="R68" t="n">
-        <v>7039016</v>
+        <v>7039001</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7411,10 +7411,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129298737</v>
+        <v>129298839</v>
       </c>
       <c r="B69" t="n">
-        <v>83007</v>
+        <v>80146</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7422,21 +7422,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7446,7 +7446,7 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>487523</v>
+        <v>487269</v>
       </c>
       <c r="R69" t="n">
         <v>7039001</v>
@@ -7508,10 +7508,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129298839</v>
+        <v>129298797</v>
       </c>
       <c r="B70" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7519,21 +7519,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7543,10 +7543,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>487269</v>
+        <v>487134</v>
       </c>
       <c r="R70" t="n">
-        <v>7039001</v>
+        <v>7039037</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7579,6 +7579,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7605,32 +7610,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129298828</v>
+        <v>129298803</v>
       </c>
       <c r="B71" t="n">
-        <v>80175</v>
+        <v>57727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7640,10 +7645,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>487269</v>
+        <v>487303</v>
       </c>
       <c r="R71" t="n">
-        <v>7039004</v>
+        <v>7039037</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7676,6 +7681,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7702,7 +7712,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129298797</v>
+        <v>129298822</v>
       </c>
       <c r="B72" t="n">
         <v>57727</v>
@@ -7737,10 +7747,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>487134</v>
+        <v>487373</v>
       </c>
       <c r="R72" t="n">
-        <v>7039037</v>
+        <v>7038897</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7804,7 +7814,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129298803</v>
+        <v>129298817</v>
       </c>
       <c r="B73" t="n">
         <v>57727</v>
@@ -7839,10 +7849,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>487303</v>
+        <v>487460</v>
       </c>
       <c r="R73" t="n">
-        <v>7039037</v>
+        <v>7038984</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7906,7 +7916,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129298822</v>
+        <v>129298800</v>
       </c>
       <c r="B74" t="n">
         <v>57727</v>
@@ -7934,17 +7944,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>487373</v>
+        <v>487288</v>
       </c>
       <c r="R74" t="n">
-        <v>7038897</v>
+        <v>7039015</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7981,7 +8007,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Födosökande hane</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8008,7 +8034,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129298817</v>
+        <v>129298821</v>
       </c>
       <c r="B75" t="n">
         <v>57727</v>
@@ -8043,10 +8069,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>487460</v>
+        <v>487368</v>
       </c>
       <c r="R75" t="n">
-        <v>7038984</v>
+        <v>7038892</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8110,61 +8136,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129298800</v>
+        <v>129298828</v>
       </c>
       <c r="B76" t="n">
-        <v>57727</v>
+        <v>80175</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>487288</v>
+        <v>487269</v>
       </c>
       <c r="R76" t="n">
-        <v>7039015</v>
+        <v>7039004</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8197,11 +8207,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Födosökande hane</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8228,32 +8233,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129298821</v>
+        <v>129298831</v>
       </c>
       <c r="B77" t="n">
-        <v>57727</v>
+        <v>82998</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8263,10 +8268,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>487368</v>
+        <v>487307</v>
       </c>
       <c r="R77" t="n">
-        <v>7038892</v>
+        <v>7039016</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8299,11 +8304,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8330,7 +8330,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129298753</v>
+        <v>129298781</v>
       </c>
       <c r="B78" t="n">
         <v>57727</v>
@@ -8365,10 +8365,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>487240</v>
+        <v>486864</v>
       </c>
       <c r="R78" t="n">
-        <v>7038959</v>
+        <v>7039272</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8432,7 +8432,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129298781</v>
+        <v>129298785</v>
       </c>
       <c r="B79" t="n">
         <v>57727</v>
@@ -8467,10 +8467,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>486864</v>
+        <v>487007</v>
       </c>
       <c r="R79" t="n">
-        <v>7039272</v>
+        <v>7039210</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8534,7 +8534,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129298785</v>
+        <v>129298753</v>
       </c>
       <c r="B80" t="n">
         <v>57727</v>
@@ -8569,10 +8569,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>487007</v>
+        <v>487240</v>
       </c>
       <c r="R80" t="n">
-        <v>7039210</v>
+        <v>7038959</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8609,7 +8609,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8840,10 +8840,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129298841</v>
+        <v>129298771</v>
       </c>
       <c r="B83" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8851,21 +8851,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8875,10 +8875,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>487515</v>
+        <v>486885</v>
       </c>
       <c r="R83" t="n">
-        <v>7038993</v>
+        <v>7039172</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8911,6 +8911,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8937,45 +8942,61 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129298771</v>
+        <v>129298847</v>
       </c>
       <c r="B84" t="n">
-        <v>57727</v>
+        <v>57587</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>100136</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>486885</v>
+        <v>486999</v>
       </c>
       <c r="R84" t="n">
-        <v>7039172</v>
+        <v>7039199</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9012,7 +9033,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Jagades av en nötskrika</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9039,61 +9060,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129298847</v>
+        <v>129298789</v>
       </c>
       <c r="B85" t="n">
-        <v>57587</v>
+        <v>57727</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100136</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>486999</v>
+        <v>487041</v>
       </c>
       <c r="R85" t="n">
-        <v>7039199</v>
+        <v>7039167</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9130,7 +9135,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Jagades av en nötskrika</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9157,7 +9162,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129298789</v>
+        <v>129298801</v>
       </c>
       <c r="B86" t="n">
         <v>57727</v>
@@ -9192,10 +9197,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>487041</v>
+        <v>487268</v>
       </c>
       <c r="R86" t="n">
-        <v>7039167</v>
+        <v>7039003</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9259,7 +9264,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129298772</v>
+        <v>129298814</v>
       </c>
       <c r="B87" t="n">
         <v>57727</v>
@@ -9294,10 +9299,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>486849</v>
+        <v>487366</v>
       </c>
       <c r="R87" t="n">
-        <v>7039185</v>
+        <v>7038997</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9334,7 +9339,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9361,7 +9366,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129298801</v>
+        <v>129298772</v>
       </c>
       <c r="B88" t="n">
         <v>57727</v>
@@ -9396,10 +9401,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>487268</v>
+        <v>486849</v>
       </c>
       <c r="R88" t="n">
-        <v>7039003</v>
+        <v>7039185</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9463,7 +9468,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129298814</v>
+        <v>129298746</v>
       </c>
       <c r="B89" t="n">
         <v>57727</v>
@@ -9498,10 +9503,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>487366</v>
+        <v>487316</v>
       </c>
       <c r="R89" t="n">
-        <v>7038997</v>
+        <v>7038914</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9538,7 +9543,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9565,10 +9570,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129298746</v>
+        <v>129298841</v>
       </c>
       <c r="B90" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9576,21 +9581,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9600,10 +9605,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>487316</v>
+        <v>487515</v>
       </c>
       <c r="R90" t="n">
-        <v>7038914</v>
+        <v>7038993</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9636,11 +9641,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9861,7 +9861,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129298768</v>
+        <v>129298752</v>
       </c>
       <c r="B93" t="n">
         <v>57727</v>
@@ -9896,10 +9896,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>487123</v>
+        <v>487246</v>
       </c>
       <c r="R93" t="n">
-        <v>7039032</v>
+        <v>7038958</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9963,7 +9963,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129298752</v>
+        <v>129298768</v>
       </c>
       <c r="B94" t="n">
         <v>57727</v>
@@ -9998,10 +9998,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>487246</v>
+        <v>487123</v>
       </c>
       <c r="R94" t="n">
-        <v>7038958</v>
+        <v>7039032</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10162,7 +10162,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129298791</v>
+        <v>129298745</v>
       </c>
       <c r="B96" t="n">
         <v>57727</v>
@@ -10197,10 +10197,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>487112</v>
+        <v>486881</v>
       </c>
       <c r="R96" t="n">
-        <v>7039182</v>
+        <v>7039175</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10264,7 +10264,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129298754</v>
+        <v>129298791</v>
       </c>
       <c r="B97" t="n">
         <v>57727</v>
@@ -10299,10 +10299,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>487222</v>
+        <v>487112</v>
       </c>
       <c r="R97" t="n">
-        <v>7038974</v>
+        <v>7039182</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10339,7 +10339,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10366,7 +10366,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129298745</v>
+        <v>129298754</v>
       </c>
       <c r="B98" t="n">
         <v>57727</v>
@@ -10401,10 +10401,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>486881</v>
+        <v>487222</v>
       </c>
       <c r="R98" t="n">
-        <v>7039175</v>
+        <v>7038974</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10441,7 +10441,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10683,32 +10683,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129298832</v>
+        <v>129298858</v>
       </c>
       <c r="B101" t="n">
-        <v>82998</v>
+        <v>82999</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>492</v>
+        <v>308</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10718,10 +10718,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>487393</v>
+        <v>487408</v>
       </c>
       <c r="R101" t="n">
-        <v>7038976</v>
+        <v>7038959</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10780,10 +10780,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129298858</v>
+        <v>129298806</v>
       </c>
       <c r="B102" t="n">
-        <v>82999</v>
+        <v>57727</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10791,21 +10791,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10815,10 +10815,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>487408</v>
+        <v>487339</v>
       </c>
       <c r="R102" t="n">
-        <v>7038959</v>
+        <v>7039009</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10851,6 +10851,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10877,7 +10882,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129298806</v>
+        <v>129298782</v>
       </c>
       <c r="B103" t="n">
         <v>57727</v>
@@ -10912,10 +10917,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>487339</v>
+        <v>486857</v>
       </c>
       <c r="R103" t="n">
-        <v>7039009</v>
+        <v>7039276</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10952,7 +10957,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10979,32 +10984,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129298782</v>
+        <v>129298832</v>
       </c>
       <c r="B104" t="n">
-        <v>57727</v>
+        <v>82998</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11014,10 +11019,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>486857</v>
+        <v>487393</v>
       </c>
       <c r="R104" t="n">
-        <v>7039276</v>
+        <v>7038976</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11050,11 +11055,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">

--- a/artfynd/A 46357-2025 artfynd.xlsx
+++ b/artfynd/A 46357-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129298851</v>
+        <v>129298751</v>
       </c>
       <c r="B2" t="n">
-        <v>91556</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487144</v>
+        <v>487263</v>
       </c>
       <c r="R2" t="n">
-        <v>7039078</v>
+        <v>7038949</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129298827</v>
+        <v>129298786</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487352</v>
+        <v>487006</v>
       </c>
       <c r="R3" t="n">
-        <v>7038906</v>
+        <v>7039175</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129298844</v>
+        <v>129298818</v>
       </c>
       <c r="B4" t="n">
-        <v>78054</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487374</v>
+        <v>487389</v>
       </c>
       <c r="R4" t="n">
-        <v>7039027</v>
+        <v>7038925</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,6 +950,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129298751</v>
+        <v>129298819</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1006,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>487263</v>
+        <v>487346</v>
       </c>
       <c r="R5" t="n">
-        <v>7038949</v>
+        <v>7038911</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129298786</v>
+        <v>129298851</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>91556</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>487006</v>
+        <v>487144</v>
       </c>
       <c r="R6" t="n">
-        <v>7039175</v>
+        <v>7039078</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,11 +1154,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129298818</v>
+        <v>129298827</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>487389</v>
+        <v>487352</v>
       </c>
       <c r="R7" t="n">
-        <v>7038925</v>
+        <v>7038906</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1250,7 +1255,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,10 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129298819</v>
+        <v>129298844</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>78054</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1293,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>487346</v>
+        <v>487374</v>
       </c>
       <c r="R8" t="n">
-        <v>7038911</v>
+        <v>7039027</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1348,11 +1353,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2083,10 +2083,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129298855</v>
+        <v>129298857</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>82999</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2094,21 +2094,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>487542</v>
+        <v>487340</v>
       </c>
       <c r="R16" t="n">
-        <v>7038985</v>
+        <v>7039016</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2180,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129298777</v>
+        <v>129298855</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486860</v>
+        <v>487542</v>
       </c>
       <c r="R17" t="n">
-        <v>7039254</v>
+        <v>7038985</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2251,11 +2251,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2282,7 +2277,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129298787</v>
+        <v>129298777</v>
       </c>
       <c r="B18" t="n">
         <v>57727</v>
@@ -2317,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486999</v>
+        <v>486860</v>
       </c>
       <c r="R18" t="n">
-        <v>7039162</v>
+        <v>7039254</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2357,7 +2352,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2384,10 +2379,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129298857</v>
+        <v>129298787</v>
       </c>
       <c r="B19" t="n">
-        <v>82999</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2395,21 +2390,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2419,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>487340</v>
+        <v>486999</v>
       </c>
       <c r="R19" t="n">
-        <v>7039016</v>
+        <v>7039162</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2455,6 +2450,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3284,10 +3284,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129298765</v>
+        <v>129298843</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3295,21 +3295,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3319,10 +3319,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>487122</v>
+        <v>487391</v>
       </c>
       <c r="R28" t="n">
-        <v>7039034</v>
+        <v>7038927</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3355,11 +3355,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3386,7 +3381,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129298770</v>
+        <v>129298793</v>
       </c>
       <c r="B29" t="n">
         <v>57727</v>
@@ -3421,10 +3416,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486972</v>
+        <v>487183</v>
       </c>
       <c r="R29" t="n">
-        <v>7039122</v>
+        <v>7039216</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3488,7 +3483,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129298778</v>
+        <v>129298823</v>
       </c>
       <c r="B30" t="n">
         <v>57727</v>
@@ -3523,10 +3518,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486871</v>
+        <v>487363</v>
       </c>
       <c r="R30" t="n">
-        <v>7039260</v>
+        <v>7038902</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3590,32 +3585,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129298843</v>
+        <v>129298846</v>
       </c>
       <c r="B31" t="n">
-        <v>80146</v>
+        <v>57831</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3625,10 +3620,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>487391</v>
+        <v>486976</v>
       </c>
       <c r="R31" t="n">
-        <v>7038927</v>
+        <v>7039216</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3687,7 +3682,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129298793</v>
+        <v>129298765</v>
       </c>
       <c r="B32" t="n">
         <v>57727</v>
@@ -3722,10 +3717,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>487183</v>
+        <v>487122</v>
       </c>
       <c r="R32" t="n">
-        <v>7039216</v>
+        <v>7039034</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3789,7 +3784,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129298823</v>
+        <v>129298770</v>
       </c>
       <c r="B33" t="n">
         <v>57727</v>
@@ -3824,10 +3819,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>487363</v>
+        <v>486972</v>
       </c>
       <c r="R33" t="n">
-        <v>7038902</v>
+        <v>7039122</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3891,27 +3886,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129298846</v>
+        <v>129298778</v>
       </c>
       <c r="B34" t="n">
-        <v>57831</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3926,10 +3921,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486976</v>
+        <v>486871</v>
       </c>
       <c r="R34" t="n">
-        <v>7039216</v>
+        <v>7039260</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3962,6 +3957,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 46357-2025 artfynd.xlsx
+++ b/artfynd/A 46357-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129298751</v>
+        <v>129298851</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>91554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487263</v>
+        <v>487144</v>
       </c>
       <c r="R2" t="n">
-        <v>7038949</v>
+        <v>7039078</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129298786</v>
+        <v>129298827</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487006</v>
+        <v>487352</v>
       </c>
       <c r="R3" t="n">
-        <v>7039175</v>
+        <v>7038906</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +847,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129298818</v>
+        <v>129298844</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>78054</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487389</v>
+        <v>487374</v>
       </c>
       <c r="R4" t="n">
-        <v>7038925</v>
+        <v>7039027</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,7 +971,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129298819</v>
+        <v>129298751</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1016,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>487346</v>
+        <v>487263</v>
       </c>
       <c r="R5" t="n">
-        <v>7038911</v>
+        <v>7038949</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129298851</v>
+        <v>129298786</v>
       </c>
       <c r="B6" t="n">
-        <v>91556</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>487144</v>
+        <v>487006</v>
       </c>
       <c r="R6" t="n">
-        <v>7039078</v>
+        <v>7039175</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1154,6 +1144,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129298827</v>
+        <v>129298818</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>487352</v>
+        <v>487389</v>
       </c>
       <c r="R7" t="n">
-        <v>7038906</v>
+        <v>7038925</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,7 +1250,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1282,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129298844</v>
+        <v>129298819</v>
       </c>
       <c r="B8" t="n">
-        <v>78054</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1293,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1317,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>487374</v>
+        <v>487346</v>
       </c>
       <c r="R8" t="n">
-        <v>7039027</v>
+        <v>7038911</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1353,6 +1348,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129298812</v>
+        <v>129298838</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1390,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>487362</v>
+        <v>487035</v>
       </c>
       <c r="R9" t="n">
-        <v>7039030</v>
+        <v>7039161</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1450,11 +1450,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1481,7 +1476,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129298759</v>
+        <v>129298812</v>
       </c>
       <c r="B10" t="n">
         <v>57727</v>
@@ -1516,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>487171</v>
+        <v>487362</v>
       </c>
       <c r="R10" t="n">
-        <v>7039000</v>
+        <v>7039030</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1583,10 +1578,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129298742</v>
+        <v>129298759</v>
       </c>
       <c r="B11" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1594,21 +1589,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>487129</v>
+        <v>487171</v>
       </c>
       <c r="R11" t="n">
-        <v>7039097</v>
+        <v>7039000</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,6 +1649,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1680,10 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129298838</v>
+        <v>129298742</v>
       </c>
       <c r="B12" t="n">
-        <v>80146</v>
+        <v>91540</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,21 +1691,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1715,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>487035</v>
+        <v>487129</v>
       </c>
       <c r="R12" t="n">
-        <v>7039161</v>
+        <v>7039097</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2484,7 +2484,7 @@
         <v>129298740</v>
       </c>
       <c r="B20" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>129298852</v>
       </c>
       <c r="B21" t="n">
-        <v>91556</v>
+        <v>91554</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2772,27 +2772,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129298830</v>
+        <v>129298775</v>
       </c>
       <c r="B23" t="n">
-        <v>57568</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2800,29 +2800,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>487123</v>
+        <v>486860</v>
       </c>
       <c r="R23" t="n">
-        <v>7039173</v>
+        <v>7039244</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2855,6 +2843,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2881,7 +2874,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129298775</v>
+        <v>129298808</v>
       </c>
       <c r="B24" t="n">
         <v>57727</v>
@@ -2916,10 +2909,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486860</v>
+        <v>487344</v>
       </c>
       <c r="R24" t="n">
-        <v>7039244</v>
+        <v>7039018</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2983,7 +2976,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129298808</v>
+        <v>129298780</v>
       </c>
       <c r="B25" t="n">
         <v>57727</v>
@@ -3018,10 +3011,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>487344</v>
+        <v>486859</v>
       </c>
       <c r="R25" t="n">
-        <v>7039018</v>
+        <v>7039262</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3058,7 +3051,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3085,27 +3078,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129298780</v>
+        <v>129298830</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>57568</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3113,17 +3106,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486859</v>
+        <v>487123</v>
       </c>
       <c r="R26" t="n">
-        <v>7039262</v>
+        <v>7039173</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3156,11 +3161,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3585,27 +3585,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129298846</v>
+        <v>129298765</v>
       </c>
       <c r="B31" t="n">
-        <v>57831</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3620,10 +3620,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486976</v>
+        <v>487122</v>
       </c>
       <c r="R31" t="n">
-        <v>7039216</v>
+        <v>7039034</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3656,6 +3656,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3682,7 +3687,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129298765</v>
+        <v>129298770</v>
       </c>
       <c r="B32" t="n">
         <v>57727</v>
@@ -3717,10 +3722,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>487122</v>
+        <v>486972</v>
       </c>
       <c r="R32" t="n">
-        <v>7039034</v>
+        <v>7039122</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3784,7 +3789,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129298770</v>
+        <v>129298778</v>
       </c>
       <c r="B33" t="n">
         <v>57727</v>
@@ -3819,10 +3824,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486972</v>
+        <v>486871</v>
       </c>
       <c r="R33" t="n">
-        <v>7039122</v>
+        <v>7039260</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3886,27 +3891,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129298778</v>
+        <v>129298846</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3921,10 +3926,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486871</v>
+        <v>486976</v>
       </c>
       <c r="R34" t="n">
-        <v>7039260</v>
+        <v>7039216</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3957,11 +3962,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4598,7 +4598,7 @@
         <v>129298854</v>
       </c>
       <c r="B41" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5401,10 +5401,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129298856</v>
+        <v>129298798</v>
       </c>
       <c r="B49" t="n">
-        <v>82873</v>
+        <v>57727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5412,21 +5412,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5436,10 +5436,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>487541</v>
+        <v>487131</v>
       </c>
       <c r="R49" t="n">
-        <v>7038983</v>
+        <v>7039049</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5472,6 +5472,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5498,10 +5503,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129298738</v>
+        <v>129298810</v>
       </c>
       <c r="B50" t="n">
-        <v>96924</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5509,21 +5514,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5533,10 +5538,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>487311</v>
+        <v>487355</v>
       </c>
       <c r="R50" t="n">
-        <v>7039063</v>
+        <v>7039005</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5569,6 +5574,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5595,10 +5605,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129298842</v>
+        <v>129298856</v>
       </c>
       <c r="B51" t="n">
-        <v>80146</v>
+        <v>82873</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5606,21 +5616,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5630,10 +5640,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>487393</v>
+        <v>487541</v>
       </c>
       <c r="R51" t="n">
-        <v>7038908</v>
+        <v>7038983</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5692,10 +5702,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129298798</v>
+        <v>129298738</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>96950</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5703,21 +5713,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5727,10 +5737,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>487131</v>
+        <v>487311</v>
       </c>
       <c r="R52" t="n">
-        <v>7039049</v>
+        <v>7039063</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5763,11 +5773,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5794,10 +5799,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129298810</v>
+        <v>129298842</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5805,21 +5810,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5829,10 +5834,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>487355</v>
+        <v>487393</v>
       </c>
       <c r="R53" t="n">
-        <v>7039005</v>
+        <v>7038908</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5865,11 +5870,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7018,10 +7018,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129298853</v>
+        <v>129298741</v>
       </c>
       <c r="B65" t="n">
-        <v>91560</v>
+        <v>91540</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7029,21 +7029,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>487415</v>
+        <v>487185</v>
       </c>
       <c r="R65" t="n">
-        <v>7038971</v>
+        <v>7039203</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7115,10 +7115,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129298811</v>
+        <v>129298853</v>
       </c>
       <c r="B66" t="n">
-        <v>57727</v>
+        <v>91558</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7126,21 +7126,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>487357</v>
+        <v>487415</v>
       </c>
       <c r="R66" t="n">
-        <v>7039009</v>
+        <v>7038971</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7186,11 +7186,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7217,10 +7212,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129298741</v>
+        <v>129298811</v>
       </c>
       <c r="B67" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7228,21 +7223,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7252,10 +7247,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>487185</v>
+        <v>487357</v>
       </c>
       <c r="R67" t="n">
-        <v>7039203</v>
+        <v>7039009</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7288,6 +7283,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7314,10 +7314,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129298737</v>
+        <v>129298800</v>
       </c>
       <c r="B68" t="n">
-        <v>83007</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7325,34 +7325,50 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>487523</v>
+        <v>487288</v>
       </c>
       <c r="R68" t="n">
-        <v>7039001</v>
+        <v>7039015</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7385,6 +7401,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Födosökande hane</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7411,10 +7432,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129298839</v>
+        <v>129298737</v>
       </c>
       <c r="B69" t="n">
-        <v>80146</v>
+        <v>83007</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7422,21 +7443,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7446,7 +7467,7 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>487269</v>
+        <v>487523</v>
       </c>
       <c r="R69" t="n">
         <v>7039001</v>
@@ -7508,32 +7529,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129298797</v>
+        <v>129298828</v>
       </c>
       <c r="B70" t="n">
-        <v>57727</v>
+        <v>80175</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7543,10 +7564,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>487134</v>
+        <v>487269</v>
       </c>
       <c r="R70" t="n">
-        <v>7039037</v>
+        <v>7039004</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7579,11 +7600,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7610,10 +7626,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129298803</v>
+        <v>129298839</v>
       </c>
       <c r="B71" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7621,21 +7637,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7645,10 +7661,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>487303</v>
+        <v>487269</v>
       </c>
       <c r="R71" t="n">
-        <v>7039037</v>
+        <v>7039001</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7681,11 +7697,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7712,7 +7723,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129298822</v>
+        <v>129298797</v>
       </c>
       <c r="B72" t="n">
         <v>57727</v>
@@ -7747,10 +7758,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>487373</v>
+        <v>487134</v>
       </c>
       <c r="R72" t="n">
-        <v>7038897</v>
+        <v>7039037</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7814,7 +7825,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129298817</v>
+        <v>129298803</v>
       </c>
       <c r="B73" t="n">
         <v>57727</v>
@@ -7849,10 +7860,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>487460</v>
+        <v>487303</v>
       </c>
       <c r="R73" t="n">
-        <v>7038984</v>
+        <v>7039037</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7916,7 +7927,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129298800</v>
+        <v>129298822</v>
       </c>
       <c r="B74" t="n">
         <v>57727</v>
@@ -7944,33 +7955,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>487288</v>
+        <v>487373</v>
       </c>
       <c r="R74" t="n">
-        <v>7039015</v>
+        <v>7038897</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8007,7 +8002,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Födosökande hane</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8034,7 +8029,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129298821</v>
+        <v>129298817</v>
       </c>
       <c r="B75" t="n">
         <v>57727</v>
@@ -8069,10 +8064,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>487368</v>
+        <v>487460</v>
       </c>
       <c r="R75" t="n">
-        <v>7038892</v>
+        <v>7038984</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8136,32 +8131,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129298828</v>
+        <v>129298831</v>
       </c>
       <c r="B76" t="n">
-        <v>80175</v>
+        <v>82998</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>492</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8171,10 +8166,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>487269</v>
+        <v>487307</v>
       </c>
       <c r="R76" t="n">
-        <v>7039004</v>
+        <v>7039016</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8233,32 +8228,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129298831</v>
+        <v>129298821</v>
       </c>
       <c r="B77" t="n">
-        <v>82998</v>
+        <v>57727</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8268,10 +8263,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>487307</v>
+        <v>487368</v>
       </c>
       <c r="R77" t="n">
-        <v>7039016</v>
+        <v>7038892</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8304,6 +8299,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8840,10 +8840,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129298771</v>
+        <v>129298841</v>
       </c>
       <c r="B83" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8851,21 +8851,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8875,10 +8875,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>486885</v>
+        <v>487515</v>
       </c>
       <c r="R83" t="n">
-        <v>7039172</v>
+        <v>7038993</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8911,11 +8911,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8942,61 +8937,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129298847</v>
+        <v>129298771</v>
       </c>
       <c r="B84" t="n">
-        <v>57587</v>
+        <v>57727</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100136</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>486999</v>
+        <v>486885</v>
       </c>
       <c r="R84" t="n">
-        <v>7039199</v>
+        <v>7039172</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9033,7 +9012,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Jagades av en nötskrika</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9060,45 +9039,61 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129298789</v>
+        <v>129298847</v>
       </c>
       <c r="B85" t="n">
-        <v>57727</v>
+        <v>57587</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>100136</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>487041</v>
+        <v>486999</v>
       </c>
       <c r="R85" t="n">
-        <v>7039167</v>
+        <v>7039199</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9135,7 +9130,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Jagades av en nötskrika</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9162,7 +9157,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129298801</v>
+        <v>129298789</v>
       </c>
       <c r="B86" t="n">
         <v>57727</v>
@@ -9197,10 +9192,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>487268</v>
+        <v>487041</v>
       </c>
       <c r="R86" t="n">
-        <v>7039003</v>
+        <v>7039167</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9264,7 +9259,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129298814</v>
+        <v>129298801</v>
       </c>
       <c r="B87" t="n">
         <v>57727</v>
@@ -9299,10 +9294,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>487366</v>
+        <v>487268</v>
       </c>
       <c r="R87" t="n">
-        <v>7038997</v>
+        <v>7039003</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9339,7 +9334,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9366,7 +9361,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129298772</v>
+        <v>129298814</v>
       </c>
       <c r="B88" t="n">
         <v>57727</v>
@@ -9401,10 +9396,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>486849</v>
+        <v>487366</v>
       </c>
       <c r="R88" t="n">
-        <v>7039185</v>
+        <v>7038997</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9441,7 +9436,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9468,7 +9463,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129298746</v>
+        <v>129298772</v>
       </c>
       <c r="B89" t="n">
         <v>57727</v>
@@ -9503,10 +9498,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>487316</v>
+        <v>486849</v>
       </c>
       <c r="R89" t="n">
-        <v>7038914</v>
+        <v>7039185</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9570,10 +9565,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129298841</v>
+        <v>129298746</v>
       </c>
       <c r="B90" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9581,21 +9576,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9605,10 +9600,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>487515</v>
+        <v>487316</v>
       </c>
       <c r="R90" t="n">
-        <v>7038993</v>
+        <v>7038914</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9641,6 +9636,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9667,10 +9667,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129298743</v>
+        <v>129298752</v>
       </c>
       <c r="B91" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9678,21 +9678,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9702,10 +9702,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>487331</v>
+        <v>487246</v>
       </c>
       <c r="R91" t="n">
-        <v>7039023</v>
+        <v>7038958</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9738,6 +9738,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9764,10 +9769,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129298836</v>
+        <v>129298768</v>
       </c>
       <c r="B92" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9775,21 +9780,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9799,10 +9804,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>486899</v>
+        <v>487123</v>
       </c>
       <c r="R92" t="n">
-        <v>7039370</v>
+        <v>7039032</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9835,6 +9840,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9861,10 +9871,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129298752</v>
+        <v>129298743</v>
       </c>
       <c r="B93" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9872,21 +9882,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9896,10 +9906,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>487246</v>
+        <v>487331</v>
       </c>
       <c r="R93" t="n">
-        <v>7038958</v>
+        <v>7039023</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9932,11 +9942,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9963,10 +9968,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129298768</v>
+        <v>129298836</v>
       </c>
       <c r="B94" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9974,21 +9979,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9998,10 +10003,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>487123</v>
+        <v>486899</v>
       </c>
       <c r="R94" t="n">
-        <v>7039032</v>
+        <v>7039370</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10034,11 +10039,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10065,32 +10065,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129298739</v>
+        <v>129298745</v>
       </c>
       <c r="B95" t="n">
-        <v>91506</v>
+        <v>57727</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10100,10 +10100,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>487384</v>
+        <v>486881</v>
       </c>
       <c r="R95" t="n">
-        <v>7038973</v>
+        <v>7039175</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10136,6 +10136,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10162,7 +10167,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129298745</v>
+        <v>129298791</v>
       </c>
       <c r="B96" t="n">
         <v>57727</v>
@@ -10197,10 +10202,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>486881</v>
+        <v>487112</v>
       </c>
       <c r="R96" t="n">
-        <v>7039175</v>
+        <v>7039182</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10264,7 +10269,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129298791</v>
+        <v>129298754</v>
       </c>
       <c r="B97" t="n">
         <v>57727</v>
@@ -10299,10 +10304,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>487112</v>
+        <v>487222</v>
       </c>
       <c r="R97" t="n">
-        <v>7039182</v>
+        <v>7038974</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10339,7 +10344,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10366,32 +10371,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129298754</v>
+        <v>129298739</v>
       </c>
       <c r="B98" t="n">
-        <v>57727</v>
+        <v>91504</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10401,10 +10406,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>487222</v>
+        <v>487384</v>
       </c>
       <c r="R98" t="n">
-        <v>7038974</v>
+        <v>7038973</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10437,11 +10442,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10683,32 +10683,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129298858</v>
+        <v>129298832</v>
       </c>
       <c r="B101" t="n">
-        <v>82999</v>
+        <v>82998</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>308</v>
+        <v>492</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10718,10 +10718,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>487408</v>
+        <v>487393</v>
       </c>
       <c r="R101" t="n">
-        <v>7038959</v>
+        <v>7038976</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10780,10 +10780,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129298806</v>
+        <v>129298858</v>
       </c>
       <c r="B102" t="n">
-        <v>57727</v>
+        <v>82999</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10791,21 +10791,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10815,10 +10815,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>487339</v>
+        <v>487408</v>
       </c>
       <c r="R102" t="n">
-        <v>7039009</v>
+        <v>7038959</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10851,11 +10851,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10882,7 +10877,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129298782</v>
+        <v>129298806</v>
       </c>
       <c r="B103" t="n">
         <v>57727</v>
@@ -10917,10 +10912,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>486857</v>
+        <v>487339</v>
       </c>
       <c r="R103" t="n">
-        <v>7039276</v>
+        <v>7039009</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10957,7 +10952,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10984,32 +10979,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129298832</v>
+        <v>129298782</v>
       </c>
       <c r="B104" t="n">
-        <v>82998</v>
+        <v>57727</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11019,10 +11014,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>487393</v>
+        <v>486857</v>
       </c>
       <c r="R104" t="n">
-        <v>7038976</v>
+        <v>7039276</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11055,6 +11050,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">

--- a/artfynd/A 46357-2025 artfynd.xlsx
+++ b/artfynd/A 46357-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129298827</v>
+        <v>129298844</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>78054</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>228579</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487352</v>
+        <v>487374</v>
       </c>
       <c r="R3" t="n">
-        <v>7038906</v>
+        <v>7039027</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129298844</v>
+        <v>129298751</v>
       </c>
       <c r="B4" t="n">
-        <v>78054</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487374</v>
+        <v>487263</v>
       </c>
       <c r="R4" t="n">
-        <v>7039027</v>
+        <v>7038949</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,7 +971,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129298751</v>
+        <v>129298818</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>487263</v>
+        <v>487389</v>
       </c>
       <c r="R5" t="n">
-        <v>7038949</v>
+        <v>7038925</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,7 +1073,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129298786</v>
+        <v>129298819</v>
       </c>
       <c r="B6" t="n">
         <v>57727</v>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>487006</v>
+        <v>487346</v>
       </c>
       <c r="R6" t="n">
-        <v>7039175</v>
+        <v>7038911</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129298818</v>
+        <v>129298786</v>
       </c>
       <c r="B7" t="n">
         <v>57727</v>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>487389</v>
+        <v>487006</v>
       </c>
       <c r="R7" t="n">
-        <v>7038925</v>
+        <v>7039175</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129298819</v>
+        <v>129298827</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>487346</v>
+        <v>487352</v>
       </c>
       <c r="R8" t="n">
-        <v>7038911</v>
+        <v>7038906</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129298838</v>
+        <v>129298742</v>
       </c>
       <c r="B9" t="n">
-        <v>80146</v>
+        <v>91540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1390,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>487035</v>
+        <v>487129</v>
       </c>
       <c r="R9" t="n">
-        <v>7039161</v>
+        <v>7039097</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129298812</v>
+        <v>129298838</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,21 +1487,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>487362</v>
+        <v>487035</v>
       </c>
       <c r="R10" t="n">
-        <v>7039030</v>
+        <v>7039161</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1547,11 +1547,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,7 +1573,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129298759</v>
+        <v>129298812</v>
       </c>
       <c r="B11" t="n">
         <v>57727</v>
@@ -1613,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>487171</v>
+        <v>487362</v>
       </c>
       <c r="R11" t="n">
-        <v>7039000</v>
+        <v>7039030</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1680,10 +1675,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129298742</v>
+        <v>129298759</v>
       </c>
       <c r="B12" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,21 +1686,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1715,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>487129</v>
+        <v>487171</v>
       </c>
       <c r="R12" t="n">
-        <v>7039097</v>
+        <v>7039000</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,6 +1746,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2083,10 +2083,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129298857</v>
+        <v>129298855</v>
       </c>
       <c r="B16" t="n">
-        <v>82999</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2094,21 +2094,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>487340</v>
+        <v>487542</v>
       </c>
       <c r="R16" t="n">
-        <v>7039016</v>
+        <v>7038985</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2180,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129298855</v>
+        <v>129298857</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>82999</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>487542</v>
+        <v>487340</v>
       </c>
       <c r="R17" t="n">
-        <v>7038985</v>
+        <v>7039016</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2772,7 +2772,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129298775</v>
+        <v>129298808</v>
       </c>
       <c r="B23" t="n">
         <v>57727</v>
@@ -2807,10 +2807,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486860</v>
+        <v>487344</v>
       </c>
       <c r="R23" t="n">
-        <v>7039244</v>
+        <v>7039018</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129298808</v>
+        <v>129298845</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>78054</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2885,21 +2885,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>487344</v>
+        <v>487526</v>
       </c>
       <c r="R24" t="n">
-        <v>7039018</v>
+        <v>7039006</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2945,11 +2945,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2976,7 +2971,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129298780</v>
+        <v>129298775</v>
       </c>
       <c r="B25" t="n">
         <v>57727</v>
@@ -3011,10 +3006,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486859</v>
+        <v>486860</v>
       </c>
       <c r="R25" t="n">
-        <v>7039262</v>
+        <v>7039244</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3051,7 +3046,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3078,27 +3073,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129298830</v>
+        <v>129298780</v>
       </c>
       <c r="B26" t="n">
-        <v>57568</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3106,29 +3101,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>487123</v>
+        <v>486859</v>
       </c>
       <c r="R26" t="n">
-        <v>7039173</v>
+        <v>7039262</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3161,6 +3144,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3187,45 +3175,57 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129298845</v>
+        <v>129298830</v>
       </c>
       <c r="B27" t="n">
-        <v>78054</v>
+        <v>57568</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228579</v>
+        <v>102621</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>487526</v>
+        <v>487123</v>
       </c>
       <c r="R27" t="n">
-        <v>7039006</v>
+        <v>7039173</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3284,10 +3284,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129298843</v>
+        <v>129298823</v>
       </c>
       <c r="B28" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3295,21 +3295,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3319,10 +3319,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>487391</v>
+        <v>487363</v>
       </c>
       <c r="R28" t="n">
-        <v>7038927</v>
+        <v>7038902</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3355,6 +3355,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3381,7 +3386,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129298793</v>
+        <v>129298765</v>
       </c>
       <c r="B29" t="n">
         <v>57727</v>
@@ -3416,10 +3421,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>487183</v>
+        <v>487122</v>
       </c>
       <c r="R29" t="n">
-        <v>7039216</v>
+        <v>7039034</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3483,7 +3488,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129298823</v>
+        <v>129298770</v>
       </c>
       <c r="B30" t="n">
         <v>57727</v>
@@ -3518,10 +3523,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>487363</v>
+        <v>486972</v>
       </c>
       <c r="R30" t="n">
-        <v>7038902</v>
+        <v>7039122</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3585,7 +3590,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129298765</v>
+        <v>129298778</v>
       </c>
       <c r="B31" t="n">
         <v>57727</v>
@@ -3620,10 +3625,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>487122</v>
+        <v>486871</v>
       </c>
       <c r="R31" t="n">
-        <v>7039034</v>
+        <v>7039260</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3687,7 +3692,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129298770</v>
+        <v>129298793</v>
       </c>
       <c r="B32" t="n">
         <v>57727</v>
@@ -3722,10 +3727,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486972</v>
+        <v>487183</v>
       </c>
       <c r="R32" t="n">
-        <v>7039122</v>
+        <v>7039216</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3789,10 +3794,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129298778</v>
+        <v>129298843</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3800,21 +3805,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3824,10 +3829,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486871</v>
+        <v>487391</v>
       </c>
       <c r="R33" t="n">
-        <v>7039260</v>
+        <v>7038927</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3860,11 +3865,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3988,7 +3988,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129298792</v>
+        <v>129298750</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>487153</v>
+        <v>487272</v>
       </c>
       <c r="R35" t="n">
-        <v>7039212</v>
+        <v>7038946</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4063,7 +4063,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4090,7 +4090,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129298750</v>
+        <v>129298769</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4125,10 +4125,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>487272</v>
+        <v>487109</v>
       </c>
       <c r="R36" t="n">
-        <v>7038946</v>
+        <v>7039040</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4192,7 +4192,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129298769</v>
+        <v>129298804</v>
       </c>
       <c r="B37" t="n">
         <v>57727</v>
@@ -4227,10 +4227,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>487109</v>
+        <v>487288</v>
       </c>
       <c r="R37" t="n">
-        <v>7039040</v>
+        <v>7039002</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129298804</v>
+        <v>129298792</v>
       </c>
       <c r="B38" t="n">
         <v>57727</v>
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>487288</v>
+        <v>487153</v>
       </c>
       <c r="R38" t="n">
-        <v>7039002</v>
+        <v>7039212</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4598,7 +4598,7 @@
         <v>129298854</v>
       </c>
       <c r="B41" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4615,14 +4615,10 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4692,10 +4688,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129298840</v>
+        <v>129298805</v>
       </c>
       <c r="B42" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4703,21 +4699,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4727,10 +4723,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>487314</v>
+        <v>487346</v>
       </c>
       <c r="R42" t="n">
-        <v>7039005</v>
+        <v>7039012</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4763,6 +4759,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4789,7 +4790,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129298805</v>
+        <v>129298809</v>
       </c>
       <c r="B43" t="n">
         <v>57727</v>
@@ -4824,10 +4825,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>487346</v>
+        <v>487348</v>
       </c>
       <c r="R43" t="n">
-        <v>7039012</v>
+        <v>7039005</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4891,7 +4892,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129298809</v>
+        <v>129298802</v>
       </c>
       <c r="B44" t="n">
         <v>57727</v>
@@ -4926,10 +4927,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>487348</v>
+        <v>487302</v>
       </c>
       <c r="R44" t="n">
-        <v>7039005</v>
+        <v>7039045</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4993,7 +4994,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129298802</v>
+        <v>129298748</v>
       </c>
       <c r="B45" t="n">
         <v>57727</v>
@@ -5028,10 +5029,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>487302</v>
+        <v>487301</v>
       </c>
       <c r="R45" t="n">
-        <v>7039045</v>
+        <v>7038925</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5197,7 +5198,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129298748</v>
+        <v>129298783</v>
       </c>
       <c r="B47" t="n">
         <v>57727</v>
@@ -5232,10 +5233,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>487301</v>
+        <v>487024</v>
       </c>
       <c r="R47" t="n">
-        <v>7038925</v>
+        <v>7039203</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5299,10 +5300,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129298783</v>
+        <v>129298840</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5310,21 +5311,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5334,10 +5335,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>487024</v>
+        <v>487314</v>
       </c>
       <c r="R48" t="n">
-        <v>7039203</v>
+        <v>7039005</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5370,11 +5371,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5401,10 +5397,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129298798</v>
+        <v>129298856</v>
       </c>
       <c r="B49" t="n">
-        <v>57727</v>
+        <v>82873</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5412,21 +5408,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5436,10 +5432,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>487131</v>
+        <v>487541</v>
       </c>
       <c r="R49" t="n">
-        <v>7039049</v>
+        <v>7038983</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5472,11 +5468,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5503,10 +5494,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129298810</v>
+        <v>129298842</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5514,21 +5505,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5538,10 +5529,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>487355</v>
+        <v>487393</v>
       </c>
       <c r="R50" t="n">
-        <v>7039005</v>
+        <v>7038908</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5574,11 +5565,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5605,10 +5591,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129298856</v>
+        <v>129298810</v>
       </c>
       <c r="B51" t="n">
-        <v>82873</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5616,21 +5602,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5640,10 +5626,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>487541</v>
+        <v>487355</v>
       </c>
       <c r="R51" t="n">
-        <v>7038983</v>
+        <v>7039005</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5676,6 +5662,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5702,10 +5693,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129298738</v>
+        <v>129298798</v>
       </c>
       <c r="B52" t="n">
-        <v>96950</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5713,21 +5704,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5737,10 +5728,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>487311</v>
+        <v>487131</v>
       </c>
       <c r="R52" t="n">
-        <v>7039063</v>
+        <v>7039049</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5773,6 +5764,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5799,10 +5795,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129298842</v>
+        <v>129298738</v>
       </c>
       <c r="B53" t="n">
-        <v>80146</v>
+        <v>96951</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5810,21 +5806,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5834,10 +5830,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>487393</v>
+        <v>487311</v>
       </c>
       <c r="R53" t="n">
-        <v>7038908</v>
+        <v>7039063</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5896,10 +5892,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129298779</v>
+        <v>129298825</v>
       </c>
       <c r="B54" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5907,21 +5903,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5931,10 +5927,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486866</v>
+        <v>487247</v>
       </c>
       <c r="R54" t="n">
-        <v>7039259</v>
+        <v>7039020</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5971,7 +5967,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5998,7 +5994,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129298749</v>
+        <v>129298779</v>
       </c>
       <c r="B55" t="n">
         <v>57727</v>
@@ -6033,10 +6029,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>487275</v>
+        <v>486866</v>
       </c>
       <c r="R55" t="n">
-        <v>7038947</v>
+        <v>7039259</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6100,10 +6096,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129298825</v>
+        <v>129298749</v>
       </c>
       <c r="B56" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6111,21 +6107,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6135,10 +6131,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>487247</v>
+        <v>487275</v>
       </c>
       <c r="R56" t="n">
-        <v>7039020</v>
+        <v>7038947</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6175,7 +6171,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6304,7 +6300,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129298776</v>
+        <v>129298816</v>
       </c>
       <c r="B58" t="n">
         <v>57727</v>
@@ -6339,10 +6335,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>486855</v>
+        <v>487389</v>
       </c>
       <c r="R58" t="n">
-        <v>7039252</v>
+        <v>7038985</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6379,7 +6375,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6406,7 +6402,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129298816</v>
+        <v>129298813</v>
       </c>
       <c r="B59" t="n">
         <v>57727</v>
@@ -6441,10 +6437,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>487389</v>
+        <v>487367</v>
       </c>
       <c r="R59" t="n">
-        <v>7038985</v>
+        <v>7038998</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6508,7 +6504,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129298813</v>
+        <v>129298820</v>
       </c>
       <c r="B60" t="n">
         <v>57727</v>
@@ -6543,10 +6539,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>487367</v>
+        <v>487354</v>
       </c>
       <c r="R60" t="n">
-        <v>7038998</v>
+        <v>7038894</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6610,7 +6606,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129298820</v>
+        <v>129298773</v>
       </c>
       <c r="B61" t="n">
         <v>57727</v>
@@ -6645,10 +6641,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>487354</v>
+        <v>486807</v>
       </c>
       <c r="R61" t="n">
-        <v>7038894</v>
+        <v>7039220</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6685,7 +6681,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6712,7 +6708,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129298774</v>
+        <v>129298776</v>
       </c>
       <c r="B62" t="n">
         <v>57727</v>
@@ -6747,10 +6743,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>486866</v>
+        <v>486855</v>
       </c>
       <c r="R62" t="n">
-        <v>7039249</v>
+        <v>7039252</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6814,7 +6810,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129298773</v>
+        <v>129298774</v>
       </c>
       <c r="B63" t="n">
         <v>57727</v>
@@ -6849,10 +6845,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>486807</v>
+        <v>486866</v>
       </c>
       <c r="R63" t="n">
-        <v>7039220</v>
+        <v>7039249</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7118,7 +7114,7 @@
         <v>129298853</v>
       </c>
       <c r="B66" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7135,14 +7131,10 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7314,61 +7306,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129298800</v>
+        <v>129298831</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>82998</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>487288</v>
+        <v>487307</v>
       </c>
       <c r="R68" t="n">
-        <v>7039015</v>
+        <v>7039016</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7401,11 +7377,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Födosökande hane</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7432,10 +7403,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129298737</v>
+        <v>129298839</v>
       </c>
       <c r="B69" t="n">
-        <v>83007</v>
+        <v>80146</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7443,21 +7414,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7467,7 +7438,7 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>487523</v>
+        <v>487269</v>
       </c>
       <c r="R69" t="n">
         <v>7039001</v>
@@ -7529,32 +7500,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129298828</v>
+        <v>129298737</v>
       </c>
       <c r="B70" t="n">
-        <v>80175</v>
+        <v>83007</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7564,10 +7535,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>487269</v>
+        <v>487523</v>
       </c>
       <c r="R70" t="n">
-        <v>7039004</v>
+        <v>7039001</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7626,32 +7597,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129298839</v>
+        <v>129298828</v>
       </c>
       <c r="B71" t="n">
-        <v>80146</v>
+        <v>80175</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7664,7 +7635,7 @@
         <v>487269</v>
       </c>
       <c r="R71" t="n">
-        <v>7039001</v>
+        <v>7039004</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8131,45 +8102,61 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129298831</v>
+        <v>129298800</v>
       </c>
       <c r="B76" t="n">
-        <v>82998</v>
+        <v>57727</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>487307</v>
+        <v>487288</v>
       </c>
       <c r="R76" t="n">
-        <v>7039016</v>
+        <v>7039015</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8202,6 +8189,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Födosökande hane</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8330,7 +8322,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129298781</v>
+        <v>129298753</v>
       </c>
       <c r="B78" t="n">
         <v>57727</v>
@@ -8365,10 +8357,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>486864</v>
+        <v>487240</v>
       </c>
       <c r="R78" t="n">
-        <v>7039272</v>
+        <v>7038959</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8432,7 +8424,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129298785</v>
+        <v>129298757</v>
       </c>
       <c r="B79" t="n">
         <v>57727</v>
@@ -8467,10 +8459,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>487007</v>
+        <v>487188</v>
       </c>
       <c r="R79" t="n">
-        <v>7039210</v>
+        <v>7038992</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8507,7 +8499,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8534,7 +8526,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129298753</v>
+        <v>129298781</v>
       </c>
       <c r="B80" t="n">
         <v>57727</v>
@@ -8569,10 +8561,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>487240</v>
+        <v>486864</v>
       </c>
       <c r="R80" t="n">
-        <v>7038959</v>
+        <v>7039272</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8636,7 +8628,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129298757</v>
+        <v>129298785</v>
       </c>
       <c r="B81" t="n">
         <v>57727</v>
@@ -8671,10 +8663,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>487188</v>
+        <v>487007</v>
       </c>
       <c r="R81" t="n">
-        <v>7038992</v>
+        <v>7039210</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8711,7 +8703,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8840,10 +8832,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129298841</v>
+        <v>129298771</v>
       </c>
       <c r="B83" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8851,21 +8843,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8875,10 +8867,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>487515</v>
+        <v>486885</v>
       </c>
       <c r="R83" t="n">
-        <v>7038993</v>
+        <v>7039172</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8911,6 +8903,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8937,7 +8934,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129298771</v>
+        <v>129298801</v>
       </c>
       <c r="B84" t="n">
         <v>57727</v>
@@ -8972,10 +8969,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>486885</v>
+        <v>487268</v>
       </c>
       <c r="R84" t="n">
-        <v>7039172</v>
+        <v>7039003</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9039,61 +9036,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129298847</v>
+        <v>129298814</v>
       </c>
       <c r="B85" t="n">
-        <v>57587</v>
+        <v>57727</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100136</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>486999</v>
+        <v>487366</v>
       </c>
       <c r="R85" t="n">
-        <v>7039199</v>
+        <v>7038997</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9130,7 +9111,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Jagades av en nötskrika</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9157,7 +9138,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129298789</v>
+        <v>129298772</v>
       </c>
       <c r="B86" t="n">
         <v>57727</v>
@@ -9192,10 +9173,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>487041</v>
+        <v>486849</v>
       </c>
       <c r="R86" t="n">
-        <v>7039167</v>
+        <v>7039185</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9259,7 +9240,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129298801</v>
+        <v>129298746</v>
       </c>
       <c r="B87" t="n">
         <v>57727</v>
@@ -9294,10 +9275,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>487268</v>
+        <v>487316</v>
       </c>
       <c r="R87" t="n">
-        <v>7039003</v>
+        <v>7038914</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9361,7 +9342,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129298814</v>
+        <v>129298789</v>
       </c>
       <c r="B88" t="n">
         <v>57727</v>
@@ -9396,10 +9377,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>487366</v>
+        <v>487041</v>
       </c>
       <c r="R88" t="n">
-        <v>7038997</v>
+        <v>7039167</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9436,7 +9417,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9463,45 +9444,61 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129298772</v>
+        <v>129298847</v>
       </c>
       <c r="B89" t="n">
-        <v>57727</v>
+        <v>57587</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>100136</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>486849</v>
+        <v>486999</v>
       </c>
       <c r="R89" t="n">
-        <v>7039185</v>
+        <v>7039199</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9538,7 +9535,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Jagades av en nötskrika</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9565,10 +9562,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129298746</v>
+        <v>129298841</v>
       </c>
       <c r="B90" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9576,21 +9573,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9600,10 +9597,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>487316</v>
+        <v>487515</v>
       </c>
       <c r="R90" t="n">
-        <v>7038914</v>
+        <v>7038993</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9636,11 +9633,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9667,10 +9659,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129298752</v>
+        <v>129298836</v>
       </c>
       <c r="B91" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9678,21 +9670,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9702,10 +9694,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>487246</v>
+        <v>486899</v>
       </c>
       <c r="R91" t="n">
-        <v>7038958</v>
+        <v>7039370</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9738,11 +9730,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9769,10 +9756,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129298768</v>
+        <v>129298743</v>
       </c>
       <c r="B92" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9780,21 +9767,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9804,10 +9791,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>487123</v>
+        <v>487331</v>
       </c>
       <c r="R92" t="n">
-        <v>7039032</v>
+        <v>7039023</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9840,11 +9827,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9871,10 +9853,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129298743</v>
+        <v>129298752</v>
       </c>
       <c r="B93" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9882,21 +9864,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9906,10 +9888,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>487331</v>
+        <v>487246</v>
       </c>
       <c r="R93" t="n">
-        <v>7039023</v>
+        <v>7038958</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9942,6 +9924,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9968,10 +9955,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129298836</v>
+        <v>129298768</v>
       </c>
       <c r="B94" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9979,21 +9966,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10003,10 +9990,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>486899</v>
+        <v>487123</v>
       </c>
       <c r="R94" t="n">
-        <v>7039370</v>
+        <v>7039032</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10039,6 +10026,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10167,7 +10159,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129298791</v>
+        <v>129298754</v>
       </c>
       <c r="B96" t="n">
         <v>57727</v>
@@ -10202,10 +10194,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>487112</v>
+        <v>487222</v>
       </c>
       <c r="R96" t="n">
-        <v>7039182</v>
+        <v>7038974</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10242,7 +10234,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10269,7 +10261,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129298754</v>
+        <v>129298791</v>
       </c>
       <c r="B97" t="n">
         <v>57727</v>
@@ -10304,10 +10296,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>487222</v>
+        <v>487112</v>
       </c>
       <c r="R97" t="n">
-        <v>7038974</v>
+        <v>7039182</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10344,7 +10336,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10468,10 +10460,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129298829</v>
+        <v>129298807</v>
       </c>
       <c r="B99" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10479,16 +10471,16 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -10496,33 +10488,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>487157</v>
+        <v>487337</v>
       </c>
       <c r="R99" t="n">
-        <v>7039100</v>
+        <v>7039015</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10555,6 +10531,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10581,10 +10562,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129298807</v>
+        <v>129298829</v>
       </c>
       <c r="B100" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10592,16 +10573,16 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -10609,17 +10590,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>487337</v>
+        <v>487157</v>
       </c>
       <c r="R100" t="n">
-        <v>7039015</v>
+        <v>7039100</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10652,11 +10649,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10979,7 +10971,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129298782</v>
+        <v>129298758</v>
       </c>
       <c r="B104" t="n">
         <v>57727</v>
@@ -11014,10 +11006,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>486857</v>
+        <v>487183</v>
       </c>
       <c r="R104" t="n">
-        <v>7039276</v>
+        <v>7038993</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11054,7 +11046,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11081,7 +11073,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129298758</v>
+        <v>129298815</v>
       </c>
       <c r="B105" t="n">
         <v>57727</v>
@@ -11116,10 +11108,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>487183</v>
+        <v>487375</v>
       </c>
       <c r="R105" t="n">
-        <v>7038993</v>
+        <v>7038981</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11183,7 +11175,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129298815</v>
+        <v>129298782</v>
       </c>
       <c r="B106" t="n">
         <v>57727</v>
@@ -11218,10 +11210,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>487375</v>
+        <v>486857</v>
       </c>
       <c r="R106" t="n">
-        <v>7038981</v>
+        <v>7039276</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11258,7 +11250,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11489,7 +11481,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129298796</v>
+        <v>129298760</v>
       </c>
       <c r="B109" t="n">
         <v>57727</v>
@@ -11524,10 +11516,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>487139</v>
+        <v>487141</v>
       </c>
       <c r="R109" t="n">
-        <v>7039088</v>
+        <v>7039023</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11564,7 +11556,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11591,7 +11583,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129298760</v>
+        <v>129298796</v>
       </c>
       <c r="B110" t="n">
         <v>57727</v>
@@ -11626,10 +11618,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>487141</v>
+        <v>487139</v>
       </c>
       <c r="R110" t="n">
-        <v>7039023</v>
+        <v>7039088</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11666,7 +11658,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 46357-2025 artfynd.xlsx
+++ b/artfynd/A 46357-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129298851</v>
+        <v>129298751</v>
       </c>
       <c r="B2" t="n">
-        <v>91554</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487144</v>
+        <v>487263</v>
       </c>
       <c r="R2" t="n">
-        <v>7039078</v>
+        <v>7038949</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,6 +748,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -760,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129298844</v>
+        <v>129298786</v>
       </c>
       <c r="B3" t="n">
-        <v>78054</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487374</v>
+        <v>487006</v>
       </c>
       <c r="R3" t="n">
-        <v>7039027</v>
+        <v>7039175</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -845,6 +850,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -857,19 +867,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129298751</v>
+        <v>129298818</v>
       </c>
       <c r="B4" t="n">
         <v>57727</v>
@@ -904,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487263</v>
+        <v>487389</v>
       </c>
       <c r="R4" t="n">
-        <v>7038949</v>
+        <v>7038925</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,19 +969,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129298818</v>
+        <v>129298819</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1006,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>487389</v>
+        <v>487346</v>
       </c>
       <c r="R5" t="n">
-        <v>7038925</v>
+        <v>7038911</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129298819</v>
+        <v>129298851</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>91554</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>487346</v>
+        <v>487144</v>
       </c>
       <c r="R6" t="n">
-        <v>7038911</v>
+        <v>7039078</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1146,11 +1156,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1163,22 +1168,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129298786</v>
+        <v>129298827</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>487006</v>
+        <v>487352</v>
       </c>
       <c r="R7" t="n">
-        <v>7039175</v>
+        <v>7038906</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1250,7 +1255,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1265,22 +1270,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129298827</v>
+        <v>129298844</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>78054</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1293,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>228579</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>487352</v>
+        <v>487374</v>
       </c>
       <c r="R8" t="n">
-        <v>7038906</v>
+        <v>7039027</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1350,11 +1355,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1367,22 +1367,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129298742</v>
+        <v>129298838</v>
       </c>
       <c r="B9" t="n">
-        <v>91540</v>
+        <v>80146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1390,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>487129</v>
+        <v>487035</v>
       </c>
       <c r="R9" t="n">
-        <v>7039097</v>
+        <v>7039161</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,22 +1464,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129298838</v>
+        <v>129298812</v>
       </c>
       <c r="B10" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,21 +1487,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>487035</v>
+        <v>487362</v>
       </c>
       <c r="R10" t="n">
-        <v>7039161</v>
+        <v>7039030</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1549,6 +1549,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1561,19 +1566,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129298812</v>
+        <v>129298759</v>
       </c>
       <c r="B11" t="n">
         <v>57727</v>
@@ -1608,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>487362</v>
+        <v>487171</v>
       </c>
       <c r="R11" t="n">
-        <v>7039030</v>
+        <v>7039000</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,22 +1668,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129298759</v>
+        <v>129298742</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1686,21 +1691,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1710,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>487171</v>
+        <v>487129</v>
       </c>
       <c r="R12" t="n">
-        <v>7039000</v>
+        <v>7039097</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,11 +1753,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1765,19 +1765,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129298761</v>
+        <v>129298799</v>
       </c>
       <c r="B13" t="n">
         <v>57727</v>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>487137</v>
+        <v>487230</v>
       </c>
       <c r="R13" t="n">
-        <v>7039024</v>
+        <v>7039041</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,19 +1867,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129298755</v>
+        <v>129298761</v>
       </c>
       <c r="B14" t="n">
         <v>57727</v>
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>487206</v>
+        <v>487137</v>
       </c>
       <c r="R14" t="n">
-        <v>7038982</v>
+        <v>7039024</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,19 +1969,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129298799</v>
+        <v>129298755</v>
       </c>
       <c r="B15" t="n">
         <v>57727</v>
@@ -2016,10 +2016,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>487230</v>
+        <v>487206</v>
       </c>
       <c r="R15" t="n">
-        <v>7039041</v>
+        <v>7038982</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2071,12 +2071,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2168,22 +2168,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129298857</v>
+        <v>129298777</v>
       </c>
       <c r="B17" t="n">
-        <v>82999</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>487340</v>
+        <v>486860</v>
       </c>
       <c r="R17" t="n">
-        <v>7039016</v>
+        <v>7039254</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2253,6 +2253,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2265,19 +2270,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129298777</v>
+        <v>129298787</v>
       </c>
       <c r="B18" t="n">
         <v>57727</v>
@@ -2312,10 +2317,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486860</v>
+        <v>486999</v>
       </c>
       <c r="R18" t="n">
-        <v>7039254</v>
+        <v>7039162</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2352,7 +2357,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2367,22 +2372,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129298787</v>
+        <v>129298857</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>82999</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2390,21 +2395,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2414,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486999</v>
+        <v>487340</v>
       </c>
       <c r="R19" t="n">
-        <v>7039162</v>
+        <v>7039016</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2452,11 +2457,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2469,22 +2469,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129298740</v>
+        <v>129298837</v>
       </c>
       <c r="B20" t="n">
-        <v>91540</v>
+        <v>80146</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>487145</v>
+        <v>487004</v>
       </c>
       <c r="R20" t="n">
-        <v>7039179</v>
+        <v>7039214</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2566,22 +2566,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129298852</v>
+        <v>129298775</v>
       </c>
       <c r="B21" t="n">
-        <v>91554</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2589,21 +2589,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>487127</v>
+        <v>486860</v>
       </c>
       <c r="R21" t="n">
-        <v>7039070</v>
+        <v>7039244</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2651,6 +2651,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2663,22 +2668,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129298837</v>
+        <v>129298845</v>
       </c>
       <c r="B22" t="n">
-        <v>80146</v>
+        <v>78054</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,21 +2691,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2710,10 +2715,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>487004</v>
+        <v>487526</v>
       </c>
       <c r="R22" t="n">
-        <v>7039214</v>
+        <v>7039006</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2760,39 +2765,39 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129298808</v>
+        <v>129298830</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>57568</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2800,17 +2805,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>487344</v>
+        <v>487123</v>
       </c>
       <c r="R23" t="n">
-        <v>7039018</v>
+        <v>7039173</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2845,11 +2862,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -2862,22 +2874,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129298845</v>
+        <v>129298808</v>
       </c>
       <c r="B24" t="n">
-        <v>78054</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2885,21 +2897,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2909,10 +2921,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>487526</v>
+        <v>487344</v>
       </c>
       <c r="R24" t="n">
-        <v>7039006</v>
+        <v>7039018</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2947,6 +2959,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -2959,19 +2976,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129298775</v>
+        <v>129298780</v>
       </c>
       <c r="B25" t="n">
         <v>57727</v>
@@ -3006,10 +3023,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486860</v>
+        <v>486859</v>
       </c>
       <c r="R25" t="n">
-        <v>7039244</v>
+        <v>7039262</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3046,7 +3063,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3061,22 +3078,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129298780</v>
+        <v>129298740</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3084,21 +3101,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3108,10 +3125,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486859</v>
+        <v>487145</v>
       </c>
       <c r="R26" t="n">
-        <v>7039262</v>
+        <v>7039179</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3146,11 +3163,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3163,69 +3175,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129298830</v>
+        <v>129298852</v>
       </c>
       <c r="B27" t="n">
-        <v>57568</v>
+        <v>91554</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102621</v>
+        <v>1204</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>487123</v>
+        <v>487127</v>
       </c>
       <c r="R27" t="n">
-        <v>7039173</v>
+        <v>7039070</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3272,22 +3272,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129298823</v>
+        <v>129298843</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3295,21 +3295,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3319,10 +3319,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>487363</v>
+        <v>487391</v>
       </c>
       <c r="R28" t="n">
-        <v>7038902</v>
+        <v>7038927</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3357,11 +3357,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3374,39 +3369,39 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129298765</v>
+        <v>129298846</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3421,10 +3416,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>487122</v>
+        <v>486976</v>
       </c>
       <c r="R29" t="n">
-        <v>7039034</v>
+        <v>7039216</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3459,11 +3454,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3476,19 +3466,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129298770</v>
+        <v>129298793</v>
       </c>
       <c r="B30" t="n">
         <v>57727</v>
@@ -3523,10 +3513,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486972</v>
+        <v>487183</v>
       </c>
       <c r="R30" t="n">
-        <v>7039122</v>
+        <v>7039216</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3578,19 +3568,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129298778</v>
+        <v>129298823</v>
       </c>
       <c r="B31" t="n">
         <v>57727</v>
@@ -3625,10 +3615,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486871</v>
+        <v>487363</v>
       </c>
       <c r="R31" t="n">
-        <v>7039260</v>
+        <v>7038902</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3680,19 +3670,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129298793</v>
+        <v>129298765</v>
       </c>
       <c r="B32" t="n">
         <v>57727</v>
@@ -3727,10 +3717,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>487183</v>
+        <v>487122</v>
       </c>
       <c r="R32" t="n">
-        <v>7039216</v>
+        <v>7039034</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3782,22 +3772,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129298843</v>
+        <v>129298770</v>
       </c>
       <c r="B33" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3805,21 +3795,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3829,10 +3819,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>487391</v>
+        <v>486972</v>
       </c>
       <c r="R33" t="n">
-        <v>7038927</v>
+        <v>7039122</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3867,6 +3857,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -3879,39 +3874,39 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129298846</v>
+        <v>129298778</v>
       </c>
       <c r="B34" t="n">
-        <v>57831</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3926,10 +3921,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486976</v>
+        <v>486871</v>
       </c>
       <c r="R34" t="n">
-        <v>7039216</v>
+        <v>7039260</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3964,6 +3959,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -3976,19 +3976,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129298750</v>
+        <v>129298792</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>487272</v>
+        <v>487153</v>
       </c>
       <c r="R35" t="n">
-        <v>7038946</v>
+        <v>7039212</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4063,7 +4063,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4078,19 +4078,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129298769</v>
+        <v>129298750</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4125,10 +4125,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>487109</v>
+        <v>487272</v>
       </c>
       <c r="R36" t="n">
-        <v>7039040</v>
+        <v>7038946</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4180,19 +4180,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129298804</v>
+        <v>129298769</v>
       </c>
       <c r="B37" t="n">
         <v>57727</v>
@@ -4227,10 +4227,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>487288</v>
+        <v>487109</v>
       </c>
       <c r="R37" t="n">
-        <v>7039002</v>
+        <v>7039040</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4282,19 +4282,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129298792</v>
+        <v>129298804</v>
       </c>
       <c r="B38" t="n">
         <v>57727</v>
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>487153</v>
+        <v>487288</v>
       </c>
       <c r="R38" t="n">
-        <v>7039212</v>
+        <v>7039002</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4384,12 +4384,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4486,22 +4486,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129298833</v>
+        <v>129298840</v>
       </c>
       <c r="B40" t="n">
-        <v>80147</v>
+        <v>80146</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4509,21 +4509,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>487265</v>
+        <v>487314</v>
       </c>
       <c r="R40" t="n">
-        <v>7038997</v>
+        <v>7039005</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4583,12 +4583,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4676,12 +4676,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4778,19 +4778,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129298809</v>
+        <v>129298795</v>
       </c>
       <c r="B43" t="n">
         <v>57727</v>
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>487348</v>
+        <v>487100</v>
       </c>
       <c r="R43" t="n">
-        <v>7039005</v>
+        <v>7039085</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4880,19 +4880,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129298802</v>
+        <v>129298748</v>
       </c>
       <c r="B44" t="n">
         <v>57727</v>
@@ -4927,10 +4927,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>487302</v>
+        <v>487301</v>
       </c>
       <c r="R44" t="n">
-        <v>7039045</v>
+        <v>7038925</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4982,19 +4982,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129298748</v>
+        <v>129298783</v>
       </c>
       <c r="B45" t="n">
         <v>57727</v>
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>487301</v>
+        <v>487024</v>
       </c>
       <c r="R45" t="n">
-        <v>7038925</v>
+        <v>7039203</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5084,19 +5084,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129298795</v>
+        <v>129298809</v>
       </c>
       <c r="B46" t="n">
         <v>57727</v>
@@ -5131,10 +5131,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>487100</v>
+        <v>487348</v>
       </c>
       <c r="R46" t="n">
-        <v>7039085</v>
+        <v>7039005</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5186,19 +5186,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129298783</v>
+        <v>129298802</v>
       </c>
       <c r="B47" t="n">
         <v>57727</v>
@@ -5233,10 +5233,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>487024</v>
+        <v>487302</v>
       </c>
       <c r="R47" t="n">
-        <v>7039203</v>
+        <v>7039045</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5288,22 +5288,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129298840</v>
+        <v>129298833</v>
       </c>
       <c r="B48" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5311,21 +5311,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5335,10 +5335,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>487314</v>
+        <v>487265</v>
       </c>
       <c r="R48" t="n">
-        <v>7039005</v>
+        <v>7038997</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5385,12 +5385,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5482,22 +5482,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129298842</v>
+        <v>129298738</v>
       </c>
       <c r="B50" t="n">
-        <v>80146</v>
+        <v>96952</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5505,21 +5505,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5529,10 +5529,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>487393</v>
+        <v>487311</v>
       </c>
       <c r="R50" t="n">
-        <v>7038908</v>
+        <v>7039063</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5579,22 +5579,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129298810</v>
+        <v>129298842</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5602,21 +5602,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5626,10 +5626,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>487355</v>
+        <v>487393</v>
       </c>
       <c r="R51" t="n">
-        <v>7039005</v>
+        <v>7038908</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5664,11 +5664,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5681,12 +5676,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5783,22 +5778,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129298738</v>
+        <v>129298810</v>
       </c>
       <c r="B53" t="n">
-        <v>96951</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5806,21 +5801,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5830,10 +5825,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>487311</v>
+        <v>487355</v>
       </c>
       <c r="R53" t="n">
-        <v>7039063</v>
+        <v>7039005</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5868,6 +5863,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -5880,12 +5880,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -5982,12 +5982,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6084,12 +6084,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6186,12 +6186,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6288,19 +6288,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129298816</v>
+        <v>129298776</v>
       </c>
       <c r="B58" t="n">
         <v>57727</v>
@@ -6335,10 +6335,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>487389</v>
+        <v>486855</v>
       </c>
       <c r="R58" t="n">
-        <v>7038985</v>
+        <v>7039252</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6390,19 +6390,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129298813</v>
+        <v>129298816</v>
       </c>
       <c r="B59" t="n">
         <v>57727</v>
@@ -6437,10 +6437,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>487367</v>
+        <v>487389</v>
       </c>
       <c r="R59" t="n">
-        <v>7038998</v>
+        <v>7038985</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6492,19 +6492,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129298820</v>
+        <v>129298813</v>
       </c>
       <c r="B60" t="n">
         <v>57727</v>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>487354</v>
+        <v>487367</v>
       </c>
       <c r="R60" t="n">
-        <v>7038894</v>
+        <v>7038998</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6594,19 +6594,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129298773</v>
+        <v>129298820</v>
       </c>
       <c r="B61" t="n">
         <v>57727</v>
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>486807</v>
+        <v>487354</v>
       </c>
       <c r="R61" t="n">
-        <v>7039220</v>
+        <v>7038894</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6681,7 +6681,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6696,19 +6696,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129298776</v>
+        <v>129298774</v>
       </c>
       <c r="B62" t="n">
         <v>57727</v>
@@ -6743,10 +6743,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>486855</v>
+        <v>486866</v>
       </c>
       <c r="R62" t="n">
-        <v>7039252</v>
+        <v>7039249</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6798,19 +6798,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129298774</v>
+        <v>129298773</v>
       </c>
       <c r="B63" t="n">
         <v>57727</v>
@@ -6845,10 +6845,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>486866</v>
+        <v>486807</v>
       </c>
       <c r="R63" t="n">
-        <v>7039249</v>
+        <v>7039220</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6900,12 +6900,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7002,22 +7002,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129298741</v>
+        <v>129298853</v>
       </c>
       <c r="B65" t="n">
-        <v>91540</v>
+        <v>91560</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7025,23 +7025,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7049,10 +7045,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>487185</v>
+        <v>487415</v>
       </c>
       <c r="R65" t="n">
-        <v>7039203</v>
+        <v>7038971</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7099,22 +7095,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129298853</v>
+        <v>129298811</v>
       </c>
       <c r="B66" t="n">
-        <v>91560</v>
+        <v>57727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7122,19 +7118,23 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7142,10 +7142,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>487415</v>
+        <v>487357</v>
       </c>
       <c r="R66" t="n">
-        <v>7038971</v>
+        <v>7039009</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7180,6 +7180,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7192,22 +7197,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129298811</v>
+        <v>129298741</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7215,21 +7220,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7239,10 +7244,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>487357</v>
+        <v>487185</v>
       </c>
       <c r="R67" t="n">
-        <v>7039009</v>
+        <v>7039203</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7277,11 +7282,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7294,44 +7294,44 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129298831</v>
+        <v>129298737</v>
       </c>
       <c r="B68" t="n">
-        <v>82998</v>
+        <v>83007</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>492</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7341,10 +7341,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>487307</v>
+        <v>487523</v>
       </c>
       <c r="R68" t="n">
-        <v>7039016</v>
+        <v>7039001</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7391,44 +7391,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129298839</v>
+        <v>129298828</v>
       </c>
       <c r="B69" t="n">
-        <v>80146</v>
+        <v>80175</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7441,7 +7441,7 @@
         <v>487269</v>
       </c>
       <c r="R69" t="n">
-        <v>7039001</v>
+        <v>7039004</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7488,22 +7488,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129298737</v>
+        <v>129298839</v>
       </c>
       <c r="B70" t="n">
-        <v>83007</v>
+        <v>80146</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7511,21 +7511,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7535,7 +7535,7 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>487523</v>
+        <v>487269</v>
       </c>
       <c r="R70" t="n">
         <v>7039001</v>
@@ -7585,44 +7585,44 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129298828</v>
+        <v>129298797</v>
       </c>
       <c r="B71" t="n">
-        <v>80175</v>
+        <v>57727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>487269</v>
+        <v>487134</v>
       </c>
       <c r="R71" t="n">
-        <v>7039004</v>
+        <v>7039037</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7670,6 +7670,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -7682,19 +7687,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129298797</v>
+        <v>129298803</v>
       </c>
       <c r="B72" t="n">
         <v>57727</v>
@@ -7729,7 +7734,7 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>487134</v>
+        <v>487303</v>
       </c>
       <c r="R72" t="n">
         <v>7039037</v>
@@ -7784,19 +7789,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129298803</v>
+        <v>129298822</v>
       </c>
       <c r="B73" t="n">
         <v>57727</v>
@@ -7831,10 +7836,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>487303</v>
+        <v>487373</v>
       </c>
       <c r="R73" t="n">
-        <v>7039037</v>
+        <v>7038897</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7886,19 +7891,19 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129298822</v>
+        <v>129298817</v>
       </c>
       <c r="B74" t="n">
         <v>57727</v>
@@ -7933,10 +7938,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>487373</v>
+        <v>487460</v>
       </c>
       <c r="R74" t="n">
-        <v>7038897</v>
+        <v>7038984</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7988,19 +7993,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129298817</v>
+        <v>129298821</v>
       </c>
       <c r="B75" t="n">
         <v>57727</v>
@@ -8035,10 +8040,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>487460</v>
+        <v>487368</v>
       </c>
       <c r="R75" t="n">
-        <v>7038984</v>
+        <v>7038892</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8090,73 +8095,57 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129298800</v>
+        <v>129298831</v>
       </c>
       <c r="B76" t="n">
-        <v>57727</v>
+        <v>82998</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>487288</v>
+        <v>487307</v>
       </c>
       <c r="R76" t="n">
-        <v>7039015</v>
+        <v>7039016</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8191,11 +8180,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Födosökande hane</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -8208,19 +8192,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129298821</v>
+        <v>129298800</v>
       </c>
       <c r="B77" t="n">
         <v>57727</v>
@@ -8248,17 +8232,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>487368</v>
+        <v>487288</v>
       </c>
       <c r="R77" t="n">
-        <v>7038892</v>
+        <v>7039015</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Födosökande hane</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8310,19 +8310,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129298753</v>
+        <v>129298781</v>
       </c>
       <c r="B78" t="n">
         <v>57727</v>
@@ -8357,10 +8357,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>487240</v>
+        <v>486864</v>
       </c>
       <c r="R78" t="n">
-        <v>7038959</v>
+        <v>7039272</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8412,19 +8412,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129298757</v>
+        <v>129298753</v>
       </c>
       <c r="B79" t="n">
         <v>57727</v>
@@ -8459,10 +8459,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>487188</v>
+        <v>487240</v>
       </c>
       <c r="R79" t="n">
-        <v>7038992</v>
+        <v>7038959</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8514,19 +8514,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129298781</v>
+        <v>129298757</v>
       </c>
       <c r="B80" t="n">
         <v>57727</v>
@@ -8561,10 +8561,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>486864</v>
+        <v>487188</v>
       </c>
       <c r="R80" t="n">
-        <v>7039272</v>
+        <v>7038992</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8616,19 +8616,19 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129298785</v>
+        <v>129298784</v>
       </c>
       <c r="B81" t="n">
         <v>57727</v>
@@ -8663,10 +8663,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>487007</v>
+        <v>487011</v>
       </c>
       <c r="R81" t="n">
-        <v>7039210</v>
+        <v>7039207</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8703,7 +8703,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8718,19 +8718,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129298784</v>
+        <v>129298785</v>
       </c>
       <c r="B82" t="n">
         <v>57727</v>
@@ -8765,10 +8765,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>487011</v>
+        <v>487007</v>
       </c>
       <c r="R82" t="n">
-        <v>7039207</v>
+        <v>7039210</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8805,7 +8805,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8820,12 +8820,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -8922,57 +8922,73 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129298801</v>
+        <v>129298847</v>
       </c>
       <c r="B84" t="n">
-        <v>57727</v>
+        <v>57587</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>100136</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>487268</v>
+        <v>486999</v>
       </c>
       <c r="R84" t="n">
-        <v>7039003</v>
+        <v>7039199</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9009,7 +9025,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Jagades av en nötskrika</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9024,19 +9040,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129298814</v>
+        <v>129298789</v>
       </c>
       <c r="B85" t="n">
         <v>57727</v>
@@ -9071,10 +9087,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>487366</v>
+        <v>487041</v>
       </c>
       <c r="R85" t="n">
-        <v>7038997</v>
+        <v>7039167</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9111,7 +9127,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9126,19 +9142,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129298772</v>
+        <v>129298801</v>
       </c>
       <c r="B86" t="n">
         <v>57727</v>
@@ -9173,10 +9189,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>486849</v>
+        <v>487268</v>
       </c>
       <c r="R86" t="n">
-        <v>7039185</v>
+        <v>7039003</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9228,12 +9244,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -9330,22 +9346,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129298789</v>
+        <v>129298841</v>
       </c>
       <c r="B88" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9353,21 +9369,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9377,10 +9393,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>487041</v>
+        <v>487515</v>
       </c>
       <c r="R88" t="n">
-        <v>7039167</v>
+        <v>7038993</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9415,11 +9431,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -9432,73 +9443,57 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129298847</v>
+        <v>129298814</v>
       </c>
       <c r="B89" t="n">
-        <v>57587</v>
+        <v>57727</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100136</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>486999</v>
+        <v>487366</v>
       </c>
       <c r="R89" t="n">
-        <v>7039199</v>
+        <v>7038997</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9535,7 +9530,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Jagades av en nötskrika</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9550,22 +9545,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129298841</v>
+        <v>129298772</v>
       </c>
       <c r="B90" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9573,21 +9568,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9597,10 +9592,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>487515</v>
+        <v>486849</v>
       </c>
       <c r="R90" t="n">
-        <v>7038993</v>
+        <v>7039185</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9635,6 +9630,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -9647,12 +9647,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -9744,22 +9744,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129298743</v>
+        <v>129298752</v>
       </c>
       <c r="B92" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9767,21 +9767,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9791,10 +9791,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>487331</v>
+        <v>487246</v>
       </c>
       <c r="R92" t="n">
-        <v>7039023</v>
+        <v>7038958</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9829,6 +9829,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
@@ -9841,19 +9846,19 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129298752</v>
+        <v>129298768</v>
       </c>
       <c r="B93" t="n">
         <v>57727</v>
@@ -9888,10 +9893,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>487246</v>
+        <v>487123</v>
       </c>
       <c r="R93" t="n">
-        <v>7038958</v>
+        <v>7039032</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9943,22 +9948,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129298768</v>
+        <v>129298743</v>
       </c>
       <c r="B94" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9966,21 +9971,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9990,10 +9995,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>487123</v>
+        <v>487331</v>
       </c>
       <c r="R94" t="n">
-        <v>7039032</v>
+        <v>7039023</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10028,11 +10033,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -10045,44 +10045,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129298745</v>
+        <v>129298739</v>
       </c>
       <c r="B95" t="n">
-        <v>57727</v>
+        <v>91504</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10092,10 +10092,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>486881</v>
+        <v>487384</v>
       </c>
       <c r="R95" t="n">
-        <v>7039175</v>
+        <v>7038973</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10130,11 +10130,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -10147,19 +10142,19 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129298754</v>
+        <v>129298745</v>
       </c>
       <c r="B96" t="n">
         <v>57727</v>
@@ -10194,10 +10189,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>487222</v>
+        <v>486881</v>
       </c>
       <c r="R96" t="n">
-        <v>7038974</v>
+        <v>7039175</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10234,7 +10229,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10249,12 +10244,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -10351,44 +10346,44 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129298739</v>
+        <v>129298754</v>
       </c>
       <c r="B98" t="n">
-        <v>91504</v>
+        <v>57727</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10398,10 +10393,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>487384</v>
+        <v>487222</v>
       </c>
       <c r="R98" t="n">
-        <v>7038973</v>
+        <v>7038974</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10436,6 +10431,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
@@ -10448,12 +10448,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -10550,12 +10550,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -10663,44 +10663,44 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129298832</v>
+        <v>129298806</v>
       </c>
       <c r="B101" t="n">
-        <v>82998</v>
+        <v>57727</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10710,10 +10710,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>487393</v>
+        <v>487339</v>
       </c>
       <c r="R101" t="n">
-        <v>7038976</v>
+        <v>7039009</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10748,6 +10748,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
@@ -10760,22 +10765,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129298858</v>
+        <v>129298782</v>
       </c>
       <c r="B102" t="n">
-        <v>82999</v>
+        <v>57727</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10783,21 +10788,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10807,10 +10812,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>487408</v>
+        <v>486857</v>
       </c>
       <c r="R102" t="n">
-        <v>7038959</v>
+        <v>7039276</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10845,6 +10850,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
@@ -10857,19 +10867,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129298806</v>
+        <v>129298758</v>
       </c>
       <c r="B103" t="n">
         <v>57727</v>
@@ -10904,10 +10914,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>487339</v>
+        <v>487183</v>
       </c>
       <c r="R103" t="n">
-        <v>7039009</v>
+        <v>7038993</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10959,19 +10969,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129298758</v>
+        <v>129298815</v>
       </c>
       <c r="B104" t="n">
         <v>57727</v>
@@ -11006,10 +11016,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>487183</v>
+        <v>487375</v>
       </c>
       <c r="R104" t="n">
-        <v>7038993</v>
+        <v>7038981</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11061,19 +11071,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129298815</v>
+        <v>129298788</v>
       </c>
       <c r="B105" t="n">
         <v>57727</v>
@@ -11108,10 +11118,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>487375</v>
+        <v>487039</v>
       </c>
       <c r="R105" t="n">
-        <v>7038981</v>
+        <v>7039164</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11163,44 +11173,44 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129298782</v>
+        <v>129298832</v>
       </c>
       <c r="B106" t="n">
-        <v>57727</v>
+        <v>82998</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11210,10 +11220,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>486857</v>
+        <v>487393</v>
       </c>
       <c r="R106" t="n">
-        <v>7039276</v>
+        <v>7038976</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11248,11 +11258,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
@@ -11265,22 +11270,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129298788</v>
+        <v>129298858</v>
       </c>
       <c r="B107" t="n">
-        <v>57727</v>
+        <v>82999</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11288,21 +11293,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11312,10 +11317,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>487039</v>
+        <v>487408</v>
       </c>
       <c r="R107" t="n">
-        <v>7039164</v>
+        <v>7038959</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11350,11 +11355,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -11367,12 +11367,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -11469,19 +11469,19 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129298760</v>
+        <v>129298796</v>
       </c>
       <c r="B109" t="n">
         <v>57727</v>
@@ -11516,10 +11516,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>487141</v>
+        <v>487139</v>
       </c>
       <c r="R109" t="n">
-        <v>7039023</v>
+        <v>7039088</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11556,7 +11556,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11571,19 +11571,19 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129298796</v>
+        <v>129298760</v>
       </c>
       <c r="B110" t="n">
         <v>57727</v>
@@ -11618,10 +11618,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>487139</v>
+        <v>487141</v>
       </c>
       <c r="R110" t="n">
-        <v>7039088</v>
+        <v>7039023</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11658,7 +11658,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11673,12 +11673,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
@@ -11775,12 +11775,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>

--- a/artfynd/A 46357-2025 artfynd.xlsx
+++ b/artfynd/A 46357-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129298751</v>
+        <v>129298786</v>
       </c>
       <c r="B2" t="n">
         <v>57727</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487263</v>
+        <v>487006</v>
       </c>
       <c r="R2" t="n">
-        <v>7038949</v>
+        <v>7039175</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129298786</v>
+        <v>129298751</v>
       </c>
       <c r="B3" t="n">
         <v>57727</v>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487006</v>
+        <v>487263</v>
       </c>
       <c r="R3" t="n">
-        <v>7039175</v>
+        <v>7038949</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129298851</v>
+        <v>129298844</v>
       </c>
       <c r="B6" t="n">
-        <v>91554</v>
+        <v>78056</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>228579</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>487144</v>
+        <v>487374</v>
       </c>
       <c r="R6" t="n">
-        <v>7039078</v>
+        <v>7039027</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129298827</v>
+        <v>129298851</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>91557</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>487352</v>
+        <v>487144</v>
       </c>
       <c r="R7" t="n">
-        <v>7038906</v>
+        <v>7039078</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1251,11 +1251,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1282,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129298844</v>
+        <v>129298827</v>
       </c>
       <c r="B8" t="n">
-        <v>78054</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1293,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228579</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1317,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>487374</v>
+        <v>487352</v>
       </c>
       <c r="R8" t="n">
-        <v>7039027</v>
+        <v>7038906</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1353,6 +1348,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1382,7 +1382,7 @@
         <v>129298838</v>
       </c>
       <c r="B9" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>129298742</v>
       </c>
       <c r="B12" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129298799</v>
+        <v>129298761</v>
       </c>
       <c r="B13" t="n">
         <v>57727</v>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>487230</v>
+        <v>487137</v>
       </c>
       <c r="R13" t="n">
-        <v>7039041</v>
+        <v>7039024</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129298761</v>
+        <v>129298755</v>
       </c>
       <c r="B14" t="n">
         <v>57727</v>
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>487137</v>
+        <v>487206</v>
       </c>
       <c r="R14" t="n">
-        <v>7039024</v>
+        <v>7038982</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1981,7 +1981,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129298755</v>
+        <v>129298799</v>
       </c>
       <c r="B15" t="n">
         <v>57727</v>
@@ -2016,10 +2016,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>487206</v>
+        <v>487230</v>
       </c>
       <c r="R15" t="n">
-        <v>7038982</v>
+        <v>7039041</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129298855</v>
+        <v>129298857</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>83003</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2094,21 +2094,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>487542</v>
+        <v>487340</v>
       </c>
       <c r="R16" t="n">
-        <v>7038985</v>
+        <v>7039016</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2180,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129298777</v>
+        <v>129298855</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486860</v>
+        <v>487542</v>
       </c>
       <c r="R17" t="n">
-        <v>7039254</v>
+        <v>7038985</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2251,11 +2251,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2282,7 +2277,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129298787</v>
+        <v>129298777</v>
       </c>
       <c r="B18" t="n">
         <v>57727</v>
@@ -2317,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486999</v>
+        <v>486860</v>
       </c>
       <c r="R18" t="n">
-        <v>7039162</v>
+        <v>7039254</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2357,7 +2352,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2384,10 +2379,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129298857</v>
+        <v>129298787</v>
       </c>
       <c r="B19" t="n">
-        <v>82999</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2395,21 +2390,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2419,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>487340</v>
+        <v>486999</v>
       </c>
       <c r="R19" t="n">
-        <v>7039016</v>
+        <v>7039162</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2455,6 +2450,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2484,7 +2484,7 @@
         <v>129298837</v>
       </c>
       <c r="B20" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2578,27 +2578,27 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129298775</v>
+        <v>129298830</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>57568</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2606,17 +2606,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486860</v>
+        <v>487123</v>
       </c>
       <c r="R21" t="n">
-        <v>7039244</v>
+        <v>7039173</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2649,11 +2661,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2683,7 +2690,7 @@
         <v>129298845</v>
       </c>
       <c r="B22" t="n">
-        <v>78054</v>
+        <v>78056</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2777,57 +2784,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129298830</v>
+        <v>129298740</v>
       </c>
       <c r="B23" t="n">
-        <v>57568</v>
+        <v>91543</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102621</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>487123</v>
+        <v>487145</v>
       </c>
       <c r="R23" t="n">
-        <v>7039173</v>
+        <v>7039179</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2886,10 +2881,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129298808</v>
+        <v>129298852</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>91557</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2897,21 +2892,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2921,10 +2916,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>487344</v>
+        <v>487127</v>
       </c>
       <c r="R24" t="n">
-        <v>7039018</v>
+        <v>7039070</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2957,11 +2952,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2988,7 +2978,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129298780</v>
+        <v>129298775</v>
       </c>
       <c r="B25" t="n">
         <v>57727</v>
@@ -3023,10 +3013,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486859</v>
+        <v>486860</v>
       </c>
       <c r="R25" t="n">
-        <v>7039262</v>
+        <v>7039244</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3063,7 +3053,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3090,10 +3080,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129298740</v>
+        <v>129298808</v>
       </c>
       <c r="B26" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3101,21 +3091,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3125,10 +3115,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>487145</v>
+        <v>487344</v>
       </c>
       <c r="R26" t="n">
-        <v>7039179</v>
+        <v>7039018</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3161,6 +3151,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3187,10 +3182,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129298852</v>
+        <v>129298780</v>
       </c>
       <c r="B27" t="n">
-        <v>91554</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3198,21 +3193,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3222,10 +3217,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>487127</v>
+        <v>486859</v>
       </c>
       <c r="R27" t="n">
-        <v>7039070</v>
+        <v>7039262</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3258,6 +3253,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3284,10 +3284,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129298843</v>
+        <v>129298765</v>
       </c>
       <c r="B28" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3295,21 +3295,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3319,10 +3319,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>487391</v>
+        <v>487122</v>
       </c>
       <c r="R28" t="n">
-        <v>7038927</v>
+        <v>7039034</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3355,6 +3355,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3381,27 +3386,27 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129298846</v>
+        <v>129298770</v>
       </c>
       <c r="B29" t="n">
-        <v>57831</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3416,10 +3421,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486976</v>
+        <v>486972</v>
       </c>
       <c r="R29" t="n">
-        <v>7039216</v>
+        <v>7039122</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3452,6 +3457,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3478,10 +3488,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129298793</v>
+        <v>129298843</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>80148</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3489,21 +3499,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3513,10 +3523,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>487183</v>
+        <v>487391</v>
       </c>
       <c r="R30" t="n">
-        <v>7039216</v>
+        <v>7038927</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3549,11 +3559,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3580,7 +3585,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129298823</v>
+        <v>129298793</v>
       </c>
       <c r="B31" t="n">
         <v>57727</v>
@@ -3615,10 +3620,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>487363</v>
+        <v>487183</v>
       </c>
       <c r="R31" t="n">
-        <v>7038902</v>
+        <v>7039216</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3682,7 +3687,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129298765</v>
+        <v>129298823</v>
       </c>
       <c r="B32" t="n">
         <v>57727</v>
@@ -3717,10 +3722,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>487122</v>
+        <v>487363</v>
       </c>
       <c r="R32" t="n">
-        <v>7039034</v>
+        <v>7038902</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3784,7 +3789,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129298770</v>
+        <v>129298778</v>
       </c>
       <c r="B33" t="n">
         <v>57727</v>
@@ -3819,10 +3824,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486972</v>
+        <v>486871</v>
       </c>
       <c r="R33" t="n">
-        <v>7039122</v>
+        <v>7039260</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3886,27 +3891,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129298778</v>
+        <v>129298846</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3921,10 +3926,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486871</v>
+        <v>486976</v>
       </c>
       <c r="R34" t="n">
-        <v>7039260</v>
+        <v>7039216</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3957,11 +3962,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3988,7 +3988,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129298792</v>
+        <v>129298769</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>487153</v>
+        <v>487109</v>
       </c>
       <c r="R35" t="n">
-        <v>7039212</v>
+        <v>7039040</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4090,7 +4090,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129298750</v>
+        <v>129298804</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4125,10 +4125,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>487272</v>
+        <v>487288</v>
       </c>
       <c r="R36" t="n">
-        <v>7038946</v>
+        <v>7039002</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4192,7 +4192,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129298769</v>
+        <v>129298792</v>
       </c>
       <c r="B37" t="n">
         <v>57727</v>
@@ -4227,10 +4227,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>487109</v>
+        <v>487153</v>
       </c>
       <c r="R37" t="n">
-        <v>7039040</v>
+        <v>7039212</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129298804</v>
+        <v>129298794</v>
       </c>
       <c r="B38" t="n">
         <v>57727</v>
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>487288</v>
+        <v>487186</v>
       </c>
       <c r="R38" t="n">
-        <v>7039002</v>
+        <v>7039192</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4396,7 +4396,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129298794</v>
+        <v>129298750</v>
       </c>
       <c r="B39" t="n">
         <v>57727</v>
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>487186</v>
+        <v>487272</v>
       </c>
       <c r="R39" t="n">
-        <v>7039192</v>
+        <v>7038946</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4498,10 +4498,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129298840</v>
+        <v>129298833</v>
       </c>
       <c r="B40" t="n">
-        <v>80146</v>
+        <v>80149</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4509,21 +4509,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>487314</v>
+        <v>487265</v>
       </c>
       <c r="R40" t="n">
-        <v>7039005</v>
+        <v>7038997</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4595,10 +4595,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129298854</v>
+        <v>129298805</v>
       </c>
       <c r="B41" t="n">
-        <v>91560</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4606,19 +4606,23 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4626,10 +4630,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>487522</v>
+        <v>487346</v>
       </c>
       <c r="R41" t="n">
-        <v>7038997</v>
+        <v>7039012</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4662,6 +4666,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4688,7 +4697,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129298805</v>
+        <v>129298802</v>
       </c>
       <c r="B42" t="n">
         <v>57727</v>
@@ -4723,10 +4732,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>487346</v>
+        <v>487302</v>
       </c>
       <c r="R42" t="n">
-        <v>7039012</v>
+        <v>7039045</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4994,10 +5003,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129298783</v>
+        <v>129298854</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>91563</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5005,23 +5014,19 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5029,10 +5034,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>487024</v>
+        <v>487522</v>
       </c>
       <c r="R45" t="n">
-        <v>7039203</v>
+        <v>7038997</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5065,11 +5070,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5096,10 +5096,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129298809</v>
+        <v>129298840</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>80148</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5107,21 +5107,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>487348</v>
+        <v>487314</v>
       </c>
       <c r="R46" t="n">
         <v>7039005</v>
@@ -5167,11 +5167,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5198,7 +5193,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129298802</v>
+        <v>129298809</v>
       </c>
       <c r="B47" t="n">
         <v>57727</v>
@@ -5233,10 +5228,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>487302</v>
+        <v>487348</v>
       </c>
       <c r="R47" t="n">
-        <v>7039045</v>
+        <v>7039005</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5300,10 +5295,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129298833</v>
+        <v>129298783</v>
       </c>
       <c r="B48" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5311,21 +5306,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5335,10 +5330,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>487265</v>
+        <v>487024</v>
       </c>
       <c r="R48" t="n">
-        <v>7038997</v>
+        <v>7039203</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5371,6 +5366,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5397,10 +5397,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129298856</v>
+        <v>129298738</v>
       </c>
       <c r="B49" t="n">
-        <v>82873</v>
+        <v>96956</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5408,21 +5408,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>53</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>487541</v>
+        <v>487311</v>
       </c>
       <c r="R49" t="n">
-        <v>7038983</v>
+        <v>7039063</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5494,10 +5494,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129298738</v>
+        <v>129298856</v>
       </c>
       <c r="B50" t="n">
-        <v>96952</v>
+        <v>82877</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5505,21 +5505,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>1312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5529,10 +5529,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>487311</v>
+        <v>487541</v>
       </c>
       <c r="R50" t="n">
-        <v>7039063</v>
+        <v>7038983</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5594,7 +5594,7 @@
         <v>129298842</v>
       </c>
       <c r="B51" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5892,10 +5892,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129298825</v>
+        <v>129298779</v>
       </c>
       <c r="B54" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5903,21 +5903,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5927,10 +5927,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>487247</v>
+        <v>486866</v>
       </c>
       <c r="R54" t="n">
-        <v>7039020</v>
+        <v>7039259</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5994,7 +5994,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129298779</v>
+        <v>129298749</v>
       </c>
       <c r="B55" t="n">
         <v>57727</v>
@@ -6029,10 +6029,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486866</v>
+        <v>487275</v>
       </c>
       <c r="R55" t="n">
-        <v>7039259</v>
+        <v>7038947</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6096,10 +6096,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129298749</v>
+        <v>129298825</v>
       </c>
       <c r="B56" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6107,21 +6107,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6131,10 +6131,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>487275</v>
+        <v>487247</v>
       </c>
       <c r="R56" t="n">
-        <v>7038947</v>
+        <v>7039020</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6198,7 +6198,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129298767</v>
+        <v>129298776</v>
       </c>
       <c r="B57" t="n">
         <v>57727</v>
@@ -6233,10 +6233,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>487123</v>
+        <v>486855</v>
       </c>
       <c r="R57" t="n">
-        <v>7039031</v>
+        <v>7039252</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6300,7 +6300,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129298776</v>
+        <v>129298774</v>
       </c>
       <c r="B58" t="n">
         <v>57727</v>
@@ -6335,10 +6335,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>486855</v>
+        <v>486866</v>
       </c>
       <c r="R58" t="n">
-        <v>7039252</v>
+        <v>7039249</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6402,7 +6402,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129298816</v>
+        <v>129298773</v>
       </c>
       <c r="B59" t="n">
         <v>57727</v>
@@ -6437,10 +6437,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>487389</v>
+        <v>486807</v>
       </c>
       <c r="R59" t="n">
-        <v>7038985</v>
+        <v>7039220</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6504,7 +6504,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129298813</v>
+        <v>129298767</v>
       </c>
       <c r="B60" t="n">
         <v>57727</v>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>487367</v>
+        <v>487123</v>
       </c>
       <c r="R60" t="n">
-        <v>7038998</v>
+        <v>7039031</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6606,7 +6606,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129298820</v>
+        <v>129298816</v>
       </c>
       <c r="B61" t="n">
         <v>57727</v>
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>487354</v>
+        <v>487389</v>
       </c>
       <c r="R61" t="n">
-        <v>7038894</v>
+        <v>7038985</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6708,7 +6708,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129298774</v>
+        <v>129298813</v>
       </c>
       <c r="B62" t="n">
         <v>57727</v>
@@ -6743,10 +6743,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>486866</v>
+        <v>487367</v>
       </c>
       <c r="R62" t="n">
-        <v>7039249</v>
+        <v>7038998</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6783,7 +6783,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6810,7 +6810,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129298773</v>
+        <v>129298820</v>
       </c>
       <c r="B63" t="n">
         <v>57727</v>
@@ -6845,10 +6845,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>486807</v>
+        <v>487354</v>
       </c>
       <c r="R63" t="n">
-        <v>7039220</v>
+        <v>7038894</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6885,7 +6885,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7014,10 +7014,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129298853</v>
+        <v>129298741</v>
       </c>
       <c r="B65" t="n">
-        <v>91560</v>
+        <v>91543</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7025,19 +7025,23 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7045,10 +7049,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>487415</v>
+        <v>487185</v>
       </c>
       <c r="R65" t="n">
-        <v>7038971</v>
+        <v>7039203</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7107,10 +7111,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129298811</v>
+        <v>129298853</v>
       </c>
       <c r="B66" t="n">
-        <v>57727</v>
+        <v>91563</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7118,23 +7122,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7142,10 +7142,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>487357</v>
+        <v>487415</v>
       </c>
       <c r="R66" t="n">
-        <v>7039009</v>
+        <v>7038971</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7178,11 +7178,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7209,10 +7204,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129298741</v>
+        <v>129298811</v>
       </c>
       <c r="B67" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7220,21 +7215,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7244,10 +7239,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>487185</v>
+        <v>487357</v>
       </c>
       <c r="R67" t="n">
-        <v>7039203</v>
+        <v>7039009</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7280,6 +7275,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7306,32 +7306,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129298737</v>
+        <v>129298831</v>
       </c>
       <c r="B68" t="n">
-        <v>83007</v>
+        <v>83002</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>492</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7341,10 +7341,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>487523</v>
+        <v>487307</v>
       </c>
       <c r="R68" t="n">
-        <v>7039001</v>
+        <v>7039016</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7403,32 +7403,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129298828</v>
+        <v>129298737</v>
       </c>
       <c r="B69" t="n">
-        <v>80175</v>
+        <v>83011</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7438,10 +7438,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>487269</v>
+        <v>487523</v>
       </c>
       <c r="R69" t="n">
-        <v>7039004</v>
+        <v>7039001</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7500,10 +7500,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129298839</v>
+        <v>129298822</v>
       </c>
       <c r="B70" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7511,21 +7511,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7535,10 +7535,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>487269</v>
+        <v>487373</v>
       </c>
       <c r="R70" t="n">
-        <v>7039001</v>
+        <v>7038897</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7571,6 +7571,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7801,7 +7806,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129298822</v>
+        <v>129298817</v>
       </c>
       <c r="B73" t="n">
         <v>57727</v>
@@ -7836,10 +7841,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>487373</v>
+        <v>487460</v>
       </c>
       <c r="R73" t="n">
-        <v>7038897</v>
+        <v>7038984</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7903,7 +7908,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129298817</v>
+        <v>129298800</v>
       </c>
       <c r="B74" t="n">
         <v>57727</v>
@@ -7931,17 +7936,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>487460</v>
+        <v>487288</v>
       </c>
       <c r="R74" t="n">
-        <v>7038984</v>
+        <v>7039015</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7978,7 +7999,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Födosökande hane</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8107,32 +8128,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129298831</v>
+        <v>129298828</v>
       </c>
       <c r="B76" t="n">
-        <v>82998</v>
+        <v>80177</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>492</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8142,10 +8163,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>487307</v>
+        <v>487269</v>
       </c>
       <c r="R76" t="n">
-        <v>7039016</v>
+        <v>7039004</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8204,10 +8225,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129298800</v>
+        <v>129298839</v>
       </c>
       <c r="B77" t="n">
-        <v>57727</v>
+        <v>80148</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8215,50 +8236,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>487288</v>
+        <v>487269</v>
       </c>
       <c r="R77" t="n">
-        <v>7039015</v>
+        <v>7039001</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8291,11 +8296,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Födosökande hane</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8424,7 +8424,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129298753</v>
+        <v>129298785</v>
       </c>
       <c r="B79" t="n">
         <v>57727</v>
@@ -8459,10 +8459,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>487240</v>
+        <v>487007</v>
       </c>
       <c r="R79" t="n">
-        <v>7038959</v>
+        <v>7039210</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8526,7 +8526,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129298757</v>
+        <v>129298784</v>
       </c>
       <c r="B80" t="n">
         <v>57727</v>
@@ -8561,10 +8561,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>487188</v>
+        <v>487011</v>
       </c>
       <c r="R80" t="n">
-        <v>7038992</v>
+        <v>7039207</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8628,7 +8628,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129298784</v>
+        <v>129298757</v>
       </c>
       <c r="B81" t="n">
         <v>57727</v>
@@ -8663,10 +8663,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>487011</v>
+        <v>487188</v>
       </c>
       <c r="R81" t="n">
-        <v>7039207</v>
+        <v>7038992</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8730,7 +8730,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129298785</v>
+        <v>129298753</v>
       </c>
       <c r="B82" t="n">
         <v>57727</v>
@@ -8765,10 +8765,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>487007</v>
+        <v>487240</v>
       </c>
       <c r="R82" t="n">
-        <v>7039210</v>
+        <v>7038959</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8805,7 +8805,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8832,45 +8832,61 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129298771</v>
+        <v>129298847</v>
       </c>
       <c r="B83" t="n">
-        <v>57727</v>
+        <v>57587</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>100136</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>486885</v>
+        <v>486999</v>
       </c>
       <c r="R83" t="n">
-        <v>7039172</v>
+        <v>7039199</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8907,7 +8923,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Jagades av en nötskrika</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8934,61 +8950,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129298847</v>
+        <v>129298789</v>
       </c>
       <c r="B84" t="n">
-        <v>57587</v>
+        <v>57727</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100136</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>486999</v>
+        <v>487041</v>
       </c>
       <c r="R84" t="n">
-        <v>7039199</v>
+        <v>7039167</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9025,7 +9025,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Jagades av en nötskrika</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9052,7 +9052,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129298789</v>
+        <v>129298771</v>
       </c>
       <c r="B85" t="n">
         <v>57727</v>
@@ -9087,10 +9087,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>487041</v>
+        <v>486885</v>
       </c>
       <c r="R85" t="n">
-        <v>7039167</v>
+        <v>7039172</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9256,7 +9256,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129298746</v>
+        <v>129298814</v>
       </c>
       <c r="B87" t="n">
         <v>57727</v>
@@ -9291,10 +9291,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>487316</v>
+        <v>487366</v>
       </c>
       <c r="R87" t="n">
-        <v>7038914</v>
+        <v>7038997</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9331,7 +9331,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9358,10 +9358,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129298841</v>
+        <v>129298772</v>
       </c>
       <c r="B88" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9369,21 +9369,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9393,10 +9393,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>487515</v>
+        <v>486849</v>
       </c>
       <c r="R88" t="n">
-        <v>7038993</v>
+        <v>7039185</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9429,6 +9429,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9455,7 +9460,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129298814</v>
+        <v>129298746</v>
       </c>
       <c r="B89" t="n">
         <v>57727</v>
@@ -9490,10 +9495,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>487366</v>
+        <v>487316</v>
       </c>
       <c r="R89" t="n">
-        <v>7038997</v>
+        <v>7038914</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9530,7 +9535,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9557,10 +9562,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129298772</v>
+        <v>129298841</v>
       </c>
       <c r="B90" t="n">
-        <v>57727</v>
+        <v>80148</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9568,21 +9573,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9592,10 +9597,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>486849</v>
+        <v>487515</v>
       </c>
       <c r="R90" t="n">
-        <v>7039185</v>
+        <v>7038993</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9628,11 +9633,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9659,10 +9659,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129298836</v>
+        <v>129298752</v>
       </c>
       <c r="B91" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9670,21 +9670,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9694,10 +9694,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>486899</v>
+        <v>487246</v>
       </c>
       <c r="R91" t="n">
-        <v>7039370</v>
+        <v>7038958</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9730,6 +9730,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9756,7 +9761,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129298752</v>
+        <v>129298768</v>
       </c>
       <c r="B92" t="n">
         <v>57727</v>
@@ -9791,10 +9796,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>487246</v>
+        <v>487123</v>
       </c>
       <c r="R92" t="n">
-        <v>7038958</v>
+        <v>7039032</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9858,10 +9863,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129298768</v>
+        <v>129298743</v>
       </c>
       <c r="B93" t="n">
-        <v>57727</v>
+        <v>91543</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9869,21 +9874,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9893,10 +9898,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>487123</v>
+        <v>487331</v>
       </c>
       <c r="R93" t="n">
-        <v>7039032</v>
+        <v>7039023</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9929,11 +9934,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9960,10 +9960,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129298743</v>
+        <v>129298836</v>
       </c>
       <c r="B94" t="n">
-        <v>91540</v>
+        <v>80148</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9971,21 +9971,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9995,10 +9995,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>487331</v>
+        <v>486899</v>
       </c>
       <c r="R94" t="n">
-        <v>7039023</v>
+        <v>7039370</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10060,7 +10060,7 @@
         <v>129298739</v>
       </c>
       <c r="B95" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129298791</v>
+        <v>129298754</v>
       </c>
       <c r="B97" t="n">
         <v>57727</v>
@@ -10291,10 +10291,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>487112</v>
+        <v>487222</v>
       </c>
       <c r="R97" t="n">
-        <v>7039182</v>
+        <v>7038974</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10331,7 +10331,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10358,7 +10358,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129298754</v>
+        <v>129298791</v>
       </c>
       <c r="B98" t="n">
         <v>57727</v>
@@ -10393,10 +10393,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>487222</v>
+        <v>487112</v>
       </c>
       <c r="R98" t="n">
-        <v>7038974</v>
+        <v>7039182</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10433,7 +10433,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10460,10 +10460,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129298807</v>
+        <v>129298829</v>
       </c>
       <c r="B99" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10471,16 +10471,16 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -10488,17 +10488,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>487337</v>
+        <v>487157</v>
       </c>
       <c r="R99" t="n">
-        <v>7039015</v>
+        <v>7039100</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10531,11 +10547,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10562,10 +10573,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129298829</v>
+        <v>129298807</v>
       </c>
       <c r="B100" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10573,16 +10584,16 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -10590,33 +10601,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>487157</v>
+        <v>487337</v>
       </c>
       <c r="R100" t="n">
-        <v>7039100</v>
+        <v>7039015</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10649,6 +10644,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10675,10 +10675,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129298806</v>
+        <v>129298858</v>
       </c>
       <c r="B101" t="n">
-        <v>57727</v>
+        <v>83003</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10686,21 +10686,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10710,10 +10710,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>487339</v>
+        <v>487408</v>
       </c>
       <c r="R101" t="n">
-        <v>7039009</v>
+        <v>7038959</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10746,11 +10746,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10981,7 +10976,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129298815</v>
+        <v>129298788</v>
       </c>
       <c r="B104" t="n">
         <v>57727</v>
@@ -11016,10 +11011,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>487375</v>
+        <v>487039</v>
       </c>
       <c r="R104" t="n">
-        <v>7038981</v>
+        <v>7039164</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11083,7 +11078,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129298788</v>
+        <v>129298806</v>
       </c>
       <c r="B105" t="n">
         <v>57727</v>
@@ -11118,10 +11113,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>487039</v>
+        <v>487339</v>
       </c>
       <c r="R105" t="n">
-        <v>7039164</v>
+        <v>7039009</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11185,32 +11180,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129298832</v>
+        <v>129298815</v>
       </c>
       <c r="B106" t="n">
-        <v>82998</v>
+        <v>57727</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11220,10 +11215,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>487393</v>
+        <v>487375</v>
       </c>
       <c r="R106" t="n">
-        <v>7038976</v>
+        <v>7038981</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11256,6 +11251,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11282,32 +11282,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129298858</v>
+        <v>129298832</v>
       </c>
       <c r="B107" t="n">
-        <v>82999</v>
+        <v>83002</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>308</v>
+        <v>492</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11317,10 +11317,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>487408</v>
+        <v>487393</v>
       </c>
       <c r="R107" t="n">
-        <v>7038959</v>
+        <v>7038976</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>

--- a/artfynd/A 46357-2025 artfynd.xlsx
+++ b/artfynd/A 46357-2025 artfynd.xlsx
@@ -1879,7 +1879,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129298755</v>
+        <v>129298799</v>
       </c>
       <c r="B14" t="n">
         <v>57727</v>
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>487206</v>
+        <v>487230</v>
       </c>
       <c r="R14" t="n">
-        <v>7038982</v>
+        <v>7039041</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1981,7 +1981,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129298799</v>
+        <v>129298755</v>
       </c>
       <c r="B15" t="n">
         <v>57727</v>
@@ -2016,10 +2016,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>487230</v>
+        <v>487206</v>
       </c>
       <c r="R15" t="n">
-        <v>7039041</v>
+        <v>7038982</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2578,27 +2578,27 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129298830</v>
+        <v>129298775</v>
       </c>
       <c r="B21" t="n">
-        <v>57568</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2606,29 +2606,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>487123</v>
+        <v>486860</v>
       </c>
       <c r="R21" t="n">
-        <v>7039173</v>
+        <v>7039244</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2661,6 +2649,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2687,10 +2680,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129298845</v>
+        <v>129298808</v>
       </c>
       <c r="B22" t="n">
-        <v>78056</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2698,21 +2691,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2722,10 +2715,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>487526</v>
+        <v>487344</v>
       </c>
       <c r="R22" t="n">
-        <v>7039006</v>
+        <v>7039018</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2758,6 +2751,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2784,10 +2782,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129298740</v>
+        <v>129298780</v>
       </c>
       <c r="B23" t="n">
-        <v>91543</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2795,21 +2793,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2819,10 +2817,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>487145</v>
+        <v>486859</v>
       </c>
       <c r="R23" t="n">
-        <v>7039179</v>
+        <v>7039262</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2855,6 +2853,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2881,10 +2884,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129298852</v>
+        <v>129298740</v>
       </c>
       <c r="B24" t="n">
-        <v>91557</v>
+        <v>91543</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2892,21 +2895,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2916,10 +2919,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>487127</v>
+        <v>487145</v>
       </c>
       <c r="R24" t="n">
-        <v>7039070</v>
+        <v>7039179</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2978,10 +2981,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129298775</v>
+        <v>129298852</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>91557</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2989,21 +2992,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3013,10 +3016,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486860</v>
+        <v>487127</v>
       </c>
       <c r="R25" t="n">
-        <v>7039244</v>
+        <v>7039070</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3049,11 +3052,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3080,27 +3078,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129298808</v>
+        <v>129298830</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>57568</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3108,17 +3106,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>487344</v>
+        <v>487123</v>
       </c>
       <c r="R26" t="n">
-        <v>7039018</v>
+        <v>7039173</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3151,11 +3161,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3182,10 +3187,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129298780</v>
+        <v>129298845</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>78056</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3193,21 +3198,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3217,10 +3222,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486859</v>
+        <v>487526</v>
       </c>
       <c r="R27" t="n">
-        <v>7039262</v>
+        <v>7039006</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3253,11 +3258,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3284,10 +3284,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129298765</v>
+        <v>129298843</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>80148</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3295,21 +3295,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3319,10 +3319,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>487122</v>
+        <v>487391</v>
       </c>
       <c r="R28" t="n">
-        <v>7039034</v>
+        <v>7038927</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3355,11 +3355,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3386,7 +3381,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129298770</v>
+        <v>129298793</v>
       </c>
       <c r="B29" t="n">
         <v>57727</v>
@@ -3421,10 +3416,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486972</v>
+        <v>487183</v>
       </c>
       <c r="R29" t="n">
-        <v>7039122</v>
+        <v>7039216</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3488,10 +3483,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129298843</v>
+        <v>129298823</v>
       </c>
       <c r="B30" t="n">
-        <v>80148</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3499,21 +3494,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3523,10 +3518,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>487391</v>
+        <v>487363</v>
       </c>
       <c r="R30" t="n">
-        <v>7038927</v>
+        <v>7038902</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3559,6 +3554,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3585,7 +3585,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129298793</v>
+        <v>129298778</v>
       </c>
       <c r="B31" t="n">
         <v>57727</v>
@@ -3620,10 +3620,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>487183</v>
+        <v>486871</v>
       </c>
       <c r="R31" t="n">
-        <v>7039216</v>
+        <v>7039260</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3687,27 +3687,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129298823</v>
+        <v>129298846</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>487363</v>
+        <v>486976</v>
       </c>
       <c r="R32" t="n">
-        <v>7038902</v>
+        <v>7039216</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3758,11 +3758,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3789,7 +3784,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129298778</v>
+        <v>129298765</v>
       </c>
       <c r="B33" t="n">
         <v>57727</v>
@@ -3824,10 +3819,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486871</v>
+        <v>487122</v>
       </c>
       <c r="R33" t="n">
-        <v>7039260</v>
+        <v>7039034</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3891,27 +3886,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129298846</v>
+        <v>129298770</v>
       </c>
       <c r="B34" t="n">
-        <v>57831</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3926,10 +3921,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486976</v>
+        <v>486972</v>
       </c>
       <c r="R34" t="n">
-        <v>7039216</v>
+        <v>7039122</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3962,6 +3957,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3988,7 +3988,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129298769</v>
+        <v>129298750</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>487109</v>
+        <v>487272</v>
       </c>
       <c r="R35" t="n">
-        <v>7039040</v>
+        <v>7038946</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4063,7 +4063,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4090,7 +4090,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129298804</v>
+        <v>129298769</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4125,10 +4125,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>487288</v>
+        <v>487109</v>
       </c>
       <c r="R36" t="n">
-        <v>7039002</v>
+        <v>7039040</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4192,7 +4192,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129298792</v>
+        <v>129298804</v>
       </c>
       <c r="B37" t="n">
         <v>57727</v>
@@ -4227,10 +4227,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>487153</v>
+        <v>487288</v>
       </c>
       <c r="R37" t="n">
-        <v>7039212</v>
+        <v>7039002</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129298794</v>
+        <v>129298792</v>
       </c>
       <c r="B38" t="n">
         <v>57727</v>
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>487186</v>
+        <v>487153</v>
       </c>
       <c r="R38" t="n">
-        <v>7039192</v>
+        <v>7039212</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4396,7 +4396,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129298750</v>
+        <v>129298794</v>
       </c>
       <c r="B39" t="n">
         <v>57727</v>
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>487272</v>
+        <v>487186</v>
       </c>
       <c r="R39" t="n">
-        <v>7038946</v>
+        <v>7039192</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4595,10 +4595,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129298805</v>
+        <v>129298840</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>80148</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4606,21 +4606,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4630,10 +4630,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>487346</v>
+        <v>487314</v>
       </c>
       <c r="R41" t="n">
-        <v>7039012</v>
+        <v>7039005</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4666,11 +4666,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4697,7 +4692,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129298802</v>
+        <v>129298795</v>
       </c>
       <c r="B42" t="n">
         <v>57727</v>
@@ -4732,10 +4727,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>487302</v>
+        <v>487100</v>
       </c>
       <c r="R42" t="n">
-        <v>7039045</v>
+        <v>7039085</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4799,7 +4794,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129298795</v>
+        <v>129298748</v>
       </c>
       <c r="B43" t="n">
         <v>57727</v>
@@ -4834,10 +4829,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>487100</v>
+        <v>487301</v>
       </c>
       <c r="R43" t="n">
-        <v>7039085</v>
+        <v>7038925</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4901,10 +4896,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129298748</v>
+        <v>129298854</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>91563</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4912,23 +4907,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -4936,10 +4927,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>487301</v>
+        <v>487522</v>
       </c>
       <c r="R44" t="n">
-        <v>7038925</v>
+        <v>7038997</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4972,11 +4963,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5003,10 +4989,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129298854</v>
+        <v>129298809</v>
       </c>
       <c r="B45" t="n">
-        <v>91563</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5014,19 +5000,23 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5034,10 +5024,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>487522</v>
+        <v>487348</v>
       </c>
       <c r="R45" t="n">
-        <v>7038997</v>
+        <v>7039005</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5070,6 +5060,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5096,10 +5091,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129298840</v>
+        <v>129298783</v>
       </c>
       <c r="B46" t="n">
-        <v>80148</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5107,21 +5102,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5131,10 +5126,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>487314</v>
+        <v>487024</v>
       </c>
       <c r="R46" t="n">
-        <v>7039005</v>
+        <v>7039203</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5167,6 +5162,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5193,7 +5193,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129298809</v>
+        <v>129298805</v>
       </c>
       <c r="B47" t="n">
         <v>57727</v>
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>487348</v>
+        <v>487346</v>
       </c>
       <c r="R47" t="n">
-        <v>7039005</v>
+        <v>7039012</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5295,7 +5295,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129298783</v>
+        <v>129298802</v>
       </c>
       <c r="B48" t="n">
         <v>57727</v>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>487024</v>
+        <v>487302</v>
       </c>
       <c r="R48" t="n">
-        <v>7039203</v>
+        <v>7039045</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5397,10 +5397,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129298738</v>
+        <v>129298856</v>
       </c>
       <c r="B49" t="n">
-        <v>96956</v>
+        <v>82877</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5408,21 +5408,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>53</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>487311</v>
+        <v>487541</v>
       </c>
       <c r="R49" t="n">
-        <v>7039063</v>
+        <v>7038983</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5494,10 +5494,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129298856</v>
+        <v>129298842</v>
       </c>
       <c r="B50" t="n">
-        <v>82877</v>
+        <v>80148</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5505,21 +5505,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5529,10 +5529,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>487541</v>
+        <v>487393</v>
       </c>
       <c r="R50" t="n">
-        <v>7038983</v>
+        <v>7038908</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5591,10 +5591,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129298842</v>
+        <v>129298798</v>
       </c>
       <c r="B51" t="n">
-        <v>80148</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5602,21 +5602,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5626,10 +5626,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>487393</v>
+        <v>487131</v>
       </c>
       <c r="R51" t="n">
-        <v>7038908</v>
+        <v>7039049</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5662,6 +5662,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5688,7 +5693,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129298798</v>
+        <v>129298810</v>
       </c>
       <c r="B52" t="n">
         <v>57727</v>
@@ -5723,10 +5728,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>487131</v>
+        <v>487355</v>
       </c>
       <c r="R52" t="n">
-        <v>7039049</v>
+        <v>7039005</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5790,10 +5795,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129298810</v>
+        <v>129298738</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>96956</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5801,21 +5806,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5825,10 +5830,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>487355</v>
+        <v>487311</v>
       </c>
       <c r="R53" t="n">
-        <v>7039005</v>
+        <v>7039063</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5861,11 +5866,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5892,7 +5892,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129298779</v>
+        <v>129298749</v>
       </c>
       <c r="B54" t="n">
         <v>57727</v>
@@ -5927,10 +5927,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486866</v>
+        <v>487275</v>
       </c>
       <c r="R54" t="n">
-        <v>7039259</v>
+        <v>7038947</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5994,10 +5994,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129298749</v>
+        <v>129298825</v>
       </c>
       <c r="B55" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6005,21 +6005,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6029,10 +6029,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>487275</v>
+        <v>487247</v>
       </c>
       <c r="R55" t="n">
-        <v>7038947</v>
+        <v>7039020</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6069,7 +6069,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6096,10 +6096,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129298825</v>
+        <v>129298779</v>
       </c>
       <c r="B56" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6107,21 +6107,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6131,10 +6131,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>487247</v>
+        <v>486866</v>
       </c>
       <c r="R56" t="n">
-        <v>7039020</v>
+        <v>7039259</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8832,61 +8832,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129298847</v>
+        <v>129298841</v>
       </c>
       <c r="B83" t="n">
-        <v>57587</v>
+        <v>80148</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100136</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>486999</v>
+        <v>487515</v>
       </c>
       <c r="R83" t="n">
-        <v>7039199</v>
+        <v>7038993</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8919,11 +8903,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Jagades av en nötskrika</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8950,45 +8929,61 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129298789</v>
+        <v>129298847</v>
       </c>
       <c r="B84" t="n">
-        <v>57727</v>
+        <v>57587</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>100136</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>487041</v>
+        <v>486999</v>
       </c>
       <c r="R84" t="n">
-        <v>7039167</v>
+        <v>7039199</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9025,7 +9020,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Jagades av en nötskrika</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9052,7 +9047,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129298771</v>
+        <v>129298789</v>
       </c>
       <c r="B85" t="n">
         <v>57727</v>
@@ -9087,10 +9082,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>486885</v>
+        <v>487041</v>
       </c>
       <c r="R85" t="n">
-        <v>7039172</v>
+        <v>7039167</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9154,7 +9149,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129298801</v>
+        <v>129298771</v>
       </c>
       <c r="B86" t="n">
         <v>57727</v>
@@ -9189,10 +9184,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>487268</v>
+        <v>486885</v>
       </c>
       <c r="R86" t="n">
-        <v>7039003</v>
+        <v>7039172</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9256,7 +9251,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129298814</v>
+        <v>129298801</v>
       </c>
       <c r="B87" t="n">
         <v>57727</v>
@@ -9291,10 +9286,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>487366</v>
+        <v>487268</v>
       </c>
       <c r="R87" t="n">
-        <v>7038997</v>
+        <v>7039003</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9331,7 +9326,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9358,7 +9353,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129298772</v>
+        <v>129298814</v>
       </c>
       <c r="B88" t="n">
         <v>57727</v>
@@ -9393,10 +9388,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>486849</v>
+        <v>487366</v>
       </c>
       <c r="R88" t="n">
-        <v>7039185</v>
+        <v>7038997</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9433,7 +9428,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9460,7 +9455,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129298746</v>
+        <v>129298772</v>
       </c>
       <c r="B89" t="n">
         <v>57727</v>
@@ -9495,10 +9490,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>487316</v>
+        <v>486849</v>
       </c>
       <c r="R89" t="n">
-        <v>7038914</v>
+        <v>7039185</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9562,10 +9557,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129298841</v>
+        <v>129298746</v>
       </c>
       <c r="B90" t="n">
-        <v>80148</v>
+        <v>57727</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9573,21 +9568,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9597,10 +9592,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>487515</v>
+        <v>487316</v>
       </c>
       <c r="R90" t="n">
-        <v>7038993</v>
+        <v>7038914</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9633,6 +9628,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10154,7 +10154,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129298745</v>
+        <v>129298791</v>
       </c>
       <c r="B96" t="n">
         <v>57727</v>
@@ -10189,10 +10189,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>486881</v>
+        <v>487112</v>
       </c>
       <c r="R96" t="n">
-        <v>7039175</v>
+        <v>7039182</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10256,7 +10256,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129298754</v>
+        <v>129298745</v>
       </c>
       <c r="B97" t="n">
         <v>57727</v>
@@ -10291,10 +10291,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>487222</v>
+        <v>486881</v>
       </c>
       <c r="R97" t="n">
-        <v>7038974</v>
+        <v>7039175</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10331,7 +10331,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10358,7 +10358,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129298791</v>
+        <v>129298754</v>
       </c>
       <c r="B98" t="n">
         <v>57727</v>
@@ -10393,10 +10393,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>487112</v>
+        <v>487222</v>
       </c>
       <c r="R98" t="n">
-        <v>7039182</v>
+        <v>7038974</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10433,7 +10433,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">

--- a/artfynd/A 46357-2025 artfynd.xlsx
+++ b/artfynd/A 46357-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129298786</v>
+        <v>129298818</v>
       </c>
       <c r="B2" t="n">
         <v>57727</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487006</v>
+        <v>487389</v>
       </c>
       <c r="R2" t="n">
-        <v>7039175</v>
+        <v>7038925</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129298751</v>
+        <v>129298819</v>
       </c>
       <c r="B3" t="n">
         <v>57727</v>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487263</v>
+        <v>487346</v>
       </c>
       <c r="R3" t="n">
-        <v>7038949</v>
+        <v>7038911</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129298818</v>
+        <v>129298827</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487389</v>
+        <v>487352</v>
       </c>
       <c r="R4" t="n">
-        <v>7038925</v>
+        <v>7038906</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129298819</v>
+        <v>129298844</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>78057</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>487346</v>
+        <v>487374</v>
       </c>
       <c r="R5" t="n">
-        <v>7038911</v>
+        <v>7039027</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1052,11 +1052,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129298844</v>
+        <v>129298851</v>
       </c>
       <c r="B6" t="n">
-        <v>78056</v>
+        <v>91559</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228579</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>487374</v>
+        <v>487144</v>
       </c>
       <c r="R6" t="n">
-        <v>7039027</v>
+        <v>7039078</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129298851</v>
+        <v>129298751</v>
       </c>
       <c r="B7" t="n">
-        <v>91557</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>487144</v>
+        <v>487263</v>
       </c>
       <c r="R7" t="n">
-        <v>7039078</v>
+        <v>7038949</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1251,6 +1246,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129298827</v>
+        <v>129298786</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>487352</v>
+        <v>487006</v>
       </c>
       <c r="R8" t="n">
-        <v>7038906</v>
+        <v>7039175</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129298838</v>
+        <v>129298812</v>
       </c>
       <c r="B9" t="n">
-        <v>80148</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1390,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>487035</v>
+        <v>487362</v>
       </c>
       <c r="R9" t="n">
-        <v>7039161</v>
+        <v>7039030</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1450,6 +1450,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1476,10 +1481,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129298812</v>
+        <v>129298742</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>91545</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,21 +1492,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>487362</v>
+        <v>487129</v>
       </c>
       <c r="R10" t="n">
-        <v>7039030</v>
+        <v>7039097</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1547,11 +1552,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,10 +1578,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129298759</v>
+        <v>129298838</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,21 +1589,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>487171</v>
+        <v>487035</v>
       </c>
       <c r="R11" t="n">
-        <v>7039000</v>
+        <v>7039161</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,11 +1649,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1680,10 +1675,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129298742</v>
+        <v>129298759</v>
       </c>
       <c r="B12" t="n">
-        <v>91543</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,21 +1686,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1715,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>487129</v>
+        <v>487171</v>
       </c>
       <c r="R12" t="n">
-        <v>7039097</v>
+        <v>7039000</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,6 +1746,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1777,7 +1777,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129298761</v>
+        <v>129298799</v>
       </c>
       <c r="B13" t="n">
         <v>57727</v>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>487137</v>
+        <v>487230</v>
       </c>
       <c r="R13" t="n">
-        <v>7039024</v>
+        <v>7039041</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129298799</v>
+        <v>129298761</v>
       </c>
       <c r="B14" t="n">
         <v>57727</v>
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>487230</v>
+        <v>487137</v>
       </c>
       <c r="R14" t="n">
-        <v>7039041</v>
+        <v>7039024</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129298857</v>
+        <v>129298855</v>
       </c>
       <c r="B16" t="n">
-        <v>83003</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2094,21 +2094,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>487340</v>
+        <v>487542</v>
       </c>
       <c r="R16" t="n">
-        <v>7039016</v>
+        <v>7038985</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2180,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129298855</v>
+        <v>129298857</v>
       </c>
       <c r="B17" t="n">
-        <v>79043</v>
+        <v>83004</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>487542</v>
+        <v>487340</v>
       </c>
       <c r="R17" t="n">
-        <v>7038985</v>
+        <v>7039016</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2277,7 +2277,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129298777</v>
+        <v>129298787</v>
       </c>
       <c r="B18" t="n">
         <v>57727</v>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486860</v>
+        <v>486999</v>
       </c>
       <c r="R18" t="n">
-        <v>7039254</v>
+        <v>7039162</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2379,7 +2379,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129298787</v>
+        <v>129298777</v>
       </c>
       <c r="B19" t="n">
         <v>57727</v>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486999</v>
+        <v>486860</v>
       </c>
       <c r="R19" t="n">
-        <v>7039162</v>
+        <v>7039254</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2481,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129298837</v>
+        <v>129298740</v>
       </c>
       <c r="B20" t="n">
-        <v>80148</v>
+        <v>91545</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>487004</v>
+        <v>487145</v>
       </c>
       <c r="R20" t="n">
-        <v>7039214</v>
+        <v>7039179</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129298775</v>
+        <v>129298852</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>91559</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2589,21 +2589,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486860</v>
+        <v>487127</v>
       </c>
       <c r="R21" t="n">
-        <v>7039244</v>
+        <v>7039070</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2649,11 +2649,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2680,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129298808</v>
+        <v>129298837</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2691,21 +2686,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2715,10 +2710,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>487344</v>
+        <v>487004</v>
       </c>
       <c r="R22" t="n">
-        <v>7039018</v>
+        <v>7039214</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2751,11 +2746,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2782,27 +2772,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129298780</v>
+        <v>129298830</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>57568</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2810,17 +2800,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486859</v>
+        <v>487123</v>
       </c>
       <c r="R23" t="n">
-        <v>7039262</v>
+        <v>7039173</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2853,11 +2855,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2884,10 +2881,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129298740</v>
+        <v>129298808</v>
       </c>
       <c r="B24" t="n">
-        <v>91543</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2895,21 +2892,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2919,10 +2916,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>487145</v>
+        <v>487344</v>
       </c>
       <c r="R24" t="n">
-        <v>7039179</v>
+        <v>7039018</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2955,6 +2952,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2981,10 +2983,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129298852</v>
+        <v>129298775</v>
       </c>
       <c r="B25" t="n">
-        <v>91557</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2992,21 +2994,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3016,10 +3018,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>487127</v>
+        <v>486860</v>
       </c>
       <c r="R25" t="n">
-        <v>7039070</v>
+        <v>7039244</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3052,6 +3054,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3078,27 +3085,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129298830</v>
+        <v>129298780</v>
       </c>
       <c r="B26" t="n">
-        <v>57568</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3106,29 +3113,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>487123</v>
+        <v>486859</v>
       </c>
       <c r="R26" t="n">
-        <v>7039173</v>
+        <v>7039262</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3161,6 +3156,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3190,7 +3190,7 @@
         <v>129298845</v>
       </c>
       <c r="B27" t="n">
-        <v>78056</v>
+        <v>78057</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3284,32 +3284,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129298843</v>
+        <v>129298846</v>
       </c>
       <c r="B28" t="n">
-        <v>80148</v>
+        <v>57831</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3319,10 +3319,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>487391</v>
+        <v>486976</v>
       </c>
       <c r="R28" t="n">
-        <v>7038927</v>
+        <v>7039216</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3381,10 +3381,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129298793</v>
+        <v>129298843</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3392,21 +3392,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3416,10 +3416,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>487183</v>
+        <v>487391</v>
       </c>
       <c r="R29" t="n">
-        <v>7039216</v>
+        <v>7038927</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3452,11 +3452,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3483,7 +3478,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129298823</v>
+        <v>129298793</v>
       </c>
       <c r="B30" t="n">
         <v>57727</v>
@@ -3518,10 +3513,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>487363</v>
+        <v>487183</v>
       </c>
       <c r="R30" t="n">
-        <v>7038902</v>
+        <v>7039216</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3585,7 +3580,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129298778</v>
+        <v>129298765</v>
       </c>
       <c r="B31" t="n">
         <v>57727</v>
@@ -3620,10 +3615,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486871</v>
+        <v>487122</v>
       </c>
       <c r="R31" t="n">
-        <v>7039260</v>
+        <v>7039034</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3687,27 +3682,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129298846</v>
+        <v>129298770</v>
       </c>
       <c r="B32" t="n">
-        <v>57831</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3722,10 +3717,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486976</v>
+        <v>486972</v>
       </c>
       <c r="R32" t="n">
-        <v>7039216</v>
+        <v>7039122</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3758,6 +3753,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3784,7 +3784,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129298765</v>
+        <v>129298823</v>
       </c>
       <c r="B33" t="n">
         <v>57727</v>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>487122</v>
+        <v>487363</v>
       </c>
       <c r="R33" t="n">
-        <v>7039034</v>
+        <v>7038902</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3886,7 +3886,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129298770</v>
+        <v>129298778</v>
       </c>
       <c r="B34" t="n">
         <v>57727</v>
@@ -3921,10 +3921,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486972</v>
+        <v>486871</v>
       </c>
       <c r="R34" t="n">
-        <v>7039122</v>
+        <v>7039260</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3988,7 +3988,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129298750</v>
+        <v>129298792</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>487272</v>
+        <v>487153</v>
       </c>
       <c r="R35" t="n">
-        <v>7038946</v>
+        <v>7039212</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4063,7 +4063,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4090,7 +4090,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129298769</v>
+        <v>129298794</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4125,10 +4125,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>487109</v>
+        <v>487186</v>
       </c>
       <c r="R36" t="n">
-        <v>7039040</v>
+        <v>7039192</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4192,7 +4192,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129298804</v>
+        <v>129298750</v>
       </c>
       <c r="B37" t="n">
         <v>57727</v>
@@ -4227,10 +4227,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>487288</v>
+        <v>487272</v>
       </c>
       <c r="R37" t="n">
-        <v>7039002</v>
+        <v>7038946</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4294,7 +4294,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129298792</v>
+        <v>129298769</v>
       </c>
       <c r="B38" t="n">
         <v>57727</v>
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>487153</v>
+        <v>487109</v>
       </c>
       <c r="R38" t="n">
-        <v>7039212</v>
+        <v>7039040</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4396,7 +4396,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129298794</v>
+        <v>129298804</v>
       </c>
       <c r="B39" t="n">
         <v>57727</v>
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>487186</v>
+        <v>487288</v>
       </c>
       <c r="R39" t="n">
-        <v>7039192</v>
+        <v>7039002</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4498,7 +4498,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129298833</v>
+        <v>129298840</v>
       </c>
       <c r="B40" t="n">
         <v>80149</v>
@@ -4509,21 +4509,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>487265</v>
+        <v>487314</v>
       </c>
       <c r="R40" t="n">
-        <v>7038997</v>
+        <v>7039005</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4595,10 +4595,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129298840</v>
+        <v>129298854</v>
       </c>
       <c r="B41" t="n">
-        <v>80148</v>
+        <v>91565</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4606,23 +4606,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4630,10 +4626,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>487314</v>
+        <v>487522</v>
       </c>
       <c r="R41" t="n">
-        <v>7039005</v>
+        <v>7038997</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4692,10 +4688,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129298795</v>
+        <v>129298833</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4703,21 +4699,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4727,10 +4723,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>487100</v>
+        <v>487265</v>
       </c>
       <c r="R42" t="n">
-        <v>7039085</v>
+        <v>7038997</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4763,11 +4759,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4794,7 +4785,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129298748</v>
+        <v>129298805</v>
       </c>
       <c r="B43" t="n">
         <v>57727</v>
@@ -4829,10 +4820,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>487301</v>
+        <v>487346</v>
       </c>
       <c r="R43" t="n">
-        <v>7038925</v>
+        <v>7039012</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4896,10 +4887,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129298854</v>
+        <v>129298809</v>
       </c>
       <c r="B44" t="n">
-        <v>91563</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4907,19 +4898,23 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -4927,10 +4922,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>487522</v>
+        <v>487348</v>
       </c>
       <c r="R44" t="n">
-        <v>7038997</v>
+        <v>7039005</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4963,6 +4958,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4989,7 +4989,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129298809</v>
+        <v>129298802</v>
       </c>
       <c r="B45" t="n">
         <v>57727</v>
@@ -5024,10 +5024,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>487348</v>
+        <v>487302</v>
       </c>
       <c r="R45" t="n">
-        <v>7039005</v>
+        <v>7039045</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5091,7 +5091,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129298783</v>
+        <v>129298795</v>
       </c>
       <c r="B46" t="n">
         <v>57727</v>
@@ -5126,10 +5126,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>487024</v>
+        <v>487100</v>
       </c>
       <c r="R46" t="n">
-        <v>7039203</v>
+        <v>7039085</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5193,7 +5193,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129298805</v>
+        <v>129298748</v>
       </c>
       <c r="B47" t="n">
         <v>57727</v>
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>487346</v>
+        <v>487301</v>
       </c>
       <c r="R47" t="n">
-        <v>7039012</v>
+        <v>7038925</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5295,7 +5295,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129298802</v>
+        <v>129298783</v>
       </c>
       <c r="B48" t="n">
         <v>57727</v>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>487302</v>
+        <v>487024</v>
       </c>
       <c r="R48" t="n">
-        <v>7039045</v>
+        <v>7039203</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5397,10 +5397,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129298856</v>
+        <v>129298738</v>
       </c>
       <c r="B49" t="n">
-        <v>82877</v>
+        <v>96958</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5408,21 +5408,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>53</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>487541</v>
+        <v>487311</v>
       </c>
       <c r="R49" t="n">
-        <v>7038983</v>
+        <v>7039063</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5494,10 +5494,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129298842</v>
+        <v>129298856</v>
       </c>
       <c r="B50" t="n">
-        <v>80148</v>
+        <v>82878</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5505,21 +5505,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5529,10 +5529,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>487393</v>
+        <v>487541</v>
       </c>
       <c r="R50" t="n">
-        <v>7038908</v>
+        <v>7038983</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5591,10 +5591,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129298798</v>
+        <v>129298842</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5602,21 +5602,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5626,10 +5626,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>487131</v>
+        <v>487393</v>
       </c>
       <c r="R51" t="n">
-        <v>7039049</v>
+        <v>7038908</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5662,11 +5662,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5795,10 +5790,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129298738</v>
+        <v>129298798</v>
       </c>
       <c r="B53" t="n">
-        <v>96956</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5806,21 +5801,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5830,10 +5825,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>487311</v>
+        <v>487131</v>
       </c>
       <c r="R53" t="n">
-        <v>7039063</v>
+        <v>7039049</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5866,6 +5861,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5994,10 +5994,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129298825</v>
+        <v>129298779</v>
       </c>
       <c r="B55" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6005,21 +6005,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6029,10 +6029,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>487247</v>
+        <v>486866</v>
       </c>
       <c r="R55" t="n">
-        <v>7039020</v>
+        <v>7039259</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6069,7 +6069,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6096,10 +6096,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129298779</v>
+        <v>129298825</v>
       </c>
       <c r="B56" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6107,21 +6107,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6131,10 +6131,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>486866</v>
+        <v>487247</v>
       </c>
       <c r="R56" t="n">
-        <v>7039259</v>
+        <v>7039020</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6300,7 +6300,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129298774</v>
+        <v>129298816</v>
       </c>
       <c r="B58" t="n">
         <v>57727</v>
@@ -6335,10 +6335,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>486866</v>
+        <v>487389</v>
       </c>
       <c r="R58" t="n">
-        <v>7039249</v>
+        <v>7038985</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6402,7 +6402,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129298773</v>
+        <v>129298813</v>
       </c>
       <c r="B59" t="n">
         <v>57727</v>
@@ -6437,10 +6437,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>486807</v>
+        <v>487367</v>
       </c>
       <c r="R59" t="n">
-        <v>7039220</v>
+        <v>7038998</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6504,7 +6504,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129298767</v>
+        <v>129298820</v>
       </c>
       <c r="B60" t="n">
         <v>57727</v>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>487123</v>
+        <v>487354</v>
       </c>
       <c r="R60" t="n">
-        <v>7039031</v>
+        <v>7038894</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6606,7 +6606,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129298816</v>
+        <v>129298774</v>
       </c>
       <c r="B61" t="n">
         <v>57727</v>
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>487389</v>
+        <v>486866</v>
       </c>
       <c r="R61" t="n">
-        <v>7038985</v>
+        <v>7039249</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6681,7 +6681,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6708,7 +6708,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129298813</v>
+        <v>129298773</v>
       </c>
       <c r="B62" t="n">
         <v>57727</v>
@@ -6743,10 +6743,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>487367</v>
+        <v>486807</v>
       </c>
       <c r="R62" t="n">
-        <v>7038998</v>
+        <v>7039220</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6783,7 +6783,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6810,10 +6810,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129298820</v>
+        <v>129298826</v>
       </c>
       <c r="B63" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6821,21 +6821,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6845,10 +6845,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>487354</v>
+        <v>487457</v>
       </c>
       <c r="R63" t="n">
-        <v>7038894</v>
+        <v>7038967</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6885,7 +6885,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6912,10 +6912,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129298826</v>
+        <v>129298767</v>
       </c>
       <c r="B64" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6923,21 +6923,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6947,10 +6947,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>487457</v>
+        <v>487123</v>
       </c>
       <c r="R64" t="n">
-        <v>7038967</v>
+        <v>7039031</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6987,7 +6987,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7017,7 +7017,7 @@
         <v>129298741</v>
       </c>
       <c r="B65" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>129298853</v>
       </c>
       <c r="B66" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         <v>129298831</v>
       </c>
       <c r="B68" t="n">
-        <v>83002</v>
+        <v>83003</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         <v>129298737</v>
       </c>
       <c r="B69" t="n">
-        <v>83011</v>
+        <v>83012</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7500,32 +7500,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129298822</v>
+        <v>129298828</v>
       </c>
       <c r="B70" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7535,10 +7535,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>487373</v>
+        <v>487269</v>
       </c>
       <c r="R70" t="n">
-        <v>7038897</v>
+        <v>7039004</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7571,11 +7571,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7602,10 +7597,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129298797</v>
+        <v>129298839</v>
       </c>
       <c r="B71" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7613,21 +7608,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7637,10 +7632,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>487134</v>
+        <v>487269</v>
       </c>
       <c r="R71" t="n">
-        <v>7039037</v>
+        <v>7039001</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7673,11 +7668,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7704,7 +7694,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129298803</v>
+        <v>129298797</v>
       </c>
       <c r="B72" t="n">
         <v>57727</v>
@@ -7739,7 +7729,7 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>487303</v>
+        <v>487134</v>
       </c>
       <c r="R72" t="n">
         <v>7039037</v>
@@ -7806,7 +7796,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129298817</v>
+        <v>129298803</v>
       </c>
       <c r="B73" t="n">
         <v>57727</v>
@@ -7841,10 +7831,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>487460</v>
+        <v>487303</v>
       </c>
       <c r="R73" t="n">
-        <v>7038984</v>
+        <v>7039037</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7908,7 +7898,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129298800</v>
+        <v>129298822</v>
       </c>
       <c r="B74" t="n">
         <v>57727</v>
@@ -7936,33 +7926,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>487288</v>
+        <v>487373</v>
       </c>
       <c r="R74" t="n">
-        <v>7039015</v>
+        <v>7038897</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7999,7 +7973,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Födosökande hane</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8026,7 +8000,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129298821</v>
+        <v>129298817</v>
       </c>
       <c r="B75" t="n">
         <v>57727</v>
@@ -8061,10 +8035,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>487368</v>
+        <v>487460</v>
       </c>
       <c r="R75" t="n">
-        <v>7038892</v>
+        <v>7038984</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8128,45 +8102,61 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129298828</v>
+        <v>129298800</v>
       </c>
       <c r="B76" t="n">
-        <v>80177</v>
+        <v>57727</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>487269</v>
+        <v>487288</v>
       </c>
       <c r="R76" t="n">
-        <v>7039004</v>
+        <v>7039015</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8199,6 +8189,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Födosökande hane</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8225,10 +8220,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129298839</v>
+        <v>129298821</v>
       </c>
       <c r="B77" t="n">
-        <v>80148</v>
+        <v>57727</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8236,21 +8231,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8260,10 +8255,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>487269</v>
+        <v>487368</v>
       </c>
       <c r="R77" t="n">
-        <v>7039001</v>
+        <v>7038892</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8296,6 +8291,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8322,7 +8322,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129298781</v>
+        <v>129298785</v>
       </c>
       <c r="B78" t="n">
         <v>57727</v>
@@ -8357,10 +8357,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>486864</v>
+        <v>487007</v>
       </c>
       <c r="R78" t="n">
-        <v>7039272</v>
+        <v>7039210</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8397,7 +8397,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8424,7 +8424,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129298785</v>
+        <v>129298753</v>
       </c>
       <c r="B79" t="n">
         <v>57727</v>
@@ -8459,10 +8459,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>487007</v>
+        <v>487240</v>
       </c>
       <c r="R79" t="n">
-        <v>7039210</v>
+        <v>7038959</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8526,7 +8526,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129298784</v>
+        <v>129298757</v>
       </c>
       <c r="B80" t="n">
         <v>57727</v>
@@ -8561,10 +8561,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>487011</v>
+        <v>487188</v>
       </c>
       <c r="R80" t="n">
-        <v>7039207</v>
+        <v>7038992</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8628,7 +8628,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129298757</v>
+        <v>129298784</v>
       </c>
       <c r="B81" t="n">
         <v>57727</v>
@@ -8663,10 +8663,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>487188</v>
+        <v>487011</v>
       </c>
       <c r="R81" t="n">
-        <v>7038992</v>
+        <v>7039207</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8730,7 +8730,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129298753</v>
+        <v>129298781</v>
       </c>
       <c r="B82" t="n">
         <v>57727</v>
@@ -8765,10 +8765,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>487240</v>
+        <v>486864</v>
       </c>
       <c r="R82" t="n">
-        <v>7038959</v>
+        <v>7039272</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8835,7 +8835,7 @@
         <v>129298841</v>
       </c>
       <c r="B83" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8929,61 +8929,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129298847</v>
+        <v>129298771</v>
       </c>
       <c r="B84" t="n">
-        <v>57587</v>
+        <v>57727</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100136</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>486999</v>
+        <v>486885</v>
       </c>
       <c r="R84" t="n">
-        <v>7039199</v>
+        <v>7039172</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9020,7 +9004,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Jagades av en nötskrika</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9149,7 +9133,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129298771</v>
+        <v>129298772</v>
       </c>
       <c r="B86" t="n">
         <v>57727</v>
@@ -9184,10 +9168,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>486885</v>
+        <v>486849</v>
       </c>
       <c r="R86" t="n">
-        <v>7039172</v>
+        <v>7039185</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9251,45 +9235,61 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129298801</v>
+        <v>129298847</v>
       </c>
       <c r="B87" t="n">
-        <v>57727</v>
+        <v>57587</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>100136</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>487268</v>
+        <v>486999</v>
       </c>
       <c r="R87" t="n">
-        <v>7039003</v>
+        <v>7039199</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9326,7 +9326,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Jagades av en nötskrika</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9353,7 +9353,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129298814</v>
+        <v>129298801</v>
       </c>
       <c r="B88" t="n">
         <v>57727</v>
@@ -9388,10 +9388,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>487366</v>
+        <v>487268</v>
       </c>
       <c r="R88" t="n">
-        <v>7038997</v>
+        <v>7039003</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9455,7 +9455,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129298772</v>
+        <v>129298814</v>
       </c>
       <c r="B89" t="n">
         <v>57727</v>
@@ -9490,10 +9490,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>486849</v>
+        <v>487366</v>
       </c>
       <c r="R89" t="n">
-        <v>7039185</v>
+        <v>7038997</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9530,7 +9530,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9659,10 +9659,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129298752</v>
+        <v>129298743</v>
       </c>
       <c r="B91" t="n">
-        <v>57727</v>
+        <v>91545</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9670,21 +9670,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9694,10 +9694,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>487246</v>
+        <v>487331</v>
       </c>
       <c r="R91" t="n">
-        <v>7038958</v>
+        <v>7039023</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9730,11 +9730,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9761,10 +9756,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129298768</v>
+        <v>129298836</v>
       </c>
       <c r="B92" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9772,21 +9767,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9796,10 +9791,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>487123</v>
+        <v>486899</v>
       </c>
       <c r="R92" t="n">
-        <v>7039032</v>
+        <v>7039370</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9832,11 +9827,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9863,10 +9853,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129298743</v>
+        <v>129298752</v>
       </c>
       <c r="B93" t="n">
-        <v>91543</v>
+        <v>57727</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9874,21 +9864,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9898,10 +9888,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>487331</v>
+        <v>487246</v>
       </c>
       <c r="R93" t="n">
-        <v>7039023</v>
+        <v>7038958</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9934,6 +9924,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9960,10 +9955,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129298836</v>
+        <v>129298768</v>
       </c>
       <c r="B94" t="n">
-        <v>80148</v>
+        <v>57727</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9971,21 +9966,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9995,10 +9990,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>486899</v>
+        <v>487123</v>
       </c>
       <c r="R94" t="n">
-        <v>7039370</v>
+        <v>7039032</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10031,6 +10026,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10057,32 +10057,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129298739</v>
+        <v>129298745</v>
       </c>
       <c r="B95" t="n">
-        <v>91507</v>
+        <v>57727</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10092,10 +10092,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>487384</v>
+        <v>486881</v>
       </c>
       <c r="R95" t="n">
-        <v>7038973</v>
+        <v>7039175</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10128,6 +10128,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10154,32 +10159,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129298791</v>
+        <v>129298739</v>
       </c>
       <c r="B96" t="n">
-        <v>57727</v>
+        <v>91509</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10189,10 +10194,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>487112</v>
+        <v>487384</v>
       </c>
       <c r="R96" t="n">
-        <v>7039182</v>
+        <v>7038973</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10225,11 +10230,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10256,7 +10256,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129298745</v>
+        <v>129298791</v>
       </c>
       <c r="B97" t="n">
         <v>57727</v>
@@ -10291,10 +10291,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>486881</v>
+        <v>487112</v>
       </c>
       <c r="R97" t="n">
-        <v>7039175</v>
+        <v>7039182</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10675,32 +10675,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129298858</v>
+        <v>129298832</v>
       </c>
       <c r="B101" t="n">
         <v>83003</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>308</v>
+        <v>492</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10710,10 +10710,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>487408</v>
+        <v>487393</v>
       </c>
       <c r="R101" t="n">
-        <v>7038959</v>
+        <v>7038976</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10772,10 +10772,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129298782</v>
+        <v>129298858</v>
       </c>
       <c r="B102" t="n">
-        <v>57727</v>
+        <v>83004</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10783,21 +10783,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10807,10 +10807,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>486857</v>
+        <v>487408</v>
       </c>
       <c r="R102" t="n">
-        <v>7039276</v>
+        <v>7038959</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10843,11 +10843,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10874,7 +10869,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129298758</v>
+        <v>129298806</v>
       </c>
       <c r="B103" t="n">
         <v>57727</v>
@@ -10909,10 +10904,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>487183</v>
+        <v>487339</v>
       </c>
       <c r="R103" t="n">
-        <v>7038993</v>
+        <v>7039009</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10976,7 +10971,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129298788</v>
+        <v>129298758</v>
       </c>
       <c r="B104" t="n">
         <v>57727</v>
@@ -11011,10 +11006,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>487039</v>
+        <v>487183</v>
       </c>
       <c r="R104" t="n">
-        <v>7039164</v>
+        <v>7038993</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11078,7 +11073,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129298806</v>
+        <v>129298788</v>
       </c>
       <c r="B105" t="n">
         <v>57727</v>
@@ -11113,10 +11108,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>487339</v>
+        <v>487039</v>
       </c>
       <c r="R105" t="n">
-        <v>7039009</v>
+        <v>7039164</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11180,7 +11175,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129298815</v>
+        <v>129298782</v>
       </c>
       <c r="B106" t="n">
         <v>57727</v>
@@ -11215,10 +11210,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>487375</v>
+        <v>486857</v>
       </c>
       <c r="R106" t="n">
-        <v>7038981</v>
+        <v>7039276</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11255,7 +11250,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11282,32 +11277,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129298832</v>
+        <v>129298815</v>
       </c>
       <c r="B107" t="n">
-        <v>83002</v>
+        <v>57727</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11317,10 +11312,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>487393</v>
+        <v>487375</v>
       </c>
       <c r="R107" t="n">
-        <v>7038976</v>
+        <v>7038981</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11353,6 +11348,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11379,7 +11379,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129298766</v>
+        <v>129298796</v>
       </c>
       <c r="B108" t="n">
         <v>57727</v>
@@ -11414,10 +11414,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>487124</v>
+        <v>487139</v>
       </c>
       <c r="R108" t="n">
-        <v>7039030</v>
+        <v>7039088</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11481,7 +11481,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129298796</v>
+        <v>129298766</v>
       </c>
       <c r="B109" t="n">
         <v>57727</v>
@@ -11516,10 +11516,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>487139</v>
+        <v>487124</v>
       </c>
       <c r="R109" t="n">
-        <v>7039088</v>
+        <v>7039030</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>

--- a/artfynd/A 46357-2025 artfynd.xlsx
+++ b/artfynd/A 46357-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129298818</v>
+        <v>129298844</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>78057</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487389</v>
+        <v>487374</v>
       </c>
       <c r="R2" t="n">
-        <v>7038925</v>
+        <v>7039027</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129298819</v>
+        <v>129298851</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>91563</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487346</v>
+        <v>487144</v>
       </c>
       <c r="R3" t="n">
-        <v>7038911</v>
+        <v>7039078</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129298827</v>
+        <v>129298786</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487352</v>
+        <v>487006</v>
       </c>
       <c r="R4" t="n">
-        <v>7038906</v>
+        <v>7039175</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +944,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129298844</v>
+        <v>129298818</v>
       </c>
       <c r="B5" t="n">
-        <v>78057</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>487374</v>
+        <v>487389</v>
       </c>
       <c r="R5" t="n">
-        <v>7039027</v>
+        <v>7038925</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1052,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129298851</v>
+        <v>129298819</v>
       </c>
       <c r="B6" t="n">
-        <v>91559</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>487144</v>
+        <v>487346</v>
       </c>
       <c r="R6" t="n">
-        <v>7039078</v>
+        <v>7038911</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,6 +1144,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129298751</v>
+        <v>129298827</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>487263</v>
+        <v>487352</v>
       </c>
       <c r="R7" t="n">
-        <v>7038949</v>
+        <v>7038906</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,7 +1277,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129298786</v>
+        <v>129298751</v>
       </c>
       <c r="B8" t="n">
         <v>57727</v>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>487006</v>
+        <v>487263</v>
       </c>
       <c r="R8" t="n">
-        <v>7039175</v>
+        <v>7038949</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129298812</v>
+        <v>129298742</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1390,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>487362</v>
+        <v>487129</v>
       </c>
       <c r="R9" t="n">
-        <v>7039030</v>
+        <v>7039097</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1450,11 +1450,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1481,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129298742</v>
+        <v>129298838</v>
       </c>
       <c r="B10" t="n">
-        <v>91545</v>
+        <v>80149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1492,21 +1487,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>487129</v>
+        <v>487035</v>
       </c>
       <c r="R10" t="n">
-        <v>7039097</v>
+        <v>7039161</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1578,10 +1573,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129298838</v>
+        <v>129298812</v>
       </c>
       <c r="B11" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,21 +1584,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1613,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>487035</v>
+        <v>487362</v>
       </c>
       <c r="R11" t="n">
-        <v>7039161</v>
+        <v>7039030</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,6 +1644,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1777,7 +1777,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129298799</v>
+        <v>129298761</v>
       </c>
       <c r="B13" t="n">
         <v>57727</v>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>487230</v>
+        <v>487137</v>
       </c>
       <c r="R13" t="n">
-        <v>7039041</v>
+        <v>7039024</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129298761</v>
+        <v>129298755</v>
       </c>
       <c r="B14" t="n">
         <v>57727</v>
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>487137</v>
+        <v>487206</v>
       </c>
       <c r="R14" t="n">
-        <v>7039024</v>
+        <v>7038982</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1981,7 +1981,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129298755</v>
+        <v>129298799</v>
       </c>
       <c r="B15" t="n">
         <v>57727</v>
@@ -2016,10 +2016,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>487206</v>
+        <v>487230</v>
       </c>
       <c r="R15" t="n">
-        <v>7038982</v>
+        <v>7039041</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129298855</v>
+        <v>129298857</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>83004</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2094,21 +2094,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>487542</v>
+        <v>487340</v>
       </c>
       <c r="R16" t="n">
-        <v>7038985</v>
+        <v>7039016</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2180,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129298857</v>
+        <v>129298855</v>
       </c>
       <c r="B17" t="n">
-        <v>83004</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>487340</v>
+        <v>487542</v>
       </c>
       <c r="R17" t="n">
-        <v>7039016</v>
+        <v>7038985</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2277,7 +2277,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129298787</v>
+        <v>129298777</v>
       </c>
       <c r="B18" t="n">
         <v>57727</v>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486999</v>
+        <v>486860</v>
       </c>
       <c r="R18" t="n">
-        <v>7039162</v>
+        <v>7039254</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2379,7 +2379,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129298777</v>
+        <v>129298787</v>
       </c>
       <c r="B19" t="n">
         <v>57727</v>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486860</v>
+        <v>486999</v>
       </c>
       <c r="R19" t="n">
-        <v>7039254</v>
+        <v>7039162</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2481,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129298740</v>
+        <v>129298845</v>
       </c>
       <c r="B20" t="n">
-        <v>91545</v>
+        <v>78057</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>487145</v>
+        <v>487526</v>
       </c>
       <c r="R20" t="n">
-        <v>7039179</v>
+        <v>7039006</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129298852</v>
+        <v>129298740</v>
       </c>
       <c r="B21" t="n">
-        <v>91559</v>
+        <v>91549</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2589,21 +2589,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>487127</v>
+        <v>487145</v>
       </c>
       <c r="R21" t="n">
-        <v>7039070</v>
+        <v>7039179</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129298837</v>
+        <v>129298852</v>
       </c>
       <c r="B22" t="n">
-        <v>80149</v>
+        <v>91563</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,21 +2686,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>487004</v>
+        <v>487127</v>
       </c>
       <c r="R22" t="n">
-        <v>7039214</v>
+        <v>7039070</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2772,27 +2772,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129298830</v>
+        <v>129298775</v>
       </c>
       <c r="B23" t="n">
-        <v>57568</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2800,29 +2800,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>487123</v>
+        <v>486860</v>
       </c>
       <c r="R23" t="n">
-        <v>7039173</v>
+        <v>7039244</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2855,6 +2843,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2983,7 +2976,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129298775</v>
+        <v>129298780</v>
       </c>
       <c r="B25" t="n">
         <v>57727</v>
@@ -3018,10 +3011,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486860</v>
+        <v>486859</v>
       </c>
       <c r="R25" t="n">
-        <v>7039244</v>
+        <v>7039262</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3058,7 +3051,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3085,10 +3078,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129298780</v>
+        <v>129298837</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3096,21 +3089,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3120,10 +3113,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486859</v>
+        <v>487004</v>
       </c>
       <c r="R26" t="n">
-        <v>7039262</v>
+        <v>7039214</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3156,11 +3149,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3187,45 +3175,57 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129298845</v>
+        <v>129298830</v>
       </c>
       <c r="B27" t="n">
-        <v>78057</v>
+        <v>57568</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228579</v>
+        <v>102621</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>487526</v>
+        <v>487123</v>
       </c>
       <c r="R27" t="n">
-        <v>7039006</v>
+        <v>7039173</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3284,27 +3284,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129298846</v>
+        <v>129298793</v>
       </c>
       <c r="B28" t="n">
-        <v>57831</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3319,7 +3319,7 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486976</v>
+        <v>487183</v>
       </c>
       <c r="R28" t="n">
         <v>7039216</v>
@@ -3355,6 +3355,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3381,10 +3386,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129298843</v>
+        <v>129298823</v>
       </c>
       <c r="B29" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3392,21 +3397,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3416,10 +3421,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>487391</v>
+        <v>487363</v>
       </c>
       <c r="R29" t="n">
-        <v>7038927</v>
+        <v>7038902</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3452,6 +3457,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3478,7 +3488,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129298793</v>
+        <v>129298765</v>
       </c>
       <c r="B30" t="n">
         <v>57727</v>
@@ -3513,10 +3523,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>487183</v>
+        <v>487122</v>
       </c>
       <c r="R30" t="n">
-        <v>7039216</v>
+        <v>7039034</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3580,7 +3590,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129298765</v>
+        <v>129298770</v>
       </c>
       <c r="B31" t="n">
         <v>57727</v>
@@ -3615,10 +3625,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>487122</v>
+        <v>486972</v>
       </c>
       <c r="R31" t="n">
-        <v>7039034</v>
+        <v>7039122</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3682,7 +3692,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129298770</v>
+        <v>129298778</v>
       </c>
       <c r="B32" t="n">
         <v>57727</v>
@@ -3717,10 +3727,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486972</v>
+        <v>486871</v>
       </c>
       <c r="R32" t="n">
-        <v>7039122</v>
+        <v>7039260</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3784,10 +3794,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129298823</v>
+        <v>129298843</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3795,21 +3805,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3819,10 +3829,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>487363</v>
+        <v>487391</v>
       </c>
       <c r="R33" t="n">
-        <v>7038902</v>
+        <v>7038927</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3855,11 +3865,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3886,27 +3891,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129298778</v>
+        <v>129298846</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3921,10 +3926,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486871</v>
+        <v>486976</v>
       </c>
       <c r="R34" t="n">
-        <v>7039260</v>
+        <v>7039216</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3957,11 +3962,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4090,7 +4090,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129298794</v>
+        <v>129298750</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4125,10 +4125,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>487186</v>
+        <v>487272</v>
       </c>
       <c r="R36" t="n">
-        <v>7039192</v>
+        <v>7038946</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4192,7 +4192,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129298750</v>
+        <v>129298769</v>
       </c>
       <c r="B37" t="n">
         <v>57727</v>
@@ -4227,10 +4227,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>487272</v>
+        <v>487109</v>
       </c>
       <c r="R37" t="n">
-        <v>7038946</v>
+        <v>7039040</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4294,7 +4294,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129298769</v>
+        <v>129298804</v>
       </c>
       <c r="B38" t="n">
         <v>57727</v>
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>487109</v>
+        <v>487288</v>
       </c>
       <c r="R38" t="n">
-        <v>7039040</v>
+        <v>7039002</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4396,7 +4396,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129298804</v>
+        <v>129298794</v>
       </c>
       <c r="B39" t="n">
         <v>57727</v>
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>487288</v>
+        <v>487186</v>
       </c>
       <c r="R39" t="n">
-        <v>7039002</v>
+        <v>7039192</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4498,10 +4498,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129298840</v>
+        <v>129298805</v>
       </c>
       <c r="B40" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4509,21 +4509,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>487314</v>
+        <v>487346</v>
       </c>
       <c r="R40" t="n">
-        <v>7039005</v>
+        <v>7039012</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4569,6 +4569,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4595,10 +4600,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129298854</v>
+        <v>129298748</v>
       </c>
       <c r="B41" t="n">
-        <v>91565</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4606,19 +4611,23 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4626,10 +4635,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>487522</v>
+        <v>487301</v>
       </c>
       <c r="R41" t="n">
-        <v>7038997</v>
+        <v>7038925</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4662,6 +4671,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4688,10 +4702,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129298833</v>
+        <v>129298783</v>
       </c>
       <c r="B42" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4699,21 +4713,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4723,10 +4737,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>487265</v>
+        <v>487024</v>
       </c>
       <c r="R42" t="n">
-        <v>7038997</v>
+        <v>7039203</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4759,6 +4773,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4785,10 +4804,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129298805</v>
+        <v>129298833</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4796,21 +4815,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4820,10 +4839,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>487346</v>
+        <v>487265</v>
       </c>
       <c r="R43" t="n">
-        <v>7039012</v>
+        <v>7038997</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4856,11 +4875,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4887,10 +4901,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129298809</v>
+        <v>129298854</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>91569</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4898,23 +4912,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -4922,10 +4932,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>487348</v>
+        <v>487522</v>
       </c>
       <c r="R44" t="n">
-        <v>7039005</v>
+        <v>7038997</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4958,11 +4968,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4989,10 +4994,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129298802</v>
+        <v>129298840</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5000,21 +5005,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5024,10 +5029,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>487302</v>
+        <v>487314</v>
       </c>
       <c r="R45" t="n">
-        <v>7039045</v>
+        <v>7039005</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5060,11 +5065,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5091,7 +5091,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129298795</v>
+        <v>129298809</v>
       </c>
       <c r="B46" t="n">
         <v>57727</v>
@@ -5126,10 +5126,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>487100</v>
+        <v>487348</v>
       </c>
       <c r="R46" t="n">
-        <v>7039085</v>
+        <v>7039005</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5193,7 +5193,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129298748</v>
+        <v>129298802</v>
       </c>
       <c r="B47" t="n">
         <v>57727</v>
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>487301</v>
+        <v>487302</v>
       </c>
       <c r="R47" t="n">
-        <v>7038925</v>
+        <v>7039045</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5295,7 +5295,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129298783</v>
+        <v>129298795</v>
       </c>
       <c r="B48" t="n">
         <v>57727</v>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>487024</v>
+        <v>487100</v>
       </c>
       <c r="R48" t="n">
-        <v>7039203</v>
+        <v>7039085</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5397,10 +5397,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129298738</v>
+        <v>129298856</v>
       </c>
       <c r="B49" t="n">
-        <v>96958</v>
+        <v>82878</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5408,21 +5408,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>53</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>487311</v>
+        <v>487541</v>
       </c>
       <c r="R49" t="n">
-        <v>7039063</v>
+        <v>7038983</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5494,10 +5494,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129298856</v>
+        <v>129298798</v>
       </c>
       <c r="B50" t="n">
-        <v>82878</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5505,21 +5505,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5529,10 +5529,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>487541</v>
+        <v>487131</v>
       </c>
       <c r="R50" t="n">
-        <v>7038983</v>
+        <v>7039049</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5565,6 +5565,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5591,10 +5596,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129298842</v>
+        <v>129298810</v>
       </c>
       <c r="B51" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5602,21 +5607,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5626,10 +5631,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>487393</v>
+        <v>487355</v>
       </c>
       <c r="R51" t="n">
-        <v>7038908</v>
+        <v>7039005</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5662,6 +5667,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5688,10 +5698,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129298810</v>
+        <v>129298738</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>96962</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5699,21 +5709,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5723,10 +5733,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>487355</v>
+        <v>487311</v>
       </c>
       <c r="R52" t="n">
-        <v>7039005</v>
+        <v>7039063</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5759,11 +5769,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5790,10 +5795,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129298798</v>
+        <v>129298842</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5801,21 +5806,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5825,10 +5830,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>487131</v>
+        <v>487393</v>
       </c>
       <c r="R53" t="n">
-        <v>7039049</v>
+        <v>7038908</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5861,11 +5866,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5892,10 +5892,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129298749</v>
+        <v>129298825</v>
       </c>
       <c r="B54" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5903,21 +5903,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5927,10 +5927,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>487275</v>
+        <v>487247</v>
       </c>
       <c r="R54" t="n">
-        <v>7038947</v>
+        <v>7039020</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6096,10 +6096,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129298825</v>
+        <v>129298749</v>
       </c>
       <c r="B56" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6107,21 +6107,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6131,10 +6131,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>487247</v>
+        <v>487275</v>
       </c>
       <c r="R56" t="n">
-        <v>7039020</v>
+        <v>7038947</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6198,7 +6198,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129298776</v>
+        <v>129298767</v>
       </c>
       <c r="B57" t="n">
         <v>57727</v>
@@ -6233,10 +6233,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>486855</v>
+        <v>487123</v>
       </c>
       <c r="R57" t="n">
-        <v>7039252</v>
+        <v>7039031</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6300,7 +6300,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129298816</v>
+        <v>129298776</v>
       </c>
       <c r="B58" t="n">
         <v>57727</v>
@@ -6335,10 +6335,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>487389</v>
+        <v>486855</v>
       </c>
       <c r="R58" t="n">
-        <v>7038985</v>
+        <v>7039252</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6402,7 +6402,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129298813</v>
+        <v>129298816</v>
       </c>
       <c r="B59" t="n">
         <v>57727</v>
@@ -6437,10 +6437,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>487367</v>
+        <v>487389</v>
       </c>
       <c r="R59" t="n">
-        <v>7038998</v>
+        <v>7038985</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6504,7 +6504,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129298820</v>
+        <v>129298813</v>
       </c>
       <c r="B60" t="n">
         <v>57727</v>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>487354</v>
+        <v>487367</v>
       </c>
       <c r="R60" t="n">
-        <v>7038894</v>
+        <v>7038998</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6606,7 +6606,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129298774</v>
+        <v>129298820</v>
       </c>
       <c r="B61" t="n">
         <v>57727</v>
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>486866</v>
+        <v>487354</v>
       </c>
       <c r="R61" t="n">
-        <v>7039249</v>
+        <v>7038894</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6681,7 +6681,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6708,7 +6708,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129298773</v>
+        <v>129298774</v>
       </c>
       <c r="B62" t="n">
         <v>57727</v>
@@ -6743,10 +6743,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>486807</v>
+        <v>486866</v>
       </c>
       <c r="R62" t="n">
-        <v>7039220</v>
+        <v>7039249</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6810,10 +6810,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129298826</v>
+        <v>129298773</v>
       </c>
       <c r="B63" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6821,21 +6821,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6845,10 +6845,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>487457</v>
+        <v>486807</v>
       </c>
       <c r="R63" t="n">
-        <v>7038967</v>
+        <v>7039220</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6885,7 +6885,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6912,10 +6912,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129298767</v>
+        <v>129298826</v>
       </c>
       <c r="B64" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6923,21 +6923,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6947,10 +6947,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>487123</v>
+        <v>487457</v>
       </c>
       <c r="R64" t="n">
-        <v>7039031</v>
+        <v>7038967</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6987,7 +6987,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7017,7 +7017,7 @@
         <v>129298741</v>
       </c>
       <c r="B65" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>129298853</v>
       </c>
       <c r="B66" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7306,32 +7306,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129298831</v>
+        <v>129298737</v>
       </c>
       <c r="B68" t="n">
-        <v>83003</v>
+        <v>83012</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>492</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7341,10 +7341,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>487307</v>
+        <v>487523</v>
       </c>
       <c r="R68" t="n">
-        <v>7039016</v>
+        <v>7039001</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7403,32 +7403,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129298737</v>
+        <v>129298828</v>
       </c>
       <c r="B69" t="n">
-        <v>83012</v>
+        <v>80178</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7438,10 +7438,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>487523</v>
+        <v>487269</v>
       </c>
       <c r="R69" t="n">
-        <v>7039001</v>
+        <v>7039004</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7500,32 +7500,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129298828</v>
+        <v>129298839</v>
       </c>
       <c r="B70" t="n">
-        <v>80178</v>
+        <v>80149</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7538,7 +7538,7 @@
         <v>487269</v>
       </c>
       <c r="R70" t="n">
-        <v>7039004</v>
+        <v>7039001</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7597,10 +7597,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129298839</v>
+        <v>129298797</v>
       </c>
       <c r="B71" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7608,21 +7608,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>487269</v>
+        <v>487134</v>
       </c>
       <c r="R71" t="n">
-        <v>7039001</v>
+        <v>7039037</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7668,6 +7668,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7694,7 +7699,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129298797</v>
+        <v>129298803</v>
       </c>
       <c r="B72" t="n">
         <v>57727</v>
@@ -7729,7 +7734,7 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>487134</v>
+        <v>487303</v>
       </c>
       <c r="R72" t="n">
         <v>7039037</v>
@@ -7796,7 +7801,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129298803</v>
+        <v>129298822</v>
       </c>
       <c r="B73" t="n">
         <v>57727</v>
@@ -7831,10 +7836,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>487303</v>
+        <v>487373</v>
       </c>
       <c r="R73" t="n">
-        <v>7039037</v>
+        <v>7038897</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7898,7 +7903,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129298822</v>
+        <v>129298817</v>
       </c>
       <c r="B74" t="n">
         <v>57727</v>
@@ -7933,10 +7938,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>487373</v>
+        <v>487460</v>
       </c>
       <c r="R74" t="n">
-        <v>7038897</v>
+        <v>7038984</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8000,7 +8005,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129298817</v>
+        <v>129298800</v>
       </c>
       <c r="B75" t="n">
         <v>57727</v>
@@ -8028,17 +8033,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>487460</v>
+        <v>487288</v>
       </c>
       <c r="R75" t="n">
-        <v>7038984</v>
+        <v>7039015</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8075,7 +8096,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Födosökande hane</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8102,7 +8123,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129298800</v>
+        <v>129298821</v>
       </c>
       <c r="B76" t="n">
         <v>57727</v>
@@ -8130,33 +8151,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>487288</v>
+        <v>487368</v>
       </c>
       <c r="R76" t="n">
-        <v>7039015</v>
+        <v>7038892</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8193,7 +8198,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Födosökande hane</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8220,32 +8225,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129298821</v>
+        <v>129298831</v>
       </c>
       <c r="B77" t="n">
-        <v>57727</v>
+        <v>83003</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8255,10 +8260,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>487368</v>
+        <v>487307</v>
       </c>
       <c r="R77" t="n">
-        <v>7038892</v>
+        <v>7039016</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8291,11 +8296,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8322,7 +8322,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129298785</v>
+        <v>129298781</v>
       </c>
       <c r="B78" t="n">
         <v>57727</v>
@@ -8357,10 +8357,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>487007</v>
+        <v>486864</v>
       </c>
       <c r="R78" t="n">
-        <v>7039210</v>
+        <v>7039272</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8397,7 +8397,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8424,7 +8424,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129298753</v>
+        <v>129298785</v>
       </c>
       <c r="B79" t="n">
         <v>57727</v>
@@ -8459,10 +8459,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>487240</v>
+        <v>487007</v>
       </c>
       <c r="R79" t="n">
-        <v>7038959</v>
+        <v>7039210</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8526,7 +8526,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129298757</v>
+        <v>129298753</v>
       </c>
       <c r="B80" t="n">
         <v>57727</v>
@@ -8561,10 +8561,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>487188</v>
+        <v>487240</v>
       </c>
       <c r="R80" t="n">
-        <v>7038992</v>
+        <v>7038959</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8628,7 +8628,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129298784</v>
+        <v>129298757</v>
       </c>
       <c r="B81" t="n">
         <v>57727</v>
@@ -8663,10 +8663,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>487011</v>
+        <v>487188</v>
       </c>
       <c r="R81" t="n">
-        <v>7039207</v>
+        <v>7038992</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8730,7 +8730,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129298781</v>
+        <v>129298784</v>
       </c>
       <c r="B82" t="n">
         <v>57727</v>
@@ -8765,10 +8765,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>486864</v>
+        <v>487011</v>
       </c>
       <c r="R82" t="n">
-        <v>7039272</v>
+        <v>7039207</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9031,45 +9031,61 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129298789</v>
+        <v>129298847</v>
       </c>
       <c r="B85" t="n">
-        <v>57727</v>
+        <v>57587</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>100136</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>487041</v>
+        <v>486999</v>
       </c>
       <c r="R85" t="n">
-        <v>7039167</v>
+        <v>7039199</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9106,7 +9122,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Jagades av en nötskrika</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9133,7 +9149,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129298772</v>
+        <v>129298789</v>
       </c>
       <c r="B86" t="n">
         <v>57727</v>
@@ -9168,10 +9184,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>486849</v>
+        <v>487041</v>
       </c>
       <c r="R86" t="n">
-        <v>7039185</v>
+        <v>7039167</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9235,61 +9251,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129298847</v>
+        <v>129298801</v>
       </c>
       <c r="B87" t="n">
-        <v>57587</v>
+        <v>57727</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100136</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>486999</v>
+        <v>487268</v>
       </c>
       <c r="R87" t="n">
-        <v>7039199</v>
+        <v>7039003</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9326,7 +9326,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Jagades av en nötskrika</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9353,7 +9353,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129298801</v>
+        <v>129298814</v>
       </c>
       <c r="B88" t="n">
         <v>57727</v>
@@ -9388,10 +9388,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>487268</v>
+        <v>487366</v>
       </c>
       <c r="R88" t="n">
-        <v>7039003</v>
+        <v>7038997</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9455,7 +9455,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129298814</v>
+        <v>129298772</v>
       </c>
       <c r="B89" t="n">
         <v>57727</v>
@@ -9490,10 +9490,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>487366</v>
+        <v>486849</v>
       </c>
       <c r="R89" t="n">
-        <v>7038997</v>
+        <v>7039185</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9530,7 +9530,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9662,7 +9662,7 @@
         <v>129298743</v>
       </c>
       <c r="B91" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10057,32 +10057,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129298745</v>
+        <v>129298739</v>
       </c>
       <c r="B95" t="n">
-        <v>57727</v>
+        <v>91513</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10092,10 +10092,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>486881</v>
+        <v>487384</v>
       </c>
       <c r="R95" t="n">
-        <v>7039175</v>
+        <v>7038973</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10128,11 +10128,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10159,32 +10154,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129298739</v>
+        <v>129298745</v>
       </c>
       <c r="B96" t="n">
-        <v>91509</v>
+        <v>57727</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10194,10 +10189,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>487384</v>
+        <v>486881</v>
       </c>
       <c r="R96" t="n">
-        <v>7038973</v>
+        <v>7039175</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10230,6 +10225,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10971,7 +10971,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129298758</v>
+        <v>129298782</v>
       </c>
       <c r="B104" t="n">
         <v>57727</v>
@@ -11006,10 +11006,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>487183</v>
+        <v>486857</v>
       </c>
       <c r="R104" t="n">
-        <v>7038993</v>
+        <v>7039276</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11046,7 +11046,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11073,7 +11073,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129298788</v>
+        <v>129298758</v>
       </c>
       <c r="B105" t="n">
         <v>57727</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>487039</v>
+        <v>487183</v>
       </c>
       <c r="R105" t="n">
-        <v>7039164</v>
+        <v>7038993</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11175,7 +11175,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129298782</v>
+        <v>129298815</v>
       </c>
       <c r="B106" t="n">
         <v>57727</v>
@@ -11210,10 +11210,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>486857</v>
+        <v>487375</v>
       </c>
       <c r="R106" t="n">
-        <v>7039276</v>
+        <v>7038981</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11250,7 +11250,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11277,7 +11277,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129298815</v>
+        <v>129298788</v>
       </c>
       <c r="B107" t="n">
         <v>57727</v>
@@ -11312,10 +11312,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>487375</v>
+        <v>487039</v>
       </c>
       <c r="R107" t="n">
-        <v>7038981</v>
+        <v>7039164</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11379,7 +11379,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129298796</v>
+        <v>129298766</v>
       </c>
       <c r="B108" t="n">
         <v>57727</v>
@@ -11414,10 +11414,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>487139</v>
+        <v>487124</v>
       </c>
       <c r="R108" t="n">
-        <v>7039088</v>
+        <v>7039030</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11481,7 +11481,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129298766</v>
+        <v>129298796</v>
       </c>
       <c r="B109" t="n">
         <v>57727</v>
@@ -11516,10 +11516,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>487124</v>
+        <v>487139</v>
       </c>
       <c r="R109" t="n">
-        <v>7039030</v>
+        <v>7039088</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>

--- a/artfynd/A 46357-2025 artfynd.xlsx
+++ b/artfynd/A 46357-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129298844</v>
+        <v>129298751</v>
       </c>
       <c r="B2" t="n">
-        <v>78057</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487374</v>
+        <v>487263</v>
       </c>
       <c r="R2" t="n">
-        <v>7039027</v>
+        <v>7038949</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129298851</v>
+        <v>129298786</v>
       </c>
       <c r="B3" t="n">
-        <v>91563</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487144</v>
+        <v>487006</v>
       </c>
       <c r="R3" t="n">
-        <v>7039078</v>
+        <v>7039175</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129298786</v>
+        <v>129298818</v>
       </c>
       <c r="B4" t="n">
         <v>57727</v>
@@ -904,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487006</v>
+        <v>487389</v>
       </c>
       <c r="R4" t="n">
-        <v>7039175</v>
+        <v>7038925</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129298818</v>
+        <v>129298819</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1006,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>487389</v>
+        <v>487346</v>
       </c>
       <c r="R5" t="n">
-        <v>7038925</v>
+        <v>7038911</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129298819</v>
+        <v>129298851</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>91564</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>487346</v>
+        <v>487144</v>
       </c>
       <c r="R6" t="n">
-        <v>7038911</v>
+        <v>7039078</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,11 +1154,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1277,10 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129298751</v>
+        <v>129298844</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>78057</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1293,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>487263</v>
+        <v>487374</v>
       </c>
       <c r="R8" t="n">
-        <v>7038949</v>
+        <v>7039027</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1348,11 +1353,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129298742</v>
+        <v>129298812</v>
       </c>
       <c r="B9" t="n">
-        <v>91549</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1390,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>487129</v>
+        <v>487362</v>
       </c>
       <c r="R9" t="n">
-        <v>7039097</v>
+        <v>7039030</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1450,6 +1450,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1476,10 +1481,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129298838</v>
+        <v>129298759</v>
       </c>
       <c r="B10" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,21 +1492,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>487035</v>
+        <v>487171</v>
       </c>
       <c r="R10" t="n">
-        <v>7039161</v>
+        <v>7039000</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1547,6 +1552,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1573,10 +1583,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129298812</v>
+        <v>129298838</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1584,21 +1594,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1608,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>487362</v>
+        <v>487035</v>
       </c>
       <c r="R11" t="n">
-        <v>7039030</v>
+        <v>7039161</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1644,11 +1654,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1675,10 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129298759</v>
+        <v>129298742</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>91550</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1686,21 +1691,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1710,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>487171</v>
+        <v>487129</v>
       </c>
       <c r="R12" t="n">
-        <v>7039000</v>
+        <v>7039097</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1746,11 +1751,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2481,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129298845</v>
+        <v>129298740</v>
       </c>
       <c r="B20" t="n">
-        <v>78057</v>
+        <v>91550</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>487526</v>
+        <v>487145</v>
       </c>
       <c r="R20" t="n">
-        <v>7039006</v>
+        <v>7039179</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129298740</v>
+        <v>129298852</v>
       </c>
       <c r="B21" t="n">
-        <v>91549</v>
+        <v>91564</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2589,21 +2589,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>487145</v>
+        <v>487127</v>
       </c>
       <c r="R21" t="n">
-        <v>7039179</v>
+        <v>7039070</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129298852</v>
+        <v>129298837</v>
       </c>
       <c r="B22" t="n">
-        <v>91563</v>
+        <v>80149</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,21 +2686,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>487127</v>
+        <v>487004</v>
       </c>
       <c r="R22" t="n">
-        <v>7039070</v>
+        <v>7039214</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3078,45 +3078,57 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129298837</v>
+        <v>129298830</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
+        <v>57568</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>102621</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>487004</v>
+        <v>487123</v>
       </c>
       <c r="R26" t="n">
-        <v>7039214</v>
+        <v>7039173</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3175,57 +3187,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129298830</v>
+        <v>129298845</v>
       </c>
       <c r="B27" t="n">
-        <v>57568</v>
+        <v>78057</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102621</v>
+        <v>228579</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>487123</v>
+        <v>487526</v>
       </c>
       <c r="R27" t="n">
-        <v>7039173</v>
+        <v>7039006</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3284,10 +3284,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129298793</v>
+        <v>129298843</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3295,21 +3295,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3319,10 +3319,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>487183</v>
+        <v>487391</v>
       </c>
       <c r="R28" t="n">
-        <v>7039216</v>
+        <v>7038927</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3355,11 +3355,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3386,27 +3381,27 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129298823</v>
+        <v>129298846</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3421,10 +3416,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>487363</v>
+        <v>486976</v>
       </c>
       <c r="R29" t="n">
-        <v>7038902</v>
+        <v>7039216</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3457,11 +3452,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3488,7 +3478,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129298765</v>
+        <v>129298793</v>
       </c>
       <c r="B30" t="n">
         <v>57727</v>
@@ -3523,10 +3513,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>487122</v>
+        <v>487183</v>
       </c>
       <c r="R30" t="n">
-        <v>7039034</v>
+        <v>7039216</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3590,7 +3580,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129298770</v>
+        <v>129298823</v>
       </c>
       <c r="B31" t="n">
         <v>57727</v>
@@ -3625,10 +3615,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486972</v>
+        <v>487363</v>
       </c>
       <c r="R31" t="n">
-        <v>7039122</v>
+        <v>7038902</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3692,7 +3682,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129298778</v>
+        <v>129298765</v>
       </c>
       <c r="B32" t="n">
         <v>57727</v>
@@ -3727,10 +3717,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486871</v>
+        <v>487122</v>
       </c>
       <c r="R32" t="n">
-        <v>7039260</v>
+        <v>7039034</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3794,10 +3784,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129298843</v>
+        <v>129298770</v>
       </c>
       <c r="B33" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3805,21 +3795,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3829,10 +3819,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>487391</v>
+        <v>486972</v>
       </c>
       <c r="R33" t="n">
-        <v>7038927</v>
+        <v>7039122</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3865,6 +3855,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3891,27 +3886,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129298846</v>
+        <v>129298778</v>
       </c>
       <c r="B34" t="n">
-        <v>57831</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3926,10 +3921,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486976</v>
+        <v>486871</v>
       </c>
       <c r="R34" t="n">
-        <v>7039216</v>
+        <v>7039260</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3962,6 +3957,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4498,10 +4498,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129298805</v>
+        <v>129298854</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>91570</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4509,23 +4509,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4533,10 +4529,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>487346</v>
+        <v>487522</v>
       </c>
       <c r="R40" t="n">
-        <v>7039012</v>
+        <v>7038997</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4569,11 +4565,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4600,10 +4591,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129298748</v>
+        <v>129298840</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4611,21 +4602,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4635,10 +4626,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>487301</v>
+        <v>487314</v>
       </c>
       <c r="R41" t="n">
-        <v>7038925</v>
+        <v>7039005</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4671,11 +4662,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4702,10 +4688,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129298783</v>
+        <v>129298833</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4713,21 +4699,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4737,10 +4723,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>487024</v>
+        <v>487265</v>
       </c>
       <c r="R42" t="n">
-        <v>7039203</v>
+        <v>7038997</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4773,11 +4759,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4804,10 +4785,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129298833</v>
+        <v>129298805</v>
       </c>
       <c r="B43" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4815,21 +4796,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4839,10 +4820,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>487265</v>
+        <v>487346</v>
       </c>
       <c r="R43" t="n">
-        <v>7038997</v>
+        <v>7039012</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4875,6 +4856,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4901,10 +4887,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129298854</v>
+        <v>129298809</v>
       </c>
       <c r="B44" t="n">
-        <v>91569</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4912,19 +4898,23 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -4932,10 +4922,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>487522</v>
+        <v>487348</v>
       </c>
       <c r="R44" t="n">
-        <v>7038997</v>
+        <v>7039005</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4968,6 +4958,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4994,10 +4989,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129298840</v>
+        <v>129298802</v>
       </c>
       <c r="B45" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5005,21 +5000,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5029,10 +5024,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>487314</v>
+        <v>487302</v>
       </c>
       <c r="R45" t="n">
-        <v>7039005</v>
+        <v>7039045</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5065,6 +5060,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5091,7 +5091,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129298809</v>
+        <v>129298795</v>
       </c>
       <c r="B46" t="n">
         <v>57727</v>
@@ -5126,10 +5126,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>487348</v>
+        <v>487100</v>
       </c>
       <c r="R46" t="n">
-        <v>7039005</v>
+        <v>7039085</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5193,7 +5193,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129298802</v>
+        <v>129298748</v>
       </c>
       <c r="B47" t="n">
         <v>57727</v>
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>487302</v>
+        <v>487301</v>
       </c>
       <c r="R47" t="n">
-        <v>7039045</v>
+        <v>7038925</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5295,7 +5295,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129298795</v>
+        <v>129298783</v>
       </c>
       <c r="B48" t="n">
         <v>57727</v>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>487100</v>
+        <v>487024</v>
       </c>
       <c r="R48" t="n">
-        <v>7039085</v>
+        <v>7039203</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5397,10 +5397,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129298856</v>
+        <v>129298738</v>
       </c>
       <c r="B49" t="n">
-        <v>82878</v>
+        <v>96970</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5408,21 +5408,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>53</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>487541</v>
+        <v>487311</v>
       </c>
       <c r="R49" t="n">
-        <v>7038983</v>
+        <v>7039063</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5698,10 +5698,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129298738</v>
+        <v>129298856</v>
       </c>
       <c r="B52" t="n">
-        <v>96962</v>
+        <v>82878</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5709,21 +5709,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>53</v>
+        <v>1312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5733,10 +5733,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>487311</v>
+        <v>487541</v>
       </c>
       <c r="R52" t="n">
-        <v>7039063</v>
+        <v>7038983</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5892,10 +5892,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129298825</v>
+        <v>129298779</v>
       </c>
       <c r="B54" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5903,21 +5903,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5927,10 +5927,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>487247</v>
+        <v>486866</v>
       </c>
       <c r="R54" t="n">
-        <v>7039020</v>
+        <v>7039259</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5994,7 +5994,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129298779</v>
+        <v>129298749</v>
       </c>
       <c r="B55" t="n">
         <v>57727</v>
@@ -6029,10 +6029,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486866</v>
+        <v>487275</v>
       </c>
       <c r="R55" t="n">
-        <v>7039259</v>
+        <v>7038947</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6096,10 +6096,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129298749</v>
+        <v>129298825</v>
       </c>
       <c r="B56" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6107,21 +6107,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6131,10 +6131,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>487275</v>
+        <v>487247</v>
       </c>
       <c r="R56" t="n">
-        <v>7038947</v>
+        <v>7039020</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7017,7 +7017,7 @@
         <v>129298741</v>
       </c>
       <c r="B65" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7111,10 +7111,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129298853</v>
+        <v>129298811</v>
       </c>
       <c r="B66" t="n">
-        <v>91569</v>
+        <v>57727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7122,19 +7122,23 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7142,10 +7146,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>487415</v>
+        <v>487357</v>
       </c>
       <c r="R66" t="n">
-        <v>7038971</v>
+        <v>7039009</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7178,6 +7182,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7204,10 +7213,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129298811</v>
+        <v>129298853</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>91570</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7215,23 +7224,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7239,10 +7244,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>487357</v>
+        <v>487415</v>
       </c>
       <c r="R67" t="n">
-        <v>7039009</v>
+        <v>7038971</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7275,11 +7280,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7306,32 +7306,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129298737</v>
+        <v>129298831</v>
       </c>
       <c r="B68" t="n">
-        <v>83012</v>
+        <v>83003</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>492</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7341,10 +7341,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>487523</v>
+        <v>487307</v>
       </c>
       <c r="R68" t="n">
-        <v>7039001</v>
+        <v>7039016</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7403,32 +7403,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129298828</v>
+        <v>129298737</v>
       </c>
       <c r="B69" t="n">
-        <v>80178</v>
+        <v>83012</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7438,10 +7438,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>487269</v>
+        <v>487523</v>
       </c>
       <c r="R69" t="n">
-        <v>7039004</v>
+        <v>7039001</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7500,32 +7500,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129298839</v>
+        <v>129298828</v>
       </c>
       <c r="B70" t="n">
-        <v>80149</v>
+        <v>80178</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7538,7 +7538,7 @@
         <v>487269</v>
       </c>
       <c r="R70" t="n">
-        <v>7039001</v>
+        <v>7039004</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7597,10 +7597,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129298797</v>
+        <v>129298839</v>
       </c>
       <c r="B71" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7608,21 +7608,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>487134</v>
+        <v>487269</v>
       </c>
       <c r="R71" t="n">
-        <v>7039037</v>
+        <v>7039001</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7668,11 +7668,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7699,7 +7694,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129298803</v>
+        <v>129298797</v>
       </c>
       <c r="B72" t="n">
         <v>57727</v>
@@ -7734,7 +7729,7 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>487303</v>
+        <v>487134</v>
       </c>
       <c r="R72" t="n">
         <v>7039037</v>
@@ -7801,7 +7796,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129298822</v>
+        <v>129298803</v>
       </c>
       <c r="B73" t="n">
         <v>57727</v>
@@ -7836,10 +7831,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>487373</v>
+        <v>487303</v>
       </c>
       <c r="R73" t="n">
-        <v>7038897</v>
+        <v>7039037</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7903,7 +7898,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129298817</v>
+        <v>129298822</v>
       </c>
       <c r="B74" t="n">
         <v>57727</v>
@@ -7938,10 +7933,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>487460</v>
+        <v>487373</v>
       </c>
       <c r="R74" t="n">
-        <v>7038984</v>
+        <v>7038897</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8005,7 +8000,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129298800</v>
+        <v>129298817</v>
       </c>
       <c r="B75" t="n">
         <v>57727</v>
@@ -8033,33 +8028,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>487288</v>
+        <v>487460</v>
       </c>
       <c r="R75" t="n">
-        <v>7039015</v>
+        <v>7038984</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8096,7 +8075,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Födosökande hane</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8123,7 +8102,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129298821</v>
+        <v>129298800</v>
       </c>
       <c r="B76" t="n">
         <v>57727</v>
@@ -8151,17 +8130,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>487368</v>
+        <v>487288</v>
       </c>
       <c r="R76" t="n">
-        <v>7038892</v>
+        <v>7039015</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8198,7 +8193,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Födosökande hane</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8225,32 +8220,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129298831</v>
+        <v>129298821</v>
       </c>
       <c r="B77" t="n">
-        <v>83003</v>
+        <v>57727</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8260,10 +8255,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>487307</v>
+        <v>487368</v>
       </c>
       <c r="R77" t="n">
-        <v>7039016</v>
+        <v>7038892</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8296,6 +8291,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9662,7 +9662,7 @@
         <v>129298743</v>
       </c>
       <c r="B91" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>129298739</v>
       </c>
       <c r="B95" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 46357-2025 artfynd.xlsx
+++ b/artfynd/A 46357-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129298751</v>
+        <v>129298851</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>91564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487263</v>
+        <v>487144</v>
       </c>
       <c r="R2" t="n">
-        <v>7038949</v>
+        <v>7039078</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129298786</v>
+        <v>129298751</v>
       </c>
       <c r="B3" t="n">
         <v>57727</v>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487006</v>
+        <v>487263</v>
       </c>
       <c r="R3" t="n">
-        <v>7039175</v>
+        <v>7038949</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +874,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129298818</v>
+        <v>129298786</v>
       </c>
       <c r="B4" t="n">
         <v>57727</v>
@@ -914,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487389</v>
+        <v>487006</v>
       </c>
       <c r="R4" t="n">
-        <v>7038925</v>
+        <v>7039175</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +976,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129298819</v>
+        <v>129298818</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1016,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>487346</v>
+        <v>487389</v>
       </c>
       <c r="R5" t="n">
-        <v>7038911</v>
+        <v>7038925</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129298851</v>
+        <v>129298819</v>
       </c>
       <c r="B6" t="n">
-        <v>91564</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>487144</v>
+        <v>487346</v>
       </c>
       <c r="R6" t="n">
-        <v>7039078</v>
+        <v>7038911</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1154,6 +1149,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1583,10 +1583,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129298838</v>
+        <v>129298742</v>
       </c>
       <c r="B11" t="n">
-        <v>80149</v>
+        <v>91550</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1594,21 +1594,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>487035</v>
+        <v>487129</v>
       </c>
       <c r="R11" t="n">
-        <v>7039161</v>
+        <v>7039097</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1680,10 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129298742</v>
+        <v>129298838</v>
       </c>
       <c r="B12" t="n">
-        <v>91550</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,21 +1691,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1715,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>487129</v>
+        <v>487035</v>
       </c>
       <c r="R12" t="n">
-        <v>7039097</v>
+        <v>7039161</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129298857</v>
+        <v>129298855</v>
       </c>
       <c r="B16" t="n">
-        <v>83004</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2094,21 +2094,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>487340</v>
+        <v>487542</v>
       </c>
       <c r="R16" t="n">
-        <v>7039016</v>
+        <v>7038985</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2180,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129298855</v>
+        <v>129298857</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>83004</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>487542</v>
+        <v>487340</v>
       </c>
       <c r="R17" t="n">
-        <v>7038985</v>
+        <v>7039016</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2481,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129298740</v>
+        <v>129298845</v>
       </c>
       <c r="B20" t="n">
-        <v>91550</v>
+        <v>78057</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>487145</v>
+        <v>487526</v>
       </c>
       <c r="R20" t="n">
-        <v>7039179</v>
+        <v>7039006</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129298852</v>
+        <v>129298780</v>
       </c>
       <c r="B21" t="n">
-        <v>91564</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2589,21 +2589,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>487127</v>
+        <v>486859</v>
       </c>
       <c r="R21" t="n">
-        <v>7039070</v>
+        <v>7039262</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2649,6 +2649,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2772,10 +2777,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129298775</v>
+        <v>129298740</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>91550</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2783,21 +2788,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2807,10 +2812,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486860</v>
+        <v>487145</v>
       </c>
       <c r="R23" t="n">
-        <v>7039244</v>
+        <v>7039179</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2843,11 +2848,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2874,10 +2874,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129298808</v>
+        <v>129298852</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>91564</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2885,21 +2885,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>487344</v>
+        <v>487127</v>
       </c>
       <c r="R24" t="n">
-        <v>7039018</v>
+        <v>7039070</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2945,11 +2945,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2976,7 +2971,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129298780</v>
+        <v>129298775</v>
       </c>
       <c r="B25" t="n">
         <v>57727</v>
@@ -3011,10 +3006,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486859</v>
+        <v>486860</v>
       </c>
       <c r="R25" t="n">
-        <v>7039262</v>
+        <v>7039244</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3051,7 +3046,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3078,27 +3073,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129298830</v>
+        <v>129298808</v>
       </c>
       <c r="B26" t="n">
-        <v>57568</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3106,29 +3101,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>487123</v>
+        <v>487344</v>
       </c>
       <c r="R26" t="n">
-        <v>7039173</v>
+        <v>7039018</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3161,6 +3144,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3187,45 +3175,57 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129298845</v>
+        <v>129298830</v>
       </c>
       <c r="B27" t="n">
-        <v>78057</v>
+        <v>57568</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228579</v>
+        <v>102621</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>487526</v>
+        <v>487123</v>
       </c>
       <c r="R27" t="n">
-        <v>7039006</v>
+        <v>7039173</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3284,10 +3284,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129298843</v>
+        <v>129298793</v>
       </c>
       <c r="B28" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3295,21 +3295,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3319,10 +3319,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>487391</v>
+        <v>487183</v>
       </c>
       <c r="R28" t="n">
-        <v>7038927</v>
+        <v>7039216</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3355,6 +3355,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3381,27 +3386,27 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129298846</v>
+        <v>129298823</v>
       </c>
       <c r="B29" t="n">
-        <v>57831</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3416,10 +3421,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486976</v>
+        <v>487363</v>
       </c>
       <c r="R29" t="n">
-        <v>7039216</v>
+        <v>7038902</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3452,6 +3457,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3478,7 +3488,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129298793</v>
+        <v>129298765</v>
       </c>
       <c r="B30" t="n">
         <v>57727</v>
@@ -3513,10 +3523,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>487183</v>
+        <v>487122</v>
       </c>
       <c r="R30" t="n">
-        <v>7039216</v>
+        <v>7039034</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3580,7 +3590,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129298823</v>
+        <v>129298770</v>
       </c>
       <c r="B31" t="n">
         <v>57727</v>
@@ -3615,10 +3625,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>487363</v>
+        <v>486972</v>
       </c>
       <c r="R31" t="n">
-        <v>7038902</v>
+        <v>7039122</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3682,7 +3692,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129298765</v>
+        <v>129298778</v>
       </c>
       <c r="B32" t="n">
         <v>57727</v>
@@ -3717,10 +3727,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>487122</v>
+        <v>486871</v>
       </c>
       <c r="R32" t="n">
-        <v>7039034</v>
+        <v>7039260</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3784,10 +3794,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129298770</v>
+        <v>129298843</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3795,21 +3805,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3819,10 +3829,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486972</v>
+        <v>487391</v>
       </c>
       <c r="R33" t="n">
-        <v>7039122</v>
+        <v>7038927</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3855,11 +3865,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3886,27 +3891,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129298778</v>
+        <v>129298846</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3921,10 +3926,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486871</v>
+        <v>486976</v>
       </c>
       <c r="R34" t="n">
-        <v>7039260</v>
+        <v>7039216</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3957,11 +3962,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3988,7 +3988,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129298792</v>
+        <v>129298794</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>487153</v>
+        <v>487186</v>
       </c>
       <c r="R35" t="n">
-        <v>7039212</v>
+        <v>7039192</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4090,7 +4090,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129298750</v>
+        <v>129298792</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4125,10 +4125,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>487272</v>
+        <v>487153</v>
       </c>
       <c r="R36" t="n">
-        <v>7038946</v>
+        <v>7039212</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4192,7 +4192,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129298769</v>
+        <v>129298750</v>
       </c>
       <c r="B37" t="n">
         <v>57727</v>
@@ -4227,10 +4227,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>487109</v>
+        <v>487272</v>
       </c>
       <c r="R37" t="n">
-        <v>7039040</v>
+        <v>7038946</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4294,7 +4294,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129298804</v>
+        <v>129298769</v>
       </c>
       <c r="B38" t="n">
         <v>57727</v>
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>487288</v>
+        <v>487109</v>
       </c>
       <c r="R38" t="n">
-        <v>7039002</v>
+        <v>7039040</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4396,7 +4396,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129298794</v>
+        <v>129298804</v>
       </c>
       <c r="B39" t="n">
         <v>57727</v>
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>487186</v>
+        <v>487288</v>
       </c>
       <c r="R39" t="n">
-        <v>7039192</v>
+        <v>7039002</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4498,10 +4498,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129298854</v>
+        <v>129298840</v>
       </c>
       <c r="B40" t="n">
-        <v>91570</v>
+        <v>80149</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4509,19 +4509,23 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4529,10 +4533,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>487522</v>
+        <v>487314</v>
       </c>
       <c r="R40" t="n">
-        <v>7038997</v>
+        <v>7039005</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4591,10 +4595,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129298840</v>
+        <v>129298805</v>
       </c>
       <c r="B41" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4602,21 +4606,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4626,10 +4630,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>487314</v>
+        <v>487346</v>
       </c>
       <c r="R41" t="n">
-        <v>7039005</v>
+        <v>7039012</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4662,6 +4666,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4688,10 +4697,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129298833</v>
+        <v>129298809</v>
       </c>
       <c r="B42" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4699,21 +4708,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4723,10 +4732,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>487265</v>
+        <v>487348</v>
       </c>
       <c r="R42" t="n">
-        <v>7038997</v>
+        <v>7039005</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4759,6 +4768,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4785,7 +4799,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129298805</v>
+        <v>129298802</v>
       </c>
       <c r="B43" t="n">
         <v>57727</v>
@@ -4820,10 +4834,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>487346</v>
+        <v>487302</v>
       </c>
       <c r="R43" t="n">
-        <v>7039012</v>
+        <v>7039045</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4887,7 +4901,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129298809</v>
+        <v>129298795</v>
       </c>
       <c r="B44" t="n">
         <v>57727</v>
@@ -4922,10 +4936,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>487348</v>
+        <v>487100</v>
       </c>
       <c r="R44" t="n">
-        <v>7039005</v>
+        <v>7039085</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4989,7 +5003,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129298802</v>
+        <v>129298748</v>
       </c>
       <c r="B45" t="n">
         <v>57727</v>
@@ -5024,10 +5038,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>487302</v>
+        <v>487301</v>
       </c>
       <c r="R45" t="n">
-        <v>7039045</v>
+        <v>7038925</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5091,7 +5105,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129298795</v>
+        <v>129298783</v>
       </c>
       <c r="B46" t="n">
         <v>57727</v>
@@ -5126,10 +5140,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>487100</v>
+        <v>487024</v>
       </c>
       <c r="R46" t="n">
-        <v>7039085</v>
+        <v>7039203</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5193,10 +5207,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129298748</v>
+        <v>129298854</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>91570</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5204,23 +5218,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5228,10 +5238,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>487301</v>
+        <v>487522</v>
       </c>
       <c r="R47" t="n">
-        <v>7038925</v>
+        <v>7038997</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5264,11 +5274,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5295,10 +5300,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129298783</v>
+        <v>129298833</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5306,21 +5311,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5330,10 +5335,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>487024</v>
+        <v>487265</v>
       </c>
       <c r="R48" t="n">
-        <v>7039203</v>
+        <v>7038997</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5366,11 +5371,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5397,10 +5397,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129298738</v>
+        <v>129298798</v>
       </c>
       <c r="B49" t="n">
-        <v>96970</v>
+        <v>57727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5408,21 +5408,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>487311</v>
+        <v>487131</v>
       </c>
       <c r="R49" t="n">
-        <v>7039063</v>
+        <v>7039049</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5468,6 +5468,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5494,7 +5499,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129298798</v>
+        <v>129298810</v>
       </c>
       <c r="B50" t="n">
         <v>57727</v>
@@ -5529,10 +5534,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>487131</v>
+        <v>487355</v>
       </c>
       <c r="R50" t="n">
-        <v>7039049</v>
+        <v>7039005</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5596,10 +5601,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129298810</v>
+        <v>129298856</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>82878</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5607,21 +5612,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5631,10 +5636,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>487355</v>
+        <v>487541</v>
       </c>
       <c r="R51" t="n">
-        <v>7039005</v>
+        <v>7038983</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5667,11 +5672,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5698,10 +5698,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129298856</v>
+        <v>129298738</v>
       </c>
       <c r="B52" t="n">
-        <v>82878</v>
+        <v>96970</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5709,21 +5709,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1312</v>
+        <v>53</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5733,10 +5733,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>487541</v>
+        <v>487311</v>
       </c>
       <c r="R52" t="n">
-        <v>7038983</v>
+        <v>7039063</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6198,10 +6198,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129298767</v>
+        <v>129298826</v>
       </c>
       <c r="B57" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6209,21 +6209,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6233,10 +6233,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>487123</v>
+        <v>487457</v>
       </c>
       <c r="R57" t="n">
-        <v>7039031</v>
+        <v>7038967</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6300,7 +6300,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129298776</v>
+        <v>129298767</v>
       </c>
       <c r="B58" t="n">
         <v>57727</v>
@@ -6335,10 +6335,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>486855</v>
+        <v>487123</v>
       </c>
       <c r="R58" t="n">
-        <v>7039252</v>
+        <v>7039031</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6402,7 +6402,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129298816</v>
+        <v>129298776</v>
       </c>
       <c r="B59" t="n">
         <v>57727</v>
@@ -6437,10 +6437,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>487389</v>
+        <v>486855</v>
       </c>
       <c r="R59" t="n">
-        <v>7038985</v>
+        <v>7039252</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6504,7 +6504,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129298813</v>
+        <v>129298816</v>
       </c>
       <c r="B60" t="n">
         <v>57727</v>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>487367</v>
+        <v>487389</v>
       </c>
       <c r="R60" t="n">
-        <v>7038998</v>
+        <v>7038985</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6606,7 +6606,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129298820</v>
+        <v>129298813</v>
       </c>
       <c r="B61" t="n">
         <v>57727</v>
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>487354</v>
+        <v>487367</v>
       </c>
       <c r="R61" t="n">
-        <v>7038894</v>
+        <v>7038998</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6708,7 +6708,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129298774</v>
+        <v>129298820</v>
       </c>
       <c r="B62" t="n">
         <v>57727</v>
@@ -6743,10 +6743,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>486866</v>
+        <v>487354</v>
       </c>
       <c r="R62" t="n">
-        <v>7039249</v>
+        <v>7038894</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6783,7 +6783,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6810,7 +6810,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129298773</v>
+        <v>129298774</v>
       </c>
       <c r="B63" t="n">
         <v>57727</v>
@@ -6845,10 +6845,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>486807</v>
+        <v>486866</v>
       </c>
       <c r="R63" t="n">
-        <v>7039220</v>
+        <v>7039249</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6912,10 +6912,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129298826</v>
+        <v>129298773</v>
       </c>
       <c r="B64" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6923,21 +6923,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6947,10 +6947,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>487457</v>
+        <v>486807</v>
       </c>
       <c r="R64" t="n">
-        <v>7038967</v>
+        <v>7039220</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6987,7 +6987,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7014,10 +7014,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129298741</v>
+        <v>129298811</v>
       </c>
       <c r="B65" t="n">
-        <v>91550</v>
+        <v>57727</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7025,21 +7025,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7049,10 +7049,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>487185</v>
+        <v>487357</v>
       </c>
       <c r="R65" t="n">
-        <v>7039203</v>
+        <v>7039009</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7085,6 +7085,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7111,10 +7116,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129298811</v>
+        <v>129298741</v>
       </c>
       <c r="B66" t="n">
-        <v>57727</v>
+        <v>91550</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7122,21 +7127,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7146,10 +7151,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>487357</v>
+        <v>487185</v>
       </c>
       <c r="R66" t="n">
-        <v>7039009</v>
+        <v>7039203</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7182,11 +7187,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7500,32 +7500,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129298828</v>
+        <v>129298797</v>
       </c>
       <c r="B70" t="n">
-        <v>80178</v>
+        <v>57727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7535,10 +7535,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>487269</v>
+        <v>487134</v>
       </c>
       <c r="R70" t="n">
-        <v>7039004</v>
+        <v>7039037</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7571,6 +7571,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7597,10 +7602,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129298839</v>
+        <v>129298803</v>
       </c>
       <c r="B71" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7608,21 +7613,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7632,10 +7637,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>487269</v>
+        <v>487303</v>
       </c>
       <c r="R71" t="n">
-        <v>7039001</v>
+        <v>7039037</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7668,6 +7673,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7694,7 +7704,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129298797</v>
+        <v>129298822</v>
       </c>
       <c r="B72" t="n">
         <v>57727</v>
@@ -7729,10 +7739,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>487134</v>
+        <v>487373</v>
       </c>
       <c r="R72" t="n">
-        <v>7039037</v>
+        <v>7038897</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7796,7 +7806,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129298803</v>
+        <v>129298817</v>
       </c>
       <c r="B73" t="n">
         <v>57727</v>
@@ -7831,10 +7841,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>487303</v>
+        <v>487460</v>
       </c>
       <c r="R73" t="n">
-        <v>7039037</v>
+        <v>7038984</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7898,7 +7908,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129298822</v>
+        <v>129298800</v>
       </c>
       <c r="B74" t="n">
         <v>57727</v>
@@ -7926,17 +7936,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>487373</v>
+        <v>487288</v>
       </c>
       <c r="R74" t="n">
-        <v>7038897</v>
+        <v>7039015</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7973,7 +7999,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Födosökande hane</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8000,7 +8026,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129298817</v>
+        <v>129298821</v>
       </c>
       <c r="B75" t="n">
         <v>57727</v>
@@ -8035,10 +8061,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>487460</v>
+        <v>487368</v>
       </c>
       <c r="R75" t="n">
-        <v>7038984</v>
+        <v>7038892</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8102,61 +8128,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129298800</v>
+        <v>129298828</v>
       </c>
       <c r="B76" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>487288</v>
+        <v>487269</v>
       </c>
       <c r="R76" t="n">
-        <v>7039015</v>
+        <v>7039004</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8189,11 +8199,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Födosökande hane</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8220,10 +8225,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129298821</v>
+        <v>129298839</v>
       </c>
       <c r="B77" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8231,21 +8236,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8255,10 +8260,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>487368</v>
+        <v>487269</v>
       </c>
       <c r="R77" t="n">
-        <v>7038892</v>
+        <v>7039001</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8291,11 +8296,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8322,7 +8322,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129298781</v>
+        <v>129298784</v>
       </c>
       <c r="B78" t="n">
         <v>57727</v>
@@ -8357,10 +8357,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>486864</v>
+        <v>487011</v>
       </c>
       <c r="R78" t="n">
-        <v>7039272</v>
+        <v>7039207</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8424,7 +8424,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129298785</v>
+        <v>129298781</v>
       </c>
       <c r="B79" t="n">
         <v>57727</v>
@@ -8459,10 +8459,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>487007</v>
+        <v>486864</v>
       </c>
       <c r="R79" t="n">
-        <v>7039210</v>
+        <v>7039272</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8628,7 +8628,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129298757</v>
+        <v>129298785</v>
       </c>
       <c r="B81" t="n">
         <v>57727</v>
@@ -8663,10 +8663,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>487188</v>
+        <v>487007</v>
       </c>
       <c r="R81" t="n">
-        <v>7038992</v>
+        <v>7039210</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8703,7 +8703,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8730,7 +8730,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129298784</v>
+        <v>129298757</v>
       </c>
       <c r="B82" t="n">
         <v>57727</v>
@@ -8765,10 +8765,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>487011</v>
+        <v>487188</v>
       </c>
       <c r="R82" t="n">
-        <v>7039207</v>
+        <v>7038992</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8832,10 +8832,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129298841</v>
+        <v>129298789</v>
       </c>
       <c r="B83" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8843,21 +8843,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8867,10 +8867,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>487515</v>
+        <v>487041</v>
       </c>
       <c r="R83" t="n">
-        <v>7038993</v>
+        <v>7039167</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8903,6 +8903,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8929,7 +8934,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129298771</v>
+        <v>129298772</v>
       </c>
       <c r="B84" t="n">
         <v>57727</v>
@@ -8964,10 +8969,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>486885</v>
+        <v>486849</v>
       </c>
       <c r="R84" t="n">
-        <v>7039172</v>
+        <v>7039185</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9031,61 +9036,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129298847</v>
+        <v>129298746</v>
       </c>
       <c r="B85" t="n">
-        <v>57587</v>
+        <v>57727</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100136</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>486999</v>
+        <v>487316</v>
       </c>
       <c r="R85" t="n">
-        <v>7039199</v>
+        <v>7038914</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9122,7 +9111,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Jagades av en nötskrika</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9149,10 +9138,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129298789</v>
+        <v>129298841</v>
       </c>
       <c r="B86" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9160,21 +9149,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9184,10 +9173,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>487041</v>
+        <v>487515</v>
       </c>
       <c r="R86" t="n">
-        <v>7039167</v>
+        <v>7038993</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9220,11 +9209,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9251,7 +9235,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129298801</v>
+        <v>129298771</v>
       </c>
       <c r="B87" t="n">
         <v>57727</v>
@@ -9286,10 +9270,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>487268</v>
+        <v>486885</v>
       </c>
       <c r="R87" t="n">
-        <v>7039003</v>
+        <v>7039172</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9353,45 +9337,61 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129298814</v>
+        <v>129298847</v>
       </c>
       <c r="B88" t="n">
-        <v>57727</v>
+        <v>57587</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>100136</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>487366</v>
+        <v>486999</v>
       </c>
       <c r="R88" t="n">
-        <v>7038997</v>
+        <v>7039199</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Jagades av en nötskrika</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9455,7 +9455,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129298772</v>
+        <v>129298801</v>
       </c>
       <c r="B89" t="n">
         <v>57727</v>
@@ -9490,10 +9490,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>486849</v>
+        <v>487268</v>
       </c>
       <c r="R89" t="n">
-        <v>7039185</v>
+        <v>7039003</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9557,7 +9557,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129298746</v>
+        <v>129298814</v>
       </c>
       <c r="B90" t="n">
         <v>57727</v>
@@ -9592,10 +9592,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>487316</v>
+        <v>487366</v>
       </c>
       <c r="R90" t="n">
-        <v>7038914</v>
+        <v>7038997</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9632,7 +9632,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10057,32 +10057,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129298739</v>
+        <v>129298745</v>
       </c>
       <c r="B95" t="n">
-        <v>91514</v>
+        <v>57727</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10092,10 +10092,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>487384</v>
+        <v>486881</v>
       </c>
       <c r="R95" t="n">
-        <v>7038973</v>
+        <v>7039175</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10128,6 +10128,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10154,7 +10159,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129298745</v>
+        <v>129298791</v>
       </c>
       <c r="B96" t="n">
         <v>57727</v>
@@ -10189,10 +10194,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>486881</v>
+        <v>487112</v>
       </c>
       <c r="R96" t="n">
-        <v>7039175</v>
+        <v>7039182</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10256,7 +10261,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129298791</v>
+        <v>129298754</v>
       </c>
       <c r="B97" t="n">
         <v>57727</v>
@@ -10291,10 +10296,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>487112</v>
+        <v>487222</v>
       </c>
       <c r="R97" t="n">
-        <v>7039182</v>
+        <v>7038974</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10331,7 +10336,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10358,32 +10363,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129298754</v>
+        <v>129298739</v>
       </c>
       <c r="B98" t="n">
-        <v>57727</v>
+        <v>91514</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10393,10 +10398,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>487222</v>
+        <v>487384</v>
       </c>
       <c r="R98" t="n">
-        <v>7038974</v>
+        <v>7038973</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10429,11 +10434,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10460,10 +10460,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129298829</v>
+        <v>129298807</v>
       </c>
       <c r="B99" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10471,16 +10471,16 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -10488,33 +10488,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>487157</v>
+        <v>487337</v>
       </c>
       <c r="R99" t="n">
-        <v>7039100</v>
+        <v>7039015</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10547,6 +10531,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10573,10 +10562,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129298807</v>
+        <v>129298829</v>
       </c>
       <c r="B100" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10584,16 +10573,16 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -10601,17 +10590,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>487337</v>
+        <v>487157</v>
       </c>
       <c r="R100" t="n">
-        <v>7039015</v>
+        <v>7039100</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10644,11 +10649,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10772,10 +10772,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129298858</v>
+        <v>129298758</v>
       </c>
       <c r="B102" t="n">
-        <v>83004</v>
+        <v>57727</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10783,21 +10783,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10807,10 +10807,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>487408</v>
+        <v>487183</v>
       </c>
       <c r="R102" t="n">
-        <v>7038959</v>
+        <v>7038993</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10843,6 +10843,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10869,10 +10874,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129298806</v>
+        <v>129298858</v>
       </c>
       <c r="B103" t="n">
-        <v>57727</v>
+        <v>83004</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10880,21 +10885,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10904,10 +10909,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>487339</v>
+        <v>487408</v>
       </c>
       <c r="R103" t="n">
-        <v>7039009</v>
+        <v>7038959</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10940,11 +10945,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11073,7 +11073,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129298758</v>
+        <v>129298788</v>
       </c>
       <c r="B105" t="n">
         <v>57727</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>487183</v>
+        <v>487039</v>
       </c>
       <c r="R105" t="n">
-        <v>7038993</v>
+        <v>7039164</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11175,7 +11175,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129298815</v>
+        <v>129298806</v>
       </c>
       <c r="B106" t="n">
         <v>57727</v>
@@ -11210,10 +11210,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>487375</v>
+        <v>487339</v>
       </c>
       <c r="R106" t="n">
-        <v>7038981</v>
+        <v>7039009</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11277,7 +11277,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129298788</v>
+        <v>129298815</v>
       </c>
       <c r="B107" t="n">
         <v>57727</v>
@@ -11312,10 +11312,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>487039</v>
+        <v>487375</v>
       </c>
       <c r="R107" t="n">
-        <v>7039164</v>
+        <v>7038981</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>

--- a/artfynd/A 46357-2025 artfynd.xlsx
+++ b/artfynd/A 46357-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129298751</v>
+        <v>129298844</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>78057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487263</v>
+        <v>487374</v>
       </c>
       <c r="R3" t="n">
-        <v>7038949</v>
+        <v>7039027</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129298786</v>
+        <v>129298751</v>
       </c>
       <c r="B4" t="n">
         <v>57727</v>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487006</v>
+        <v>487263</v>
       </c>
       <c r="R4" t="n">
-        <v>7039175</v>
+        <v>7038949</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,7 +971,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129298818</v>
+        <v>129298786</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1011,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>487389</v>
+        <v>487006</v>
       </c>
       <c r="R5" t="n">
-        <v>7038925</v>
+        <v>7039175</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,7 +1073,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129298819</v>
+        <v>129298818</v>
       </c>
       <c r="B6" t="n">
         <v>57727</v>
@@ -1113,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>487346</v>
+        <v>487389</v>
       </c>
       <c r="R6" t="n">
-        <v>7038911</v>
+        <v>7038925</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129298827</v>
+        <v>129298819</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>487352</v>
+        <v>487346</v>
       </c>
       <c r="R7" t="n">
-        <v>7038906</v>
+        <v>7038911</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,7 +1250,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1282,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129298844</v>
+        <v>129298827</v>
       </c>
       <c r="B8" t="n">
-        <v>78057</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1293,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228579</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1317,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>487374</v>
+        <v>487352</v>
       </c>
       <c r="R8" t="n">
-        <v>7039027</v>
+        <v>7038906</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1353,6 +1348,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129298812</v>
+        <v>129298742</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>91550</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1390,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>487362</v>
+        <v>487129</v>
       </c>
       <c r="R9" t="n">
-        <v>7039030</v>
+        <v>7039097</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1450,11 +1450,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1481,7 +1476,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129298759</v>
+        <v>129298812</v>
       </c>
       <c r="B10" t="n">
         <v>57727</v>
@@ -1516,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>487171</v>
+        <v>487362</v>
       </c>
       <c r="R10" t="n">
-        <v>7039000</v>
+        <v>7039030</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1583,10 +1578,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129298742</v>
+        <v>129298759</v>
       </c>
       <c r="B11" t="n">
-        <v>91550</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1594,21 +1589,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>487129</v>
+        <v>487171</v>
       </c>
       <c r="R11" t="n">
-        <v>7039097</v>
+        <v>7039000</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,6 +1649,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2481,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129298845</v>
+        <v>129298740</v>
       </c>
       <c r="B20" t="n">
-        <v>78057</v>
+        <v>91550</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>487526</v>
+        <v>487145</v>
       </c>
       <c r="R20" t="n">
-        <v>7039006</v>
+        <v>7039179</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129298780</v>
+        <v>129298852</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>91564</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2589,21 +2589,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>486859</v>
+        <v>487127</v>
       </c>
       <c r="R21" t="n">
-        <v>7039262</v>
+        <v>7039070</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2649,11 +2649,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2680,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129298837</v>
+        <v>129298775</v>
       </c>
       <c r="B22" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2691,21 +2686,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2715,10 +2710,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>487004</v>
+        <v>486860</v>
       </c>
       <c r="R22" t="n">
-        <v>7039214</v>
+        <v>7039244</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2751,6 +2746,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2777,10 +2777,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129298740</v>
+        <v>129298808</v>
       </c>
       <c r="B23" t="n">
-        <v>91550</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2788,21 +2788,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2812,10 +2812,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>487145</v>
+        <v>487344</v>
       </c>
       <c r="R23" t="n">
-        <v>7039179</v>
+        <v>7039018</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2848,6 +2848,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2874,45 +2879,57 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129298852</v>
+        <v>129298830</v>
       </c>
       <c r="B24" t="n">
-        <v>91564</v>
+        <v>57568</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>102621</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>487127</v>
+        <v>487123</v>
       </c>
       <c r="R24" t="n">
-        <v>7039070</v>
+        <v>7039173</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2971,7 +2988,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129298775</v>
+        <v>129298780</v>
       </c>
       <c r="B25" t="n">
         <v>57727</v>
@@ -3006,10 +3023,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486860</v>
+        <v>486859</v>
       </c>
       <c r="R25" t="n">
-        <v>7039244</v>
+        <v>7039262</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3046,7 +3063,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3073,10 +3090,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129298808</v>
+        <v>129298837</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3084,21 +3101,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3108,10 +3125,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>487344</v>
+        <v>487004</v>
       </c>
       <c r="R26" t="n">
-        <v>7039018</v>
+        <v>7039214</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3144,11 +3161,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3175,57 +3187,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129298830</v>
+        <v>129298845</v>
       </c>
       <c r="B27" t="n">
-        <v>57568</v>
+        <v>78057</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102621</v>
+        <v>228579</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>487123</v>
+        <v>487526</v>
       </c>
       <c r="R27" t="n">
-        <v>7039173</v>
+        <v>7039006</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3284,27 +3284,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129298793</v>
+        <v>129298846</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3319,7 +3319,7 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>487183</v>
+        <v>486976</v>
       </c>
       <c r="R28" t="n">
         <v>7039216</v>
@@ -3355,11 +3355,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3386,7 +3381,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129298823</v>
+        <v>129298793</v>
       </c>
       <c r="B29" t="n">
         <v>57727</v>
@@ -3421,10 +3416,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>487363</v>
+        <v>487183</v>
       </c>
       <c r="R29" t="n">
-        <v>7038902</v>
+        <v>7039216</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3488,7 +3483,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129298765</v>
+        <v>129298823</v>
       </c>
       <c r="B30" t="n">
         <v>57727</v>
@@ -3523,10 +3518,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>487122</v>
+        <v>487363</v>
       </c>
       <c r="R30" t="n">
-        <v>7039034</v>
+        <v>7038902</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3590,7 +3585,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129298770</v>
+        <v>129298765</v>
       </c>
       <c r="B31" t="n">
         <v>57727</v>
@@ -3625,10 +3620,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486972</v>
+        <v>487122</v>
       </c>
       <c r="R31" t="n">
-        <v>7039122</v>
+        <v>7039034</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3692,7 +3687,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129298778</v>
+        <v>129298770</v>
       </c>
       <c r="B32" t="n">
         <v>57727</v>
@@ -3727,10 +3722,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486871</v>
+        <v>486972</v>
       </c>
       <c r="R32" t="n">
-        <v>7039260</v>
+        <v>7039122</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3794,10 +3789,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129298843</v>
+        <v>129298778</v>
       </c>
       <c r="B33" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3805,21 +3800,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3829,10 +3824,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>487391</v>
+        <v>486871</v>
       </c>
       <c r="R33" t="n">
-        <v>7038927</v>
+        <v>7039260</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3865,6 +3860,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3891,32 +3891,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129298846</v>
+        <v>129298843</v>
       </c>
       <c r="B34" t="n">
-        <v>57831</v>
+        <v>80149</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486976</v>
+        <v>487391</v>
       </c>
       <c r="R34" t="n">
-        <v>7039216</v>
+        <v>7038927</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3988,7 +3988,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129298794</v>
+        <v>129298769</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>487186</v>
+        <v>487109</v>
       </c>
       <c r="R35" t="n">
-        <v>7039192</v>
+        <v>7039040</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4090,7 +4090,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129298792</v>
+        <v>129298794</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4125,10 +4125,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>487153</v>
+        <v>487186</v>
       </c>
       <c r="R36" t="n">
-        <v>7039212</v>
+        <v>7039192</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4192,7 +4192,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129298750</v>
+        <v>129298792</v>
       </c>
       <c r="B37" t="n">
         <v>57727</v>
@@ -4227,10 +4227,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>487272</v>
+        <v>487153</v>
       </c>
       <c r="R37" t="n">
-        <v>7038946</v>
+        <v>7039212</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4294,7 +4294,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129298769</v>
+        <v>129298750</v>
       </c>
       <c r="B38" t="n">
         <v>57727</v>
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>487109</v>
+        <v>487272</v>
       </c>
       <c r="R38" t="n">
-        <v>7039040</v>
+        <v>7038946</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4498,10 +4498,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129298840</v>
+        <v>129298833</v>
       </c>
       <c r="B40" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4509,21 +4509,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>487314</v>
+        <v>487265</v>
       </c>
       <c r="R40" t="n">
-        <v>7039005</v>
+        <v>7038997</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4595,10 +4595,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129298805</v>
+        <v>129298840</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4606,21 +4606,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4630,10 +4630,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>487346</v>
+        <v>487314</v>
       </c>
       <c r="R41" t="n">
-        <v>7039012</v>
+        <v>7039005</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4666,11 +4666,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4697,7 +4692,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129298809</v>
+        <v>129298795</v>
       </c>
       <c r="B42" t="n">
         <v>57727</v>
@@ -4732,10 +4727,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>487348</v>
+        <v>487100</v>
       </c>
       <c r="R42" t="n">
-        <v>7039005</v>
+        <v>7039085</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4799,7 +4794,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129298802</v>
+        <v>129298748</v>
       </c>
       <c r="B43" t="n">
         <v>57727</v>
@@ -4834,10 +4829,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>487302</v>
+        <v>487301</v>
       </c>
       <c r="R43" t="n">
-        <v>7039045</v>
+        <v>7038925</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4901,7 +4896,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129298795</v>
+        <v>129298783</v>
       </c>
       <c r="B44" t="n">
         <v>57727</v>
@@ -4936,10 +4931,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>487100</v>
+        <v>487024</v>
       </c>
       <c r="R44" t="n">
-        <v>7039085</v>
+        <v>7039203</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5003,10 +4998,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129298748</v>
+        <v>129298854</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>91570</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5014,23 +5009,19 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5038,10 +5029,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>487301</v>
+        <v>487522</v>
       </c>
       <c r="R45" t="n">
-        <v>7038925</v>
+        <v>7038997</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5074,11 +5065,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5105,7 +5091,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129298783</v>
+        <v>129298805</v>
       </c>
       <c r="B46" t="n">
         <v>57727</v>
@@ -5140,10 +5126,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>487024</v>
+        <v>487346</v>
       </c>
       <c r="R46" t="n">
-        <v>7039203</v>
+        <v>7039012</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5207,10 +5193,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129298854</v>
+        <v>129298809</v>
       </c>
       <c r="B47" t="n">
-        <v>91570</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5218,19 +5204,23 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5238,10 +5228,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>487522</v>
+        <v>487348</v>
       </c>
       <c r="R47" t="n">
-        <v>7038997</v>
+        <v>7039005</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5274,6 +5264,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5300,10 +5295,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129298833</v>
+        <v>129298802</v>
       </c>
       <c r="B48" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5311,21 +5306,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5335,10 +5330,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>487265</v>
+        <v>487302</v>
       </c>
       <c r="R48" t="n">
-        <v>7038997</v>
+        <v>7039045</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5371,6 +5366,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5397,10 +5397,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129298798</v>
+        <v>129298738</v>
       </c>
       <c r="B49" t="n">
-        <v>57727</v>
+        <v>96970</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5408,21 +5408,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>487131</v>
+        <v>487311</v>
       </c>
       <c r="R49" t="n">
-        <v>7039049</v>
+        <v>7039063</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5468,11 +5468,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5499,10 +5494,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129298810</v>
+        <v>129298856</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>82878</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5510,21 +5505,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5534,10 +5529,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>487355</v>
+        <v>487541</v>
       </c>
       <c r="R50" t="n">
-        <v>7039005</v>
+        <v>7038983</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5570,11 +5565,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5601,10 +5591,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129298856</v>
+        <v>129298842</v>
       </c>
       <c r="B51" t="n">
-        <v>82878</v>
+        <v>80149</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5612,21 +5602,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5636,10 +5626,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>487541</v>
+        <v>487393</v>
       </c>
       <c r="R51" t="n">
-        <v>7038983</v>
+        <v>7038908</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5698,10 +5688,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129298738</v>
+        <v>129298810</v>
       </c>
       <c r="B52" t="n">
-        <v>96970</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5709,21 +5699,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5733,10 +5723,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>487311</v>
+        <v>487355</v>
       </c>
       <c r="R52" t="n">
-        <v>7039063</v>
+        <v>7039005</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5769,6 +5759,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5795,10 +5790,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129298842</v>
+        <v>129298798</v>
       </c>
       <c r="B53" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5806,21 +5801,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5830,10 +5825,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>487393</v>
+        <v>487131</v>
       </c>
       <c r="R53" t="n">
-        <v>7038908</v>
+        <v>7039049</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5866,6 +5861,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6198,10 +6198,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129298826</v>
+        <v>129298820</v>
       </c>
       <c r="B57" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6209,21 +6209,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6233,10 +6233,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>487457</v>
+        <v>487354</v>
       </c>
       <c r="R57" t="n">
-        <v>7038967</v>
+        <v>7038894</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6300,7 +6300,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129298767</v>
+        <v>129298774</v>
       </c>
       <c r="B58" t="n">
         <v>57727</v>
@@ -6335,10 +6335,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>487123</v>
+        <v>486866</v>
       </c>
       <c r="R58" t="n">
-        <v>7039031</v>
+        <v>7039249</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6402,7 +6402,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129298776</v>
+        <v>129298773</v>
       </c>
       <c r="B59" t="n">
         <v>57727</v>
@@ -6437,10 +6437,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>486855</v>
+        <v>486807</v>
       </c>
       <c r="R59" t="n">
-        <v>7039252</v>
+        <v>7039220</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6504,7 +6504,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129298816</v>
+        <v>129298767</v>
       </c>
       <c r="B60" t="n">
         <v>57727</v>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>487389</v>
+        <v>487123</v>
       </c>
       <c r="R60" t="n">
-        <v>7038985</v>
+        <v>7039031</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6606,7 +6606,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129298813</v>
+        <v>129298776</v>
       </c>
       <c r="B61" t="n">
         <v>57727</v>
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>487367</v>
+        <v>486855</v>
       </c>
       <c r="R61" t="n">
-        <v>7038998</v>
+        <v>7039252</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6681,7 +6681,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6708,7 +6708,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129298820</v>
+        <v>129298816</v>
       </c>
       <c r="B62" t="n">
         <v>57727</v>
@@ -6743,10 +6743,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>487354</v>
+        <v>487389</v>
       </c>
       <c r="R62" t="n">
-        <v>7038894</v>
+        <v>7038985</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6810,7 +6810,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129298774</v>
+        <v>129298813</v>
       </c>
       <c r="B63" t="n">
         <v>57727</v>
@@ -6845,10 +6845,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>486866</v>
+        <v>487367</v>
       </c>
       <c r="R63" t="n">
-        <v>7039249</v>
+        <v>7038998</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6885,7 +6885,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6912,10 +6912,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129298773</v>
+        <v>129298826</v>
       </c>
       <c r="B64" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6923,21 +6923,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6947,10 +6947,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>486807</v>
+        <v>487457</v>
       </c>
       <c r="R64" t="n">
-        <v>7039220</v>
+        <v>7038967</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6987,7 +6987,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7014,10 +7014,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129298811</v>
+        <v>129298853</v>
       </c>
       <c r="B65" t="n">
-        <v>57727</v>
+        <v>91570</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7025,23 +7025,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7049,10 +7045,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>487357</v>
+        <v>487415</v>
       </c>
       <c r="R65" t="n">
-        <v>7039009</v>
+        <v>7038971</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7085,11 +7081,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7213,10 +7204,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129298853</v>
+        <v>129298811</v>
       </c>
       <c r="B67" t="n">
-        <v>91570</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7224,19 +7215,23 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7244,10 +7239,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>487415</v>
+        <v>487357</v>
       </c>
       <c r="R67" t="n">
-        <v>7038971</v>
+        <v>7039009</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7280,6 +7275,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8832,10 +8832,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129298789</v>
+        <v>129298841</v>
       </c>
       <c r="B83" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8843,21 +8843,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8867,10 +8867,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>487041</v>
+        <v>487515</v>
       </c>
       <c r="R83" t="n">
-        <v>7039167</v>
+        <v>7038993</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8903,11 +8903,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8934,7 +8929,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129298772</v>
+        <v>129298771</v>
       </c>
       <c r="B84" t="n">
         <v>57727</v>
@@ -8969,10 +8964,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>486849</v>
+        <v>486885</v>
       </c>
       <c r="R84" t="n">
-        <v>7039185</v>
+        <v>7039172</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9036,45 +9031,61 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129298746</v>
+        <v>129298847</v>
       </c>
       <c r="B85" t="n">
-        <v>57727</v>
+        <v>57587</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>100136</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>487316</v>
+        <v>486999</v>
       </c>
       <c r="R85" t="n">
-        <v>7038914</v>
+        <v>7039199</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9111,7 +9122,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Jagades av en nötskrika</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9138,10 +9149,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129298841</v>
+        <v>129298789</v>
       </c>
       <c r="B86" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9149,21 +9160,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9173,10 +9184,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>487515</v>
+        <v>487041</v>
       </c>
       <c r="R86" t="n">
-        <v>7038993</v>
+        <v>7039167</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9209,6 +9220,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9235,7 +9251,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129298771</v>
+        <v>129298801</v>
       </c>
       <c r="B87" t="n">
         <v>57727</v>
@@ -9270,10 +9286,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>486885</v>
+        <v>487268</v>
       </c>
       <c r="R87" t="n">
-        <v>7039172</v>
+        <v>7039003</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9337,61 +9353,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129298847</v>
+        <v>129298814</v>
       </c>
       <c r="B88" t="n">
-        <v>57587</v>
+        <v>57727</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100136</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>486999</v>
+        <v>487366</v>
       </c>
       <c r="R88" t="n">
-        <v>7039199</v>
+        <v>7038997</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Jagades av en nötskrika</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9455,7 +9455,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129298801</v>
+        <v>129298772</v>
       </c>
       <c r="B89" t="n">
         <v>57727</v>
@@ -9490,10 +9490,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>487268</v>
+        <v>486849</v>
       </c>
       <c r="R89" t="n">
-        <v>7039003</v>
+        <v>7039185</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9557,7 +9557,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129298814</v>
+        <v>129298746</v>
       </c>
       <c r="B90" t="n">
         <v>57727</v>
@@ -9592,10 +9592,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>487366</v>
+        <v>487316</v>
       </c>
       <c r="R90" t="n">
-        <v>7038997</v>
+        <v>7038914</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9632,7 +9632,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10675,32 +10675,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129298832</v>
+        <v>129298858</v>
       </c>
       <c r="B101" t="n">
-        <v>83003</v>
+        <v>83004</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>492</v>
+        <v>308</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10710,10 +10710,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>487393</v>
+        <v>487408</v>
       </c>
       <c r="R101" t="n">
-        <v>7038976</v>
+        <v>7038959</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10772,32 +10772,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129298758</v>
+        <v>129298832</v>
       </c>
       <c r="B102" t="n">
-        <v>57727</v>
+        <v>83003</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10807,10 +10807,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>487183</v>
+        <v>487393</v>
       </c>
       <c r="R102" t="n">
-        <v>7038993</v>
+        <v>7038976</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10843,11 +10843,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10874,10 +10869,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129298858</v>
+        <v>129298782</v>
       </c>
       <c r="B103" t="n">
-        <v>83004</v>
+        <v>57727</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10885,21 +10880,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10909,10 +10904,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>487408</v>
+        <v>486857</v>
       </c>
       <c r="R103" t="n">
-        <v>7038959</v>
+        <v>7039276</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10945,6 +10940,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10971,7 +10971,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129298782</v>
+        <v>129298788</v>
       </c>
       <c r="B104" t="n">
         <v>57727</v>
@@ -11006,10 +11006,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>486857</v>
+        <v>487039</v>
       </c>
       <c r="R104" t="n">
-        <v>7039276</v>
+        <v>7039164</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11046,7 +11046,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11073,7 +11073,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129298788</v>
+        <v>129298806</v>
       </c>
       <c r="B105" t="n">
         <v>57727</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>487039</v>
+        <v>487339</v>
       </c>
       <c r="R105" t="n">
-        <v>7039164</v>
+        <v>7039009</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11175,7 +11175,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129298806</v>
+        <v>129298758</v>
       </c>
       <c r="B106" t="n">
         <v>57727</v>
@@ -11210,10 +11210,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>487339</v>
+        <v>487183</v>
       </c>
       <c r="R106" t="n">
-        <v>7039009</v>
+        <v>7038993</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>

--- a/artfynd/A 46357-2025 artfynd.xlsx
+++ b/artfynd/A 46357-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129298851</v>
       </c>
       <c r="B2" t="n">
-        <v>91564</v>
+        <v>91567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129298844</v>
+        <v>129298751</v>
       </c>
       <c r="B3" t="n">
-        <v>78057</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487374</v>
+        <v>487263</v>
       </c>
       <c r="R3" t="n">
-        <v>7039027</v>
+        <v>7038949</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,7 +874,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129298751</v>
+        <v>129298786</v>
       </c>
       <c r="B4" t="n">
         <v>57727</v>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487263</v>
+        <v>487006</v>
       </c>
       <c r="R4" t="n">
-        <v>7038949</v>
+        <v>7039175</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +976,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129298786</v>
+        <v>129298818</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1006,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>487006</v>
+        <v>487389</v>
       </c>
       <c r="R5" t="n">
-        <v>7039175</v>
+        <v>7038925</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,7 +1078,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129298818</v>
+        <v>129298819</v>
       </c>
       <c r="B6" t="n">
         <v>57727</v>
@@ -1108,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>487389</v>
+        <v>487346</v>
       </c>
       <c r="R6" t="n">
-        <v>7038925</v>
+        <v>7038911</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129298819</v>
+        <v>129298827</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>487346</v>
+        <v>487352</v>
       </c>
       <c r="R7" t="n">
-        <v>7038911</v>
+        <v>7038906</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1250,7 +1255,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,10 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129298827</v>
+        <v>129298844</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>78057</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1293,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>228579</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>487352</v>
+        <v>487374</v>
       </c>
       <c r="R8" t="n">
-        <v>7038906</v>
+        <v>7039027</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1348,11 +1353,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1382,7 +1382,7 @@
         <v>129298742</v>
       </c>
       <c r="B9" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129298812</v>
+        <v>129298838</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,21 +1487,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>487362</v>
+        <v>487035</v>
       </c>
       <c r="R10" t="n">
-        <v>7039030</v>
+        <v>7039161</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1547,11 +1547,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,7 +1573,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129298759</v>
+        <v>129298812</v>
       </c>
       <c r="B11" t="n">
         <v>57727</v>
@@ -1613,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>487171</v>
+        <v>487362</v>
       </c>
       <c r="R11" t="n">
-        <v>7039000</v>
+        <v>7039030</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1680,10 +1675,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129298838</v>
+        <v>129298759</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,21 +1686,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1715,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>487035</v>
+        <v>487171</v>
       </c>
       <c r="R12" t="n">
-        <v>7039161</v>
+        <v>7039000</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,6 +1746,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2083,10 +2083,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129298855</v>
+        <v>129298857</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>83004</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2094,21 +2094,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>487542</v>
+        <v>487340</v>
       </c>
       <c r="R16" t="n">
-        <v>7038985</v>
+        <v>7039016</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2180,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129298857</v>
+        <v>129298777</v>
       </c>
       <c r="B17" t="n">
-        <v>83004</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>487340</v>
+        <v>486860</v>
       </c>
       <c r="R17" t="n">
-        <v>7039016</v>
+        <v>7039254</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2251,6 +2251,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2277,7 +2282,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129298777</v>
+        <v>129298787</v>
       </c>
       <c r="B18" t="n">
         <v>57727</v>
@@ -2312,10 +2317,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486860</v>
+        <v>486999</v>
       </c>
       <c r="R18" t="n">
-        <v>7039254</v>
+        <v>7039162</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2352,7 +2357,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2379,10 +2384,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129298787</v>
+        <v>129298855</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2390,21 +2395,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2414,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486999</v>
+        <v>487542</v>
       </c>
       <c r="R19" t="n">
-        <v>7039162</v>
+        <v>7038985</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2450,11 +2455,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2481,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129298740</v>
+        <v>129298837</v>
       </c>
       <c r="B20" t="n">
-        <v>91550</v>
+        <v>80149</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>487145</v>
+        <v>487004</v>
       </c>
       <c r="R20" t="n">
-        <v>7039179</v>
+        <v>7039214</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129298852</v>
+        <v>129298845</v>
       </c>
       <c r="B21" t="n">
-        <v>91564</v>
+        <v>78057</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2589,21 +2589,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1204</v>
+        <v>228579</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>487127</v>
+        <v>487526</v>
       </c>
       <c r="R21" t="n">
-        <v>7039070</v>
+        <v>7039006</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129298775</v>
+        <v>129298740</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,21 +2686,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486860</v>
+        <v>487145</v>
       </c>
       <c r="R22" t="n">
-        <v>7039244</v>
+        <v>7039179</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2746,11 +2746,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2777,10 +2772,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129298808</v>
+        <v>129298852</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>91567</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2788,21 +2783,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2812,10 +2807,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>487344</v>
+        <v>487127</v>
       </c>
       <c r="R23" t="n">
-        <v>7039018</v>
+        <v>7039070</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2848,11 +2843,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2879,27 +2869,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129298830</v>
+        <v>129298775</v>
       </c>
       <c r="B24" t="n">
-        <v>57568</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2907,29 +2897,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>487123</v>
+        <v>486860</v>
       </c>
       <c r="R24" t="n">
-        <v>7039173</v>
+        <v>7039244</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2962,6 +2940,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2988,7 +2971,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129298780</v>
+        <v>129298808</v>
       </c>
       <c r="B25" t="n">
         <v>57727</v>
@@ -3023,10 +3006,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486859</v>
+        <v>487344</v>
       </c>
       <c r="R25" t="n">
-        <v>7039262</v>
+        <v>7039018</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3063,7 +3046,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3090,10 +3073,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129298837</v>
+        <v>129298780</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3101,21 +3084,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3125,10 +3108,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>487004</v>
+        <v>486859</v>
       </c>
       <c r="R26" t="n">
-        <v>7039214</v>
+        <v>7039262</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3161,6 +3144,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3187,45 +3175,57 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129298845</v>
+        <v>129298830</v>
       </c>
       <c r="B27" t="n">
-        <v>78057</v>
+        <v>57568</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228579</v>
+        <v>102621</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>487526</v>
+        <v>487123</v>
       </c>
       <c r="R27" t="n">
-        <v>7039006</v>
+        <v>7039173</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3284,32 +3284,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129298846</v>
+        <v>129298843</v>
       </c>
       <c r="B28" t="n">
-        <v>57831</v>
+        <v>80149</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3319,10 +3319,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>486976</v>
+        <v>487391</v>
       </c>
       <c r="R28" t="n">
-        <v>7039216</v>
+        <v>7038927</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3891,32 +3891,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129298843</v>
+        <v>129298846</v>
       </c>
       <c r="B34" t="n">
-        <v>80149</v>
+        <v>57831</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>487391</v>
+        <v>486976</v>
       </c>
       <c r="R34" t="n">
-        <v>7038927</v>
+        <v>7039216</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3988,7 +3988,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129298769</v>
+        <v>129298792</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>487109</v>
+        <v>487153</v>
       </c>
       <c r="R35" t="n">
-        <v>7039040</v>
+        <v>7039212</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4090,7 +4090,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129298794</v>
+        <v>129298750</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4125,10 +4125,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>487186</v>
+        <v>487272</v>
       </c>
       <c r="R36" t="n">
-        <v>7039192</v>
+        <v>7038946</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4192,7 +4192,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129298792</v>
+        <v>129298769</v>
       </c>
       <c r="B37" t="n">
         <v>57727</v>
@@ -4227,10 +4227,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>487153</v>
+        <v>487109</v>
       </c>
       <c r="R37" t="n">
-        <v>7039212</v>
+        <v>7039040</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129298750</v>
+        <v>129298804</v>
       </c>
       <c r="B38" t="n">
         <v>57727</v>
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>487272</v>
+        <v>487288</v>
       </c>
       <c r="R38" t="n">
-        <v>7038946</v>
+        <v>7039002</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4396,7 +4396,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129298804</v>
+        <v>129298794</v>
       </c>
       <c r="B39" t="n">
         <v>57727</v>
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>487288</v>
+        <v>487186</v>
       </c>
       <c r="R39" t="n">
-        <v>7039002</v>
+        <v>7039192</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4498,10 +4498,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129298833</v>
+        <v>129298854</v>
       </c>
       <c r="B40" t="n">
-        <v>80150</v>
+        <v>91573</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4509,23 +4509,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4533,7 +4529,7 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>487265</v>
+        <v>487522</v>
       </c>
       <c r="R40" t="n">
         <v>7038997</v>
@@ -4595,10 +4591,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129298840</v>
+        <v>129298833</v>
       </c>
       <c r="B41" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4606,21 +4602,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4630,10 +4626,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>487314</v>
+        <v>487265</v>
       </c>
       <c r="R41" t="n">
-        <v>7039005</v>
+        <v>7038997</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4692,7 +4688,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129298795</v>
+        <v>129298805</v>
       </c>
       <c r="B42" t="n">
         <v>57727</v>
@@ -4727,10 +4723,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>487100</v>
+        <v>487346</v>
       </c>
       <c r="R42" t="n">
-        <v>7039085</v>
+        <v>7039012</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4794,7 +4790,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129298748</v>
+        <v>129298809</v>
       </c>
       <c r="B43" t="n">
         <v>57727</v>
@@ -4829,10 +4825,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>487301</v>
+        <v>487348</v>
       </c>
       <c r="R43" t="n">
-        <v>7038925</v>
+        <v>7039005</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4896,7 +4892,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129298783</v>
+        <v>129298802</v>
       </c>
       <c r="B44" t="n">
         <v>57727</v>
@@ -4931,10 +4927,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>487024</v>
+        <v>487302</v>
       </c>
       <c r="R44" t="n">
-        <v>7039203</v>
+        <v>7039045</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4998,10 +4994,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129298854</v>
+        <v>129298795</v>
       </c>
       <c r="B45" t="n">
-        <v>91570</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5009,19 +5005,23 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>487522</v>
+        <v>487100</v>
       </c>
       <c r="R45" t="n">
-        <v>7038997</v>
+        <v>7039085</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5065,6 +5065,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5091,7 +5096,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129298805</v>
+        <v>129298748</v>
       </c>
       <c r="B46" t="n">
         <v>57727</v>
@@ -5126,10 +5131,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>487346</v>
+        <v>487301</v>
       </c>
       <c r="R46" t="n">
-        <v>7039012</v>
+        <v>7038925</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5193,7 +5198,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129298809</v>
+        <v>129298783</v>
       </c>
       <c r="B47" t="n">
         <v>57727</v>
@@ -5228,10 +5233,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>487348</v>
+        <v>487024</v>
       </c>
       <c r="R47" t="n">
-        <v>7039005</v>
+        <v>7039203</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5295,10 +5300,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129298802</v>
+        <v>129298840</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5306,21 +5311,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5330,10 +5335,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>487302</v>
+        <v>487314</v>
       </c>
       <c r="R48" t="n">
-        <v>7039045</v>
+        <v>7039005</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5366,11 +5371,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5400,7 +5400,7 @@
         <v>129298738</v>
       </c>
       <c r="B49" t="n">
-        <v>96970</v>
+        <v>96973</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5591,10 +5591,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129298842</v>
+        <v>129298798</v>
       </c>
       <c r="B51" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5602,21 +5602,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5626,10 +5626,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>487393</v>
+        <v>487131</v>
       </c>
       <c r="R51" t="n">
-        <v>7038908</v>
+        <v>7039049</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5662,6 +5662,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5790,10 +5795,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129298798</v>
+        <v>129298842</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5801,21 +5806,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5825,10 +5830,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>487131</v>
+        <v>487393</v>
       </c>
       <c r="R53" t="n">
-        <v>7039049</v>
+        <v>7038908</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5861,11 +5866,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6198,7 +6198,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129298820</v>
+        <v>129298767</v>
       </c>
       <c r="B57" t="n">
         <v>57727</v>
@@ -6233,10 +6233,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>487354</v>
+        <v>487123</v>
       </c>
       <c r="R57" t="n">
-        <v>7038894</v>
+        <v>7039031</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6300,7 +6300,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129298774</v>
+        <v>129298776</v>
       </c>
       <c r="B58" t="n">
         <v>57727</v>
@@ -6335,10 +6335,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>486866</v>
+        <v>486855</v>
       </c>
       <c r="R58" t="n">
-        <v>7039249</v>
+        <v>7039252</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6402,7 +6402,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129298773</v>
+        <v>129298816</v>
       </c>
       <c r="B59" t="n">
         <v>57727</v>
@@ -6437,10 +6437,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>486807</v>
+        <v>487389</v>
       </c>
       <c r="R59" t="n">
-        <v>7039220</v>
+        <v>7038985</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6504,7 +6504,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129298767</v>
+        <v>129298813</v>
       </c>
       <c r="B60" t="n">
         <v>57727</v>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>487123</v>
+        <v>487367</v>
       </c>
       <c r="R60" t="n">
-        <v>7039031</v>
+        <v>7038998</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6606,7 +6606,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129298776</v>
+        <v>129298820</v>
       </c>
       <c r="B61" t="n">
         <v>57727</v>
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>486855</v>
+        <v>487354</v>
       </c>
       <c r="R61" t="n">
-        <v>7039252</v>
+        <v>7038894</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6681,7 +6681,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6708,7 +6708,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129298816</v>
+        <v>129298774</v>
       </c>
       <c r="B62" t="n">
         <v>57727</v>
@@ -6743,10 +6743,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>487389</v>
+        <v>486866</v>
       </c>
       <c r="R62" t="n">
-        <v>7038985</v>
+        <v>7039249</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6783,7 +6783,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6810,7 +6810,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129298813</v>
+        <v>129298773</v>
       </c>
       <c r="B63" t="n">
         <v>57727</v>
@@ -6845,10 +6845,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>487367</v>
+        <v>486807</v>
       </c>
       <c r="R63" t="n">
-        <v>7038998</v>
+        <v>7039220</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6885,7 +6885,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7014,10 +7014,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129298853</v>
+        <v>129298811</v>
       </c>
       <c r="B65" t="n">
-        <v>91570</v>
+        <v>57727</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7025,19 +7025,23 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7045,10 +7049,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>487415</v>
+        <v>487357</v>
       </c>
       <c r="R65" t="n">
-        <v>7038971</v>
+        <v>7039009</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7081,6 +7085,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7110,7 +7119,7 @@
         <v>129298741</v>
       </c>
       <c r="B66" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7204,10 +7213,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129298811</v>
+        <v>129298853</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7215,23 +7224,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7239,10 +7244,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>487357</v>
+        <v>487415</v>
       </c>
       <c r="R67" t="n">
-        <v>7039009</v>
+        <v>7038971</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7275,11 +7280,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7306,32 +7306,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129298831</v>
+        <v>129298737</v>
       </c>
       <c r="B68" t="n">
-        <v>83003</v>
+        <v>83012</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>492</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7341,10 +7341,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>487307</v>
+        <v>487523</v>
       </c>
       <c r="R68" t="n">
-        <v>7039016</v>
+        <v>7039001</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7403,10 +7403,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129298737</v>
+        <v>129298839</v>
       </c>
       <c r="B69" t="n">
-        <v>83012</v>
+        <v>80149</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7414,21 +7414,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7438,7 +7438,7 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>487523</v>
+        <v>487269</v>
       </c>
       <c r="R69" t="n">
         <v>7039001</v>
@@ -7500,32 +7500,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129298797</v>
+        <v>129298831</v>
       </c>
       <c r="B70" t="n">
-        <v>57727</v>
+        <v>83003</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7535,10 +7535,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>487134</v>
+        <v>487307</v>
       </c>
       <c r="R70" t="n">
-        <v>7039037</v>
+        <v>7039016</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7571,11 +7571,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7602,32 +7597,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129298803</v>
+        <v>129298828</v>
       </c>
       <c r="B71" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7637,10 +7632,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>487303</v>
+        <v>487269</v>
       </c>
       <c r="R71" t="n">
-        <v>7039037</v>
+        <v>7039004</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7673,11 +7668,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7704,7 +7694,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129298822</v>
+        <v>129298797</v>
       </c>
       <c r="B72" t="n">
         <v>57727</v>
@@ -7739,10 +7729,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>487373</v>
+        <v>487134</v>
       </c>
       <c r="R72" t="n">
-        <v>7038897</v>
+        <v>7039037</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7806,7 +7796,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129298817</v>
+        <v>129298803</v>
       </c>
       <c r="B73" t="n">
         <v>57727</v>
@@ -7841,10 +7831,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>487460</v>
+        <v>487303</v>
       </c>
       <c r="R73" t="n">
-        <v>7038984</v>
+        <v>7039037</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7908,7 +7898,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129298800</v>
+        <v>129298822</v>
       </c>
       <c r="B74" t="n">
         <v>57727</v>
@@ -7936,33 +7926,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>487288</v>
+        <v>487373</v>
       </c>
       <c r="R74" t="n">
-        <v>7039015</v>
+        <v>7038897</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7999,7 +7973,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Födosökande hane</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8026,7 +8000,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129298821</v>
+        <v>129298817</v>
       </c>
       <c r="B75" t="n">
         <v>57727</v>
@@ -8061,10 +8035,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>487368</v>
+        <v>487460</v>
       </c>
       <c r="R75" t="n">
-        <v>7038892</v>
+        <v>7038984</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8128,45 +8102,61 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129298828</v>
+        <v>129298800</v>
       </c>
       <c r="B76" t="n">
-        <v>80178</v>
+        <v>57727</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>487269</v>
+        <v>487288</v>
       </c>
       <c r="R76" t="n">
-        <v>7039004</v>
+        <v>7039015</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8199,6 +8189,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Födosökande hane</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8225,10 +8220,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129298839</v>
+        <v>129298821</v>
       </c>
       <c r="B77" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8236,21 +8231,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8260,10 +8255,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>487269</v>
+        <v>487368</v>
       </c>
       <c r="R77" t="n">
-        <v>7039001</v>
+        <v>7038892</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8296,6 +8291,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8322,7 +8322,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129298784</v>
+        <v>129298781</v>
       </c>
       <c r="B78" t="n">
         <v>57727</v>
@@ -8357,10 +8357,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>487011</v>
+        <v>486864</v>
       </c>
       <c r="R78" t="n">
-        <v>7039207</v>
+        <v>7039272</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8424,7 +8424,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129298781</v>
+        <v>129298785</v>
       </c>
       <c r="B79" t="n">
         <v>57727</v>
@@ -8459,10 +8459,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>486864</v>
+        <v>487007</v>
       </c>
       <c r="R79" t="n">
-        <v>7039272</v>
+        <v>7039210</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8628,7 +8628,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129298785</v>
+        <v>129298757</v>
       </c>
       <c r="B81" t="n">
         <v>57727</v>
@@ -8663,10 +8663,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>487007</v>
+        <v>487188</v>
       </c>
       <c r="R81" t="n">
-        <v>7039210</v>
+        <v>7038992</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8703,7 +8703,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8730,7 +8730,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129298757</v>
+        <v>129298784</v>
       </c>
       <c r="B82" t="n">
         <v>57727</v>
@@ -8765,10 +8765,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>487188</v>
+        <v>487011</v>
       </c>
       <c r="R82" t="n">
-        <v>7038992</v>
+        <v>7039207</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9662,7 +9662,7 @@
         <v>129298743</v>
       </c>
       <c r="B91" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10057,32 +10057,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129298745</v>
+        <v>129298739</v>
       </c>
       <c r="B95" t="n">
-        <v>57727</v>
+        <v>91517</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10092,10 +10092,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>486881</v>
+        <v>487384</v>
       </c>
       <c r="R95" t="n">
-        <v>7039175</v>
+        <v>7038973</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10128,11 +10128,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10159,7 +10154,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129298791</v>
+        <v>129298745</v>
       </c>
       <c r="B96" t="n">
         <v>57727</v>
@@ -10194,10 +10189,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>487112</v>
+        <v>486881</v>
       </c>
       <c r="R96" t="n">
-        <v>7039182</v>
+        <v>7039175</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10363,32 +10358,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129298739</v>
+        <v>129298791</v>
       </c>
       <c r="B98" t="n">
-        <v>91514</v>
+        <v>57727</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10398,10 +10393,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>487384</v>
+        <v>487112</v>
       </c>
       <c r="R98" t="n">
-        <v>7038973</v>
+        <v>7039182</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10434,6 +10429,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10460,10 +10460,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129298807</v>
+        <v>129298829</v>
       </c>
       <c r="B99" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10471,16 +10471,16 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -10488,17 +10488,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>487337</v>
+        <v>487157</v>
       </c>
       <c r="R99" t="n">
-        <v>7039015</v>
+        <v>7039100</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10531,11 +10547,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10562,10 +10573,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129298829</v>
+        <v>129298807</v>
       </c>
       <c r="B100" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10573,16 +10584,16 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -10590,33 +10601,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>487157</v>
+        <v>487337</v>
       </c>
       <c r="R100" t="n">
-        <v>7039100</v>
+        <v>7039015</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10649,6 +10644,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10675,32 +10675,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129298858</v>
+        <v>129298832</v>
       </c>
       <c r="B101" t="n">
-        <v>83004</v>
+        <v>83003</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>308</v>
+        <v>492</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10710,10 +10710,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>487408</v>
+        <v>487393</v>
       </c>
       <c r="R101" t="n">
-        <v>7038959</v>
+        <v>7038976</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10772,32 +10772,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129298832</v>
+        <v>129298858</v>
       </c>
       <c r="B102" t="n">
-        <v>83003</v>
+        <v>83004</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>492</v>
+        <v>308</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10807,10 +10807,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>487393</v>
+        <v>487408</v>
       </c>
       <c r="R102" t="n">
-        <v>7038976</v>
+        <v>7038959</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10869,7 +10869,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129298782</v>
+        <v>129298806</v>
       </c>
       <c r="B103" t="n">
         <v>57727</v>
@@ -10904,10 +10904,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>486857</v>
+        <v>487339</v>
       </c>
       <c r="R103" t="n">
-        <v>7039276</v>
+        <v>7039009</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10944,7 +10944,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10971,7 +10971,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129298788</v>
+        <v>129298782</v>
       </c>
       <c r="B104" t="n">
         <v>57727</v>
@@ -11006,10 +11006,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>487039</v>
+        <v>486857</v>
       </c>
       <c r="R104" t="n">
-        <v>7039164</v>
+        <v>7039276</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11046,7 +11046,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11073,7 +11073,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129298806</v>
+        <v>129298758</v>
       </c>
       <c r="B105" t="n">
         <v>57727</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>487339</v>
+        <v>487183</v>
       </c>
       <c r="R105" t="n">
-        <v>7039009</v>
+        <v>7038993</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11175,7 +11175,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129298758</v>
+        <v>129298815</v>
       </c>
       <c r="B106" t="n">
         <v>57727</v>
@@ -11210,10 +11210,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>487183</v>
+        <v>487375</v>
       </c>
       <c r="R106" t="n">
-        <v>7038993</v>
+        <v>7038981</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11277,7 +11277,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129298815</v>
+        <v>129298788</v>
       </c>
       <c r="B107" t="n">
         <v>57727</v>
@@ -11312,10 +11312,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>487375</v>
+        <v>487039</v>
       </c>
       <c r="R107" t="n">
-        <v>7038981</v>
+        <v>7039164</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>

--- a/artfynd/A 46357-2025 artfynd.xlsx
+++ b/artfynd/A 46357-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129298851</v>
+        <v>129298827</v>
       </c>
       <c r="B2" t="n">
-        <v>91567</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487144</v>
+        <v>487352</v>
       </c>
       <c r="R2" t="n">
-        <v>7039078</v>
+        <v>7038906</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129298751</v>
+        <v>129298844</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>78057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487263</v>
+        <v>487374</v>
       </c>
       <c r="R3" t="n">
-        <v>7038949</v>
+        <v>7039027</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,7 +874,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129298786</v>
+        <v>129298751</v>
       </c>
       <c r="B4" t="n">
         <v>57727</v>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487006</v>
+        <v>487263</v>
       </c>
       <c r="R4" t="n">
-        <v>7039175</v>
+        <v>7038949</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,7 +976,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129298818</v>
+        <v>129298786</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>487389</v>
+        <v>487006</v>
       </c>
       <c r="R5" t="n">
-        <v>7038925</v>
+        <v>7039175</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129298819</v>
+        <v>129298851</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>91567</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>487346</v>
+        <v>487144</v>
       </c>
       <c r="R6" t="n">
-        <v>7038911</v>
+        <v>7039078</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,11 +1149,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129298827</v>
+        <v>129298818</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>487352</v>
+        <v>487389</v>
       </c>
       <c r="R7" t="n">
-        <v>7038906</v>
+        <v>7038925</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,7 +1250,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1282,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129298844</v>
+        <v>129298819</v>
       </c>
       <c r="B8" t="n">
-        <v>78057</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1293,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1317,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>487374</v>
+        <v>487346</v>
       </c>
       <c r="R8" t="n">
-        <v>7039027</v>
+        <v>7038911</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1353,6 +1348,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129298742</v>
+        <v>129298838</v>
       </c>
       <c r="B9" t="n">
-        <v>91553</v>
+        <v>80149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1390,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>487129</v>
+        <v>487035</v>
       </c>
       <c r="R9" t="n">
-        <v>7039097</v>
+        <v>7039161</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129298838</v>
+        <v>129298812</v>
       </c>
       <c r="B10" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,21 +1487,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>487035</v>
+        <v>487362</v>
       </c>
       <c r="R10" t="n">
-        <v>7039161</v>
+        <v>7039030</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1547,6 +1547,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1573,7 +1578,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129298812</v>
+        <v>129298759</v>
       </c>
       <c r="B11" t="n">
         <v>57727</v>
@@ -1608,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>487362</v>
+        <v>487171</v>
       </c>
       <c r="R11" t="n">
-        <v>7039030</v>
+        <v>7039000</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1675,10 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129298759</v>
+        <v>129298742</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1686,21 +1691,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1710,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>487171</v>
+        <v>487129</v>
       </c>
       <c r="R12" t="n">
-        <v>7039000</v>
+        <v>7039097</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1746,11 +1751,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2180,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129298777</v>
+        <v>129298855</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486860</v>
+        <v>487542</v>
       </c>
       <c r="R17" t="n">
-        <v>7039254</v>
+        <v>7038985</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2251,11 +2251,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2282,7 +2277,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129298787</v>
+        <v>129298777</v>
       </c>
       <c r="B18" t="n">
         <v>57727</v>
@@ -2317,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486999</v>
+        <v>486860</v>
       </c>
       <c r="R18" t="n">
-        <v>7039162</v>
+        <v>7039254</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2357,7 +2352,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2384,10 +2379,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129298855</v>
+        <v>129298787</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2395,21 +2390,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2419,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>487542</v>
+        <v>486999</v>
       </c>
       <c r="R19" t="n">
-        <v>7038985</v>
+        <v>7039162</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2455,6 +2450,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2481,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129298837</v>
+        <v>129298775</v>
       </c>
       <c r="B20" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>487004</v>
+        <v>486860</v>
       </c>
       <c r="R20" t="n">
-        <v>7039214</v>
+        <v>7039244</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2552,6 +2552,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2578,10 +2583,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129298845</v>
+        <v>129298808</v>
       </c>
       <c r="B21" t="n">
-        <v>78057</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2589,21 +2594,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2618,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>487526</v>
+        <v>487344</v>
       </c>
       <c r="R21" t="n">
-        <v>7039006</v>
+        <v>7039018</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2649,6 +2654,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2675,10 +2685,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129298740</v>
+        <v>129298780</v>
       </c>
       <c r="B22" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,21 +2696,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2710,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>487145</v>
+        <v>486859</v>
       </c>
       <c r="R22" t="n">
-        <v>7039179</v>
+        <v>7039262</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2746,6 +2756,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2772,10 +2787,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129298852</v>
+        <v>129298740</v>
       </c>
       <c r="B23" t="n">
-        <v>91567</v>
+        <v>91553</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2783,21 +2798,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2807,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>487127</v>
+        <v>487145</v>
       </c>
       <c r="R23" t="n">
-        <v>7039070</v>
+        <v>7039179</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2869,10 +2884,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129298775</v>
+        <v>129298852</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>91567</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2880,21 +2895,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2904,10 +2919,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486860</v>
+        <v>487127</v>
       </c>
       <c r="R24" t="n">
-        <v>7039244</v>
+        <v>7039070</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2940,11 +2955,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2971,27 +2981,27 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129298808</v>
+        <v>129298830</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>57568</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2999,17 +3009,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>487344</v>
+        <v>487123</v>
       </c>
       <c r="R25" t="n">
-        <v>7039018</v>
+        <v>7039173</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3042,11 +3064,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3073,10 +3090,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129298780</v>
+        <v>129298837</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3084,21 +3101,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3108,10 +3125,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486859</v>
+        <v>487004</v>
       </c>
       <c r="R26" t="n">
-        <v>7039262</v>
+        <v>7039214</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3144,11 +3161,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3175,57 +3187,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129298830</v>
+        <v>129298845</v>
       </c>
       <c r="B27" t="n">
-        <v>57568</v>
+        <v>78057</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102621</v>
+        <v>228579</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>487123</v>
+        <v>487526</v>
       </c>
       <c r="R27" t="n">
-        <v>7039173</v>
+        <v>7039006</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3284,10 +3284,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129298843</v>
+        <v>129298793</v>
       </c>
       <c r="B28" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3295,21 +3295,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3319,10 +3319,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>487391</v>
+        <v>487183</v>
       </c>
       <c r="R28" t="n">
-        <v>7038927</v>
+        <v>7039216</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3355,6 +3355,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3381,7 +3386,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129298793</v>
+        <v>129298823</v>
       </c>
       <c r="B29" t="n">
         <v>57727</v>
@@ -3416,10 +3421,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>487183</v>
+        <v>487363</v>
       </c>
       <c r="R29" t="n">
-        <v>7039216</v>
+        <v>7038902</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3483,7 +3488,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129298823</v>
+        <v>129298770</v>
       </c>
       <c r="B30" t="n">
         <v>57727</v>
@@ -3518,10 +3523,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>487363</v>
+        <v>486972</v>
       </c>
       <c r="R30" t="n">
-        <v>7038902</v>
+        <v>7039122</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3585,7 +3590,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129298765</v>
+        <v>129298778</v>
       </c>
       <c r="B31" t="n">
         <v>57727</v>
@@ -3620,10 +3625,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>487122</v>
+        <v>486871</v>
       </c>
       <c r="R31" t="n">
-        <v>7039034</v>
+        <v>7039260</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3687,7 +3692,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129298770</v>
+        <v>129298765</v>
       </c>
       <c r="B32" t="n">
         <v>57727</v>
@@ -3722,10 +3727,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486972</v>
+        <v>487122</v>
       </c>
       <c r="R32" t="n">
-        <v>7039122</v>
+        <v>7039034</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3789,10 +3794,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129298778</v>
+        <v>129298843</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3800,21 +3805,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3824,10 +3829,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486871</v>
+        <v>487391</v>
       </c>
       <c r="R33" t="n">
-        <v>7039260</v>
+        <v>7038927</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3860,11 +3865,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4498,10 +4498,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129298854</v>
+        <v>129298833</v>
       </c>
       <c r="B40" t="n">
-        <v>91573</v>
+        <v>80150</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4509,19 +4509,23 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4529,7 +4533,7 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>487522</v>
+        <v>487265</v>
       </c>
       <c r="R40" t="n">
         <v>7038997</v>
@@ -4591,10 +4595,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129298833</v>
+        <v>129298854</v>
       </c>
       <c r="B41" t="n">
-        <v>80150</v>
+        <v>91573</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4602,23 +4606,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>487265</v>
+        <v>487522</v>
       </c>
       <c r="R41" t="n">
         <v>7038997</v>
@@ -4688,7 +4688,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129298805</v>
+        <v>129298748</v>
       </c>
       <c r="B42" t="n">
         <v>57727</v>
@@ -4723,10 +4723,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>487346</v>
+        <v>487301</v>
       </c>
       <c r="R42" t="n">
-        <v>7039012</v>
+        <v>7038925</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4790,7 +4790,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129298809</v>
+        <v>129298783</v>
       </c>
       <c r="B43" t="n">
         <v>57727</v>
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>487348</v>
+        <v>487024</v>
       </c>
       <c r="R43" t="n">
-        <v>7039005</v>
+        <v>7039203</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4892,10 +4892,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129298802</v>
+        <v>129298840</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4903,21 +4903,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4927,10 +4927,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>487302</v>
+        <v>487314</v>
       </c>
       <c r="R44" t="n">
-        <v>7039045</v>
+        <v>7039005</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4963,11 +4963,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4994,7 +4989,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129298795</v>
+        <v>129298805</v>
       </c>
       <c r="B45" t="n">
         <v>57727</v>
@@ -5029,10 +5024,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>487100</v>
+        <v>487346</v>
       </c>
       <c r="R45" t="n">
-        <v>7039085</v>
+        <v>7039012</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5096,7 +5091,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129298748</v>
+        <v>129298809</v>
       </c>
       <c r="B46" t="n">
         <v>57727</v>
@@ -5131,10 +5126,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>487301</v>
+        <v>487348</v>
       </c>
       <c r="R46" t="n">
-        <v>7038925</v>
+        <v>7039005</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5198,7 +5193,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129298783</v>
+        <v>129298802</v>
       </c>
       <c r="B47" t="n">
         <v>57727</v>
@@ -5233,10 +5228,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>487024</v>
+        <v>487302</v>
       </c>
       <c r="R47" t="n">
-        <v>7039203</v>
+        <v>7039045</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5300,10 +5295,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129298840</v>
+        <v>129298795</v>
       </c>
       <c r="B48" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5311,21 +5306,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5335,10 +5330,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>487314</v>
+        <v>487100</v>
       </c>
       <c r="R48" t="n">
-        <v>7039005</v>
+        <v>7039085</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5371,6 +5366,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5494,10 +5494,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129298856</v>
+        <v>129298798</v>
       </c>
       <c r="B50" t="n">
-        <v>82878</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5505,21 +5505,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5529,10 +5529,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>487541</v>
+        <v>487131</v>
       </c>
       <c r="R50" t="n">
-        <v>7038983</v>
+        <v>7039049</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5565,6 +5565,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5591,10 +5596,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129298798</v>
+        <v>129298856</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>82878</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5602,21 +5607,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5626,10 +5631,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>487131</v>
+        <v>487541</v>
       </c>
       <c r="R51" t="n">
-        <v>7039049</v>
+        <v>7038983</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5662,11 +5667,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5693,10 +5693,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129298810</v>
+        <v>129298842</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5704,21 +5704,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5728,10 +5728,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>487355</v>
+        <v>487393</v>
       </c>
       <c r="R52" t="n">
-        <v>7039005</v>
+        <v>7038908</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5764,11 +5764,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5795,10 +5790,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129298842</v>
+        <v>129298810</v>
       </c>
       <c r="B53" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5806,21 +5801,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5830,10 +5825,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>487393</v>
+        <v>487355</v>
       </c>
       <c r="R53" t="n">
-        <v>7038908</v>
+        <v>7039005</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5866,6 +5861,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5892,10 +5892,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129298779</v>
+        <v>129298825</v>
       </c>
       <c r="B54" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5903,21 +5903,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5927,10 +5927,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486866</v>
+        <v>487247</v>
       </c>
       <c r="R54" t="n">
-        <v>7039259</v>
+        <v>7039020</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5994,7 +5994,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129298749</v>
+        <v>129298779</v>
       </c>
       <c r="B55" t="n">
         <v>57727</v>
@@ -6029,10 +6029,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>487275</v>
+        <v>486866</v>
       </c>
       <c r="R55" t="n">
-        <v>7038947</v>
+        <v>7039259</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6096,10 +6096,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129298825</v>
+        <v>129298749</v>
       </c>
       <c r="B56" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6107,21 +6107,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6131,10 +6131,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>487247</v>
+        <v>487275</v>
       </c>
       <c r="R56" t="n">
-        <v>7039020</v>
+        <v>7038947</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6198,7 +6198,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129298767</v>
+        <v>129298776</v>
       </c>
       <c r="B57" t="n">
         <v>57727</v>
@@ -6233,10 +6233,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>487123</v>
+        <v>486855</v>
       </c>
       <c r="R57" t="n">
-        <v>7039031</v>
+        <v>7039252</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6300,7 +6300,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129298776</v>
+        <v>129298820</v>
       </c>
       <c r="B58" t="n">
         <v>57727</v>
@@ -6335,10 +6335,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>486855</v>
+        <v>487354</v>
       </c>
       <c r="R58" t="n">
-        <v>7039252</v>
+        <v>7038894</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6402,7 +6402,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129298816</v>
+        <v>129298773</v>
       </c>
       <c r="B59" t="n">
         <v>57727</v>
@@ -6437,10 +6437,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>487389</v>
+        <v>486807</v>
       </c>
       <c r="R59" t="n">
-        <v>7038985</v>
+        <v>7039220</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6504,7 +6504,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129298813</v>
+        <v>129298767</v>
       </c>
       <c r="B60" t="n">
         <v>57727</v>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>487367</v>
+        <v>487123</v>
       </c>
       <c r="R60" t="n">
-        <v>7038998</v>
+        <v>7039031</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6606,7 +6606,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129298820</v>
+        <v>129298816</v>
       </c>
       <c r="B61" t="n">
         <v>57727</v>
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>487354</v>
+        <v>487389</v>
       </c>
       <c r="R61" t="n">
-        <v>7038894</v>
+        <v>7038985</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6708,7 +6708,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129298774</v>
+        <v>129298813</v>
       </c>
       <c r="B62" t="n">
         <v>57727</v>
@@ -6743,10 +6743,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>486866</v>
+        <v>487367</v>
       </c>
       <c r="R62" t="n">
-        <v>7039249</v>
+        <v>7038998</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6783,7 +6783,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6810,7 +6810,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129298773</v>
+        <v>129298774</v>
       </c>
       <c r="B63" t="n">
         <v>57727</v>
@@ -6845,10 +6845,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>486807</v>
+        <v>486866</v>
       </c>
       <c r="R63" t="n">
-        <v>7039220</v>
+        <v>7039249</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7014,10 +7014,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129298811</v>
+        <v>129298853</v>
       </c>
       <c r="B65" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7025,23 +7025,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7049,10 +7045,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>487357</v>
+        <v>487415</v>
       </c>
       <c r="R65" t="n">
-        <v>7039009</v>
+        <v>7038971</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7085,11 +7081,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7213,10 +7204,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129298853</v>
+        <v>129298811</v>
       </c>
       <c r="B67" t="n">
-        <v>91573</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7224,19 +7215,23 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7244,10 +7239,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>487415</v>
+        <v>487357</v>
       </c>
       <c r="R67" t="n">
-        <v>7038971</v>
+        <v>7039009</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7280,6 +7275,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7306,10 +7306,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129298737</v>
+        <v>129298797</v>
       </c>
       <c r="B68" t="n">
-        <v>83012</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7317,21 +7317,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7341,10 +7341,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>487523</v>
+        <v>487134</v>
       </c>
       <c r="R68" t="n">
-        <v>7039001</v>
+        <v>7039037</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7377,6 +7377,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7403,10 +7408,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129298839</v>
+        <v>129298800</v>
       </c>
       <c r="B69" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7414,34 +7419,50 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>487269</v>
+        <v>487288</v>
       </c>
       <c r="R69" t="n">
-        <v>7039001</v>
+        <v>7039015</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7474,6 +7495,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Födosökande hane</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7500,32 +7526,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129298831</v>
+        <v>129298821</v>
       </c>
       <c r="B70" t="n">
-        <v>83003</v>
+        <v>57727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7535,10 +7561,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>487307</v>
+        <v>487368</v>
       </c>
       <c r="R70" t="n">
-        <v>7039016</v>
+        <v>7038892</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7571,6 +7597,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7597,32 +7628,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129298828</v>
+        <v>129298803</v>
       </c>
       <c r="B71" t="n">
-        <v>80178</v>
+        <v>57727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7632,10 +7663,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>487269</v>
+        <v>487303</v>
       </c>
       <c r="R71" t="n">
-        <v>7039004</v>
+        <v>7039037</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7668,6 +7699,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7694,7 +7730,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129298797</v>
+        <v>129298817</v>
       </c>
       <c r="B72" t="n">
         <v>57727</v>
@@ -7729,10 +7765,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>487134</v>
+        <v>487460</v>
       </c>
       <c r="R72" t="n">
-        <v>7039037</v>
+        <v>7038984</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7796,32 +7832,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129298803</v>
+        <v>129298831</v>
       </c>
       <c r="B73" t="n">
-        <v>57727</v>
+        <v>83003</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7831,10 +7867,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>487303</v>
+        <v>487307</v>
       </c>
       <c r="R73" t="n">
-        <v>7039037</v>
+        <v>7039016</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7867,11 +7903,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7898,10 +7929,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129298822</v>
+        <v>129298737</v>
       </c>
       <c r="B74" t="n">
-        <v>57727</v>
+        <v>83012</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7909,21 +7940,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7933,10 +7964,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>487373</v>
+        <v>487523</v>
       </c>
       <c r="R74" t="n">
-        <v>7038897</v>
+        <v>7039001</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7969,11 +8000,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8000,32 +8026,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129298817</v>
+        <v>129298828</v>
       </c>
       <c r="B75" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8035,10 +8061,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>487460</v>
+        <v>487269</v>
       </c>
       <c r="R75" t="n">
-        <v>7038984</v>
+        <v>7039004</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8071,11 +8097,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8102,10 +8123,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129298800</v>
+        <v>129298839</v>
       </c>
       <c r="B76" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8113,50 +8134,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>487288</v>
+        <v>487269</v>
       </c>
       <c r="R76" t="n">
-        <v>7039015</v>
+        <v>7039001</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8189,11 +8194,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Födosökande hane</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8220,7 +8220,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129298821</v>
+        <v>129298822</v>
       </c>
       <c r="B77" t="n">
         <v>57727</v>
@@ -8255,10 +8255,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>487368</v>
+        <v>487373</v>
       </c>
       <c r="R77" t="n">
-        <v>7038892</v>
+        <v>7038897</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8322,7 +8322,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129298781</v>
+        <v>129298785</v>
       </c>
       <c r="B78" t="n">
         <v>57727</v>
@@ -8357,10 +8357,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>486864</v>
+        <v>487007</v>
       </c>
       <c r="R78" t="n">
-        <v>7039272</v>
+        <v>7039210</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8397,7 +8397,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8424,7 +8424,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129298785</v>
+        <v>129298757</v>
       </c>
       <c r="B79" t="n">
         <v>57727</v>
@@ -8459,10 +8459,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>487007</v>
+        <v>487188</v>
       </c>
       <c r="R79" t="n">
-        <v>7039210</v>
+        <v>7038992</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8526,7 +8526,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129298753</v>
+        <v>129298784</v>
       </c>
       <c r="B80" t="n">
         <v>57727</v>
@@ -8561,10 +8561,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>487240</v>
+        <v>487011</v>
       </c>
       <c r="R80" t="n">
-        <v>7038959</v>
+        <v>7039207</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8628,7 +8628,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129298757</v>
+        <v>129298781</v>
       </c>
       <c r="B81" t="n">
         <v>57727</v>
@@ -8663,10 +8663,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>487188</v>
+        <v>486864</v>
       </c>
       <c r="R81" t="n">
-        <v>7038992</v>
+        <v>7039272</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8730,7 +8730,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129298784</v>
+        <v>129298753</v>
       </c>
       <c r="B82" t="n">
         <v>57727</v>
@@ -8765,10 +8765,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>487011</v>
+        <v>487240</v>
       </c>
       <c r="R82" t="n">
-        <v>7039207</v>
+        <v>7038959</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8832,10 +8832,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129298841</v>
+        <v>129298771</v>
       </c>
       <c r="B83" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8843,21 +8843,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8867,10 +8867,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>487515</v>
+        <v>486885</v>
       </c>
       <c r="R83" t="n">
-        <v>7038993</v>
+        <v>7039172</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8903,6 +8903,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8929,7 +8934,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129298771</v>
+        <v>129298801</v>
       </c>
       <c r="B84" t="n">
         <v>57727</v>
@@ -8964,10 +8969,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>486885</v>
+        <v>487268</v>
       </c>
       <c r="R84" t="n">
-        <v>7039172</v>
+        <v>7039003</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9031,61 +9036,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129298847</v>
+        <v>129298789</v>
       </c>
       <c r="B85" t="n">
-        <v>57587</v>
+        <v>57727</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100136</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>486999</v>
+        <v>487041</v>
       </c>
       <c r="R85" t="n">
-        <v>7039199</v>
+        <v>7039167</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9122,7 +9111,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Jagades av en nötskrika</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9149,7 +9138,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129298789</v>
+        <v>129298814</v>
       </c>
       <c r="B86" t="n">
         <v>57727</v>
@@ -9184,10 +9173,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>487041</v>
+        <v>487366</v>
       </c>
       <c r="R86" t="n">
-        <v>7039167</v>
+        <v>7038997</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9224,7 +9213,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9251,7 +9240,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129298801</v>
+        <v>129298772</v>
       </c>
       <c r="B87" t="n">
         <v>57727</v>
@@ -9286,10 +9275,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>487268</v>
+        <v>486849</v>
       </c>
       <c r="R87" t="n">
-        <v>7039003</v>
+        <v>7039185</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9353,7 +9342,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129298814</v>
+        <v>129298746</v>
       </c>
       <c r="B88" t="n">
         <v>57727</v>
@@ -9388,10 +9377,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>487366</v>
+        <v>487316</v>
       </c>
       <c r="R88" t="n">
-        <v>7038997</v>
+        <v>7038914</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9428,7 +9417,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9455,10 +9444,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129298772</v>
+        <v>129298841</v>
       </c>
       <c r="B89" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9466,21 +9455,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9490,10 +9479,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>486849</v>
+        <v>487515</v>
       </c>
       <c r="R89" t="n">
-        <v>7039185</v>
+        <v>7038993</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9526,11 +9515,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9557,45 +9541,61 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129298746</v>
+        <v>129298847</v>
       </c>
       <c r="B90" t="n">
-        <v>57727</v>
+        <v>57587</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>100136</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>487316</v>
+        <v>486999</v>
       </c>
       <c r="R90" t="n">
-        <v>7038914</v>
+        <v>7039199</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9632,7 +9632,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Jagades av en nötskrika</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9853,7 +9853,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129298752</v>
+        <v>129298768</v>
       </c>
       <c r="B93" t="n">
         <v>57727</v>
@@ -9888,10 +9888,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>487246</v>
+        <v>487123</v>
       </c>
       <c r="R93" t="n">
-        <v>7038958</v>
+        <v>7039032</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9955,7 +9955,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129298768</v>
+        <v>129298752</v>
       </c>
       <c r="B94" t="n">
         <v>57727</v>
@@ -9990,10 +9990,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>487123</v>
+        <v>487246</v>
       </c>
       <c r="R94" t="n">
-        <v>7039032</v>
+        <v>7038958</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10256,7 +10256,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129298754</v>
+        <v>129298791</v>
       </c>
       <c r="B97" t="n">
         <v>57727</v>
@@ -10291,10 +10291,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>487222</v>
+        <v>487112</v>
       </c>
       <c r="R97" t="n">
-        <v>7038974</v>
+        <v>7039182</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10331,7 +10331,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10358,7 +10358,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129298791</v>
+        <v>129298754</v>
       </c>
       <c r="B98" t="n">
         <v>57727</v>
@@ -10393,10 +10393,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>487112</v>
+        <v>487222</v>
       </c>
       <c r="R98" t="n">
-        <v>7039182</v>
+        <v>7038974</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10433,7 +10433,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11379,7 +11379,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129298766</v>
+        <v>129298760</v>
       </c>
       <c r="B108" t="n">
         <v>57727</v>
@@ -11414,10 +11414,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>487124</v>
+        <v>487141</v>
       </c>
       <c r="R108" t="n">
-        <v>7039030</v>
+        <v>7039023</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11454,7 +11454,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11481,7 +11481,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129298796</v>
+        <v>129298766</v>
       </c>
       <c r="B109" t="n">
         <v>57727</v>
@@ -11516,10 +11516,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>487139</v>
+        <v>487124</v>
       </c>
       <c r="R109" t="n">
-        <v>7039088</v>
+        <v>7039030</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11583,7 +11583,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129298760</v>
+        <v>129298796</v>
       </c>
       <c r="B110" t="n">
         <v>57727</v>
@@ -11618,10 +11618,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>487141</v>
+        <v>487139</v>
       </c>
       <c r="R110" t="n">
-        <v>7039023</v>
+        <v>7039088</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11658,7 +11658,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 46357-2025 artfynd.xlsx
+++ b/artfynd/A 46357-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129298844</v>
+        <v>129298851</v>
       </c>
       <c r="B3" t="n">
-        <v>78057</v>
+        <v>91567</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228579</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487374</v>
+        <v>487144</v>
       </c>
       <c r="R3" t="n">
-        <v>7039027</v>
+        <v>7039078</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,7 +874,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129298751</v>
+        <v>129298818</v>
       </c>
       <c r="B4" t="n">
         <v>57727</v>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487263</v>
+        <v>487389</v>
       </c>
       <c r="R4" t="n">
-        <v>7038949</v>
+        <v>7038925</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,7 +976,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129298786</v>
+        <v>129298819</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>487006</v>
+        <v>487346</v>
       </c>
       <c r="R5" t="n">
-        <v>7039175</v>
+        <v>7038911</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129298851</v>
+        <v>129298751</v>
       </c>
       <c r="B6" t="n">
-        <v>91567</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>487144</v>
+        <v>487263</v>
       </c>
       <c r="R6" t="n">
-        <v>7039078</v>
+        <v>7038949</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,6 +1149,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,7 +1180,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129298818</v>
+        <v>129298786</v>
       </c>
       <c r="B7" t="n">
         <v>57727</v>
@@ -1210,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>487389</v>
+        <v>487006</v>
       </c>
       <c r="R7" t="n">
-        <v>7038925</v>
+        <v>7039175</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,10 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129298819</v>
+        <v>129298844</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>78057</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1293,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>487346</v>
+        <v>487374</v>
       </c>
       <c r="R8" t="n">
-        <v>7038911</v>
+        <v>7039027</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1348,11 +1353,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129298812</v>
+        <v>129298742</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,21 +1487,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>487362</v>
+        <v>487129</v>
       </c>
       <c r="R10" t="n">
-        <v>7039030</v>
+        <v>7039097</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1547,11 +1547,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,7 +1573,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129298759</v>
+        <v>129298812</v>
       </c>
       <c r="B11" t="n">
         <v>57727</v>
@@ -1613,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>487171</v>
+        <v>487362</v>
       </c>
       <c r="R11" t="n">
-        <v>7039000</v>
+        <v>7039030</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1680,10 +1675,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129298742</v>
+        <v>129298759</v>
       </c>
       <c r="B12" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,21 +1686,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1715,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>487129</v>
+        <v>487171</v>
       </c>
       <c r="R12" t="n">
-        <v>7039097</v>
+        <v>7039000</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,6 +1746,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2083,10 +2083,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129298857</v>
+        <v>129298855</v>
       </c>
       <c r="B16" t="n">
-        <v>83004</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2094,21 +2094,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>487340</v>
+        <v>487542</v>
       </c>
       <c r="R16" t="n">
-        <v>7039016</v>
+        <v>7038985</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2180,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129298855</v>
+        <v>129298777</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>487542</v>
+        <v>486860</v>
       </c>
       <c r="R17" t="n">
-        <v>7038985</v>
+        <v>7039254</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2251,6 +2251,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2277,7 +2282,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129298777</v>
+        <v>129298787</v>
       </c>
       <c r="B18" t="n">
         <v>57727</v>
@@ -2312,10 +2317,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486860</v>
+        <v>486999</v>
       </c>
       <c r="R18" t="n">
-        <v>7039254</v>
+        <v>7039162</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2352,7 +2357,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2379,10 +2384,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129298787</v>
+        <v>129298857</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>83004</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2390,21 +2395,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2414,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486999</v>
+        <v>487340</v>
       </c>
       <c r="R19" t="n">
-        <v>7039162</v>
+        <v>7039016</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2450,11 +2455,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2481,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129298775</v>
+        <v>129298740</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486860</v>
+        <v>487145</v>
       </c>
       <c r="R20" t="n">
-        <v>7039244</v>
+        <v>7039179</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2552,11 +2552,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2583,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129298808</v>
+        <v>129298852</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>91567</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2594,21 +2589,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2618,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>487344</v>
+        <v>487127</v>
       </c>
       <c r="R21" t="n">
-        <v>7039018</v>
+        <v>7039070</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2654,11 +2649,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2685,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129298780</v>
+        <v>129298837</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2696,21 +2686,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2720,10 +2710,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486859</v>
+        <v>487004</v>
       </c>
       <c r="R22" t="n">
-        <v>7039262</v>
+        <v>7039214</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2756,11 +2746,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2787,45 +2772,57 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129298740</v>
+        <v>129298830</v>
       </c>
       <c r="B23" t="n">
-        <v>91553</v>
+        <v>57568</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>102621</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>487145</v>
+        <v>487123</v>
       </c>
       <c r="R23" t="n">
-        <v>7039179</v>
+        <v>7039173</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2884,10 +2881,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129298852</v>
+        <v>129298775</v>
       </c>
       <c r="B24" t="n">
-        <v>91567</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2895,21 +2892,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2919,10 +2916,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>487127</v>
+        <v>486860</v>
       </c>
       <c r="R24" t="n">
-        <v>7039070</v>
+        <v>7039244</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2955,6 +2952,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2981,27 +2983,27 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129298830</v>
+        <v>129298808</v>
       </c>
       <c r="B25" t="n">
-        <v>57568</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3009,29 +3011,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>487123</v>
+        <v>487344</v>
       </c>
       <c r="R25" t="n">
-        <v>7039173</v>
+        <v>7039018</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3064,6 +3054,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3090,10 +3085,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129298837</v>
+        <v>129298780</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3101,21 +3096,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3125,10 +3120,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>487004</v>
+        <v>486859</v>
       </c>
       <c r="R26" t="n">
-        <v>7039214</v>
+        <v>7039262</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3161,6 +3156,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3284,7 +3284,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129298793</v>
+        <v>129298823</v>
       </c>
       <c r="B28" t="n">
         <v>57727</v>
@@ -3319,10 +3319,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>487183</v>
+        <v>487363</v>
       </c>
       <c r="R28" t="n">
-        <v>7039216</v>
+        <v>7038902</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3386,7 +3386,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129298823</v>
+        <v>129298793</v>
       </c>
       <c r="B29" t="n">
         <v>57727</v>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>487363</v>
+        <v>487183</v>
       </c>
       <c r="R29" t="n">
-        <v>7038902</v>
+        <v>7039216</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3488,7 +3488,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129298770</v>
+        <v>129298765</v>
       </c>
       <c r="B30" t="n">
         <v>57727</v>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>486972</v>
+        <v>487122</v>
       </c>
       <c r="R30" t="n">
-        <v>7039122</v>
+        <v>7039034</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3590,7 +3590,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129298778</v>
+        <v>129298770</v>
       </c>
       <c r="B31" t="n">
         <v>57727</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486871</v>
+        <v>486972</v>
       </c>
       <c r="R31" t="n">
-        <v>7039260</v>
+        <v>7039122</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3692,7 +3692,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129298765</v>
+        <v>129298778</v>
       </c>
       <c r="B32" t="n">
         <v>57727</v>
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>487122</v>
+        <v>486871</v>
       </c>
       <c r="R32" t="n">
-        <v>7039034</v>
+        <v>7039260</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3988,7 +3988,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129298792</v>
+        <v>129298769</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>487153</v>
+        <v>487109</v>
       </c>
       <c r="R35" t="n">
-        <v>7039212</v>
+        <v>7039040</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4090,7 +4090,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129298750</v>
+        <v>129298794</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4125,10 +4125,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>487272</v>
+        <v>487186</v>
       </c>
       <c r="R36" t="n">
-        <v>7038946</v>
+        <v>7039192</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4192,7 +4192,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129298769</v>
+        <v>129298792</v>
       </c>
       <c r="B37" t="n">
         <v>57727</v>
@@ -4227,10 +4227,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>487109</v>
+        <v>487153</v>
       </c>
       <c r="R37" t="n">
-        <v>7039040</v>
+        <v>7039212</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129298804</v>
+        <v>129298750</v>
       </c>
       <c r="B38" t="n">
         <v>57727</v>
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>487288</v>
+        <v>487272</v>
       </c>
       <c r="R38" t="n">
-        <v>7039002</v>
+        <v>7038946</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4396,7 +4396,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129298794</v>
+        <v>129298804</v>
       </c>
       <c r="B39" t="n">
         <v>57727</v>
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>487186</v>
+        <v>487288</v>
       </c>
       <c r="R39" t="n">
-        <v>7039192</v>
+        <v>7039002</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4498,10 +4498,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129298833</v>
+        <v>129298809</v>
       </c>
       <c r="B40" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4509,21 +4509,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>487265</v>
+        <v>487348</v>
       </c>
       <c r="R40" t="n">
-        <v>7038997</v>
+        <v>7039005</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4569,6 +4569,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4595,10 +4600,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129298854</v>
+        <v>129298802</v>
       </c>
       <c r="B41" t="n">
-        <v>91573</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4606,19 +4611,23 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4626,10 +4635,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>487522</v>
+        <v>487302</v>
       </c>
       <c r="R41" t="n">
-        <v>7038997</v>
+        <v>7039045</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4662,6 +4671,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4688,7 +4702,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129298748</v>
+        <v>129298795</v>
       </c>
       <c r="B42" t="n">
         <v>57727</v>
@@ -4723,10 +4737,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>487301</v>
+        <v>487100</v>
       </c>
       <c r="R42" t="n">
-        <v>7038925</v>
+        <v>7039085</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4790,7 +4804,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129298783</v>
+        <v>129298748</v>
       </c>
       <c r="B43" t="n">
         <v>57727</v>
@@ -4825,10 +4839,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>487024</v>
+        <v>487301</v>
       </c>
       <c r="R43" t="n">
-        <v>7039203</v>
+        <v>7038925</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4892,10 +4906,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129298840</v>
+        <v>129298783</v>
       </c>
       <c r="B44" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4903,21 +4917,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4927,10 +4941,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>487314</v>
+        <v>487024</v>
       </c>
       <c r="R44" t="n">
-        <v>7039005</v>
+        <v>7039203</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4963,6 +4977,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4989,10 +5008,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129298805</v>
+        <v>129298833</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5000,21 +5019,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5024,10 +5043,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>487346</v>
+        <v>487265</v>
       </c>
       <c r="R45" t="n">
-        <v>7039012</v>
+        <v>7038997</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5060,11 +5079,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5091,10 +5105,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129298809</v>
+        <v>129298854</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5102,23 +5116,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5126,10 +5136,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>487348</v>
+        <v>487522</v>
       </c>
       <c r="R46" t="n">
-        <v>7039005</v>
+        <v>7038997</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5162,11 +5172,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5193,10 +5198,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129298802</v>
+        <v>129298840</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5204,21 +5209,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5228,10 +5233,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>487302</v>
+        <v>487314</v>
       </c>
       <c r="R47" t="n">
-        <v>7039045</v>
+        <v>7039005</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5264,11 +5269,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5295,7 +5295,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129298795</v>
+        <v>129298805</v>
       </c>
       <c r="B48" t="n">
         <v>57727</v>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>487100</v>
+        <v>487346</v>
       </c>
       <c r="R48" t="n">
-        <v>7039085</v>
+        <v>7039012</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5397,10 +5397,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129298738</v>
+        <v>129298842</v>
       </c>
       <c r="B49" t="n">
-        <v>96973</v>
+        <v>80149</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5408,21 +5408,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>487311</v>
+        <v>487393</v>
       </c>
       <c r="R49" t="n">
-        <v>7039063</v>
+        <v>7038908</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5596,10 +5596,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129298856</v>
+        <v>129298810</v>
       </c>
       <c r="B51" t="n">
-        <v>82878</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5607,21 +5607,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5631,10 +5631,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>487541</v>
+        <v>487355</v>
       </c>
       <c r="R51" t="n">
-        <v>7038983</v>
+        <v>7039005</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5667,6 +5667,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5693,10 +5698,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129298842</v>
+        <v>129298856</v>
       </c>
       <c r="B52" t="n">
-        <v>80149</v>
+        <v>82878</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5704,21 +5709,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5728,10 +5733,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>487393</v>
+        <v>487541</v>
       </c>
       <c r="R52" t="n">
-        <v>7038908</v>
+        <v>7038983</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5790,10 +5795,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129298810</v>
+        <v>129298738</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>96973</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5801,21 +5806,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5825,10 +5830,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>487355</v>
+        <v>487311</v>
       </c>
       <c r="R53" t="n">
-        <v>7039005</v>
+        <v>7039063</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5861,11 +5866,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6198,7 +6198,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129298776</v>
+        <v>129298774</v>
       </c>
       <c r="B57" t="n">
         <v>57727</v>
@@ -6233,10 +6233,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>486855</v>
+        <v>486866</v>
       </c>
       <c r="R57" t="n">
-        <v>7039252</v>
+        <v>7039249</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6300,7 +6300,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129298820</v>
+        <v>129298773</v>
       </c>
       <c r="B58" t="n">
         <v>57727</v>
@@ -6335,10 +6335,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>487354</v>
+        <v>486807</v>
       </c>
       <c r="R58" t="n">
-        <v>7038894</v>
+        <v>7039220</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6402,7 +6402,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129298773</v>
+        <v>129298767</v>
       </c>
       <c r="B59" t="n">
         <v>57727</v>
@@ -6437,10 +6437,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>486807</v>
+        <v>487123</v>
       </c>
       <c r="R59" t="n">
-        <v>7039220</v>
+        <v>7039031</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6504,7 +6504,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129298767</v>
+        <v>129298776</v>
       </c>
       <c r="B60" t="n">
         <v>57727</v>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>487123</v>
+        <v>486855</v>
       </c>
       <c r="R60" t="n">
-        <v>7039031</v>
+        <v>7039252</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6810,7 +6810,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129298774</v>
+        <v>129298820</v>
       </c>
       <c r="B63" t="n">
         <v>57727</v>
@@ -6845,10 +6845,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>486866</v>
+        <v>487354</v>
       </c>
       <c r="R63" t="n">
-        <v>7039249</v>
+        <v>7038894</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6885,7 +6885,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7014,10 +7014,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129298853</v>
+        <v>129298741</v>
       </c>
       <c r="B65" t="n">
-        <v>91573</v>
+        <v>91553</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7025,19 +7025,23 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7045,10 +7049,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>487415</v>
+        <v>487185</v>
       </c>
       <c r="R65" t="n">
-        <v>7038971</v>
+        <v>7039203</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7107,10 +7111,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129298741</v>
+        <v>129298853</v>
       </c>
       <c r="B66" t="n">
-        <v>91553</v>
+        <v>91573</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7118,23 +7122,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7142,10 +7142,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>487185</v>
+        <v>487415</v>
       </c>
       <c r="R66" t="n">
-        <v>7039203</v>
+        <v>7038971</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7306,10 +7306,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129298797</v>
+        <v>129298737</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>83012</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7317,21 +7317,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7341,10 +7341,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>487134</v>
+        <v>487523</v>
       </c>
       <c r="R68" t="n">
-        <v>7039037</v>
+        <v>7039001</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7377,11 +7377,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7408,61 +7403,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129298800</v>
+        <v>129298828</v>
       </c>
       <c r="B69" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>487288</v>
+        <v>487269</v>
       </c>
       <c r="R69" t="n">
-        <v>7039015</v>
+        <v>7039004</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7495,11 +7474,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Födosökande hane</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7526,10 +7500,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129298821</v>
+        <v>129298839</v>
       </c>
       <c r="B70" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7537,21 +7511,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7561,10 +7535,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>487368</v>
+        <v>487269</v>
       </c>
       <c r="R70" t="n">
-        <v>7038892</v>
+        <v>7039001</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7597,11 +7571,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7628,7 +7597,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129298803</v>
+        <v>129298797</v>
       </c>
       <c r="B71" t="n">
         <v>57727</v>
@@ -7663,7 +7632,7 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>487303</v>
+        <v>487134</v>
       </c>
       <c r="R71" t="n">
         <v>7039037</v>
@@ -7730,32 +7699,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129298817</v>
+        <v>129298831</v>
       </c>
       <c r="B72" t="n">
-        <v>57727</v>
+        <v>83003</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7765,10 +7734,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>487460</v>
+        <v>487307</v>
       </c>
       <c r="R72" t="n">
-        <v>7038984</v>
+        <v>7039016</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7801,11 +7770,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7832,32 +7796,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129298831</v>
+        <v>129298803</v>
       </c>
       <c r="B73" t="n">
-        <v>83003</v>
+        <v>57727</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7867,10 +7831,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>487307</v>
+        <v>487303</v>
       </c>
       <c r="R73" t="n">
-        <v>7039016</v>
+        <v>7039037</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7903,6 +7867,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7929,10 +7898,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129298737</v>
+        <v>129298822</v>
       </c>
       <c r="B74" t="n">
-        <v>83012</v>
+        <v>57727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7940,21 +7909,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7964,10 +7933,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>487523</v>
+        <v>487373</v>
       </c>
       <c r="R74" t="n">
-        <v>7039001</v>
+        <v>7038897</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8000,6 +7969,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8026,32 +8000,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129298828</v>
+        <v>129298817</v>
       </c>
       <c r="B75" t="n">
-        <v>80178</v>
+        <v>57727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8061,10 +8035,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>487269</v>
+        <v>487460</v>
       </c>
       <c r="R75" t="n">
-        <v>7039004</v>
+        <v>7038984</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8097,6 +8071,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8123,10 +8102,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129298839</v>
+        <v>129298800</v>
       </c>
       <c r="B76" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8134,34 +8113,50 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>487269</v>
+        <v>487288</v>
       </c>
       <c r="R76" t="n">
-        <v>7039001</v>
+        <v>7039015</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8194,6 +8189,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Födosökande hane</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8220,7 +8220,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129298822</v>
+        <v>129298821</v>
       </c>
       <c r="B77" t="n">
         <v>57727</v>
@@ -8255,10 +8255,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>487373</v>
+        <v>487368</v>
       </c>
       <c r="R77" t="n">
-        <v>7038897</v>
+        <v>7038892</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8322,7 +8322,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129298785</v>
+        <v>129298784</v>
       </c>
       <c r="B78" t="n">
         <v>57727</v>
@@ -8357,10 +8357,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>487007</v>
+        <v>487011</v>
       </c>
       <c r="R78" t="n">
-        <v>7039210</v>
+        <v>7039207</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8397,7 +8397,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8424,7 +8424,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129298757</v>
+        <v>129298781</v>
       </c>
       <c r="B79" t="n">
         <v>57727</v>
@@ -8459,10 +8459,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>487188</v>
+        <v>486864</v>
       </c>
       <c r="R79" t="n">
-        <v>7038992</v>
+        <v>7039272</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8526,7 +8526,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129298784</v>
+        <v>129298785</v>
       </c>
       <c r="B80" t="n">
         <v>57727</v>
@@ -8561,10 +8561,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>487011</v>
+        <v>487007</v>
       </c>
       <c r="R80" t="n">
-        <v>7039207</v>
+        <v>7039210</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8601,7 +8601,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8628,7 +8628,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129298781</v>
+        <v>129298753</v>
       </c>
       <c r="B81" t="n">
         <v>57727</v>
@@ -8663,10 +8663,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>486864</v>
+        <v>487240</v>
       </c>
       <c r="R81" t="n">
-        <v>7039272</v>
+        <v>7038959</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8730,7 +8730,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129298753</v>
+        <v>129298757</v>
       </c>
       <c r="B82" t="n">
         <v>57727</v>
@@ -8765,10 +8765,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>487240</v>
+        <v>487188</v>
       </c>
       <c r="R82" t="n">
-        <v>7038959</v>
+        <v>7038992</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8832,10 +8832,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129298771</v>
+        <v>129298841</v>
       </c>
       <c r="B83" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8843,21 +8843,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8867,10 +8867,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>486885</v>
+        <v>487515</v>
       </c>
       <c r="R83" t="n">
-        <v>7039172</v>
+        <v>7038993</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8903,11 +8903,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8934,7 +8929,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129298801</v>
+        <v>129298789</v>
       </c>
       <c r="B84" t="n">
         <v>57727</v>
@@ -8969,10 +8964,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>487268</v>
+        <v>487041</v>
       </c>
       <c r="R84" t="n">
-        <v>7039003</v>
+        <v>7039167</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9036,7 +9031,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129298789</v>
+        <v>129298772</v>
       </c>
       <c r="B85" t="n">
         <v>57727</v>
@@ -9071,10 +9066,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>487041</v>
+        <v>486849</v>
       </c>
       <c r="R85" t="n">
-        <v>7039167</v>
+        <v>7039185</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9138,7 +9133,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129298814</v>
+        <v>129298771</v>
       </c>
       <c r="B86" t="n">
         <v>57727</v>
@@ -9173,10 +9168,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>487366</v>
+        <v>486885</v>
       </c>
       <c r="R86" t="n">
-        <v>7038997</v>
+        <v>7039172</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9213,7 +9208,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9240,45 +9235,61 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129298772</v>
+        <v>129298847</v>
       </c>
       <c r="B87" t="n">
-        <v>57727</v>
+        <v>57587</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>100136</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>486849</v>
+        <v>486999</v>
       </c>
       <c r="R87" t="n">
-        <v>7039185</v>
+        <v>7039199</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9315,7 +9326,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Jagades av en nötskrika</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9342,7 +9353,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129298746</v>
+        <v>129298801</v>
       </c>
       <c r="B88" t="n">
         <v>57727</v>
@@ -9377,10 +9388,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>487316</v>
+        <v>487268</v>
       </c>
       <c r="R88" t="n">
-        <v>7038914</v>
+        <v>7039003</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9444,10 +9455,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129298841</v>
+        <v>129298814</v>
       </c>
       <c r="B89" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9455,21 +9466,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9479,10 +9490,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>487515</v>
+        <v>487366</v>
       </c>
       <c r="R89" t="n">
-        <v>7038993</v>
+        <v>7038997</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9515,6 +9526,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9541,61 +9557,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129298847</v>
+        <v>129298746</v>
       </c>
       <c r="B90" t="n">
-        <v>57587</v>
+        <v>57727</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100136</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>486999</v>
+        <v>487316</v>
       </c>
       <c r="R90" t="n">
-        <v>7039199</v>
+        <v>7038914</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9632,7 +9632,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Jagades av en nötskrika</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9853,7 +9853,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129298768</v>
+        <v>129298752</v>
       </c>
       <c r="B93" t="n">
         <v>57727</v>
@@ -9888,10 +9888,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>487123</v>
+        <v>487246</v>
       </c>
       <c r="R93" t="n">
-        <v>7039032</v>
+        <v>7038958</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9955,7 +9955,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129298752</v>
+        <v>129298768</v>
       </c>
       <c r="B94" t="n">
         <v>57727</v>
@@ -9990,10 +9990,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>487246</v>
+        <v>487123</v>
       </c>
       <c r="R94" t="n">
-        <v>7038958</v>
+        <v>7039032</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10057,32 +10057,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129298739</v>
+        <v>129298745</v>
       </c>
       <c r="B95" t="n">
-        <v>91517</v>
+        <v>57727</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10092,10 +10092,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>487384</v>
+        <v>486881</v>
       </c>
       <c r="R95" t="n">
-        <v>7038973</v>
+        <v>7039175</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10128,6 +10128,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10154,7 +10159,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129298745</v>
+        <v>129298791</v>
       </c>
       <c r="B96" t="n">
         <v>57727</v>
@@ -10189,10 +10194,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>486881</v>
+        <v>487112</v>
       </c>
       <c r="R96" t="n">
-        <v>7039175</v>
+        <v>7039182</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10256,7 +10261,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129298791</v>
+        <v>129298754</v>
       </c>
       <c r="B97" t="n">
         <v>57727</v>
@@ -10291,10 +10296,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>487112</v>
+        <v>487222</v>
       </c>
       <c r="R97" t="n">
-        <v>7039182</v>
+        <v>7038974</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10331,7 +10336,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10358,32 +10363,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129298754</v>
+        <v>129298739</v>
       </c>
       <c r="B98" t="n">
-        <v>57727</v>
+        <v>91517</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10393,10 +10398,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>487222</v>
+        <v>487384</v>
       </c>
       <c r="R98" t="n">
-        <v>7038974</v>
+        <v>7038973</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10429,11 +10434,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11379,7 +11379,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129298760</v>
+        <v>129298766</v>
       </c>
       <c r="B108" t="n">
         <v>57727</v>
@@ -11414,10 +11414,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>487141</v>
+        <v>487124</v>
       </c>
       <c r="R108" t="n">
-        <v>7039023</v>
+        <v>7039030</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11454,7 +11454,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11481,7 +11481,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129298766</v>
+        <v>129298796</v>
       </c>
       <c r="B109" t="n">
         <v>57727</v>
@@ -11516,10 +11516,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>487124</v>
+        <v>487139</v>
       </c>
       <c r="R109" t="n">
-        <v>7039030</v>
+        <v>7039088</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11583,7 +11583,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129298796</v>
+        <v>129298760</v>
       </c>
       <c r="B110" t="n">
         <v>57727</v>
@@ -11618,10 +11618,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>487139</v>
+        <v>487141</v>
       </c>
       <c r="R110" t="n">
-        <v>7039088</v>
+        <v>7039023</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11658,7 +11658,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 46357-2025 artfynd.xlsx
+++ b/artfynd/A 46357-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129298827</v>
+        <v>129298851</v>
       </c>
       <c r="B2" t="n">
-        <v>57887</v>
+        <v>91567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487352</v>
+        <v>487144</v>
       </c>
       <c r="R2" t="n">
-        <v>7038906</v>
+        <v>7039078</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129298851</v>
+        <v>129298751</v>
       </c>
       <c r="B3" t="n">
-        <v>91567</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487144</v>
+        <v>487263</v>
       </c>
       <c r="R3" t="n">
-        <v>7039078</v>
+        <v>7038949</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,7 +874,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129298818</v>
+        <v>129298786</v>
       </c>
       <c r="B4" t="n">
         <v>57727</v>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487389</v>
+        <v>487006</v>
       </c>
       <c r="R4" t="n">
-        <v>7038925</v>
+        <v>7039175</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,7 +976,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129298819</v>
+        <v>129298818</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>487346</v>
+        <v>487389</v>
       </c>
       <c r="R5" t="n">
-        <v>7038911</v>
+        <v>7038925</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,7 +1078,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129298751</v>
+        <v>129298819</v>
       </c>
       <c r="B6" t="n">
         <v>57727</v>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>487263</v>
+        <v>487346</v>
       </c>
       <c r="R6" t="n">
-        <v>7038949</v>
+        <v>7038911</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129298786</v>
+        <v>129298827</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>487006</v>
+        <v>487352</v>
       </c>
       <c r="R7" t="n">
-        <v>7039175</v>
+        <v>7038906</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129298838</v>
+        <v>129298742</v>
       </c>
       <c r="B9" t="n">
-        <v>80149</v>
+        <v>91553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1390,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>487035</v>
+        <v>487129</v>
       </c>
       <c r="R9" t="n">
-        <v>7039161</v>
+        <v>7039097</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129298742</v>
+        <v>129298812</v>
       </c>
       <c r="B10" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,21 +1487,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>487129</v>
+        <v>487362</v>
       </c>
       <c r="R10" t="n">
-        <v>7039097</v>
+        <v>7039030</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1547,6 +1547,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1573,7 +1578,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129298812</v>
+        <v>129298759</v>
       </c>
       <c r="B11" t="n">
         <v>57727</v>
@@ -1608,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>487362</v>
+        <v>487171</v>
       </c>
       <c r="R11" t="n">
-        <v>7039030</v>
+        <v>7039000</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1675,10 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129298759</v>
+        <v>129298838</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1686,21 +1691,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1710,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>487171</v>
+        <v>487035</v>
       </c>
       <c r="R12" t="n">
-        <v>7039000</v>
+        <v>7039161</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1746,11 +1751,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2083,10 +2083,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129298855</v>
+        <v>129298777</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2094,21 +2094,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>487542</v>
+        <v>486860</v>
       </c>
       <c r="R16" t="n">
-        <v>7038985</v>
+        <v>7039254</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2154,6 +2154,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2180,7 +2185,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129298777</v>
+        <v>129298787</v>
       </c>
       <c r="B17" t="n">
         <v>57727</v>
@@ -2215,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486860</v>
+        <v>486999</v>
       </c>
       <c r="R17" t="n">
-        <v>7039254</v>
+        <v>7039162</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2255,7 +2260,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2282,10 +2287,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129298787</v>
+        <v>129298857</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>83004</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2293,21 +2298,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2317,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486999</v>
+        <v>487340</v>
       </c>
       <c r="R18" t="n">
-        <v>7039162</v>
+        <v>7039016</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2353,11 +2358,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2384,10 +2384,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129298857</v>
+        <v>129298855</v>
       </c>
       <c r="B19" t="n">
-        <v>83004</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2395,21 +2395,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>487340</v>
+        <v>487542</v>
       </c>
       <c r="R19" t="n">
-        <v>7039016</v>
+        <v>7038985</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2481,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129298740</v>
+        <v>129298775</v>
       </c>
       <c r="B20" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>487145</v>
+        <v>486860</v>
       </c>
       <c r="R20" t="n">
-        <v>7039179</v>
+        <v>7039244</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2552,6 +2552,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2578,10 +2583,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129298852</v>
+        <v>129298808</v>
       </c>
       <c r="B21" t="n">
-        <v>91567</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2589,21 +2594,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2618,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>487127</v>
+        <v>487344</v>
       </c>
       <c r="R21" t="n">
-        <v>7039070</v>
+        <v>7039018</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2649,6 +2654,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2675,10 +2685,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129298837</v>
+        <v>129298780</v>
       </c>
       <c r="B22" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,21 +2696,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2710,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>487004</v>
+        <v>486859</v>
       </c>
       <c r="R22" t="n">
-        <v>7039214</v>
+        <v>7039262</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2746,6 +2756,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2881,10 +2896,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129298775</v>
+        <v>129298845</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>78057</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2892,21 +2907,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2916,10 +2931,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486860</v>
+        <v>487526</v>
       </c>
       <c r="R24" t="n">
-        <v>7039244</v>
+        <v>7039006</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2952,11 +2967,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2983,10 +2993,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129298808</v>
+        <v>129298740</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2994,21 +3004,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3018,10 +3028,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>487344</v>
+        <v>487145</v>
       </c>
       <c r="R25" t="n">
-        <v>7039018</v>
+        <v>7039179</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3054,11 +3064,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3085,10 +3090,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129298780</v>
+        <v>129298852</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>91567</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3096,21 +3101,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3120,10 +3125,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486859</v>
+        <v>487127</v>
       </c>
       <c r="R26" t="n">
-        <v>7039262</v>
+        <v>7039070</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3156,11 +3161,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3187,10 +3187,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129298845</v>
+        <v>129298837</v>
       </c>
       <c r="B27" t="n">
-        <v>78057</v>
+        <v>80149</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3198,21 +3198,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3222,10 +3222,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>487526</v>
+        <v>487004</v>
       </c>
       <c r="R27" t="n">
-        <v>7039006</v>
+        <v>7039214</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3284,7 +3284,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129298823</v>
+        <v>129298793</v>
       </c>
       <c r="B28" t="n">
         <v>57727</v>
@@ -3319,10 +3319,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>487363</v>
+        <v>487183</v>
       </c>
       <c r="R28" t="n">
-        <v>7038902</v>
+        <v>7039216</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3386,7 +3386,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129298793</v>
+        <v>129298823</v>
       </c>
       <c r="B29" t="n">
         <v>57727</v>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>487183</v>
+        <v>487363</v>
       </c>
       <c r="R29" t="n">
-        <v>7039216</v>
+        <v>7038902</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3988,7 +3988,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129298769</v>
+        <v>129298792</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>487109</v>
+        <v>487153</v>
       </c>
       <c r="R35" t="n">
-        <v>7039040</v>
+        <v>7039212</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4090,7 +4090,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129298794</v>
+        <v>129298750</v>
       </c>
       <c r="B36" t="n">
         <v>57727</v>
@@ -4125,10 +4125,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>487186</v>
+        <v>487272</v>
       </c>
       <c r="R36" t="n">
-        <v>7039192</v>
+        <v>7038946</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4192,7 +4192,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129298792</v>
+        <v>129298769</v>
       </c>
       <c r="B37" t="n">
         <v>57727</v>
@@ -4227,10 +4227,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>487153</v>
+        <v>487109</v>
       </c>
       <c r="R37" t="n">
-        <v>7039212</v>
+        <v>7039040</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129298750</v>
+        <v>129298804</v>
       </c>
       <c r="B38" t="n">
         <v>57727</v>
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>487272</v>
+        <v>487288</v>
       </c>
       <c r="R38" t="n">
-        <v>7038946</v>
+        <v>7039002</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4396,7 +4396,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129298804</v>
+        <v>129298794</v>
       </c>
       <c r="B39" t="n">
         <v>57727</v>
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>487288</v>
+        <v>487186</v>
       </c>
       <c r="R39" t="n">
-        <v>7039002</v>
+        <v>7039192</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4498,10 +4498,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129298809</v>
+        <v>129298833</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4509,21 +4509,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>487348</v>
+        <v>487265</v>
       </c>
       <c r="R40" t="n">
-        <v>7039005</v>
+        <v>7038997</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4569,11 +4569,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4600,10 +4595,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129298802</v>
+        <v>129298854</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4611,23 +4606,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4635,10 +4626,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>487302</v>
+        <v>487522</v>
       </c>
       <c r="R41" t="n">
-        <v>7039045</v>
+        <v>7038997</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4671,11 +4662,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4702,7 +4688,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129298795</v>
+        <v>129298805</v>
       </c>
       <c r="B42" t="n">
         <v>57727</v>
@@ -4737,10 +4723,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>487100</v>
+        <v>487346</v>
       </c>
       <c r="R42" t="n">
-        <v>7039085</v>
+        <v>7039012</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4804,7 +4790,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129298748</v>
+        <v>129298809</v>
       </c>
       <c r="B43" t="n">
         <v>57727</v>
@@ -4839,10 +4825,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>487301</v>
+        <v>487348</v>
       </c>
       <c r="R43" t="n">
-        <v>7038925</v>
+        <v>7039005</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4906,7 +4892,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129298783</v>
+        <v>129298802</v>
       </c>
       <c r="B44" t="n">
         <v>57727</v>
@@ -4941,10 +4927,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>487024</v>
+        <v>487302</v>
       </c>
       <c r="R44" t="n">
-        <v>7039203</v>
+        <v>7039045</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5008,10 +4994,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129298833</v>
+        <v>129298795</v>
       </c>
       <c r="B45" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5019,21 +5005,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5043,10 +5029,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>487265</v>
+        <v>487100</v>
       </c>
       <c r="R45" t="n">
-        <v>7038997</v>
+        <v>7039085</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5079,6 +5065,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5105,10 +5096,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129298854</v>
+        <v>129298748</v>
       </c>
       <c r="B46" t="n">
-        <v>91573</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5116,19 +5107,23 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5136,10 +5131,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>487522</v>
+        <v>487301</v>
       </c>
       <c r="R46" t="n">
-        <v>7038997</v>
+        <v>7038925</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5172,6 +5167,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5198,10 +5198,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129298840</v>
+        <v>129298783</v>
       </c>
       <c r="B47" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5209,21 +5209,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5233,10 +5233,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>487314</v>
+        <v>487024</v>
       </c>
       <c r="R47" t="n">
-        <v>7039005</v>
+        <v>7039203</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5269,6 +5269,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5295,10 +5300,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129298805</v>
+        <v>129298840</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5306,21 +5311,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5330,10 +5335,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>487346</v>
+        <v>487314</v>
       </c>
       <c r="R48" t="n">
-        <v>7039012</v>
+        <v>7039005</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5366,11 +5371,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5397,10 +5397,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129298842</v>
+        <v>129298798</v>
       </c>
       <c r="B49" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5408,21 +5408,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>487393</v>
+        <v>487131</v>
       </c>
       <c r="R49" t="n">
-        <v>7038908</v>
+        <v>7039049</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5468,6 +5468,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5494,7 +5499,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129298798</v>
+        <v>129298810</v>
       </c>
       <c r="B50" t="n">
         <v>57727</v>
@@ -5529,10 +5534,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>487131</v>
+        <v>487355</v>
       </c>
       <c r="R50" t="n">
-        <v>7039049</v>
+        <v>7039005</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5596,10 +5601,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129298810</v>
+        <v>129298842</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5607,21 +5612,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5631,10 +5636,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>487355</v>
+        <v>487393</v>
       </c>
       <c r="R51" t="n">
-        <v>7039005</v>
+        <v>7038908</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5667,11 +5672,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5698,10 +5698,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129298856</v>
+        <v>129298738</v>
       </c>
       <c r="B52" t="n">
-        <v>82878</v>
+        <v>96973</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5709,21 +5709,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1312</v>
+        <v>53</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5733,10 +5733,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>487541</v>
+        <v>487311</v>
       </c>
       <c r="R52" t="n">
-        <v>7038983</v>
+        <v>7039063</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5795,10 +5795,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129298738</v>
+        <v>129298856</v>
       </c>
       <c r="B53" t="n">
-        <v>96973</v>
+        <v>82878</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5806,21 +5806,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>53</v>
+        <v>1312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5830,10 +5830,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>487311</v>
+        <v>487541</v>
       </c>
       <c r="R53" t="n">
-        <v>7039063</v>
+        <v>7038983</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6198,7 +6198,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129298774</v>
+        <v>129298767</v>
       </c>
       <c r="B57" t="n">
         <v>57727</v>
@@ -6233,10 +6233,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>486866</v>
+        <v>487123</v>
       </c>
       <c r="R57" t="n">
-        <v>7039249</v>
+        <v>7039031</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6300,7 +6300,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129298773</v>
+        <v>129298776</v>
       </c>
       <c r="B58" t="n">
         <v>57727</v>
@@ -6335,10 +6335,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>486807</v>
+        <v>486855</v>
       </c>
       <c r="R58" t="n">
-        <v>7039220</v>
+        <v>7039252</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6402,7 +6402,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129298767</v>
+        <v>129298816</v>
       </c>
       <c r="B59" t="n">
         <v>57727</v>
@@ -6437,10 +6437,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>487123</v>
+        <v>487389</v>
       </c>
       <c r="R59" t="n">
-        <v>7039031</v>
+        <v>7038985</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6504,7 +6504,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129298776</v>
+        <v>129298813</v>
       </c>
       <c r="B60" t="n">
         <v>57727</v>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>486855</v>
+        <v>487367</v>
       </c>
       <c r="R60" t="n">
-        <v>7039252</v>
+        <v>7038998</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6606,7 +6606,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129298816</v>
+        <v>129298820</v>
       </c>
       <c r="B61" t="n">
         <v>57727</v>
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>487389</v>
+        <v>487354</v>
       </c>
       <c r="R61" t="n">
-        <v>7038985</v>
+        <v>7038894</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6708,7 +6708,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129298813</v>
+        <v>129298774</v>
       </c>
       <c r="B62" t="n">
         <v>57727</v>
@@ -6743,10 +6743,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>487367</v>
+        <v>486866</v>
       </c>
       <c r="R62" t="n">
-        <v>7038998</v>
+        <v>7039249</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6783,7 +6783,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6810,7 +6810,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129298820</v>
+        <v>129298773</v>
       </c>
       <c r="B63" t="n">
         <v>57727</v>
@@ -6845,10 +6845,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>487354</v>
+        <v>486807</v>
       </c>
       <c r="R63" t="n">
-        <v>7038894</v>
+        <v>7039220</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6885,7 +6885,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7306,32 +7306,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129298737</v>
+        <v>129298828</v>
       </c>
       <c r="B68" t="n">
-        <v>83012</v>
+        <v>80178</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7341,10 +7341,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>487523</v>
+        <v>487269</v>
       </c>
       <c r="R68" t="n">
-        <v>7039001</v>
+        <v>7039004</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7403,32 +7403,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129298828</v>
+        <v>129298839</v>
       </c>
       <c r="B69" t="n">
-        <v>80178</v>
+        <v>80149</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7441,7 +7441,7 @@
         <v>487269</v>
       </c>
       <c r="R69" t="n">
-        <v>7039004</v>
+        <v>7039001</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7500,10 +7500,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129298839</v>
+        <v>129298797</v>
       </c>
       <c r="B70" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7511,21 +7511,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7535,10 +7535,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>487269</v>
+        <v>487134</v>
       </c>
       <c r="R70" t="n">
-        <v>7039001</v>
+        <v>7039037</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7571,6 +7571,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7597,7 +7602,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129298797</v>
+        <v>129298803</v>
       </c>
       <c r="B71" t="n">
         <v>57727</v>
@@ -7632,7 +7637,7 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>487134</v>
+        <v>487303</v>
       </c>
       <c r="R71" t="n">
         <v>7039037</v>
@@ -7699,32 +7704,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129298831</v>
+        <v>129298822</v>
       </c>
       <c r="B72" t="n">
-        <v>83003</v>
+        <v>57727</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7734,10 +7739,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>487307</v>
+        <v>487373</v>
       </c>
       <c r="R72" t="n">
-        <v>7039016</v>
+        <v>7038897</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7770,6 +7775,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7796,7 +7806,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129298803</v>
+        <v>129298817</v>
       </c>
       <c r="B73" t="n">
         <v>57727</v>
@@ -7831,10 +7841,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>487303</v>
+        <v>487460</v>
       </c>
       <c r="R73" t="n">
-        <v>7039037</v>
+        <v>7038984</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7898,7 +7908,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129298822</v>
+        <v>129298800</v>
       </c>
       <c r="B74" t="n">
         <v>57727</v>
@@ -7926,17 +7936,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>487373</v>
+        <v>487288</v>
       </c>
       <c r="R74" t="n">
-        <v>7038897</v>
+        <v>7039015</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7973,7 +7999,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Födosökande hane</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8000,7 +8026,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129298817</v>
+        <v>129298821</v>
       </c>
       <c r="B75" t="n">
         <v>57727</v>
@@ -8035,10 +8061,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>487460</v>
+        <v>487368</v>
       </c>
       <c r="R75" t="n">
-        <v>7038984</v>
+        <v>7038892</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8102,61 +8128,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129298800</v>
+        <v>129298831</v>
       </c>
       <c r="B76" t="n">
-        <v>57727</v>
+        <v>83003</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>487288</v>
+        <v>487307</v>
       </c>
       <c r="R76" t="n">
-        <v>7039015</v>
+        <v>7039016</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8189,11 +8199,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Födosökande hane</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8220,10 +8225,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129298821</v>
+        <v>129298737</v>
       </c>
       <c r="B77" t="n">
-        <v>57727</v>
+        <v>83012</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8231,21 +8236,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8255,10 +8260,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>487368</v>
+        <v>487523</v>
       </c>
       <c r="R77" t="n">
-        <v>7038892</v>
+        <v>7039001</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8291,11 +8296,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8322,7 +8322,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129298784</v>
+        <v>129298781</v>
       </c>
       <c r="B78" t="n">
         <v>57727</v>
@@ -8357,10 +8357,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>487011</v>
+        <v>486864</v>
       </c>
       <c r="R78" t="n">
-        <v>7039207</v>
+        <v>7039272</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8424,7 +8424,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129298781</v>
+        <v>129298785</v>
       </c>
       <c r="B79" t="n">
         <v>57727</v>
@@ -8459,10 +8459,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>486864</v>
+        <v>487007</v>
       </c>
       <c r="R79" t="n">
-        <v>7039272</v>
+        <v>7039210</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8526,7 +8526,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129298785</v>
+        <v>129298753</v>
       </c>
       <c r="B80" t="n">
         <v>57727</v>
@@ -8561,10 +8561,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>487007</v>
+        <v>487240</v>
       </c>
       <c r="R80" t="n">
-        <v>7039210</v>
+        <v>7038959</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8601,7 +8601,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8628,7 +8628,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129298753</v>
+        <v>129298757</v>
       </c>
       <c r="B81" t="n">
         <v>57727</v>
@@ -8663,10 +8663,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>487240</v>
+        <v>487188</v>
       </c>
       <c r="R81" t="n">
-        <v>7038959</v>
+        <v>7038992</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8730,7 +8730,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129298757</v>
+        <v>129298784</v>
       </c>
       <c r="B82" t="n">
         <v>57727</v>
@@ -8765,10 +8765,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>487188</v>
+        <v>487011</v>
       </c>
       <c r="R82" t="n">
-        <v>7038992</v>
+        <v>7039207</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8929,7 +8929,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129298789</v>
+        <v>129298771</v>
       </c>
       <c r="B84" t="n">
         <v>57727</v>
@@ -8964,10 +8964,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>487041</v>
+        <v>486885</v>
       </c>
       <c r="R84" t="n">
-        <v>7039167</v>
+        <v>7039172</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9031,45 +9031,61 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129298772</v>
+        <v>129298847</v>
       </c>
       <c r="B85" t="n">
-        <v>57727</v>
+        <v>57587</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>100136</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>486849</v>
+        <v>486999</v>
       </c>
       <c r="R85" t="n">
-        <v>7039185</v>
+        <v>7039199</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9106,7 +9122,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Jagades av en nötskrika</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9133,7 +9149,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129298771</v>
+        <v>129298789</v>
       </c>
       <c r="B86" t="n">
         <v>57727</v>
@@ -9168,10 +9184,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>486885</v>
+        <v>487041</v>
       </c>
       <c r="R86" t="n">
-        <v>7039172</v>
+        <v>7039167</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9235,61 +9251,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129298847</v>
+        <v>129298801</v>
       </c>
       <c r="B87" t="n">
-        <v>57587</v>
+        <v>57727</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100136</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>486999</v>
+        <v>487268</v>
       </c>
       <c r="R87" t="n">
-        <v>7039199</v>
+        <v>7039003</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9326,7 +9326,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Jagades av en nötskrika</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9353,7 +9353,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129298801</v>
+        <v>129298814</v>
       </c>
       <c r="B88" t="n">
         <v>57727</v>
@@ -9388,10 +9388,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>487268</v>
+        <v>487366</v>
       </c>
       <c r="R88" t="n">
-        <v>7039003</v>
+        <v>7038997</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9455,7 +9455,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129298814</v>
+        <v>129298772</v>
       </c>
       <c r="B89" t="n">
         <v>57727</v>
@@ -9490,10 +9490,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>487366</v>
+        <v>486849</v>
       </c>
       <c r="R89" t="n">
-        <v>7038997</v>
+        <v>7039185</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9530,7 +9530,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9756,10 +9756,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129298836</v>
+        <v>129298752</v>
       </c>
       <c r="B92" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9767,21 +9767,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9791,10 +9791,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>486899</v>
+        <v>487246</v>
       </c>
       <c r="R92" t="n">
-        <v>7039370</v>
+        <v>7038958</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9827,6 +9827,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9853,7 +9858,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129298752</v>
+        <v>129298768</v>
       </c>
       <c r="B93" t="n">
         <v>57727</v>
@@ -9888,10 +9893,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>487246</v>
+        <v>487123</v>
       </c>
       <c r="R93" t="n">
-        <v>7038958</v>
+        <v>7039032</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9955,10 +9960,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129298768</v>
+        <v>129298836</v>
       </c>
       <c r="B94" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9966,21 +9971,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9990,10 +9995,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>487123</v>
+        <v>486899</v>
       </c>
       <c r="R94" t="n">
-        <v>7039032</v>
+        <v>7039370</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10026,11 +10031,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10057,32 +10057,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129298745</v>
+        <v>129298739</v>
       </c>
       <c r="B95" t="n">
-        <v>57727</v>
+        <v>91517</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10092,10 +10092,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>486881</v>
+        <v>487384</v>
       </c>
       <c r="R95" t="n">
-        <v>7039175</v>
+        <v>7038973</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10128,11 +10128,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10159,7 +10154,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129298791</v>
+        <v>129298745</v>
       </c>
       <c r="B96" t="n">
         <v>57727</v>
@@ -10194,10 +10189,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>487112</v>
+        <v>486881</v>
       </c>
       <c r="R96" t="n">
-        <v>7039182</v>
+        <v>7039175</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10261,7 +10256,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129298754</v>
+        <v>129298791</v>
       </c>
       <c r="B97" t="n">
         <v>57727</v>
@@ -10296,10 +10291,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>487222</v>
+        <v>487112</v>
       </c>
       <c r="R97" t="n">
-        <v>7038974</v>
+        <v>7039182</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10336,7 +10331,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10363,32 +10358,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129298739</v>
+        <v>129298754</v>
       </c>
       <c r="B98" t="n">
-        <v>91517</v>
+        <v>57727</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10398,10 +10393,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>487384</v>
+        <v>487222</v>
       </c>
       <c r="R98" t="n">
-        <v>7038973</v>
+        <v>7038974</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10434,6 +10429,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">

--- a/artfynd/A 46357-2025 artfynd.xlsx
+++ b/artfynd/A 46357-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129298851</v>
+        <v>129298827</v>
       </c>
       <c r="B2" t="n">
-        <v>91567</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487144</v>
+        <v>487352</v>
       </c>
       <c r="R2" t="n">
-        <v>7039078</v>
+        <v>7038906</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129298751</v>
+        <v>129298844</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>78057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487263</v>
+        <v>487374</v>
       </c>
       <c r="R3" t="n">
-        <v>7038949</v>
+        <v>7039027</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129298786</v>
+        <v>129298851</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>91567</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487006</v>
+        <v>487144</v>
       </c>
       <c r="R4" t="n">
-        <v>7039175</v>
+        <v>7039078</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,7 +971,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129298818</v>
+        <v>129298751</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1011,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>487389</v>
+        <v>487263</v>
       </c>
       <c r="R5" t="n">
-        <v>7038925</v>
+        <v>7038949</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,7 +1073,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129298819</v>
+        <v>129298786</v>
       </c>
       <c r="B6" t="n">
         <v>57727</v>
@@ -1113,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>487346</v>
+        <v>487006</v>
       </c>
       <c r="R6" t="n">
-        <v>7038911</v>
+        <v>7039175</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129298827</v>
+        <v>129298818</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>487352</v>
+        <v>487389</v>
       </c>
       <c r="R7" t="n">
-        <v>7038906</v>
+        <v>7038925</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,7 +1250,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1282,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129298844</v>
+        <v>129298819</v>
       </c>
       <c r="B8" t="n">
-        <v>78057</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1293,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1317,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>487374</v>
+        <v>487346</v>
       </c>
       <c r="R8" t="n">
-        <v>7039027</v>
+        <v>7038911</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1353,6 +1348,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2083,10 +2083,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129298777</v>
+        <v>129298857</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>83004</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2094,21 +2094,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486860</v>
+        <v>487340</v>
       </c>
       <c r="R16" t="n">
-        <v>7039254</v>
+        <v>7039016</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2154,11 +2154,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2185,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129298787</v>
+        <v>129298855</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2196,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2220,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486999</v>
+        <v>487542</v>
       </c>
       <c r="R17" t="n">
-        <v>7039162</v>
+        <v>7038985</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2256,11 +2251,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2287,10 +2277,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129298857</v>
+        <v>129298777</v>
       </c>
       <c r="B18" t="n">
-        <v>83004</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2298,21 +2288,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>487340</v>
+        <v>486860</v>
       </c>
       <c r="R18" t="n">
-        <v>7039016</v>
+        <v>7039254</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2358,6 +2348,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2384,10 +2379,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129298855</v>
+        <v>129298787</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2395,21 +2390,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2419,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>487542</v>
+        <v>486999</v>
       </c>
       <c r="R19" t="n">
-        <v>7038985</v>
+        <v>7039162</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2455,6 +2450,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2481,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129298775</v>
+        <v>129298837</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>486860</v>
+        <v>487004</v>
       </c>
       <c r="R20" t="n">
-        <v>7039244</v>
+        <v>7039214</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2552,11 +2552,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2583,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129298808</v>
+        <v>129298740</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2594,21 +2589,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2618,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>487344</v>
+        <v>487145</v>
       </c>
       <c r="R21" t="n">
-        <v>7039018</v>
+        <v>7039179</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2654,11 +2649,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2685,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129298780</v>
+        <v>129298852</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>91567</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2696,21 +2686,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2720,10 +2710,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>486859</v>
+        <v>487127</v>
       </c>
       <c r="R22" t="n">
-        <v>7039262</v>
+        <v>7039070</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2756,11 +2746,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2993,10 +2978,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129298740</v>
+        <v>129298775</v>
       </c>
       <c r="B25" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3004,21 +2989,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3028,10 +3013,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>487145</v>
+        <v>486860</v>
       </c>
       <c r="R25" t="n">
-        <v>7039179</v>
+        <v>7039244</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3064,6 +3049,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3090,10 +3080,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129298852</v>
+        <v>129298808</v>
       </c>
       <c r="B26" t="n">
-        <v>91567</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3101,21 +3091,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3125,10 +3115,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>487127</v>
+        <v>487344</v>
       </c>
       <c r="R26" t="n">
-        <v>7039070</v>
+        <v>7039018</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3161,6 +3151,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3187,10 +3182,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129298837</v>
+        <v>129298780</v>
       </c>
       <c r="B27" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3198,21 +3193,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3222,10 +3217,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>487004</v>
+        <v>486859</v>
       </c>
       <c r="R27" t="n">
-        <v>7039214</v>
+        <v>7039262</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3258,6 +3253,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3794,32 +3794,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129298843</v>
+        <v>129298846</v>
       </c>
       <c r="B33" t="n">
-        <v>80149</v>
+        <v>57831</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>487391</v>
+        <v>486976</v>
       </c>
       <c r="R33" t="n">
-        <v>7038927</v>
+        <v>7039216</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3891,32 +3891,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129298846</v>
+        <v>129298843</v>
       </c>
       <c r="B34" t="n">
-        <v>57831</v>
+        <v>80149</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486976</v>
+        <v>487391</v>
       </c>
       <c r="R34" t="n">
-        <v>7039216</v>
+        <v>7038927</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4595,10 +4595,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129298854</v>
+        <v>129298805</v>
       </c>
       <c r="B41" t="n">
-        <v>91573</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4606,19 +4606,23 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4626,10 +4630,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>487522</v>
+        <v>487346</v>
       </c>
       <c r="R41" t="n">
-        <v>7038997</v>
+        <v>7039012</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4662,6 +4666,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4688,7 +4697,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129298805</v>
+        <v>129298809</v>
       </c>
       <c r="B42" t="n">
         <v>57727</v>
@@ -4723,10 +4732,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>487346</v>
+        <v>487348</v>
       </c>
       <c r="R42" t="n">
-        <v>7039012</v>
+        <v>7039005</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4790,7 +4799,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129298809</v>
+        <v>129298802</v>
       </c>
       <c r="B43" t="n">
         <v>57727</v>
@@ -4825,10 +4834,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>487348</v>
+        <v>487302</v>
       </c>
       <c r="R43" t="n">
-        <v>7039005</v>
+        <v>7039045</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4892,7 +4901,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129298802</v>
+        <v>129298795</v>
       </c>
       <c r="B44" t="n">
         <v>57727</v>
@@ -4927,10 +4936,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>487302</v>
+        <v>487100</v>
       </c>
       <c r="R44" t="n">
-        <v>7039045</v>
+        <v>7039085</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4994,7 +5003,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129298795</v>
+        <v>129298748</v>
       </c>
       <c r="B45" t="n">
         <v>57727</v>
@@ -5029,10 +5038,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>487100</v>
+        <v>487301</v>
       </c>
       <c r="R45" t="n">
-        <v>7039085</v>
+        <v>7038925</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5096,7 +5105,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129298748</v>
+        <v>129298783</v>
       </c>
       <c r="B46" t="n">
         <v>57727</v>
@@ -5131,10 +5140,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>487301</v>
+        <v>487024</v>
       </c>
       <c r="R46" t="n">
-        <v>7038925</v>
+        <v>7039203</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5198,10 +5207,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129298783</v>
+        <v>129298854</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5209,23 +5218,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5233,10 +5238,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>487024</v>
+        <v>487522</v>
       </c>
       <c r="R47" t="n">
-        <v>7039203</v>
+        <v>7038997</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5269,11 +5274,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5397,10 +5397,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129298798</v>
+        <v>129298842</v>
       </c>
       <c r="B49" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5408,21 +5408,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>487131</v>
+        <v>487393</v>
       </c>
       <c r="R49" t="n">
-        <v>7039049</v>
+        <v>7038908</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5468,11 +5468,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5499,7 +5494,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129298810</v>
+        <v>129298798</v>
       </c>
       <c r="B50" t="n">
         <v>57727</v>
@@ -5534,10 +5529,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>487355</v>
+        <v>487131</v>
       </c>
       <c r="R50" t="n">
-        <v>7039005</v>
+        <v>7039049</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5601,10 +5596,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129298842</v>
+        <v>129298810</v>
       </c>
       <c r="B51" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5612,21 +5607,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5636,10 +5631,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>487393</v>
+        <v>487355</v>
       </c>
       <c r="R51" t="n">
-        <v>7038908</v>
+        <v>7039005</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5672,6 +5667,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5892,10 +5892,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129298825</v>
+        <v>129298779</v>
       </c>
       <c r="B54" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5903,21 +5903,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5927,10 +5927,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>487247</v>
+        <v>486866</v>
       </c>
       <c r="R54" t="n">
-        <v>7039020</v>
+        <v>7039259</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5994,7 +5994,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129298779</v>
+        <v>129298749</v>
       </c>
       <c r="B55" t="n">
         <v>57727</v>
@@ -6029,10 +6029,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486866</v>
+        <v>487275</v>
       </c>
       <c r="R55" t="n">
-        <v>7039259</v>
+        <v>7038947</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6096,10 +6096,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129298749</v>
+        <v>129298825</v>
       </c>
       <c r="B56" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6107,21 +6107,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6131,10 +6131,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>487275</v>
+        <v>487247</v>
       </c>
       <c r="R56" t="n">
-        <v>7038947</v>
+        <v>7039020</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7014,10 +7014,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129298741</v>
+        <v>129298853</v>
       </c>
       <c r="B65" t="n">
-        <v>91553</v>
+        <v>91573</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7025,23 +7025,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7049,10 +7045,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>487185</v>
+        <v>487415</v>
       </c>
       <c r="R65" t="n">
-        <v>7039203</v>
+        <v>7038971</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7111,10 +7107,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129298853</v>
+        <v>129298741</v>
       </c>
       <c r="B66" t="n">
-        <v>91573</v>
+        <v>91553</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7122,19 +7118,23 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7142,10 +7142,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>487415</v>
+        <v>487185</v>
       </c>
       <c r="R66" t="n">
-        <v>7038971</v>
+        <v>7039203</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9031,61 +9031,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129298847</v>
+        <v>129298789</v>
       </c>
       <c r="B85" t="n">
-        <v>57587</v>
+        <v>57727</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100136</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>486999</v>
+        <v>487041</v>
       </c>
       <c r="R85" t="n">
-        <v>7039199</v>
+        <v>7039167</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9122,7 +9106,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Jagades av en nötskrika</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9149,7 +9133,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129298789</v>
+        <v>129298801</v>
       </c>
       <c r="B86" t="n">
         <v>57727</v>
@@ -9184,10 +9168,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>487041</v>
+        <v>487268</v>
       </c>
       <c r="R86" t="n">
-        <v>7039167</v>
+        <v>7039003</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9251,7 +9235,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129298801</v>
+        <v>129298814</v>
       </c>
       <c r="B87" t="n">
         <v>57727</v>
@@ -9286,10 +9270,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>487268</v>
+        <v>487366</v>
       </c>
       <c r="R87" t="n">
-        <v>7039003</v>
+        <v>7038997</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9326,7 +9310,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9353,7 +9337,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129298814</v>
+        <v>129298772</v>
       </c>
       <c r="B88" t="n">
         <v>57727</v>
@@ -9388,10 +9372,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>487366</v>
+        <v>486849</v>
       </c>
       <c r="R88" t="n">
-        <v>7038997</v>
+        <v>7039185</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9428,7 +9412,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9455,7 +9439,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129298772</v>
+        <v>129298746</v>
       </c>
       <c r="B89" t="n">
         <v>57727</v>
@@ -9490,10 +9474,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>486849</v>
+        <v>487316</v>
       </c>
       <c r="R89" t="n">
-        <v>7039185</v>
+        <v>7038914</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9557,45 +9541,61 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129298746</v>
+        <v>129298847</v>
       </c>
       <c r="B90" t="n">
-        <v>57727</v>
+        <v>57587</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>100136</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>487316</v>
+        <v>486999</v>
       </c>
       <c r="R90" t="n">
-        <v>7038914</v>
+        <v>7039199</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9632,7 +9632,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Jagades av en nötskrika</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9659,10 +9659,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129298743</v>
+        <v>129298836</v>
       </c>
       <c r="B91" t="n">
-        <v>91553</v>
+        <v>80149</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9670,21 +9670,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9694,10 +9694,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>487331</v>
+        <v>486899</v>
       </c>
       <c r="R91" t="n">
-        <v>7039023</v>
+        <v>7039370</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9960,10 +9960,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129298836</v>
+        <v>129298743</v>
       </c>
       <c r="B94" t="n">
-        <v>80149</v>
+        <v>91553</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9971,21 +9971,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9995,10 +9995,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>486899</v>
+        <v>487331</v>
       </c>
       <c r="R94" t="n">
-        <v>7039370</v>
+        <v>7039023</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10057,32 +10057,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129298739</v>
+        <v>129298745</v>
       </c>
       <c r="B95" t="n">
-        <v>91517</v>
+        <v>57727</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10092,10 +10092,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>487384</v>
+        <v>486881</v>
       </c>
       <c r="R95" t="n">
-        <v>7038973</v>
+        <v>7039175</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10128,6 +10128,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10154,7 +10159,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129298745</v>
+        <v>129298791</v>
       </c>
       <c r="B96" t="n">
         <v>57727</v>
@@ -10189,10 +10194,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>486881</v>
+        <v>487112</v>
       </c>
       <c r="R96" t="n">
-        <v>7039175</v>
+        <v>7039182</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10256,7 +10261,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129298791</v>
+        <v>129298754</v>
       </c>
       <c r="B97" t="n">
         <v>57727</v>
@@ -10291,10 +10296,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>487112</v>
+        <v>487222</v>
       </c>
       <c r="R97" t="n">
-        <v>7039182</v>
+        <v>7038974</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10331,7 +10336,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10358,32 +10363,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129298754</v>
+        <v>129298739</v>
       </c>
       <c r="B98" t="n">
-        <v>57727</v>
+        <v>91517</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10393,10 +10398,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>487222</v>
+        <v>487384</v>
       </c>
       <c r="R98" t="n">
-        <v>7038974</v>
+        <v>7038973</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10429,11 +10434,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10675,32 +10675,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129298832</v>
+        <v>129298806</v>
       </c>
       <c r="B101" t="n">
-        <v>83003</v>
+        <v>57727</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10710,10 +10710,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>487393</v>
+        <v>487339</v>
       </c>
       <c r="R101" t="n">
-        <v>7038976</v>
+        <v>7039009</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10746,6 +10746,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10772,10 +10777,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129298858</v>
+        <v>129298782</v>
       </c>
       <c r="B102" t="n">
-        <v>83004</v>
+        <v>57727</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10783,21 +10788,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10807,10 +10812,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>487408</v>
+        <v>486857</v>
       </c>
       <c r="R102" t="n">
-        <v>7038959</v>
+        <v>7039276</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10843,6 +10848,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10869,7 +10879,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129298806</v>
+        <v>129298758</v>
       </c>
       <c r="B103" t="n">
         <v>57727</v>
@@ -10904,10 +10914,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>487339</v>
+        <v>487183</v>
       </c>
       <c r="R103" t="n">
-        <v>7039009</v>
+        <v>7038993</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10971,7 +10981,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129298782</v>
+        <v>129298815</v>
       </c>
       <c r="B104" t="n">
         <v>57727</v>
@@ -11006,10 +11016,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>486857</v>
+        <v>487375</v>
       </c>
       <c r="R104" t="n">
-        <v>7039276</v>
+        <v>7038981</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11046,7 +11056,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11073,7 +11083,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129298758</v>
+        <v>129298788</v>
       </c>
       <c r="B105" t="n">
         <v>57727</v>
@@ -11108,10 +11118,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>487183</v>
+        <v>487039</v>
       </c>
       <c r="R105" t="n">
-        <v>7038993</v>
+        <v>7039164</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11175,32 +11185,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129298815</v>
+        <v>129298832</v>
       </c>
       <c r="B106" t="n">
-        <v>57727</v>
+        <v>83003</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11210,10 +11220,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>487375</v>
+        <v>487393</v>
       </c>
       <c r="R106" t="n">
-        <v>7038981</v>
+        <v>7038976</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11246,11 +11256,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11277,10 +11282,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129298788</v>
+        <v>129298858</v>
       </c>
       <c r="B107" t="n">
-        <v>57727</v>
+        <v>83004</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11288,21 +11293,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11312,10 +11317,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>487039</v>
+        <v>487408</v>
       </c>
       <c r="R107" t="n">
-        <v>7039164</v>
+        <v>7038959</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11348,11 +11353,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD107" t="b">

--- a/artfynd/A 46357-2025 artfynd.xlsx
+++ b/artfynd/A 46357-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129298827</v>
+        <v>129298751</v>
       </c>
       <c r="B2" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487352</v>
+        <v>487263</v>
       </c>
       <c r="R2" t="n">
-        <v>7038906</v>
+        <v>7038949</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129298844</v>
+        <v>129298786</v>
       </c>
       <c r="B3" t="n">
-        <v>78057</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487374</v>
+        <v>487006</v>
       </c>
       <c r="R3" t="n">
-        <v>7039027</v>
+        <v>7039175</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129298851</v>
+        <v>129298818</v>
       </c>
       <c r="B4" t="n">
-        <v>91567</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487144</v>
+        <v>487389</v>
       </c>
       <c r="R4" t="n">
-        <v>7039078</v>
+        <v>7038925</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,6 +950,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129298751</v>
+        <v>129298819</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1006,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>487263</v>
+        <v>487346</v>
       </c>
       <c r="R5" t="n">
-        <v>7038949</v>
+        <v>7038911</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129298786</v>
+        <v>129298827</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>487006</v>
+        <v>487352</v>
       </c>
       <c r="R6" t="n">
-        <v>7039175</v>
+        <v>7038906</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1148,7 +1158,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129298818</v>
+        <v>129298851</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>91567</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>487389</v>
+        <v>487144</v>
       </c>
       <c r="R7" t="n">
-        <v>7038925</v>
+        <v>7039078</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,11 +1256,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,10 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129298819</v>
+        <v>129298844</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>78057</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1293,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>487346</v>
+        <v>487374</v>
       </c>
       <c r="R8" t="n">
-        <v>7038911</v>
+        <v>7039027</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1348,11 +1353,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129298742</v>
+        <v>129298838</v>
       </c>
       <c r="B9" t="n">
-        <v>91553</v>
+        <v>80149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1390,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>487129</v>
+        <v>487035</v>
       </c>
       <c r="R9" t="n">
-        <v>7039097</v>
+        <v>7039161</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1680,10 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129298838</v>
+        <v>129298742</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>91553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,21 +1691,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1715,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>487035</v>
+        <v>487129</v>
       </c>
       <c r="R12" t="n">
-        <v>7039161</v>
+        <v>7039097</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2180,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129298855</v>
+        <v>129298777</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>487542</v>
+        <v>486860</v>
       </c>
       <c r="R17" t="n">
-        <v>7038985</v>
+        <v>7039254</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2251,6 +2251,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2277,7 +2282,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129298777</v>
+        <v>129298787</v>
       </c>
       <c r="B18" t="n">
         <v>57727</v>
@@ -2312,10 +2317,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486860</v>
+        <v>486999</v>
       </c>
       <c r="R18" t="n">
-        <v>7039254</v>
+        <v>7039162</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2352,7 +2357,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2379,10 +2384,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129298787</v>
+        <v>129298855</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2390,21 +2395,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2414,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486999</v>
+        <v>487542</v>
       </c>
       <c r="R19" t="n">
-        <v>7039162</v>
+        <v>7038985</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2450,11 +2455,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2481,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129298837</v>
+        <v>129298852</v>
       </c>
       <c r="B20" t="n">
-        <v>80149</v>
+        <v>91567</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>487004</v>
+        <v>487127</v>
       </c>
       <c r="R20" t="n">
-        <v>7039214</v>
+        <v>7039070</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129298852</v>
+        <v>129298837</v>
       </c>
       <c r="B22" t="n">
-        <v>91567</v>
+        <v>80149</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,21 +2686,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>487127</v>
+        <v>487004</v>
       </c>
       <c r="R22" t="n">
-        <v>7039070</v>
+        <v>7039214</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2772,27 +2772,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129298830</v>
+        <v>129298775</v>
       </c>
       <c r="B23" t="n">
-        <v>57568</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2800,29 +2800,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>487123</v>
+        <v>486860</v>
       </c>
       <c r="R23" t="n">
-        <v>7039173</v>
+        <v>7039244</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2855,6 +2843,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2881,10 +2874,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129298845</v>
+        <v>129298808</v>
       </c>
       <c r="B24" t="n">
-        <v>78057</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2892,21 +2885,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2916,10 +2909,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>487526</v>
+        <v>487344</v>
       </c>
       <c r="R24" t="n">
-        <v>7039006</v>
+        <v>7039018</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2952,6 +2945,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2978,7 +2976,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129298775</v>
+        <v>129298780</v>
       </c>
       <c r="B25" t="n">
         <v>57727</v>
@@ -3013,10 +3011,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486860</v>
+        <v>486859</v>
       </c>
       <c r="R25" t="n">
-        <v>7039244</v>
+        <v>7039262</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3053,7 +3051,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3080,27 +3078,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129298808</v>
+        <v>129298830</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>57568</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3108,17 +3106,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>487344</v>
+        <v>487123</v>
       </c>
       <c r="R26" t="n">
-        <v>7039018</v>
+        <v>7039173</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3151,11 +3161,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3182,10 +3187,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129298780</v>
+        <v>129298845</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>78057</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3193,21 +3198,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3217,10 +3222,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>486859</v>
+        <v>487526</v>
       </c>
       <c r="R27" t="n">
-        <v>7039262</v>
+        <v>7039006</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3253,11 +3258,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3284,10 +3284,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129298793</v>
+        <v>129298843</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3295,21 +3295,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3319,10 +3319,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>487183</v>
+        <v>487391</v>
       </c>
       <c r="R28" t="n">
-        <v>7039216</v>
+        <v>7038927</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3355,11 +3355,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3386,27 +3381,27 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129298823</v>
+        <v>129298846</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3421,10 +3416,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>487363</v>
+        <v>486976</v>
       </c>
       <c r="R29" t="n">
-        <v>7038902</v>
+        <v>7039216</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3457,11 +3452,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3488,7 +3478,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129298765</v>
+        <v>129298793</v>
       </c>
       <c r="B30" t="n">
         <v>57727</v>
@@ -3523,10 +3513,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>487122</v>
+        <v>487183</v>
       </c>
       <c r="R30" t="n">
-        <v>7039034</v>
+        <v>7039216</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3590,7 +3580,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129298770</v>
+        <v>129298823</v>
       </c>
       <c r="B31" t="n">
         <v>57727</v>
@@ -3625,10 +3615,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>486972</v>
+        <v>487363</v>
       </c>
       <c r="R31" t="n">
-        <v>7039122</v>
+        <v>7038902</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3692,7 +3682,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129298778</v>
+        <v>129298765</v>
       </c>
       <c r="B32" t="n">
         <v>57727</v>
@@ -3727,10 +3717,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486871</v>
+        <v>487122</v>
       </c>
       <c r="R32" t="n">
-        <v>7039260</v>
+        <v>7039034</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3794,27 +3784,27 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129298846</v>
+        <v>129298770</v>
       </c>
       <c r="B33" t="n">
-        <v>57831</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3829,10 +3819,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486976</v>
+        <v>486972</v>
       </c>
       <c r="R33" t="n">
-        <v>7039216</v>
+        <v>7039122</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3865,6 +3855,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3891,10 +3886,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129298843</v>
+        <v>129298778</v>
       </c>
       <c r="B34" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3902,21 +3897,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3926,10 +3921,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>487391</v>
+        <v>486871</v>
       </c>
       <c r="R34" t="n">
-        <v>7038927</v>
+        <v>7039260</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3962,6 +3957,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4498,10 +4498,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129298833</v>
+        <v>129298840</v>
       </c>
       <c r="B40" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4509,21 +4509,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>487265</v>
+        <v>487314</v>
       </c>
       <c r="R40" t="n">
-        <v>7038997</v>
+        <v>7039005</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4595,10 +4595,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129298805</v>
+        <v>129298833</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4606,21 +4606,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4630,10 +4630,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>487346</v>
+        <v>487265</v>
       </c>
       <c r="R41" t="n">
-        <v>7039012</v>
+        <v>7038997</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4666,11 +4666,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4697,10 +4692,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129298809</v>
+        <v>129298854</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4708,23 +4703,19 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -4732,10 +4723,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>487348</v>
+        <v>487522</v>
       </c>
       <c r="R42" t="n">
-        <v>7039005</v>
+        <v>7038997</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4768,11 +4759,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4799,7 +4785,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129298802</v>
+        <v>129298805</v>
       </c>
       <c r="B43" t="n">
         <v>57727</v>
@@ -4834,10 +4820,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>487302</v>
+        <v>487346</v>
       </c>
       <c r="R43" t="n">
-        <v>7039045</v>
+        <v>7039012</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4901,7 +4887,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129298795</v>
+        <v>129298809</v>
       </c>
       <c r="B44" t="n">
         <v>57727</v>
@@ -4936,10 +4922,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>487100</v>
+        <v>487348</v>
       </c>
       <c r="R44" t="n">
-        <v>7039085</v>
+        <v>7039005</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5003,7 +4989,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129298748</v>
+        <v>129298802</v>
       </c>
       <c r="B45" t="n">
         <v>57727</v>
@@ -5038,10 +5024,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>487301</v>
+        <v>487302</v>
       </c>
       <c r="R45" t="n">
-        <v>7038925</v>
+        <v>7039045</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5105,7 +5091,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129298783</v>
+        <v>129298795</v>
       </c>
       <c r="B46" t="n">
         <v>57727</v>
@@ -5140,10 +5126,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>487024</v>
+        <v>487100</v>
       </c>
       <c r="R46" t="n">
-        <v>7039203</v>
+        <v>7039085</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5207,10 +5193,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129298854</v>
+        <v>129298748</v>
       </c>
       <c r="B47" t="n">
-        <v>91573</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5218,19 +5204,23 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5238,10 +5228,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>487522</v>
+        <v>487301</v>
       </c>
       <c r="R47" t="n">
-        <v>7038997</v>
+        <v>7038925</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5274,6 +5264,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5300,10 +5295,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129298840</v>
+        <v>129298783</v>
       </c>
       <c r="B48" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5311,21 +5306,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5335,10 +5330,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>487314</v>
+        <v>487024</v>
       </c>
       <c r="R48" t="n">
-        <v>7039005</v>
+        <v>7039203</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5371,6 +5366,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5494,10 +5494,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129298798</v>
+        <v>129298856</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>82878</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5505,21 +5505,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5529,10 +5529,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>487131</v>
+        <v>487541</v>
       </c>
       <c r="R50" t="n">
-        <v>7039049</v>
+        <v>7038983</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5565,11 +5565,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5596,10 +5591,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129298810</v>
+        <v>129298738</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>96973</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5607,21 +5602,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5631,10 +5626,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>487355</v>
+        <v>487311</v>
       </c>
       <c r="R51" t="n">
-        <v>7039005</v>
+        <v>7039063</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5667,11 +5662,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5698,10 +5688,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129298738</v>
+        <v>129298798</v>
       </c>
       <c r="B52" t="n">
-        <v>96973</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5709,21 +5699,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5733,10 +5723,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>487311</v>
+        <v>487131</v>
       </c>
       <c r="R52" t="n">
-        <v>7039063</v>
+        <v>7039049</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5769,6 +5759,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5795,10 +5790,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129298856</v>
+        <v>129298810</v>
       </c>
       <c r="B53" t="n">
-        <v>82878</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5806,21 +5801,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5830,10 +5825,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>487541</v>
+        <v>487355</v>
       </c>
       <c r="R53" t="n">
-        <v>7038983</v>
+        <v>7039005</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5866,6 +5861,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6198,10 +6198,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129298767</v>
+        <v>129298826</v>
       </c>
       <c r="B57" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6209,21 +6209,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6233,10 +6233,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>487123</v>
+        <v>487457</v>
       </c>
       <c r="R57" t="n">
-        <v>7039031</v>
+        <v>7038967</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6300,7 +6300,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129298776</v>
+        <v>129298767</v>
       </c>
       <c r="B58" t="n">
         <v>57727</v>
@@ -6335,10 +6335,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>486855</v>
+        <v>487123</v>
       </c>
       <c r="R58" t="n">
-        <v>7039252</v>
+        <v>7039031</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6402,7 +6402,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129298816</v>
+        <v>129298776</v>
       </c>
       <c r="B59" t="n">
         <v>57727</v>
@@ -6437,10 +6437,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>487389</v>
+        <v>486855</v>
       </c>
       <c r="R59" t="n">
-        <v>7038985</v>
+        <v>7039252</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6504,7 +6504,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129298813</v>
+        <v>129298816</v>
       </c>
       <c r="B60" t="n">
         <v>57727</v>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>487367</v>
+        <v>487389</v>
       </c>
       <c r="R60" t="n">
-        <v>7038998</v>
+        <v>7038985</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6606,7 +6606,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129298820</v>
+        <v>129298813</v>
       </c>
       <c r="B61" t="n">
         <v>57727</v>
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>487354</v>
+        <v>487367</v>
       </c>
       <c r="R61" t="n">
-        <v>7038894</v>
+        <v>7038998</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6708,7 +6708,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129298774</v>
+        <v>129298820</v>
       </c>
       <c r="B62" t="n">
         <v>57727</v>
@@ -6743,10 +6743,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>486866</v>
+        <v>487354</v>
       </c>
       <c r="R62" t="n">
-        <v>7039249</v>
+        <v>7038894</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6783,7 +6783,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6810,7 +6810,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129298773</v>
+        <v>129298774</v>
       </c>
       <c r="B63" t="n">
         <v>57727</v>
@@ -6845,10 +6845,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>486807</v>
+        <v>486866</v>
       </c>
       <c r="R63" t="n">
-        <v>7039220</v>
+        <v>7039249</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6912,10 +6912,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129298826</v>
+        <v>129298773</v>
       </c>
       <c r="B64" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6923,21 +6923,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6947,10 +6947,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>487457</v>
+        <v>486807</v>
       </c>
       <c r="R64" t="n">
-        <v>7038967</v>
+        <v>7039220</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6987,7 +6987,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7014,10 +7014,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129298853</v>
+        <v>129298741</v>
       </c>
       <c r="B65" t="n">
-        <v>91573</v>
+        <v>91553</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7025,19 +7025,23 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7045,10 +7049,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>487415</v>
+        <v>487185</v>
       </c>
       <c r="R65" t="n">
-        <v>7038971</v>
+        <v>7039203</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7107,10 +7111,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129298741</v>
+        <v>129298853</v>
       </c>
       <c r="B66" t="n">
-        <v>91553</v>
+        <v>91573</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7118,23 +7122,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7142,10 +7142,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>487185</v>
+        <v>487415</v>
       </c>
       <c r="R66" t="n">
-        <v>7039203</v>
+        <v>7038971</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7306,32 +7306,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129298828</v>
+        <v>129298737</v>
       </c>
       <c r="B68" t="n">
-        <v>80178</v>
+        <v>83012</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7341,10 +7341,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>487269</v>
+        <v>487523</v>
       </c>
       <c r="R68" t="n">
-        <v>7039004</v>
+        <v>7039001</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7403,32 +7403,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129298839</v>
+        <v>129298831</v>
       </c>
       <c r="B69" t="n">
-        <v>80149</v>
+        <v>83003</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>492</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7438,10 +7438,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>487269</v>
+        <v>487307</v>
       </c>
       <c r="R69" t="n">
-        <v>7039001</v>
+        <v>7039016</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7500,32 +7500,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129298797</v>
+        <v>129298828</v>
       </c>
       <c r="B70" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7535,10 +7535,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>487134</v>
+        <v>487269</v>
       </c>
       <c r="R70" t="n">
-        <v>7039037</v>
+        <v>7039004</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7571,11 +7571,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7602,10 +7597,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129298803</v>
+        <v>129298839</v>
       </c>
       <c r="B71" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7613,21 +7608,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7637,10 +7632,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>487303</v>
+        <v>487269</v>
       </c>
       <c r="R71" t="n">
-        <v>7039037</v>
+        <v>7039001</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7673,11 +7668,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7704,7 +7694,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129298822</v>
+        <v>129298797</v>
       </c>
       <c r="B72" t="n">
         <v>57727</v>
@@ -7739,10 +7729,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>487373</v>
+        <v>487134</v>
       </c>
       <c r="R72" t="n">
-        <v>7038897</v>
+        <v>7039037</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7806,7 +7796,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129298817</v>
+        <v>129298803</v>
       </c>
       <c r="B73" t="n">
         <v>57727</v>
@@ -7841,10 +7831,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>487460</v>
+        <v>487303</v>
       </c>
       <c r="R73" t="n">
-        <v>7038984</v>
+        <v>7039037</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7908,7 +7898,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129298800</v>
+        <v>129298822</v>
       </c>
       <c r="B74" t="n">
         <v>57727</v>
@@ -7936,33 +7926,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>487288</v>
+        <v>487373</v>
       </c>
       <c r="R74" t="n">
-        <v>7039015</v>
+        <v>7038897</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7999,7 +7973,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Födosökande hane</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8026,7 +8000,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129298821</v>
+        <v>129298817</v>
       </c>
       <c r="B75" t="n">
         <v>57727</v>
@@ -8061,10 +8035,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>487368</v>
+        <v>487460</v>
       </c>
       <c r="R75" t="n">
-        <v>7038892</v>
+        <v>7038984</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8128,45 +8102,61 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129298831</v>
+        <v>129298800</v>
       </c>
       <c r="B76" t="n">
-        <v>83003</v>
+        <v>57727</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>487307</v>
+        <v>487288</v>
       </c>
       <c r="R76" t="n">
-        <v>7039016</v>
+        <v>7039015</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8199,6 +8189,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Födosökande hane</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8225,10 +8220,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129298737</v>
+        <v>129298821</v>
       </c>
       <c r="B77" t="n">
-        <v>83012</v>
+        <v>57727</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8236,21 +8231,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8260,10 +8255,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>487523</v>
+        <v>487368</v>
       </c>
       <c r="R77" t="n">
-        <v>7039001</v>
+        <v>7038892</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8296,6 +8291,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8832,10 +8832,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129298841</v>
+        <v>129298771</v>
       </c>
       <c r="B83" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8843,21 +8843,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8867,10 +8867,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>487515</v>
+        <v>486885</v>
       </c>
       <c r="R83" t="n">
-        <v>7038993</v>
+        <v>7039172</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8903,6 +8903,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8929,45 +8934,61 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129298771</v>
+        <v>129298847</v>
       </c>
       <c r="B84" t="n">
-        <v>57727</v>
+        <v>57587</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>100136</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>486885</v>
+        <v>486999</v>
       </c>
       <c r="R84" t="n">
-        <v>7039172</v>
+        <v>7039199</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9004,7 +9025,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Jagades av en nötskrika</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9541,61 +9562,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129298847</v>
+        <v>129298841</v>
       </c>
       <c r="B90" t="n">
-        <v>57587</v>
+        <v>80149</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100136</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>486999</v>
+        <v>487515</v>
       </c>
       <c r="R90" t="n">
-        <v>7039199</v>
+        <v>7038993</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9628,11 +9633,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Jagades av en nötskrika</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9659,10 +9659,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129298836</v>
+        <v>129298743</v>
       </c>
       <c r="B91" t="n">
-        <v>80149</v>
+        <v>91553</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9670,21 +9670,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9694,10 +9694,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>486899</v>
+        <v>487331</v>
       </c>
       <c r="R91" t="n">
-        <v>7039370</v>
+        <v>7039023</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9756,10 +9756,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129298752</v>
+        <v>129298836</v>
       </c>
       <c r="B92" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9767,21 +9767,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9791,10 +9791,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>487246</v>
+        <v>486899</v>
       </c>
       <c r="R92" t="n">
-        <v>7038958</v>
+        <v>7039370</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9827,11 +9827,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9858,7 +9853,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129298768</v>
+        <v>129298752</v>
       </c>
       <c r="B93" t="n">
         <v>57727</v>
@@ -9893,10 +9888,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>487123</v>
+        <v>487246</v>
       </c>
       <c r="R93" t="n">
-        <v>7039032</v>
+        <v>7038958</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9960,10 +9955,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129298743</v>
+        <v>129298768</v>
       </c>
       <c r="B94" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9971,21 +9966,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9995,10 +9990,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>487331</v>
+        <v>487123</v>
       </c>
       <c r="R94" t="n">
-        <v>7039023</v>
+        <v>7039032</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10031,6 +10026,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10057,32 +10057,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129298745</v>
+        <v>129298739</v>
       </c>
       <c r="B95" t="n">
-        <v>57727</v>
+        <v>91517</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10092,10 +10092,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>486881</v>
+        <v>487384</v>
       </c>
       <c r="R95" t="n">
-        <v>7039175</v>
+        <v>7038973</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10128,11 +10128,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10159,7 +10154,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129298791</v>
+        <v>129298745</v>
       </c>
       <c r="B96" t="n">
         <v>57727</v>
@@ -10194,10 +10189,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>487112</v>
+        <v>486881</v>
       </c>
       <c r="R96" t="n">
-        <v>7039182</v>
+        <v>7039175</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10261,7 +10256,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129298754</v>
+        <v>129298791</v>
       </c>
       <c r="B97" t="n">
         <v>57727</v>
@@ -10296,10 +10291,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>487222</v>
+        <v>487112</v>
       </c>
       <c r="R97" t="n">
-        <v>7038974</v>
+        <v>7039182</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10336,7 +10331,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10363,32 +10358,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129298739</v>
+        <v>129298754</v>
       </c>
       <c r="B98" t="n">
-        <v>91517</v>
+        <v>57727</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10398,10 +10393,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>487384</v>
+        <v>487222</v>
       </c>
       <c r="R98" t="n">
-        <v>7038973</v>
+        <v>7038974</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10434,6 +10429,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10460,10 +10460,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129298829</v>
+        <v>129298807</v>
       </c>
       <c r="B99" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10471,16 +10471,16 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -10488,33 +10488,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>487157</v>
+        <v>487337</v>
       </c>
       <c r="R99" t="n">
-        <v>7039100</v>
+        <v>7039015</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10547,6 +10531,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10573,10 +10562,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129298807</v>
+        <v>129298829</v>
       </c>
       <c r="B100" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10584,16 +10573,16 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -10601,17 +10590,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>487337</v>
+        <v>487157</v>
       </c>
       <c r="R100" t="n">
-        <v>7039015</v>
+        <v>7039100</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10644,11 +10649,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11185,32 +11185,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129298832</v>
+        <v>129298858</v>
       </c>
       <c r="B106" t="n">
-        <v>83003</v>
+        <v>83004</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>492</v>
+        <v>308</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11220,10 +11220,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>487393</v>
+        <v>487408</v>
       </c>
       <c r="R106" t="n">
-        <v>7038976</v>
+        <v>7038959</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11282,32 +11282,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129298858</v>
+        <v>129298832</v>
       </c>
       <c r="B107" t="n">
-        <v>83004</v>
+        <v>83003</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>308</v>
+        <v>492</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11317,10 +11317,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>487408</v>
+        <v>487393</v>
       </c>
       <c r="R107" t="n">
-        <v>7038959</v>
+        <v>7038976</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>

--- a/artfynd/A 46357-2025 artfynd.xlsx
+++ b/artfynd/A 46357-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129298751</v>
+        <v>129298851</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>91595</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487263</v>
+        <v>487144</v>
       </c>
       <c r="R2" t="n">
-        <v>7038949</v>
+        <v>7039078</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129298786</v>
+        <v>129298751</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487006</v>
+        <v>487263</v>
       </c>
       <c r="R3" t="n">
-        <v>7039175</v>
+        <v>7038949</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129298818</v>
+        <v>129298786</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487389</v>
+        <v>487006</v>
       </c>
       <c r="R4" t="n">
-        <v>7038925</v>
+        <v>7039175</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129298819</v>
+        <v>129298818</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>487346</v>
+        <v>487389</v>
       </c>
       <c r="R5" t="n">
-        <v>7038911</v>
+        <v>7038925</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129298827</v>
+        <v>129298819</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>57730</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>487352</v>
+        <v>487346</v>
       </c>
       <c r="R6" t="n">
-        <v>7038906</v>
+        <v>7038911</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,7 +1153,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129298851</v>
+        <v>129298827</v>
       </c>
       <c r="B7" t="n">
-        <v>91567</v>
+        <v>57890</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1220,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>487144</v>
+        <v>487352</v>
       </c>
       <c r="R7" t="n">
-        <v>7039078</v>
+        <v>7038906</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1256,6 +1251,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,7 +1285,7 @@
         <v>129298844</v>
       </c>
       <c r="B8" t="n">
-        <v>78057</v>
+        <v>78083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129298838</v>
+        <v>129298742</v>
       </c>
       <c r="B9" t="n">
-        <v>80149</v>
+        <v>91581</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1390,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>487035</v>
+        <v>487129</v>
       </c>
       <c r="R9" t="n">
-        <v>7039161</v>
+        <v>7039097</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129298812</v>
+        <v>129298838</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>80175</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,21 +1487,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>487362</v>
+        <v>487035</v>
       </c>
       <c r="R10" t="n">
-        <v>7039030</v>
+        <v>7039161</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1547,11 +1547,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,10 +1573,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129298759</v>
+        <v>129298812</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1613,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>487171</v>
+        <v>487362</v>
       </c>
       <c r="R11" t="n">
-        <v>7039000</v>
+        <v>7039030</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1680,10 +1675,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129298742</v>
+        <v>129298759</v>
       </c>
       <c r="B12" t="n">
-        <v>91553</v>
+        <v>57730</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,21 +1686,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1715,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>487129</v>
+        <v>487171</v>
       </c>
       <c r="R12" t="n">
-        <v>7039097</v>
+        <v>7039000</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,6 +1746,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1780,7 +1780,7 @@
         <v>129298761</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>129298755</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>129298799</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>129298857</v>
       </c>
       <c r="B16" t="n">
-        <v>83004</v>
+        <v>83031</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2180,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129298777</v>
+        <v>129298855</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486860</v>
+        <v>487542</v>
       </c>
       <c r="R17" t="n">
-        <v>7039254</v>
+        <v>7038985</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2251,11 +2251,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2282,10 +2277,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129298787</v>
+        <v>129298777</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2317,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486999</v>
+        <v>486860</v>
       </c>
       <c r="R18" t="n">
-        <v>7039162</v>
+        <v>7039254</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2357,7 +2352,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2384,10 +2379,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129298855</v>
+        <v>129298787</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>57730</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2395,21 +2390,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2419,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>487542</v>
+        <v>486999</v>
       </c>
       <c r="R19" t="n">
-        <v>7038985</v>
+        <v>7039162</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2455,6 +2450,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2481,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129298852</v>
+        <v>129298740</v>
       </c>
       <c r="B20" t="n">
-        <v>91567</v>
+        <v>91581</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>487127</v>
+        <v>487145</v>
       </c>
       <c r="R20" t="n">
-        <v>7039070</v>
+        <v>7039179</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129298740</v>
+        <v>129298852</v>
       </c>
       <c r="B21" t="n">
-        <v>91553</v>
+        <v>91595</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2589,21 +2589,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>487145</v>
+        <v>487127</v>
       </c>
       <c r="R21" t="n">
-        <v>7039179</v>
+        <v>7039070</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129298837</v>
+        <v>129298845</v>
       </c>
       <c r="B22" t="n">
-        <v>80149</v>
+        <v>78083</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,21 +2686,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>487004</v>
+        <v>487526</v>
       </c>
       <c r="R22" t="n">
-        <v>7039214</v>
+        <v>7039006</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2772,10 +2772,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129298775</v>
+        <v>129298837</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>80175</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2783,21 +2783,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2807,10 +2807,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>486860</v>
+        <v>487004</v>
       </c>
       <c r="R23" t="n">
-        <v>7039244</v>
+        <v>7039214</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2843,11 +2843,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2874,10 +2869,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129298808</v>
+        <v>129298775</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2909,10 +2904,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>487344</v>
+        <v>486860</v>
       </c>
       <c r="R24" t="n">
-        <v>7039018</v>
+        <v>7039244</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2976,10 +2971,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129298780</v>
+        <v>129298808</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3011,10 +3006,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>486859</v>
+        <v>487344</v>
       </c>
       <c r="R25" t="n">
-        <v>7039262</v>
+        <v>7039018</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3051,7 +3046,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3078,27 +3073,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129298830</v>
+        <v>129298780</v>
       </c>
       <c r="B26" t="n">
-        <v>57568</v>
+        <v>57730</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3106,29 +3101,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>487123</v>
+        <v>486859</v>
       </c>
       <c r="R26" t="n">
-        <v>7039173</v>
+        <v>7039262</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3161,6 +3144,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3187,45 +3175,57 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129298845</v>
+        <v>129298830</v>
       </c>
       <c r="B27" t="n">
-        <v>78057</v>
+        <v>57571</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228579</v>
+        <v>102621</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>487526</v>
+        <v>487123</v>
       </c>
       <c r="R27" t="n">
-        <v>7039006</v>
+        <v>7039173</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3287,7 +3287,7 @@
         <v>129298843</v>
       </c>
       <c r="B28" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3381,27 +3381,27 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129298846</v>
+        <v>129298793</v>
       </c>
       <c r="B29" t="n">
-        <v>57831</v>
+        <v>57730</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3416,7 +3416,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>486976</v>
+        <v>487183</v>
       </c>
       <c r="R29" t="n">
         <v>7039216</v>
@@ -3452,6 +3452,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3478,10 +3483,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129298793</v>
+        <v>129298823</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3513,10 +3518,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>487183</v>
+        <v>487363</v>
       </c>
       <c r="R30" t="n">
-        <v>7039216</v>
+        <v>7038902</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3580,10 +3585,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129298823</v>
+        <v>129298765</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3615,10 +3620,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>487363</v>
+        <v>487122</v>
       </c>
       <c r="R31" t="n">
-        <v>7038902</v>
+        <v>7039034</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3682,10 +3687,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129298765</v>
+        <v>129298770</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3717,10 +3722,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>487122</v>
+        <v>486972</v>
       </c>
       <c r="R32" t="n">
-        <v>7039034</v>
+        <v>7039122</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3784,10 +3789,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129298770</v>
+        <v>129298778</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3819,10 +3824,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486972</v>
+        <v>486871</v>
       </c>
       <c r="R33" t="n">
-        <v>7039122</v>
+        <v>7039260</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3886,27 +3891,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129298778</v>
+        <v>129298846</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>57834</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3921,10 +3926,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486871</v>
+        <v>486976</v>
       </c>
       <c r="R34" t="n">
-        <v>7039260</v>
+        <v>7039216</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3957,11 +3962,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3991,7 +3991,7 @@
         <v>129298792</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>129298750</v>
       </c>
       <c r="B36" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v>129298769</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>129298804</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>129298794</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4498,10 +4498,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129298840</v>
+        <v>129298854</v>
       </c>
       <c r="B40" t="n">
-        <v>80149</v>
+        <v>91601</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4509,23 +4509,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4533,10 +4529,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>487314</v>
+        <v>487522</v>
       </c>
       <c r="R40" t="n">
-        <v>7039005</v>
+        <v>7038997</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4595,10 +4591,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129298833</v>
+        <v>129298840</v>
       </c>
       <c r="B41" t="n">
-        <v>80150</v>
+        <v>80175</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4606,21 +4602,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4630,10 +4626,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>487265</v>
+        <v>487314</v>
       </c>
       <c r="R41" t="n">
-        <v>7038997</v>
+        <v>7039005</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4692,10 +4688,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129298854</v>
+        <v>129298833</v>
       </c>
       <c r="B42" t="n">
-        <v>91573</v>
+        <v>80176</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4703,19 +4699,23 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>487522</v>
+        <v>487265</v>
       </c>
       <c r="R42" t="n">
         <v>7038997</v>
@@ -4788,7 +4788,7 @@
         <v>129298805</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>129298809</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>129298802</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         <v>129298795</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>129298748</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>129298783</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5397,10 +5397,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129298842</v>
+        <v>129298738</v>
       </c>
       <c r="B49" t="n">
-        <v>80149</v>
+        <v>97002</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5408,21 +5408,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>487393</v>
+        <v>487311</v>
       </c>
       <c r="R49" t="n">
-        <v>7038908</v>
+        <v>7039063</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5494,10 +5494,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129298856</v>
+        <v>129298842</v>
       </c>
       <c r="B50" t="n">
-        <v>82878</v>
+        <v>80175</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5505,21 +5505,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5529,10 +5529,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>487541</v>
+        <v>487393</v>
       </c>
       <c r="R50" t="n">
-        <v>7038983</v>
+        <v>7038908</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5591,10 +5591,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129298738</v>
+        <v>129298856</v>
       </c>
       <c r="B51" t="n">
-        <v>96973</v>
+        <v>82905</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5602,21 +5602,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>53</v>
+        <v>1312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5626,10 +5626,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>487311</v>
+        <v>487541</v>
       </c>
       <c r="R51" t="n">
-        <v>7039063</v>
+        <v>7038983</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5691,7 +5691,7 @@
         <v>129298798</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         <v>129298810</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5892,10 +5892,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129298779</v>
+        <v>129298825</v>
       </c>
       <c r="B54" t="n">
-        <v>57727</v>
+        <v>57890</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5903,21 +5903,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5927,10 +5927,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486866</v>
+        <v>487247</v>
       </c>
       <c r="R54" t="n">
-        <v>7039259</v>
+        <v>7039020</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5994,10 +5994,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129298749</v>
+        <v>129298779</v>
       </c>
       <c r="B55" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6029,10 +6029,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>487275</v>
+        <v>486866</v>
       </c>
       <c r="R55" t="n">
-        <v>7038947</v>
+        <v>7039259</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6096,10 +6096,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129298825</v>
+        <v>129298749</v>
       </c>
       <c r="B56" t="n">
-        <v>57887</v>
+        <v>57730</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6107,21 +6107,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6131,10 +6131,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>487247</v>
+        <v>487275</v>
       </c>
       <c r="R56" t="n">
-        <v>7039020</v>
+        <v>7038947</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6201,7 +6201,7 @@
         <v>129298826</v>
       </c>
       <c r="B57" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6303,7 +6303,7 @@
         <v>129298767</v>
       </c>
       <c r="B58" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>129298776</v>
       </c>
       <c r="B59" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>129298816</v>
       </c>
       <c r="B60" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>129298813</v>
       </c>
       <c r="B61" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>129298820</v>
       </c>
       <c r="B62" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>129298774</v>
       </c>
       <c r="B63" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         <v>129298773</v>
       </c>
       <c r="B64" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>129298741</v>
       </c>
       <c r="B65" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>129298853</v>
       </c>
       <c r="B66" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>129298811</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7306,32 +7306,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129298737</v>
+        <v>129298831</v>
       </c>
       <c r="B68" t="n">
-        <v>83012</v>
+        <v>83030</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>492</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7341,10 +7341,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>487523</v>
+        <v>487307</v>
       </c>
       <c r="R68" t="n">
-        <v>7039001</v>
+        <v>7039016</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7403,32 +7403,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129298831</v>
+        <v>129298737</v>
       </c>
       <c r="B69" t="n">
-        <v>83003</v>
+        <v>83039</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>492</v>
+        <v>6440</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7438,10 +7438,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>487307</v>
+        <v>487523</v>
       </c>
       <c r="R69" t="n">
-        <v>7039016</v>
+        <v>7039001</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7503,7 +7503,7 @@
         <v>129298828</v>
       </c>
       <c r="B70" t="n">
-        <v>80178</v>
+        <v>80204</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>129298839</v>
       </c>
       <c r="B71" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>129298797</v>
       </c>
       <c r="B72" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v>129298803</v>
       </c>
       <c r="B73" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>129298822</v>
       </c>
       <c r="B74" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
         <v>129298817</v>
       </c>
       <c r="B75" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>129298800</v>
       </c>
       <c r="B76" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>129298821</v>
       </c>
       <c r="B77" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>129298781</v>
       </c>
       <c r="B78" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>129298785</v>
       </c>
       <c r="B79" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>129298753</v>
       </c>
       <c r="B80" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>129298757</v>
       </c>
       <c r="B81" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>129298784</v>
       </c>
       <c r="B82" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8832,10 +8832,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129298771</v>
+        <v>129298841</v>
       </c>
       <c r="B83" t="n">
-        <v>57727</v>
+        <v>80175</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8843,21 +8843,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8867,10 +8867,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>486885</v>
+        <v>487515</v>
       </c>
       <c r="R83" t="n">
-        <v>7039172</v>
+        <v>7038993</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8903,11 +8903,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8937,7 +8932,7 @@
         <v>129298847</v>
       </c>
       <c r="B84" t="n">
-        <v>57587</v>
+        <v>57590</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9052,10 +9047,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129298789</v>
+        <v>129298771</v>
       </c>
       <c r="B85" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9087,10 +9082,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>487041</v>
+        <v>486885</v>
       </c>
       <c r="R85" t="n">
-        <v>7039167</v>
+        <v>7039172</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9154,10 +9149,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129298801</v>
+        <v>129298789</v>
       </c>
       <c r="B86" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9189,10 +9184,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>487268</v>
+        <v>487041</v>
       </c>
       <c r="R86" t="n">
-        <v>7039003</v>
+        <v>7039167</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9256,10 +9251,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129298814</v>
+        <v>129298801</v>
       </c>
       <c r="B87" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9291,10 +9286,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>487366</v>
+        <v>487268</v>
       </c>
       <c r="R87" t="n">
-        <v>7038997</v>
+        <v>7039003</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9331,7 +9326,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9358,10 +9353,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129298772</v>
+        <v>129298814</v>
       </c>
       <c r="B88" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9393,10 +9388,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>486849</v>
+        <v>487366</v>
       </c>
       <c r="R88" t="n">
-        <v>7039185</v>
+        <v>7038997</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9433,7 +9428,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9460,10 +9455,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129298746</v>
+        <v>129298772</v>
       </c>
       <c r="B89" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9495,10 +9490,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>487316</v>
+        <v>486849</v>
       </c>
       <c r="R89" t="n">
-        <v>7038914</v>
+        <v>7039185</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9562,10 +9557,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129298841</v>
+        <v>129298746</v>
       </c>
       <c r="B90" t="n">
-        <v>80149</v>
+        <v>57730</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9573,21 +9568,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9597,10 +9592,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>487515</v>
+        <v>487316</v>
       </c>
       <c r="R90" t="n">
-        <v>7038993</v>
+        <v>7038914</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9633,6 +9628,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9662,7 +9662,7 @@
         <v>129298743</v>
       </c>
       <c r="B91" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9756,10 +9756,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129298836</v>
+        <v>129298752</v>
       </c>
       <c r="B92" t="n">
-        <v>80149</v>
+        <v>57730</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9767,21 +9767,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9791,10 +9791,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>486899</v>
+        <v>487246</v>
       </c>
       <c r="R92" t="n">
-        <v>7039370</v>
+        <v>7038958</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9827,6 +9827,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9853,10 +9858,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129298752</v>
+        <v>129298768</v>
       </c>
       <c r="B93" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9888,10 +9893,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>487246</v>
+        <v>487123</v>
       </c>
       <c r="R93" t="n">
-        <v>7038958</v>
+        <v>7039032</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9955,10 +9960,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129298768</v>
+        <v>129298836</v>
       </c>
       <c r="B94" t="n">
-        <v>57727</v>
+        <v>80175</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9966,21 +9971,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9990,10 +9995,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>487123</v>
+        <v>486899</v>
       </c>
       <c r="R94" t="n">
-        <v>7039032</v>
+        <v>7039370</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10026,11 +10031,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10057,32 +10057,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129298739</v>
+        <v>129298745</v>
       </c>
       <c r="B95" t="n">
-        <v>91517</v>
+        <v>57730</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10092,10 +10092,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>487384</v>
+        <v>486881</v>
       </c>
       <c r="R95" t="n">
-        <v>7038973</v>
+        <v>7039175</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10128,6 +10128,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10154,10 +10159,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129298745</v>
+        <v>129298791</v>
       </c>
       <c r="B96" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10189,10 +10194,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>486881</v>
+        <v>487112</v>
       </c>
       <c r="R96" t="n">
-        <v>7039175</v>
+        <v>7039182</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10256,10 +10261,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129298791</v>
+        <v>129298754</v>
       </c>
       <c r="B97" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10291,10 +10296,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>487112</v>
+        <v>487222</v>
       </c>
       <c r="R97" t="n">
-        <v>7039182</v>
+        <v>7038974</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10331,7 +10336,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10358,32 +10363,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129298754</v>
+        <v>129298739</v>
       </c>
       <c r="B98" t="n">
-        <v>57727</v>
+        <v>91545</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10393,10 +10398,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>487222</v>
+        <v>487384</v>
       </c>
       <c r="R98" t="n">
-        <v>7038974</v>
+        <v>7038973</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10429,11 +10434,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10463,7 +10463,7 @@
         <v>129298807</v>
       </c>
       <c r="B99" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10565,7 +10565,7 @@
         <v>129298829</v>
       </c>
       <c r="B100" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10675,10 +10675,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129298806</v>
+        <v>129298858</v>
       </c>
       <c r="B101" t="n">
-        <v>57727</v>
+        <v>83031</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10686,21 +10686,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10710,10 +10710,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>487339</v>
+        <v>487408</v>
       </c>
       <c r="R101" t="n">
-        <v>7039009</v>
+        <v>7038959</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10746,11 +10746,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10777,10 +10772,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129298782</v>
+        <v>129298806</v>
       </c>
       <c r="B102" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10812,10 +10807,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>486857</v>
+        <v>487339</v>
       </c>
       <c r="R102" t="n">
-        <v>7039276</v>
+        <v>7039009</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10852,7 +10847,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10879,10 +10874,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129298758</v>
+        <v>129298782</v>
       </c>
       <c r="B103" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10914,10 +10909,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>487183</v>
+        <v>486857</v>
       </c>
       <c r="R103" t="n">
-        <v>7038993</v>
+        <v>7039276</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10954,7 +10949,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10981,10 +10976,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129298815</v>
+        <v>129298758</v>
       </c>
       <c r="B104" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11016,10 +11011,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>487375</v>
+        <v>487183</v>
       </c>
       <c r="R104" t="n">
-        <v>7038981</v>
+        <v>7038993</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11083,10 +11078,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129298788</v>
+        <v>129298815</v>
       </c>
       <c r="B105" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11118,10 +11113,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>487039</v>
+        <v>487375</v>
       </c>
       <c r="R105" t="n">
-        <v>7039164</v>
+        <v>7038981</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11185,10 +11180,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129298858</v>
+        <v>129298788</v>
       </c>
       <c r="B106" t="n">
-        <v>83004</v>
+        <v>57730</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11196,21 +11191,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11220,10 +11215,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>487408</v>
+        <v>487039</v>
       </c>
       <c r="R106" t="n">
-        <v>7038959</v>
+        <v>7039164</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11256,6 +11251,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11285,7 +11285,7 @@
         <v>129298832</v>
       </c>
       <c r="B107" t="n">
-        <v>83003</v>
+        <v>83030</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>129298766</v>
       </c>
       <c r="B108" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11484,7 +11484,7 @@
         <v>129298796</v>
       </c>
       <c r="B109" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>129298760</v>
       </c>
       <c r="B110" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>129298790</v>
       </c>
       <c r="B111" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 46357-2025 artfynd.xlsx
+++ b/artfynd/A 46357-2025 artfynd.xlsx
@@ -1476,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129298838</v>
+        <v>129298812</v>
       </c>
       <c r="B10" t="n">
-        <v>80175</v>
+        <v>57730</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,21 +1487,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>487035</v>
+        <v>487362</v>
       </c>
       <c r="R10" t="n">
-        <v>7039161</v>
+        <v>7039030</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1547,6 +1547,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1573,7 +1578,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129298812</v>
+        <v>129298759</v>
       </c>
       <c r="B11" t="n">
         <v>57730</v>
@@ -1608,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>487362</v>
+        <v>487171</v>
       </c>
       <c r="R11" t="n">
-        <v>7039030</v>
+        <v>7039000</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1675,10 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129298759</v>
+        <v>129298838</v>
       </c>
       <c r="B12" t="n">
-        <v>57730</v>
+        <v>80175</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1686,21 +1691,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1710,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>487171</v>
+        <v>487035</v>
       </c>
       <c r="R12" t="n">
-        <v>7039000</v>
+        <v>7039161</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1746,11 +1751,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -7014,10 +7014,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129298741</v>
+        <v>129298853</v>
       </c>
       <c r="B65" t="n">
-        <v>91581</v>
+        <v>91601</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7025,23 +7025,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7049,10 +7045,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>487185</v>
+        <v>487415</v>
       </c>
       <c r="R65" t="n">
-        <v>7039203</v>
+        <v>7038971</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7111,10 +7107,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129298853</v>
+        <v>129298811</v>
       </c>
       <c r="B66" t="n">
-        <v>91601</v>
+        <v>57730</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7122,19 +7118,23 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7142,10 +7142,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>487415</v>
+        <v>487357</v>
       </c>
       <c r="R66" t="n">
-        <v>7038971</v>
+        <v>7039009</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7178,6 +7178,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7204,10 +7209,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129298811</v>
+        <v>129298741</v>
       </c>
       <c r="B67" t="n">
-        <v>57730</v>
+        <v>91581</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7215,21 +7220,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7239,10 +7244,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>487357</v>
+        <v>487185</v>
       </c>
       <c r="R67" t="n">
-        <v>7039009</v>
+        <v>7039203</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7275,11 +7280,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9659,10 +9659,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129298743</v>
+        <v>129298836</v>
       </c>
       <c r="B91" t="n">
-        <v>91581</v>
+        <v>80175</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9670,21 +9670,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9694,10 +9694,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>487331</v>
+        <v>486899</v>
       </c>
       <c r="R91" t="n">
-        <v>7039023</v>
+        <v>7039370</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9756,10 +9756,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129298752</v>
+        <v>129298743</v>
       </c>
       <c r="B92" t="n">
-        <v>57730</v>
+        <v>91581</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9767,21 +9767,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9791,10 +9791,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>487246</v>
+        <v>487331</v>
       </c>
       <c r="R92" t="n">
-        <v>7038958</v>
+        <v>7039023</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9827,11 +9827,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9858,7 +9853,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129298768</v>
+        <v>129298752</v>
       </c>
       <c r="B93" t="n">
         <v>57730</v>
@@ -9893,10 +9888,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>487123</v>
+        <v>487246</v>
       </c>
       <c r="R93" t="n">
-        <v>7039032</v>
+        <v>7038958</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9960,10 +9955,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129298836</v>
+        <v>129298768</v>
       </c>
       <c r="B94" t="n">
-        <v>80175</v>
+        <v>57730</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9971,21 +9966,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9995,10 +9990,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>486899</v>
+        <v>487123</v>
       </c>
       <c r="R94" t="n">
-        <v>7039370</v>
+        <v>7039032</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10031,6 +10026,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD94" t="b">

--- a/artfynd/A 46357-2025 artfynd.xlsx
+++ b/artfynd/A 46357-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129298851</v>
+        <v>129298844</v>
       </c>
       <c r="B2" t="n">
-        <v>91595</v>
+        <v>78088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>228579</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487144</v>
+        <v>487374</v>
       </c>
       <c r="R2" t="n">
-        <v>7039078</v>
+        <v>7039027</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129298751</v>
+        <v>129298851</v>
       </c>
       <c r="B3" t="n">
-        <v>57730</v>
+        <v>91601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487263</v>
+        <v>487144</v>
       </c>
       <c r="R3" t="n">
-        <v>7038949</v>
+        <v>7039078</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -845,11 +845,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -862,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129298786</v>
+        <v>129298827</v>
       </c>
       <c r="B4" t="n">
-        <v>57730</v>
+        <v>57895</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487006</v>
+        <v>487352</v>
       </c>
       <c r="R4" t="n">
-        <v>7039175</v>
+        <v>7038906</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,7 +944,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -964,22 +959,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129298818</v>
+        <v>129298742</v>
       </c>
       <c r="B5" t="n">
-        <v>57730</v>
+        <v>91587</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>487389</v>
+        <v>487129</v>
       </c>
       <c r="R5" t="n">
-        <v>7038925</v>
+        <v>7039097</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1049,11 +1044,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1066,22 +1056,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129298819</v>
+        <v>129298838</v>
       </c>
       <c r="B6" t="n">
-        <v>57730</v>
+        <v>80180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>487346</v>
+        <v>487035</v>
       </c>
       <c r="R6" t="n">
-        <v>7038911</v>
+        <v>7039161</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1151,11 +1141,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1168,22 +1153,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129298827</v>
+        <v>129298857</v>
       </c>
       <c r="B7" t="n">
-        <v>57890</v>
+        <v>83036</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>487352</v>
+        <v>487340</v>
       </c>
       <c r="R7" t="n">
-        <v>7038906</v>
+        <v>7039016</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1253,11 +1238,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1270,22 +1250,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129298844</v>
+        <v>129298855</v>
       </c>
       <c r="B8" t="n">
-        <v>78083</v>
+        <v>79075</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1293,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1317,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>487374</v>
+        <v>487542</v>
       </c>
       <c r="R8" t="n">
-        <v>7039027</v>
+        <v>7038985</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,22 +1347,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129298742</v>
+        <v>129298845</v>
       </c>
       <c r="B9" t="n">
-        <v>91581</v>
+        <v>78088</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1414,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>487129</v>
+        <v>487526</v>
       </c>
       <c r="R9" t="n">
-        <v>7039097</v>
+        <v>7039006</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,22 +1444,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129298812</v>
+        <v>129298740</v>
       </c>
       <c r="B10" t="n">
-        <v>57730</v>
+        <v>91587</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>487362</v>
+        <v>487145</v>
       </c>
       <c r="R10" t="n">
-        <v>7039030</v>
+        <v>7039179</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1549,11 +1529,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1566,22 +1541,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129298759</v>
+        <v>129298852</v>
       </c>
       <c r="B11" t="n">
-        <v>57730</v>
+        <v>91601</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1613,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>487171</v>
+        <v>487127</v>
       </c>
       <c r="R11" t="n">
-        <v>7039000</v>
+        <v>7039070</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,11 +1626,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1668,22 +1638,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129298838</v>
+        <v>129298837</v>
       </c>
       <c r="B12" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1715,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>487035</v>
+        <v>487004</v>
       </c>
       <c r="R12" t="n">
-        <v>7039161</v>
+        <v>7039214</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1765,22 +1735,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129298761</v>
+        <v>129298843</v>
       </c>
       <c r="B13" t="n">
-        <v>57730</v>
+        <v>80180</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1788,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1812,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>487137</v>
+        <v>487391</v>
       </c>
       <c r="R13" t="n">
-        <v>7039024</v>
+        <v>7038927</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1850,11 +1820,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1867,39 +1832,39 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129298755</v>
+        <v>129298846</v>
       </c>
       <c r="B14" t="n">
-        <v>57730</v>
+        <v>57839</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1914,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>487206</v>
+        <v>486976</v>
       </c>
       <c r="R14" t="n">
-        <v>7038982</v>
+        <v>7039216</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,11 +1917,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -1969,22 +1929,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129298799</v>
+        <v>129298833</v>
       </c>
       <c r="B15" t="n">
-        <v>57730</v>
+        <v>80181</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1992,21 +1952,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2016,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>487230</v>
+        <v>487265</v>
       </c>
       <c r="R15" t="n">
-        <v>7039041</v>
+        <v>7038997</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2054,11 +2014,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2071,22 +2026,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129298857</v>
+        <v>129298854</v>
       </c>
       <c r="B16" t="n">
-        <v>83031</v>
+        <v>91607</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2094,23 +2049,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>308</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2118,10 +2069,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>487340</v>
+        <v>487522</v>
       </c>
       <c r="R16" t="n">
-        <v>7039016</v>
+        <v>7038997</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2168,22 +2119,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129298855</v>
+        <v>129298840</v>
       </c>
       <c r="B17" t="n">
-        <v>79070</v>
+        <v>80180</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2142,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2166,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>487542</v>
+        <v>487314</v>
       </c>
       <c r="R17" t="n">
-        <v>7038985</v>
+        <v>7039005</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2265,22 +2216,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129298777</v>
+        <v>129298856</v>
       </c>
       <c r="B18" t="n">
-        <v>57730</v>
+        <v>82910</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,21 +2239,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2312,10 +2263,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486860</v>
+        <v>487541</v>
       </c>
       <c r="R18" t="n">
-        <v>7039254</v>
+        <v>7038983</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2350,11 +2301,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2367,22 +2313,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129298787</v>
+        <v>129298738</v>
       </c>
       <c r="B19" t="n">
-        <v>57730</v>
+        <v>97014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2390,21 +2336,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2414,10 +2360,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>486999</v>
+        <v>487311</v>
       </c>
       <c r="R19" t="n">
-        <v>7039162</v>
+        <v>7039063</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2452,11 +2398,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2469,22 +2410,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129298740</v>
+        <v>129298842</v>
       </c>
       <c r="B20" t="n">
-        <v>91581</v>
+        <v>80180</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2433,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2457,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>487145</v>
+        <v>487393</v>
       </c>
       <c r="R20" t="n">
-        <v>7039179</v>
+        <v>7038908</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2566,22 +2507,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129298852</v>
+        <v>129298825</v>
       </c>
       <c r="B21" t="n">
-        <v>91595</v>
+        <v>57895</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2589,21 +2530,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1204</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2554,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>487127</v>
+        <v>487247</v>
       </c>
       <c r="R21" t="n">
-        <v>7039070</v>
+        <v>7039020</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2651,6 +2592,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2663,22 +2609,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129298845</v>
+        <v>129298826</v>
       </c>
       <c r="B22" t="n">
-        <v>78083</v>
+        <v>57895</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,21 +2632,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228579</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2710,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>487526</v>
+        <v>487457</v>
       </c>
       <c r="R22" t="n">
-        <v>7039006</v>
+        <v>7038967</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2748,6 +2694,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2760,22 +2711,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129298837</v>
+        <v>129298741</v>
       </c>
       <c r="B23" t="n">
-        <v>80175</v>
+        <v>91587</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2783,21 +2734,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2807,10 +2758,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>487004</v>
+        <v>487185</v>
       </c>
       <c r="R23" t="n">
-        <v>7039214</v>
+        <v>7039203</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2857,22 +2808,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129298775</v>
+        <v>129298853</v>
       </c>
       <c r="B24" t="n">
-        <v>57730</v>
+        <v>91607</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2880,23 +2831,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -2904,10 +2851,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>486860</v>
+        <v>487415</v>
       </c>
       <c r="R24" t="n">
-        <v>7039244</v>
+        <v>7038971</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2942,11 +2889,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -2959,44 +2901,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129298808</v>
+        <v>129298831</v>
       </c>
       <c r="B25" t="n">
-        <v>57730</v>
+        <v>83035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3006,10 +2948,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>487344</v>
+        <v>487307</v>
       </c>
       <c r="R25" t="n">
-        <v>7039018</v>
+        <v>7039016</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3044,11 +2986,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3061,44 +2998,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129298780</v>
+        <v>129298828</v>
       </c>
       <c r="B26" t="n">
-        <v>57730</v>
+        <v>80209</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3108,10 +3045,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>486859</v>
+        <v>487269</v>
       </c>
       <c r="R26" t="n">
-        <v>7039262</v>
+        <v>7039004</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3146,11 +3083,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3163,69 +3095,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129298830</v>
+        <v>129298737</v>
       </c>
       <c r="B27" t="n">
-        <v>57571</v>
+        <v>83044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102621</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>487123</v>
+        <v>487523</v>
       </c>
       <c r="R27" t="n">
-        <v>7039173</v>
+        <v>7039001</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3272,22 +3192,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129298843</v>
+        <v>129298839</v>
       </c>
       <c r="B28" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3319,10 +3239,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>487391</v>
+        <v>487269</v>
       </c>
       <c r="R28" t="n">
-        <v>7038927</v>
+        <v>7039001</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3369,22 +3289,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129298793</v>
+        <v>129298841</v>
       </c>
       <c r="B29" t="n">
-        <v>57730</v>
+        <v>80180</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3392,21 +3312,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3416,10 +3336,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>487183</v>
+        <v>487515</v>
       </c>
       <c r="R29" t="n">
-        <v>7039216</v>
+        <v>7038993</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3454,11 +3374,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3471,22 +3386,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129298823</v>
+        <v>129298743</v>
       </c>
       <c r="B30" t="n">
-        <v>57730</v>
+        <v>91587</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3494,21 +3409,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3518,10 +3433,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>487363</v>
+        <v>487331</v>
       </c>
       <c r="R30" t="n">
-        <v>7038902</v>
+        <v>7039023</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3556,11 +3471,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3573,22 +3483,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129298765</v>
+        <v>129298836</v>
       </c>
       <c r="B31" t="n">
-        <v>57730</v>
+        <v>80180</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3596,21 +3506,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3620,10 +3530,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>487122</v>
+        <v>486899</v>
       </c>
       <c r="R31" t="n">
-        <v>7039034</v>
+        <v>7039370</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3658,11 +3568,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3675,44 +3580,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129298770</v>
+        <v>129298739</v>
       </c>
       <c r="B32" t="n">
-        <v>57730</v>
+        <v>91551</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3722,10 +3627,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>486972</v>
+        <v>487384</v>
       </c>
       <c r="R32" t="n">
-        <v>7039122</v>
+        <v>7038973</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3760,11 +3665,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3777,22 +3677,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129298778</v>
+        <v>129298829</v>
       </c>
       <c r="B33" t="n">
-        <v>57730</v>
+        <v>57732</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3800,16 +3700,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3817,17 +3717,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>486871</v>
+        <v>487157</v>
       </c>
       <c r="R33" t="n">
-        <v>7039260</v>
+        <v>7039100</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3862,11 +3778,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -3879,44 +3790,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129298846</v>
+        <v>129298858</v>
       </c>
       <c r="B34" t="n">
-        <v>57834</v>
+        <v>83036</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103031</v>
+        <v>308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3926,10 +3837,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>486976</v>
+        <v>487408</v>
       </c>
       <c r="R34" t="n">
-        <v>7039216</v>
+        <v>7038959</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3976,44 +3887,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129298792</v>
+        <v>129298832</v>
       </c>
       <c r="B35" t="n">
-        <v>57730</v>
+        <v>83035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4023,10 +3934,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>487153</v>
+        <v>487393</v>
       </c>
       <c r="R35" t="n">
-        <v>7039212</v>
+        <v>7038976</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4061,11 +3972,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4078,22 +3984,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129298750</v>
+        <v>129298751</v>
       </c>
       <c r="B36" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4125,10 +4031,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>487272</v>
+        <v>487263</v>
       </c>
       <c r="R36" t="n">
-        <v>7038946</v>
+        <v>7038949</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4165,7 +4071,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4180,22 +4086,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129298769</v>
+        <v>129298786</v>
       </c>
       <c r="B37" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4227,10 +4133,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>487109</v>
+        <v>487006</v>
       </c>
       <c r="R37" t="n">
-        <v>7039040</v>
+        <v>7039175</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4282,22 +4188,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129298804</v>
+        <v>129298818</v>
       </c>
       <c r="B38" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4329,10 +4235,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>487288</v>
+        <v>487389</v>
       </c>
       <c r="R38" t="n">
-        <v>7039002</v>
+        <v>7038925</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4384,22 +4290,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129298794</v>
+        <v>129298819</v>
       </c>
       <c r="B39" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4431,10 +4337,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>487186</v>
+        <v>487346</v>
       </c>
       <c r="R39" t="n">
-        <v>7039192</v>
+        <v>7038911</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4486,22 +4392,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129298854</v>
+        <v>129298812</v>
       </c>
       <c r="B40" t="n">
-        <v>91601</v>
+        <v>57735</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4509,19 +4415,23 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4529,10 +4439,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>487522</v>
+        <v>487362</v>
       </c>
       <c r="R40" t="n">
-        <v>7038997</v>
+        <v>7039030</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4567,6 +4477,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4579,22 +4494,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129298840</v>
+        <v>129298759</v>
       </c>
       <c r="B41" t="n">
-        <v>80175</v>
+        <v>57735</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4602,21 +4517,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4626,10 +4541,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>487314</v>
+        <v>487171</v>
       </c>
       <c r="R41" t="n">
-        <v>7039005</v>
+        <v>7039000</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4664,6 +4579,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4676,22 +4596,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129298833</v>
+        <v>129298755</v>
       </c>
       <c r="B42" t="n">
-        <v>80176</v>
+        <v>57735</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4699,21 +4619,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4723,10 +4643,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>487265</v>
+        <v>487206</v>
       </c>
       <c r="R42" t="n">
-        <v>7038997</v>
+        <v>7038982</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4761,6 +4681,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -4773,22 +4698,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129298805</v>
+        <v>129298799</v>
       </c>
       <c r="B43" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4820,10 +4745,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>487346</v>
+        <v>487230</v>
       </c>
       <c r="R43" t="n">
-        <v>7039012</v>
+        <v>7039041</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4875,22 +4800,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129298809</v>
+        <v>129298761</v>
       </c>
       <c r="B44" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4922,10 +4847,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>487348</v>
+        <v>487137</v>
       </c>
       <c r="R44" t="n">
-        <v>7039005</v>
+        <v>7039024</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4977,22 +4902,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129298802</v>
+        <v>129298777</v>
       </c>
       <c r="B45" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5024,10 +4949,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>487302</v>
+        <v>486860</v>
       </c>
       <c r="R45" t="n">
-        <v>7039045</v>
+        <v>7039254</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5064,7 +4989,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5079,22 +5004,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129298795</v>
+        <v>129298787</v>
       </c>
       <c r="B46" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5126,10 +5051,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>487100</v>
+        <v>486999</v>
       </c>
       <c r="R46" t="n">
-        <v>7039085</v>
+        <v>7039162</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5181,22 +5106,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129298748</v>
+        <v>129298775</v>
       </c>
       <c r="B47" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5228,10 +5153,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>487301</v>
+        <v>486860</v>
       </c>
       <c r="R47" t="n">
-        <v>7038925</v>
+        <v>7039244</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5283,22 +5208,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129298783</v>
+        <v>129298808</v>
       </c>
       <c r="B48" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5330,10 +5255,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>487024</v>
+        <v>487344</v>
       </c>
       <c r="R48" t="n">
-        <v>7039203</v>
+        <v>7039018</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5385,22 +5310,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129298738</v>
+        <v>129298780</v>
       </c>
       <c r="B49" t="n">
-        <v>97002</v>
+        <v>57735</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5408,21 +5333,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5432,10 +5357,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>487311</v>
+        <v>486859</v>
       </c>
       <c r="R49" t="n">
-        <v>7039063</v>
+        <v>7039262</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5470,6 +5395,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5482,57 +5412,69 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129298842</v>
+        <v>129298830</v>
       </c>
       <c r="B50" t="n">
-        <v>80175</v>
+        <v>57576</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>102621</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>487393</v>
+        <v>487123</v>
       </c>
       <c r="R50" t="n">
-        <v>7038908</v>
+        <v>7039173</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5579,22 +5521,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129298856</v>
+        <v>129298765</v>
       </c>
       <c r="B51" t="n">
-        <v>82905</v>
+        <v>57735</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5602,21 +5544,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5626,10 +5568,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>487541</v>
+        <v>487122</v>
       </c>
       <c r="R51" t="n">
-        <v>7038983</v>
+        <v>7039034</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5664,6 +5606,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5676,22 +5623,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129298798</v>
+        <v>129298793</v>
       </c>
       <c r="B52" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5723,10 +5670,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>487131</v>
+        <v>487183</v>
       </c>
       <c r="R52" t="n">
-        <v>7039049</v>
+        <v>7039216</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5778,22 +5725,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129298810</v>
+        <v>129298823</v>
       </c>
       <c r="B53" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5825,10 +5772,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>487355</v>
+        <v>487363</v>
       </c>
       <c r="R53" t="n">
-        <v>7039005</v>
+        <v>7038902</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5880,22 +5827,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129298825</v>
+        <v>129298770</v>
       </c>
       <c r="B54" t="n">
-        <v>57890</v>
+        <v>57735</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5903,21 +5850,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5927,10 +5874,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>487247</v>
+        <v>486972</v>
       </c>
       <c r="R54" t="n">
-        <v>7039020</v>
+        <v>7039122</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5967,7 +5914,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5982,22 +5929,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129298779</v>
+        <v>129298778</v>
       </c>
       <c r="B55" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6029,10 +5976,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486866</v>
+        <v>486871</v>
       </c>
       <c r="R55" t="n">
-        <v>7039259</v>
+        <v>7039260</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6069,7 +6016,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6084,22 +6031,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129298749</v>
+        <v>129298792</v>
       </c>
       <c r="B56" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6131,10 +6078,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>487275</v>
+        <v>487153</v>
       </c>
       <c r="R56" t="n">
-        <v>7038947</v>
+        <v>7039212</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6171,7 +6118,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6186,22 +6133,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129298826</v>
+        <v>129298750</v>
       </c>
       <c r="B57" t="n">
-        <v>57890</v>
+        <v>57735</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6209,21 +6156,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6233,10 +6180,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>487457</v>
+        <v>487272</v>
       </c>
       <c r="R57" t="n">
-        <v>7038967</v>
+        <v>7038946</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6273,7 +6220,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6288,22 +6235,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129298767</v>
+        <v>129298794</v>
       </c>
       <c r="B58" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6335,10 +6282,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>487123</v>
+        <v>487186</v>
       </c>
       <c r="R58" t="n">
-        <v>7039031</v>
+        <v>7039192</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6390,22 +6337,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129298776</v>
+        <v>129298769</v>
       </c>
       <c r="B59" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6437,10 +6384,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>486855</v>
+        <v>487109</v>
       </c>
       <c r="R59" t="n">
-        <v>7039252</v>
+        <v>7039040</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6477,7 +6424,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6492,22 +6439,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129298816</v>
+        <v>129298804</v>
       </c>
       <c r="B60" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6539,10 +6486,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>487389</v>
+        <v>487288</v>
       </c>
       <c r="R60" t="n">
-        <v>7038985</v>
+        <v>7039002</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6594,22 +6541,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129298813</v>
+        <v>129298809</v>
       </c>
       <c r="B61" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6641,10 +6588,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>487367</v>
+        <v>487348</v>
       </c>
       <c r="R61" t="n">
-        <v>7038998</v>
+        <v>7039005</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6696,22 +6643,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129298820</v>
+        <v>129298795</v>
       </c>
       <c r="B62" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6743,10 +6690,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>487354</v>
+        <v>487100</v>
       </c>
       <c r="R62" t="n">
-        <v>7038894</v>
+        <v>7039085</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6798,22 +6745,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129298774</v>
+        <v>129298748</v>
       </c>
       <c r="B63" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6845,10 +6792,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>486866</v>
+        <v>487301</v>
       </c>
       <c r="R63" t="n">
-        <v>7039249</v>
+        <v>7038925</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6885,7 +6832,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6900,22 +6847,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129298773</v>
+        <v>129298783</v>
       </c>
       <c r="B64" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6947,10 +6894,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>486807</v>
+        <v>487024</v>
       </c>
       <c r="R64" t="n">
-        <v>7039220</v>
+        <v>7039203</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6987,7 +6934,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7002,22 +6949,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129298853</v>
+        <v>129298805</v>
       </c>
       <c r="B65" t="n">
-        <v>91601</v>
+        <v>57735</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7025,19 +6972,23 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7045,10 +6996,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>487415</v>
+        <v>487346</v>
       </c>
       <c r="R65" t="n">
-        <v>7038971</v>
+        <v>7039012</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7083,6 +7034,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7095,22 +7051,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129298811</v>
+        <v>129298802</v>
       </c>
       <c r="B66" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7142,10 +7098,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>487357</v>
+        <v>487302</v>
       </c>
       <c r="R66" t="n">
-        <v>7039009</v>
+        <v>7039045</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7182,7 +7138,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7197,22 +7153,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129298741</v>
+        <v>129298798</v>
       </c>
       <c r="B67" t="n">
-        <v>91581</v>
+        <v>57735</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7220,21 +7176,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7244,10 +7200,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>487185</v>
+        <v>487131</v>
       </c>
       <c r="R67" t="n">
-        <v>7039203</v>
+        <v>7039049</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7282,6 +7238,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7294,44 +7255,44 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129298831</v>
+        <v>129298810</v>
       </c>
       <c r="B68" t="n">
-        <v>83030</v>
+        <v>57735</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7341,10 +7302,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>487307</v>
+        <v>487355</v>
       </c>
       <c r="R68" t="n">
-        <v>7039016</v>
+        <v>7039005</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7379,6 +7340,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7391,22 +7357,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129298737</v>
+        <v>129298779</v>
       </c>
       <c r="B69" t="n">
-        <v>83039</v>
+        <v>57735</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7414,21 +7380,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7438,10 +7404,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>487523</v>
+        <v>486866</v>
       </c>
       <c r="R69" t="n">
-        <v>7039001</v>
+        <v>7039259</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7476,6 +7442,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -7488,44 +7459,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129298828</v>
+        <v>129298749</v>
       </c>
       <c r="B70" t="n">
-        <v>80204</v>
+        <v>57735</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7535,10 +7506,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>487269</v>
+        <v>487275</v>
       </c>
       <c r="R70" t="n">
-        <v>7039004</v>
+        <v>7038947</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7573,6 +7544,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -7585,22 +7561,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129298839</v>
+        <v>129298776</v>
       </c>
       <c r="B71" t="n">
-        <v>80175</v>
+        <v>57735</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7608,21 +7584,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7632,10 +7608,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>487269</v>
+        <v>486855</v>
       </c>
       <c r="R71" t="n">
-        <v>7039001</v>
+        <v>7039252</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7670,6 +7646,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -7682,22 +7663,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129298797</v>
+        <v>129298816</v>
       </c>
       <c r="B72" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7729,10 +7710,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>487134</v>
+        <v>487389</v>
       </c>
       <c r="R72" t="n">
-        <v>7039037</v>
+        <v>7038985</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7784,22 +7765,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129298803</v>
+        <v>129298820</v>
       </c>
       <c r="B73" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7831,10 +7812,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>487303</v>
+        <v>487354</v>
       </c>
       <c r="R73" t="n">
-        <v>7039037</v>
+        <v>7038894</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7886,22 +7867,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129298822</v>
+        <v>129298774</v>
       </c>
       <c r="B74" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7933,10 +7914,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>487373</v>
+        <v>486866</v>
       </c>
       <c r="R74" t="n">
-        <v>7038897</v>
+        <v>7039249</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7973,7 +7954,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7988,22 +7969,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129298817</v>
+        <v>129298773</v>
       </c>
       <c r="B75" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8035,10 +8016,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>487460</v>
+        <v>486807</v>
       </c>
       <c r="R75" t="n">
-        <v>7038984</v>
+        <v>7039220</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8075,7 +8056,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8090,22 +8071,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129298800</v>
+        <v>129298767</v>
       </c>
       <c r="B76" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8130,33 +8111,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>487288</v>
+        <v>487123</v>
       </c>
       <c r="R76" t="n">
-        <v>7039015</v>
+        <v>7039031</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8193,7 +8158,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Födosökande hane</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8208,22 +8173,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129298821</v>
+        <v>129298813</v>
       </c>
       <c r="B77" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8255,10 +8220,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>487368</v>
+        <v>487367</v>
       </c>
       <c r="R77" t="n">
-        <v>7038892</v>
+        <v>7038998</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8310,22 +8275,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129298781</v>
+        <v>129298811</v>
       </c>
       <c r="B78" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8357,10 +8322,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>486864</v>
+        <v>487357</v>
       </c>
       <c r="R78" t="n">
-        <v>7039272</v>
+        <v>7039009</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8397,7 +8362,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8412,22 +8377,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129298785</v>
+        <v>129298797</v>
       </c>
       <c r="B79" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8459,10 +8424,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>487007</v>
+        <v>487134</v>
       </c>
       <c r="R79" t="n">
-        <v>7039210</v>
+        <v>7039037</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8499,7 +8464,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8514,22 +8479,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129298753</v>
+        <v>129298822</v>
       </c>
       <c r="B80" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8561,10 +8526,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>487240</v>
+        <v>487373</v>
       </c>
       <c r="R80" t="n">
-        <v>7038959</v>
+        <v>7038897</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8616,22 +8581,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129298757</v>
+        <v>129298817</v>
       </c>
       <c r="B81" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8663,10 +8628,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>487188</v>
+        <v>487460</v>
       </c>
       <c r="R81" t="n">
-        <v>7038992</v>
+        <v>7038984</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8718,22 +8683,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129298784</v>
+        <v>129298800</v>
       </c>
       <c r="B82" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8758,17 +8723,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>487011</v>
+        <v>487288</v>
       </c>
       <c r="R82" t="n">
-        <v>7039207</v>
+        <v>7039015</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8805,7 +8786,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Födosökande hane</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8820,22 +8801,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129298841</v>
+        <v>129298821</v>
       </c>
       <c r="B83" t="n">
-        <v>80175</v>
+        <v>57735</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8843,21 +8824,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8867,10 +8848,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>487515</v>
+        <v>487368</v>
       </c>
       <c r="R83" t="n">
-        <v>7038993</v>
+        <v>7038892</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8905,6 +8886,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -8917,73 +8903,57 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129298847</v>
+        <v>129298803</v>
       </c>
       <c r="B84" t="n">
-        <v>57590</v>
+        <v>57735</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100136</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>486999</v>
+        <v>487303</v>
       </c>
       <c r="R84" t="n">
-        <v>7039199</v>
+        <v>7039037</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9020,7 +8990,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Jagades av en nötskrika</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9035,22 +9005,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129298771</v>
+        <v>129298781</v>
       </c>
       <c r="B85" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9082,10 +9052,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>486885</v>
+        <v>486864</v>
       </c>
       <c r="R85" t="n">
-        <v>7039172</v>
+        <v>7039272</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9137,22 +9107,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129298789</v>
+        <v>129298785</v>
       </c>
       <c r="B86" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9184,10 +9154,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>487041</v>
+        <v>487007</v>
       </c>
       <c r="R86" t="n">
-        <v>7039167</v>
+        <v>7039210</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9224,7 +9194,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9239,22 +9209,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129298801</v>
+        <v>129298753</v>
       </c>
       <c r="B87" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9286,10 +9256,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>487268</v>
+        <v>487240</v>
       </c>
       <c r="R87" t="n">
-        <v>7039003</v>
+        <v>7038959</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9341,22 +9311,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129298814</v>
+        <v>129298757</v>
       </c>
       <c r="B88" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9388,10 +9358,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>487366</v>
+        <v>487188</v>
       </c>
       <c r="R88" t="n">
-        <v>7038997</v>
+        <v>7038992</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9428,7 +9398,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9443,22 +9413,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129298772</v>
+        <v>129298784</v>
       </c>
       <c r="B89" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9490,10 +9460,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>486849</v>
+        <v>487011</v>
       </c>
       <c r="R89" t="n">
-        <v>7039185</v>
+        <v>7039207</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9545,22 +9515,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129298746</v>
+        <v>129298814</v>
       </c>
       <c r="B90" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9592,10 +9562,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>487316</v>
+        <v>487366</v>
       </c>
       <c r="R90" t="n">
-        <v>7038914</v>
+        <v>7038997</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9632,7 +9602,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9647,22 +9617,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129298836</v>
+        <v>129298771</v>
       </c>
       <c r="B91" t="n">
-        <v>80175</v>
+        <v>57735</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9670,21 +9640,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9694,10 +9664,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>486899</v>
+        <v>486885</v>
       </c>
       <c r="R91" t="n">
-        <v>7039370</v>
+        <v>7039172</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9732,6 +9702,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -9744,22 +9719,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129298743</v>
+        <v>129298789</v>
       </c>
       <c r="B92" t="n">
-        <v>91581</v>
+        <v>57735</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9767,21 +9742,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9791,10 +9766,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>487331</v>
+        <v>487041</v>
       </c>
       <c r="R92" t="n">
-        <v>7039023</v>
+        <v>7039167</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9829,6 +9804,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
@@ -9841,22 +9821,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129298752</v>
+        <v>129298801</v>
       </c>
       <c r="B93" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9888,10 +9868,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>487246</v>
+        <v>487268</v>
       </c>
       <c r="R93" t="n">
-        <v>7038958</v>
+        <v>7039003</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9943,22 +9923,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129298768</v>
+        <v>129298772</v>
       </c>
       <c r="B94" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9990,10 +9970,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>487123</v>
+        <v>486849</v>
       </c>
       <c r="R94" t="n">
-        <v>7039032</v>
+        <v>7039185</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10045,22 +10025,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129298745</v>
+        <v>129298746</v>
       </c>
       <c r="B95" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10092,10 +10072,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>486881</v>
+        <v>487316</v>
       </c>
       <c r="R95" t="n">
-        <v>7039175</v>
+        <v>7038914</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10147,57 +10127,73 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129298791</v>
+        <v>129298847</v>
       </c>
       <c r="B96" t="n">
-        <v>57730</v>
+        <v>57595</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>100136</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>487112</v>
+        <v>486999</v>
       </c>
       <c r="R96" t="n">
-        <v>7039182</v>
+        <v>7039199</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10234,7 +10230,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Jagades av en nötskrika</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10249,22 +10245,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129298754</v>
+        <v>129298752</v>
       </c>
       <c r="B97" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10296,10 +10292,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>487222</v>
+        <v>487246</v>
       </c>
       <c r="R97" t="n">
-        <v>7038974</v>
+        <v>7038958</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10336,7 +10332,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10351,44 +10347,44 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129298739</v>
+        <v>129298768</v>
       </c>
       <c r="B98" t="n">
-        <v>91545</v>
+        <v>57735</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10398,10 +10394,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>487384</v>
+        <v>487123</v>
       </c>
       <c r="R98" t="n">
-        <v>7038973</v>
+        <v>7039032</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10436,6 +10432,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
@@ -10448,22 +10449,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129298807</v>
+        <v>129298745</v>
       </c>
       <c r="B99" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10495,10 +10496,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>487337</v>
+        <v>486881</v>
       </c>
       <c r="R99" t="n">
-        <v>7039015</v>
+        <v>7039175</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10550,22 +10551,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129298829</v>
+        <v>129298791</v>
       </c>
       <c r="B100" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10573,16 +10574,16 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -10590,33 +10591,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>487157</v>
+        <v>487112</v>
       </c>
       <c r="R100" t="n">
-        <v>7039100</v>
+        <v>7039182</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10651,6 +10636,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -10663,22 +10653,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129298858</v>
+        <v>129298754</v>
       </c>
       <c r="B101" t="n">
-        <v>83031</v>
+        <v>57735</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10686,21 +10676,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10710,10 +10700,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>487408</v>
+        <v>487222</v>
       </c>
       <c r="R101" t="n">
-        <v>7038959</v>
+        <v>7038974</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10748,6 +10738,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
@@ -10760,22 +10755,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129298806</v>
+        <v>129298807</v>
       </c>
       <c r="B102" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10807,10 +10802,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>487339</v>
+        <v>487337</v>
       </c>
       <c r="R102" t="n">
-        <v>7039009</v>
+        <v>7039015</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10862,22 +10857,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129298782</v>
+        <v>129298806</v>
       </c>
       <c r="B103" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10909,10 +10904,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>486857</v>
+        <v>487339</v>
       </c>
       <c r="R103" t="n">
-        <v>7039276</v>
+        <v>7039009</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10949,7 +10944,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10964,22 +10959,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129298758</v>
+        <v>129298782</v>
       </c>
       <c r="B104" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11011,10 +11006,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>487183</v>
+        <v>486857</v>
       </c>
       <c r="R104" t="n">
-        <v>7038993</v>
+        <v>7039276</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11051,7 +11046,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11066,22 +11061,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129298815</v>
+        <v>129298758</v>
       </c>
       <c r="B105" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11113,10 +11108,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>487375</v>
+        <v>487183</v>
       </c>
       <c r="R105" t="n">
-        <v>7038981</v>
+        <v>7038993</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11168,22 +11163,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129298788</v>
+        <v>129298815</v>
       </c>
       <c r="B106" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11215,10 +11210,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>487039</v>
+        <v>487375</v>
       </c>
       <c r="R106" t="n">
-        <v>7039164</v>
+        <v>7038981</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11270,44 +11265,44 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129298832</v>
+        <v>129298788</v>
       </c>
       <c r="B107" t="n">
-        <v>83030</v>
+        <v>57735</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11317,10 +11312,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>487393</v>
+        <v>487039</v>
       </c>
       <c r="R107" t="n">
-        <v>7038976</v>
+        <v>7039164</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11355,6 +11350,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -11367,22 +11367,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129298766</v>
+        <v>129298796</v>
       </c>
       <c r="B108" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11414,10 +11414,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>487124</v>
+        <v>487139</v>
       </c>
       <c r="R108" t="n">
-        <v>7039030</v>
+        <v>7039088</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11469,22 +11469,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129298796</v>
+        <v>129298790</v>
       </c>
       <c r="B109" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11516,10 +11516,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>487139</v>
+        <v>487044</v>
       </c>
       <c r="R109" t="n">
-        <v>7039088</v>
+        <v>7039168</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11571,22 +11571,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129298760</v>
+        <v>129298766</v>
       </c>
       <c r="B110" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11618,10 +11618,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>487141</v>
+        <v>487124</v>
       </c>
       <c r="R110" t="n">
-        <v>7039023</v>
+        <v>7039030</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11658,7 +11658,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11673,22 +11673,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129298790</v>
+        <v>129298760</v>
       </c>
       <c r="B111" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11720,10 +11720,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>487044</v>
+        <v>487141</v>
       </c>
       <c r="R111" t="n">
-        <v>7039168</v>
+        <v>7039023</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11760,7 +11760,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11775,12 +11775,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>

--- a/artfynd/A 46357-2025 artfynd.xlsx
+++ b/artfynd/A 46357-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129298844</v>
+        <v>129298851</v>
       </c>
       <c r="B2" t="n">
-        <v>78088</v>
+        <v>91602</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228579</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487374</v>
+        <v>487144</v>
       </c>
       <c r="R2" t="n">
-        <v>7039027</v>
+        <v>7039078</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129298851</v>
+        <v>129298827</v>
       </c>
       <c r="B3" t="n">
-        <v>91601</v>
+        <v>57896</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487144</v>
+        <v>487352</v>
       </c>
       <c r="R3" t="n">
-        <v>7039078</v>
+        <v>7038906</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129298827</v>
+        <v>129298844</v>
       </c>
       <c r="B4" t="n">
-        <v>57895</v>
+        <v>78089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>228579</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487352</v>
+        <v>487374</v>
       </c>
       <c r="R4" t="n">
-        <v>7038906</v>
+        <v>7039027</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,7 +974,7 @@
         <v>129298742</v>
       </c>
       <c r="B5" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>129298838</v>
       </c>
       <c r="B6" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129298857</v>
       </c>
       <c r="B7" t="n">
-        <v>83036</v>
+        <v>83037</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>129298855</v>
       </c>
       <c r="B8" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129298845</v>
+        <v>129298837</v>
       </c>
       <c r="B9" t="n">
-        <v>78088</v>
+        <v>80181</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>487526</v>
+        <v>487004</v>
       </c>
       <c r="R9" t="n">
-        <v>7039006</v>
+        <v>7039214</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,7 +1459,7 @@
         <v>129298740</v>
       </c>
       <c r="B10" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>129298852</v>
       </c>
       <c r="B11" t="n">
-        <v>91601</v>
+        <v>91602</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129298837</v>
+        <v>129298845</v>
       </c>
       <c r="B12" t="n">
-        <v>80180</v>
+        <v>78089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>487004</v>
+        <v>487526</v>
       </c>
       <c r="R12" t="n">
-        <v>7039214</v>
+        <v>7039006</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129298843</v>
+        <v>129298846</v>
       </c>
       <c r="B13" t="n">
-        <v>80180</v>
+        <v>57840</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>487391</v>
+        <v>486976</v>
       </c>
       <c r="R13" t="n">
-        <v>7038927</v>
+        <v>7039216</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129298846</v>
+        <v>129298843</v>
       </c>
       <c r="B14" t="n">
-        <v>57839</v>
+        <v>80181</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486976</v>
+        <v>487391</v>
       </c>
       <c r="R14" t="n">
-        <v>7039216</v>
+        <v>7038927</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1941,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129298833</v>
+        <v>129298854</v>
       </c>
       <c r="B15" t="n">
-        <v>80181</v>
+        <v>91608</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1952,23 +1952,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -1976,7 +1972,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>487265</v>
+        <v>487522</v>
       </c>
       <c r="R15" t="n">
         <v>7038997</v>
@@ -2038,10 +2034,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129298854</v>
+        <v>129298840</v>
       </c>
       <c r="B16" t="n">
-        <v>91607</v>
+        <v>80181</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,19 +2045,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>487522</v>
+        <v>487314</v>
       </c>
       <c r="R16" t="n">
-        <v>7038997</v>
+        <v>7039005</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129298840</v>
+        <v>129298833</v>
       </c>
       <c r="B17" t="n">
-        <v>80180</v>
+        <v>80182</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>487314</v>
+        <v>487265</v>
       </c>
       <c r="R17" t="n">
-        <v>7039005</v>
+        <v>7038997</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129298856</v>
+        <v>129298738</v>
       </c>
       <c r="B18" t="n">
-        <v>82910</v>
+        <v>97015</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2239,21 +2239,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2263,10 +2263,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>487541</v>
+        <v>487311</v>
       </c>
       <c r="R18" t="n">
-        <v>7038983</v>
+        <v>7039063</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2325,10 +2325,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129298738</v>
+        <v>129298856</v>
       </c>
       <c r="B19" t="n">
-        <v>97014</v>
+        <v>82911</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2336,21 +2336,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>487311</v>
+        <v>487541</v>
       </c>
       <c r="R19" t="n">
-        <v>7039063</v>
+        <v>7038983</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2425,7 +2425,7 @@
         <v>129298842</v>
       </c>
       <c r="B20" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>129298825</v>
       </c>
       <c r="B21" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>129298826</v>
       </c>
       <c r="B22" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>129298741</v>
       </c>
       <c r="B23" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>129298853</v>
       </c>
       <c r="B24" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2913,32 +2913,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129298831</v>
+        <v>129298737</v>
       </c>
       <c r="B25" t="n">
-        <v>83035</v>
+        <v>83045</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>492</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2948,10 +2948,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>487307</v>
+        <v>487523</v>
       </c>
       <c r="R25" t="n">
-        <v>7039016</v>
+        <v>7039001</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3013,7 +3013,7 @@
         <v>129298828</v>
       </c>
       <c r="B26" t="n">
-        <v>80209</v>
+        <v>80210</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3107,10 +3107,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129298737</v>
+        <v>129298839</v>
       </c>
       <c r="B27" t="n">
-        <v>83044</v>
+        <v>80181</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3118,21 +3118,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>487523</v>
+        <v>487269</v>
       </c>
       <c r="R27" t="n">
         <v>7039001</v>
@@ -3204,32 +3204,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129298839</v>
+        <v>129298831</v>
       </c>
       <c r="B28" t="n">
-        <v>80180</v>
+        <v>83036</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>492</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3239,10 +3239,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>487269</v>
+        <v>487307</v>
       </c>
       <c r="R28" t="n">
-        <v>7039001</v>
+        <v>7039016</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3304,7 +3304,7 @@
         <v>129298841</v>
       </c>
       <c r="B29" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>129298743</v>
       </c>
       <c r="B30" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>129298836</v>
       </c>
       <c r="B31" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>129298739</v>
       </c>
       <c r="B32" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>129298829</v>
       </c>
       <c r="B33" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3802,32 +3802,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129298858</v>
+        <v>129298832</v>
       </c>
       <c r="B34" t="n">
         <v>83036</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>308</v>
+        <v>492</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>487408</v>
+        <v>487393</v>
       </c>
       <c r="R34" t="n">
-        <v>7038959</v>
+        <v>7038976</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3899,32 +3899,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129298832</v>
+        <v>129298858</v>
       </c>
       <c r="B35" t="n">
-        <v>83035</v>
+        <v>83037</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>492</v>
+        <v>308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>487393</v>
+        <v>487408</v>
       </c>
       <c r="R35" t="n">
-        <v>7038976</v>
+        <v>7038959</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3996,10 +3996,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129298751</v>
+        <v>129298818</v>
       </c>
       <c r="B36" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4031,10 +4031,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>487263</v>
+        <v>487389</v>
       </c>
       <c r="R36" t="n">
-        <v>7038949</v>
+        <v>7038925</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4098,10 +4098,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129298786</v>
+        <v>129298751</v>
       </c>
       <c r="B37" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>487006</v>
+        <v>487263</v>
       </c>
       <c r="R37" t="n">
-        <v>7039175</v>
+        <v>7038949</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4200,10 +4200,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129298818</v>
+        <v>129298786</v>
       </c>
       <c r="B38" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4235,10 +4235,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>487389</v>
+        <v>487006</v>
       </c>
       <c r="R38" t="n">
-        <v>7038925</v>
+        <v>7039175</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4305,7 +4305,7 @@
         <v>129298819</v>
       </c>
       <c r="B39" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>129298812</v>
       </c>
       <c r="B40" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>129298759</v>
       </c>
       <c r="B41" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>129298755</v>
       </c>
       <c r="B42" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>129298799</v>
       </c>
       <c r="B43" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>129298761</v>
       </c>
       <c r="B44" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4914,10 +4914,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129298777</v>
+        <v>129298787</v>
       </c>
       <c r="B45" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486860</v>
+        <v>486999</v>
       </c>
       <c r="R45" t="n">
-        <v>7039254</v>
+        <v>7039162</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4989,7 +4989,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5016,10 +5016,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129298787</v>
+        <v>129298777</v>
       </c>
       <c r="B46" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5051,10 +5051,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486999</v>
+        <v>486860</v>
       </c>
       <c r="R46" t="n">
-        <v>7039162</v>
+        <v>7039254</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5118,10 +5118,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129298775</v>
+        <v>129298808</v>
       </c>
       <c r="B47" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5153,10 +5153,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486860</v>
+        <v>487344</v>
       </c>
       <c r="R47" t="n">
-        <v>7039244</v>
+        <v>7039018</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5220,10 +5220,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129298808</v>
+        <v>129298775</v>
       </c>
       <c r="B48" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5255,10 +5255,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>487344</v>
+        <v>486860</v>
       </c>
       <c r="R48" t="n">
-        <v>7039018</v>
+        <v>7039244</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5325,7 +5325,7 @@
         <v>129298780</v>
       </c>
       <c r="B49" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>129298830</v>
       </c>
       <c r="B50" t="n">
-        <v>57576</v>
+        <v>57577</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>129298765</v>
       </c>
       <c r="B51" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5635,10 +5635,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129298793</v>
+        <v>129298770</v>
       </c>
       <c r="B52" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5670,10 +5670,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>487183</v>
+        <v>486972</v>
       </c>
       <c r="R52" t="n">
-        <v>7039216</v>
+        <v>7039122</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129298823</v>
+        <v>129298778</v>
       </c>
       <c r="B53" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>487363</v>
+        <v>486871</v>
       </c>
       <c r="R53" t="n">
-        <v>7038902</v>
+        <v>7039260</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5839,10 +5839,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129298770</v>
+        <v>129298793</v>
       </c>
       <c r="B54" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5874,10 +5874,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486972</v>
+        <v>487183</v>
       </c>
       <c r="R54" t="n">
-        <v>7039122</v>
+        <v>7039216</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5941,10 +5941,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129298778</v>
+        <v>129298823</v>
       </c>
       <c r="B55" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5976,10 +5976,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486871</v>
+        <v>487363</v>
       </c>
       <c r="R55" t="n">
-        <v>7039260</v>
+        <v>7038902</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6043,10 +6043,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129298792</v>
+        <v>129298804</v>
       </c>
       <c r="B56" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6078,10 +6078,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>487153</v>
+        <v>487288</v>
       </c>
       <c r="R56" t="n">
-        <v>7039212</v>
+        <v>7039002</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6145,10 +6145,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129298750</v>
+        <v>129298792</v>
       </c>
       <c r="B57" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6180,10 +6180,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>487272</v>
+        <v>487153</v>
       </c>
       <c r="R57" t="n">
-        <v>7038946</v>
+        <v>7039212</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6247,10 +6247,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129298794</v>
+        <v>129298750</v>
       </c>
       <c r="B58" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6282,10 +6282,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>487186</v>
+        <v>487272</v>
       </c>
       <c r="R58" t="n">
-        <v>7039192</v>
+        <v>7038946</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6352,7 +6352,7 @@
         <v>129298769</v>
       </c>
       <c r="B59" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6451,10 +6451,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129298804</v>
+        <v>129298794</v>
       </c>
       <c r="B60" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6486,10 +6486,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>487288</v>
+        <v>487186</v>
       </c>
       <c r="R60" t="n">
-        <v>7039002</v>
+        <v>7039192</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6553,10 +6553,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129298809</v>
+        <v>129298805</v>
       </c>
       <c r="B61" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6588,10 +6588,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>487348</v>
+        <v>487346</v>
       </c>
       <c r="R61" t="n">
-        <v>7039005</v>
+        <v>7039012</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6655,10 +6655,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129298795</v>
+        <v>129298809</v>
       </c>
       <c r="B62" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6690,10 +6690,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>487100</v>
+        <v>487348</v>
       </c>
       <c r="R62" t="n">
-        <v>7039085</v>
+        <v>7039005</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6757,10 +6757,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129298748</v>
+        <v>129298802</v>
       </c>
       <c r="B63" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6792,10 +6792,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>487301</v>
+        <v>487302</v>
       </c>
       <c r="R63" t="n">
-        <v>7038925</v>
+        <v>7039045</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6859,10 +6859,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129298783</v>
+        <v>129298748</v>
       </c>
       <c r="B64" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6894,10 +6894,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>487024</v>
+        <v>487301</v>
       </c>
       <c r="R64" t="n">
-        <v>7039203</v>
+        <v>7038925</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6961,10 +6961,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129298805</v>
+        <v>129298795</v>
       </c>
       <c r="B65" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>487346</v>
+        <v>487100</v>
       </c>
       <c r="R65" t="n">
-        <v>7039012</v>
+        <v>7039085</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7063,10 +7063,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129298802</v>
+        <v>129298783</v>
       </c>
       <c r="B66" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>487302</v>
+        <v>487024</v>
       </c>
       <c r="R66" t="n">
-        <v>7039045</v>
+        <v>7039203</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7168,7 +7168,7 @@
         <v>129298798</v>
       </c>
       <c r="B67" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>129298810</v>
       </c>
       <c r="B68" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7369,10 +7369,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129298779</v>
+        <v>129298749</v>
       </c>
       <c r="B69" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7404,10 +7404,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>486866</v>
+        <v>487275</v>
       </c>
       <c r="R69" t="n">
-        <v>7039259</v>
+        <v>7038947</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7471,10 +7471,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129298749</v>
+        <v>129298779</v>
       </c>
       <c r="B70" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7506,10 +7506,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>487275</v>
+        <v>486866</v>
       </c>
       <c r="R70" t="n">
-        <v>7038947</v>
+        <v>7039259</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7573,10 +7573,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129298776</v>
+        <v>129298767</v>
       </c>
       <c r="B71" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7608,10 +7608,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>486855</v>
+        <v>487123</v>
       </c>
       <c r="R71" t="n">
-        <v>7039252</v>
+        <v>7039031</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7678,7 +7678,7 @@
         <v>129298816</v>
       </c>
       <c r="B72" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7777,10 +7777,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129298820</v>
+        <v>129298774</v>
       </c>
       <c r="B73" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7812,10 +7812,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>487354</v>
+        <v>486866</v>
       </c>
       <c r="R73" t="n">
-        <v>7038894</v>
+        <v>7039249</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7852,7 +7852,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7879,10 +7879,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129298774</v>
+        <v>129298773</v>
       </c>
       <c r="B74" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7914,10 +7914,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>486866</v>
+        <v>486807</v>
       </c>
       <c r="R74" t="n">
-        <v>7039249</v>
+        <v>7039220</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7981,10 +7981,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129298773</v>
+        <v>129298776</v>
       </c>
       <c r="B75" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8016,10 +8016,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>486807</v>
+        <v>486855</v>
       </c>
       <c r="R75" t="n">
-        <v>7039220</v>
+        <v>7039252</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8083,10 +8083,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129298767</v>
+        <v>129298813</v>
       </c>
       <c r="B76" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8118,10 +8118,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>487123</v>
+        <v>487367</v>
       </c>
       <c r="R76" t="n">
-        <v>7039031</v>
+        <v>7038998</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8185,10 +8185,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129298813</v>
+        <v>129298820</v>
       </c>
       <c r="B77" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8220,10 +8220,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>487367</v>
+        <v>487354</v>
       </c>
       <c r="R77" t="n">
-        <v>7038998</v>
+        <v>7038894</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8290,7 +8290,7 @@
         <v>129298811</v>
       </c>
       <c r="B78" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8389,10 +8389,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129298797</v>
+        <v>129298803</v>
       </c>
       <c r="B79" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>487134</v>
+        <v>487303</v>
       </c>
       <c r="R79" t="n">
         <v>7039037</v>
@@ -8491,10 +8491,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129298822</v>
+        <v>129298817</v>
       </c>
       <c r="B80" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8526,10 +8526,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>487373</v>
+        <v>487460</v>
       </c>
       <c r="R80" t="n">
-        <v>7038897</v>
+        <v>7038984</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8593,10 +8593,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129298817</v>
+        <v>129298800</v>
       </c>
       <c r="B81" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8621,17 +8621,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>487460</v>
+        <v>487288</v>
       </c>
       <c r="R81" t="n">
-        <v>7038984</v>
+        <v>7039015</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8668,7 +8684,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Födosökande hane</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8695,10 +8711,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129298800</v>
+        <v>129298797</v>
       </c>
       <c r="B82" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8723,33 +8739,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>487288</v>
+        <v>487134</v>
       </c>
       <c r="R82" t="n">
-        <v>7039015</v>
+        <v>7039037</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Födosökande hane</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8813,10 +8813,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129298821</v>
+        <v>129298822</v>
       </c>
       <c r="B83" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8848,10 +8848,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>487368</v>
+        <v>487373</v>
       </c>
       <c r="R83" t="n">
-        <v>7038892</v>
+        <v>7038897</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8915,10 +8915,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129298803</v>
+        <v>129298821</v>
       </c>
       <c r="B84" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8950,10 +8950,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>487303</v>
+        <v>487368</v>
       </c>
       <c r="R84" t="n">
-        <v>7039037</v>
+        <v>7038892</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9017,10 +9017,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129298781</v>
+        <v>129298753</v>
       </c>
       <c r="B85" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9052,10 +9052,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>486864</v>
+        <v>487240</v>
       </c>
       <c r="R85" t="n">
-        <v>7039272</v>
+        <v>7038959</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9119,10 +9119,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129298785</v>
+        <v>129298757</v>
       </c>
       <c r="B86" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9154,10 +9154,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>487007</v>
+        <v>487188</v>
       </c>
       <c r="R86" t="n">
-        <v>7039210</v>
+        <v>7038992</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9194,7 +9194,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9221,10 +9221,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129298753</v>
+        <v>129298781</v>
       </c>
       <c r="B87" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9256,10 +9256,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>487240</v>
+        <v>486864</v>
       </c>
       <c r="R87" t="n">
-        <v>7038959</v>
+        <v>7039272</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9323,10 +9323,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129298757</v>
+        <v>129298785</v>
       </c>
       <c r="B88" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9358,10 +9358,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>487188</v>
+        <v>487007</v>
       </c>
       <c r="R88" t="n">
-        <v>7038992</v>
+        <v>7039210</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9428,7 +9428,7 @@
         <v>129298784</v>
       </c>
       <c r="B89" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9527,10 +9527,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129298814</v>
+        <v>129298801</v>
       </c>
       <c r="B90" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9562,10 +9562,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>487366</v>
+        <v>487268</v>
       </c>
       <c r="R90" t="n">
-        <v>7038997</v>
+        <v>7039003</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9629,10 +9629,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129298771</v>
+        <v>129298746</v>
       </c>
       <c r="B91" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9664,10 +9664,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>486885</v>
+        <v>487316</v>
       </c>
       <c r="R91" t="n">
-        <v>7039172</v>
+        <v>7038914</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9731,10 +9731,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129298789</v>
+        <v>129298771</v>
       </c>
       <c r="B92" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9766,10 +9766,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>487041</v>
+        <v>486885</v>
       </c>
       <c r="R92" t="n">
-        <v>7039167</v>
+        <v>7039172</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9833,45 +9833,61 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129298801</v>
+        <v>129298847</v>
       </c>
       <c r="B93" t="n">
-        <v>57735</v>
+        <v>57596</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>100136</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>487268</v>
+        <v>486999</v>
       </c>
       <c r="R93" t="n">
-        <v>7039003</v>
+        <v>7039199</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9908,7 +9924,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Jagades av en nötskrika</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9935,10 +9951,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129298772</v>
+        <v>129298789</v>
       </c>
       <c r="B94" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9970,10 +9986,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>486849</v>
+        <v>487041</v>
       </c>
       <c r="R94" t="n">
-        <v>7039185</v>
+        <v>7039167</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10037,10 +10053,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129298746</v>
+        <v>129298814</v>
       </c>
       <c r="B95" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10072,10 +10088,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>487316</v>
+        <v>487366</v>
       </c>
       <c r="R95" t="n">
-        <v>7038914</v>
+        <v>7038997</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10112,7 +10128,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10139,61 +10155,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129298847</v>
+        <v>129298772</v>
       </c>
       <c r="B96" t="n">
-        <v>57595</v>
+        <v>57736</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100136</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>486999</v>
+        <v>486849</v>
       </c>
       <c r="R96" t="n">
-        <v>7039199</v>
+        <v>7039185</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10230,7 +10230,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Jagades av en nötskrika</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10260,7 +10260,7 @@
         <v>129298752</v>
       </c>
       <c r="B97" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>129298768</v>
       </c>
       <c r="B98" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
         <v>129298745</v>
       </c>
       <c r="B99" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10563,10 +10563,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129298791</v>
+        <v>129298754</v>
       </c>
       <c r="B100" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10598,10 +10598,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>487112</v>
+        <v>487222</v>
       </c>
       <c r="R100" t="n">
-        <v>7039182</v>
+        <v>7038974</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10638,7 +10638,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10665,10 +10665,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129298754</v>
+        <v>129298791</v>
       </c>
       <c r="B101" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10700,10 +10700,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>487222</v>
+        <v>487112</v>
       </c>
       <c r="R101" t="n">
-        <v>7038974</v>
+        <v>7039182</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10740,7 +10740,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10770,7 +10770,7 @@
         <v>129298807</v>
       </c>
       <c r="B102" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
         <v>129298806</v>
       </c>
       <c r="B103" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10971,10 +10971,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129298782</v>
+        <v>129298758</v>
       </c>
       <c r="B104" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11006,10 +11006,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>486857</v>
+        <v>487183</v>
       </c>
       <c r="R104" t="n">
-        <v>7039276</v>
+        <v>7038993</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11046,7 +11046,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11073,10 +11073,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129298758</v>
+        <v>129298782</v>
       </c>
       <c r="B105" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>487183</v>
+        <v>486857</v>
       </c>
       <c r="R105" t="n">
-        <v>7038993</v>
+        <v>7039276</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11148,7 +11148,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11178,7 +11178,7 @@
         <v>129298815</v>
       </c>
       <c r="B106" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>129298788</v>
       </c>
       <c r="B107" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11379,10 +11379,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129298796</v>
+        <v>129298766</v>
       </c>
       <c r="B108" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11414,10 +11414,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>487139</v>
+        <v>487124</v>
       </c>
       <c r="R108" t="n">
-        <v>7039088</v>
+        <v>7039030</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11481,10 +11481,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129298790</v>
+        <v>129298760</v>
       </c>
       <c r="B109" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11516,10 +11516,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>487044</v>
+        <v>487141</v>
       </c>
       <c r="R109" t="n">
-        <v>7039168</v>
+        <v>7039023</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11556,7 +11556,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11583,10 +11583,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129298766</v>
+        <v>129298796</v>
       </c>
       <c r="B110" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11618,10 +11618,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>487124</v>
+        <v>487139</v>
       </c>
       <c r="R110" t="n">
-        <v>7039030</v>
+        <v>7039088</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11685,10 +11685,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129298760</v>
+        <v>129298790</v>
       </c>
       <c r="B111" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11720,10 +11720,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>487141</v>
+        <v>487044</v>
       </c>
       <c r="R111" t="n">
-        <v>7039023</v>
+        <v>7039168</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11760,7 +11760,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD111" t="b">

--- a/artfynd/A 46357-2025 artfynd.xlsx
+++ b/artfynd/A 46357-2025 artfynd.xlsx
@@ -2228,10 +2228,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129298738</v>
+        <v>129298842</v>
       </c>
       <c r="B18" t="n">
-        <v>97015</v>
+        <v>80181</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2239,21 +2239,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2263,10 +2263,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>487311</v>
+        <v>487393</v>
       </c>
       <c r="R18" t="n">
-        <v>7039063</v>
+        <v>7038908</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2325,10 +2325,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129298856</v>
+        <v>129298738</v>
       </c>
       <c r="B19" t="n">
-        <v>82911</v>
+        <v>97015</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2336,21 +2336,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>487541</v>
+        <v>487311</v>
       </c>
       <c r="R19" t="n">
-        <v>7038983</v>
+        <v>7039063</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2422,10 +2422,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129298842</v>
+        <v>129298856</v>
       </c>
       <c r="B20" t="n">
-        <v>80181</v>
+        <v>82911</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2433,21 +2433,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2457,10 +2457,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>487393</v>
+        <v>487541</v>
       </c>
       <c r="R20" t="n">
-        <v>7038908</v>
+        <v>7038983</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -6553,7 +6553,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129298805</v>
+        <v>129298795</v>
       </c>
       <c r="B61" t="n">
         <v>57736</v>
@@ -6588,10 +6588,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>487346</v>
+        <v>487100</v>
       </c>
       <c r="R61" t="n">
-        <v>7039012</v>
+        <v>7039085</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6655,7 +6655,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129298809</v>
+        <v>129298783</v>
       </c>
       <c r="B62" t="n">
         <v>57736</v>
@@ -6690,10 +6690,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>487348</v>
+        <v>487024</v>
       </c>
       <c r="R62" t="n">
-        <v>7039005</v>
+        <v>7039203</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6757,7 +6757,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129298802</v>
+        <v>129298805</v>
       </c>
       <c r="B63" t="n">
         <v>57736</v>
@@ -6792,10 +6792,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>487302</v>
+        <v>487346</v>
       </c>
       <c r="R63" t="n">
-        <v>7039045</v>
+        <v>7039012</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6859,7 +6859,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129298748</v>
+        <v>129298809</v>
       </c>
       <c r="B64" t="n">
         <v>57736</v>
@@ -6894,10 +6894,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>487301</v>
+        <v>487348</v>
       </c>
       <c r="R64" t="n">
-        <v>7038925</v>
+        <v>7039005</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6961,7 +6961,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129298795</v>
+        <v>129298802</v>
       </c>
       <c r="B65" t="n">
         <v>57736</v>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>487100</v>
+        <v>487302</v>
       </c>
       <c r="R65" t="n">
-        <v>7039085</v>
+        <v>7039045</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7063,7 +7063,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129298783</v>
+        <v>129298748</v>
       </c>
       <c r="B66" t="n">
         <v>57736</v>
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>487024</v>
+        <v>487301</v>
       </c>
       <c r="R66" t="n">
-        <v>7039203</v>
+        <v>7038925</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7369,7 +7369,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129298749</v>
+        <v>129298779</v>
       </c>
       <c r="B69" t="n">
         <v>57736</v>
@@ -7404,10 +7404,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>487275</v>
+        <v>486866</v>
       </c>
       <c r="R69" t="n">
-        <v>7038947</v>
+        <v>7039259</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7471,7 +7471,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129298779</v>
+        <v>129298749</v>
       </c>
       <c r="B70" t="n">
         <v>57736</v>
@@ -7506,10 +7506,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>486866</v>
+        <v>487275</v>
       </c>
       <c r="R70" t="n">
-        <v>7039259</v>
+        <v>7038947</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>

--- a/artfynd/A 46357-2025 artfynd.xlsx
+++ b/artfynd/A 46357-2025 artfynd.xlsx
@@ -3996,7 +3996,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129298818</v>
+        <v>129298751</v>
       </c>
       <c r="B36" t="n">
         <v>57736</v>
@@ -4031,10 +4031,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>487389</v>
+        <v>487263</v>
       </c>
       <c r="R36" t="n">
-        <v>7038925</v>
+        <v>7038949</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4098,7 +4098,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129298751</v>
+        <v>129298786</v>
       </c>
       <c r="B37" t="n">
         <v>57736</v>
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>487263</v>
+        <v>487006</v>
       </c>
       <c r="R37" t="n">
-        <v>7038949</v>
+        <v>7039175</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4200,7 +4200,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129298786</v>
+        <v>129298818</v>
       </c>
       <c r="B38" t="n">
         <v>57736</v>
@@ -4235,10 +4235,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>487006</v>
+        <v>487389</v>
       </c>
       <c r="R38" t="n">
-        <v>7039175</v>
+        <v>7038925</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4608,7 +4608,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129298755</v>
+        <v>129298761</v>
       </c>
       <c r="B42" t="n">
         <v>57736</v>
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>487206</v>
+        <v>487137</v>
       </c>
       <c r="R42" t="n">
-        <v>7038982</v>
+        <v>7039024</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4710,7 +4710,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129298799</v>
+        <v>129298755</v>
       </c>
       <c r="B43" t="n">
         <v>57736</v>
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>487230</v>
+        <v>487206</v>
       </c>
       <c r="R43" t="n">
-        <v>7039041</v>
+        <v>7038982</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4812,7 +4812,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129298761</v>
+        <v>129298799</v>
       </c>
       <c r="B44" t="n">
         <v>57736</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>487137</v>
+        <v>487230</v>
       </c>
       <c r="R44" t="n">
-        <v>7039024</v>
+        <v>7039041</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4914,7 +4914,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129298787</v>
+        <v>129298777</v>
       </c>
       <c r="B45" t="n">
         <v>57736</v>
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>486999</v>
+        <v>486860</v>
       </c>
       <c r="R45" t="n">
-        <v>7039162</v>
+        <v>7039254</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4989,7 +4989,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5016,7 +5016,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129298777</v>
+        <v>129298787</v>
       </c>
       <c r="B46" t="n">
         <v>57736</v>
@@ -5051,10 +5051,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>486860</v>
+        <v>486999</v>
       </c>
       <c r="R46" t="n">
-        <v>7039254</v>
+        <v>7039162</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5118,27 +5118,27 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129298808</v>
+        <v>129298830</v>
       </c>
       <c r="B47" t="n">
-        <v>57736</v>
+        <v>57577</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5146,17 +5146,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>487344</v>
+        <v>487123</v>
       </c>
       <c r="R47" t="n">
-        <v>7039018</v>
+        <v>7039173</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5189,11 +5201,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5322,7 +5329,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129298780</v>
+        <v>129298808</v>
       </c>
       <c r="B49" t="n">
         <v>57736</v>
@@ -5357,10 +5364,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486859</v>
+        <v>487344</v>
       </c>
       <c r="R49" t="n">
-        <v>7039262</v>
+        <v>7039018</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5397,7 +5404,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5424,27 +5431,27 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129298830</v>
+        <v>129298780</v>
       </c>
       <c r="B50" t="n">
-        <v>57577</v>
+        <v>57736</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5452,29 +5459,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>487123</v>
+        <v>486859</v>
       </c>
       <c r="R50" t="n">
-        <v>7039173</v>
+        <v>7039262</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5507,6 +5502,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5533,7 +5533,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129298765</v>
+        <v>129298793</v>
       </c>
       <c r="B51" t="n">
         <v>57736</v>
@@ -5568,10 +5568,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>487122</v>
+        <v>487183</v>
       </c>
       <c r="R51" t="n">
-        <v>7039034</v>
+        <v>7039216</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5635,7 +5635,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129298770</v>
+        <v>129298823</v>
       </c>
       <c r="B52" t="n">
         <v>57736</v>
@@ -5670,10 +5670,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>486972</v>
+        <v>487363</v>
       </c>
       <c r="R52" t="n">
-        <v>7039122</v>
+        <v>7038902</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5737,7 +5737,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129298778</v>
+        <v>129298765</v>
       </c>
       <c r="B53" t="n">
         <v>57736</v>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486871</v>
+        <v>487122</v>
       </c>
       <c r="R53" t="n">
-        <v>7039260</v>
+        <v>7039034</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129298793</v>
+        <v>129298770</v>
       </c>
       <c r="B54" t="n">
         <v>57736</v>
@@ -5874,10 +5874,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>487183</v>
+        <v>486972</v>
       </c>
       <c r="R54" t="n">
-        <v>7039216</v>
+        <v>7039122</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5941,7 +5941,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129298823</v>
+        <v>129298778</v>
       </c>
       <c r="B55" t="n">
         <v>57736</v>
@@ -5976,10 +5976,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>487363</v>
+        <v>486871</v>
       </c>
       <c r="R55" t="n">
-        <v>7038902</v>
+        <v>7039260</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6043,7 +6043,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129298804</v>
+        <v>129298792</v>
       </c>
       <c r="B56" t="n">
         <v>57736</v>
@@ -6078,10 +6078,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>487288</v>
+        <v>487153</v>
       </c>
       <c r="R56" t="n">
-        <v>7039002</v>
+        <v>7039212</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6145,7 +6145,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129298792</v>
+        <v>129298750</v>
       </c>
       <c r="B57" t="n">
         <v>57736</v>
@@ -6180,10 +6180,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>487153</v>
+        <v>487272</v>
       </c>
       <c r="R57" t="n">
-        <v>7039212</v>
+        <v>7038946</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6247,7 +6247,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129298750</v>
+        <v>129298769</v>
       </c>
       <c r="B58" t="n">
         <v>57736</v>
@@ -6282,10 +6282,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>487272</v>
+        <v>487109</v>
       </c>
       <c r="R58" t="n">
-        <v>7038946</v>
+        <v>7039040</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6349,7 +6349,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129298769</v>
+        <v>129298804</v>
       </c>
       <c r="B59" t="n">
         <v>57736</v>
@@ -6384,10 +6384,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>487109</v>
+        <v>487288</v>
       </c>
       <c r="R59" t="n">
-        <v>7039040</v>
+        <v>7039002</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6553,7 +6553,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129298795</v>
+        <v>129298805</v>
       </c>
       <c r="B61" t="n">
         <v>57736</v>
@@ -6588,10 +6588,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>487100</v>
+        <v>487346</v>
       </c>
       <c r="R61" t="n">
-        <v>7039085</v>
+        <v>7039012</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6655,7 +6655,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129298783</v>
+        <v>129298809</v>
       </c>
       <c r="B62" t="n">
         <v>57736</v>
@@ -6690,10 +6690,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>487024</v>
+        <v>487348</v>
       </c>
       <c r="R62" t="n">
-        <v>7039203</v>
+        <v>7039005</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6757,7 +6757,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129298805</v>
+        <v>129298802</v>
       </c>
       <c r="B63" t="n">
         <v>57736</v>
@@ -6792,10 +6792,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>487346</v>
+        <v>487302</v>
       </c>
       <c r="R63" t="n">
-        <v>7039012</v>
+        <v>7039045</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6859,7 +6859,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129298809</v>
+        <v>129298795</v>
       </c>
       <c r="B64" t="n">
         <v>57736</v>
@@ -6894,10 +6894,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>487348</v>
+        <v>487100</v>
       </c>
       <c r="R64" t="n">
-        <v>7039005</v>
+        <v>7039085</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6961,7 +6961,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129298802</v>
+        <v>129298748</v>
       </c>
       <c r="B65" t="n">
         <v>57736</v>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>487302</v>
+        <v>487301</v>
       </c>
       <c r="R65" t="n">
-        <v>7039045</v>
+        <v>7038925</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7063,7 +7063,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129298748</v>
+        <v>129298783</v>
       </c>
       <c r="B66" t="n">
         <v>57736</v>
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>487301</v>
+        <v>487024</v>
       </c>
       <c r="R66" t="n">
-        <v>7038925</v>
+        <v>7039203</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7675,7 +7675,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129298816</v>
+        <v>129298776</v>
       </c>
       <c r="B72" t="n">
         <v>57736</v>
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>487389</v>
+        <v>486855</v>
       </c>
       <c r="R72" t="n">
-        <v>7038985</v>
+        <v>7039252</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7777,7 +7777,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129298774</v>
+        <v>129298816</v>
       </c>
       <c r="B73" t="n">
         <v>57736</v>
@@ -7812,10 +7812,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>486866</v>
+        <v>487389</v>
       </c>
       <c r="R73" t="n">
-        <v>7039249</v>
+        <v>7038985</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7852,7 +7852,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7879,7 +7879,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129298773</v>
+        <v>129298813</v>
       </c>
       <c r="B74" t="n">
         <v>57736</v>
@@ -7914,10 +7914,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>486807</v>
+        <v>487367</v>
       </c>
       <c r="R74" t="n">
-        <v>7039220</v>
+        <v>7038998</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7981,7 +7981,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129298776</v>
+        <v>129298820</v>
       </c>
       <c r="B75" t="n">
         <v>57736</v>
@@ -8016,10 +8016,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>486855</v>
+        <v>487354</v>
       </c>
       <c r="R75" t="n">
-        <v>7039252</v>
+        <v>7038894</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8056,7 +8056,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8083,7 +8083,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129298813</v>
+        <v>129298774</v>
       </c>
       <c r="B76" t="n">
         <v>57736</v>
@@ -8118,10 +8118,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>487367</v>
+        <v>486866</v>
       </c>
       <c r="R76" t="n">
-        <v>7038998</v>
+        <v>7039249</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8158,7 +8158,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8185,7 +8185,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129298820</v>
+        <v>129298773</v>
       </c>
       <c r="B77" t="n">
         <v>57736</v>
@@ -8220,10 +8220,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>487354</v>
+        <v>486807</v>
       </c>
       <c r="R77" t="n">
-        <v>7038894</v>
+        <v>7039220</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8260,7 +8260,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8389,7 +8389,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129298803</v>
+        <v>129298797</v>
       </c>
       <c r="B79" t="n">
         <v>57736</v>
@@ -8424,7 +8424,7 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>487303</v>
+        <v>487134</v>
       </c>
       <c r="R79" t="n">
         <v>7039037</v>
@@ -8491,7 +8491,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129298817</v>
+        <v>129298803</v>
       </c>
       <c r="B80" t="n">
         <v>57736</v>
@@ -8526,10 +8526,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>487460</v>
+        <v>487303</v>
       </c>
       <c r="R80" t="n">
-        <v>7038984</v>
+        <v>7039037</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8593,7 +8593,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129298800</v>
+        <v>129298822</v>
       </c>
       <c r="B81" t="n">
         <v>57736</v>
@@ -8621,33 +8621,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>487288</v>
+        <v>487373</v>
       </c>
       <c r="R81" t="n">
-        <v>7039015</v>
+        <v>7038897</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8684,7 +8668,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Födosökande hane</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8711,7 +8695,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129298797</v>
+        <v>129298817</v>
       </c>
       <c r="B82" t="n">
         <v>57736</v>
@@ -8746,10 +8730,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>487134</v>
+        <v>487460</v>
       </c>
       <c r="R82" t="n">
-        <v>7039037</v>
+        <v>7038984</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8813,7 +8797,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129298822</v>
+        <v>129298800</v>
       </c>
       <c r="B83" t="n">
         <v>57736</v>
@@ -8841,17 +8825,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>487373</v>
+        <v>487288</v>
       </c>
       <c r="R83" t="n">
-        <v>7038897</v>
+        <v>7039015</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Födosökande hane</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9017,7 +9017,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129298753</v>
+        <v>129298781</v>
       </c>
       <c r="B85" t="n">
         <v>57736</v>
@@ -9052,10 +9052,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>487240</v>
+        <v>486864</v>
       </c>
       <c r="R85" t="n">
-        <v>7038959</v>
+        <v>7039272</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9119,7 +9119,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129298757</v>
+        <v>129298785</v>
       </c>
       <c r="B86" t="n">
         <v>57736</v>
@@ -9154,10 +9154,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>487188</v>
+        <v>487007</v>
       </c>
       <c r="R86" t="n">
-        <v>7038992</v>
+        <v>7039210</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9194,7 +9194,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9221,7 +9221,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129298781</v>
+        <v>129298753</v>
       </c>
       <c r="B87" t="n">
         <v>57736</v>
@@ -9256,10 +9256,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>486864</v>
+        <v>487240</v>
       </c>
       <c r="R87" t="n">
-        <v>7039272</v>
+        <v>7038959</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9323,7 +9323,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129298785</v>
+        <v>129298757</v>
       </c>
       <c r="B88" t="n">
         <v>57736</v>
@@ -9358,10 +9358,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>487007</v>
+        <v>487188</v>
       </c>
       <c r="R88" t="n">
-        <v>7039210</v>
+        <v>7038992</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9527,7 +9527,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129298801</v>
+        <v>129298771</v>
       </c>
       <c r="B90" t="n">
         <v>57736</v>
@@ -9562,10 +9562,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>487268</v>
+        <v>486885</v>
       </c>
       <c r="R90" t="n">
-        <v>7039003</v>
+        <v>7039172</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9629,45 +9629,61 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129298746</v>
+        <v>129298847</v>
       </c>
       <c r="B91" t="n">
-        <v>57736</v>
+        <v>57596</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>100136</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>487316</v>
+        <v>486999</v>
       </c>
       <c r="R91" t="n">
-        <v>7038914</v>
+        <v>7039199</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9704,7 +9720,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Jagades av en nötskrika</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9731,7 +9747,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129298771</v>
+        <v>129298789</v>
       </c>
       <c r="B92" t="n">
         <v>57736</v>
@@ -9766,10 +9782,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>486885</v>
+        <v>487041</v>
       </c>
       <c r="R92" t="n">
-        <v>7039172</v>
+        <v>7039167</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9833,61 +9849,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129298847</v>
+        <v>129298801</v>
       </c>
       <c r="B93" t="n">
-        <v>57596</v>
+        <v>57736</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100136</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>486999</v>
+        <v>487268</v>
       </c>
       <c r="R93" t="n">
-        <v>7039199</v>
+        <v>7039003</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9924,7 +9924,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Jagades av en nötskrika</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9951,7 +9951,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129298789</v>
+        <v>129298814</v>
       </c>
       <c r="B94" t="n">
         <v>57736</v>
@@ -9986,10 +9986,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>487041</v>
+        <v>487366</v>
       </c>
       <c r="R94" t="n">
-        <v>7039167</v>
+        <v>7038997</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10053,7 +10053,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129298814</v>
+        <v>129298772</v>
       </c>
       <c r="B95" t="n">
         <v>57736</v>
@@ -10088,10 +10088,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>487366</v>
+        <v>486849</v>
       </c>
       <c r="R95" t="n">
-        <v>7038997</v>
+        <v>7039185</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10128,7 +10128,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10155,7 +10155,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129298772</v>
+        <v>129298746</v>
       </c>
       <c r="B96" t="n">
         <v>57736</v>
@@ -10190,10 +10190,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>486849</v>
+        <v>487316</v>
       </c>
       <c r="R96" t="n">
-        <v>7039185</v>
+        <v>7038914</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10563,7 +10563,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129298754</v>
+        <v>129298791</v>
       </c>
       <c r="B100" t="n">
         <v>57736</v>
@@ -10598,10 +10598,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>487222</v>
+        <v>487112</v>
       </c>
       <c r="R100" t="n">
-        <v>7038974</v>
+        <v>7039182</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10638,7 +10638,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10665,7 +10665,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129298791</v>
+        <v>129298754</v>
       </c>
       <c r="B101" t="n">
         <v>57736</v>
@@ -10700,10 +10700,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>487112</v>
+        <v>487222</v>
       </c>
       <c r="R101" t="n">
-        <v>7039182</v>
+        <v>7038974</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10740,7 +10740,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10971,7 +10971,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129298758</v>
+        <v>129298782</v>
       </c>
       <c r="B104" t="n">
         <v>57736</v>
@@ -11006,10 +11006,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>487183</v>
+        <v>486857</v>
       </c>
       <c r="R104" t="n">
-        <v>7038993</v>
+        <v>7039276</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11046,7 +11046,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11073,7 +11073,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129298782</v>
+        <v>129298758</v>
       </c>
       <c r="B105" t="n">
         <v>57736</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>486857</v>
+        <v>487183</v>
       </c>
       <c r="R105" t="n">
-        <v>7039276</v>
+        <v>7038993</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11148,7 +11148,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11481,7 +11481,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129298760</v>
+        <v>129298796</v>
       </c>
       <c r="B109" t="n">
         <v>57736</v>
@@ -11516,10 +11516,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>487141</v>
+        <v>487139</v>
       </c>
       <c r="R109" t="n">
-        <v>7039023</v>
+        <v>7039088</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11556,7 +11556,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11583,7 +11583,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129298796</v>
+        <v>129298760</v>
       </c>
       <c r="B110" t="n">
         <v>57736</v>
@@ -11618,10 +11618,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>487139</v>
+        <v>487141</v>
       </c>
       <c r="R110" t="n">
-        <v>7039088</v>
+        <v>7039023</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11658,7 +11658,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 46357-2025 artfynd.xlsx
+++ b/artfynd/A 46357-2025 artfynd.xlsx
@@ -4404,7 +4404,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129298812</v>
+        <v>129298759</v>
       </c>
       <c r="B40" t="n">
         <v>57736</v>
@@ -4439,10 +4439,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>487362</v>
+        <v>487171</v>
       </c>
       <c r="R40" t="n">
-        <v>7039030</v>
+        <v>7039000</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4506,7 +4506,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129298759</v>
+        <v>129298812</v>
       </c>
       <c r="B41" t="n">
         <v>57736</v>
@@ -4541,10 +4541,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>487171</v>
+        <v>487362</v>
       </c>
       <c r="R41" t="n">
-        <v>7039000</v>
+        <v>7039030</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5635,7 +5635,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129298823</v>
+        <v>129298765</v>
       </c>
       <c r="B52" t="n">
         <v>57736</v>
@@ -5670,10 +5670,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>487363</v>
+        <v>487122</v>
       </c>
       <c r="R52" t="n">
-        <v>7038902</v>
+        <v>7039034</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5737,7 +5737,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129298765</v>
+        <v>129298770</v>
       </c>
       <c r="B53" t="n">
         <v>57736</v>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>487122</v>
+        <v>486972</v>
       </c>
       <c r="R53" t="n">
-        <v>7039034</v>
+        <v>7039122</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129298770</v>
+        <v>129298778</v>
       </c>
       <c r="B54" t="n">
         <v>57736</v>
@@ -5874,10 +5874,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486972</v>
+        <v>486871</v>
       </c>
       <c r="R54" t="n">
-        <v>7039122</v>
+        <v>7039260</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5941,7 +5941,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129298778</v>
+        <v>129298823</v>
       </c>
       <c r="B55" t="n">
         <v>57736</v>
@@ -5976,10 +5976,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486871</v>
+        <v>487363</v>
       </c>
       <c r="R55" t="n">
-        <v>7039260</v>
+        <v>7038902</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6553,7 +6553,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129298805</v>
+        <v>129298802</v>
       </c>
       <c r="B61" t="n">
         <v>57736</v>
@@ -6588,10 +6588,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>487346</v>
+        <v>487302</v>
       </c>
       <c r="R61" t="n">
-        <v>7039012</v>
+        <v>7039045</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6655,7 +6655,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129298809</v>
+        <v>129298795</v>
       </c>
       <c r="B62" t="n">
         <v>57736</v>
@@ -6690,10 +6690,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>487348</v>
+        <v>487100</v>
       </c>
       <c r="R62" t="n">
-        <v>7039005</v>
+        <v>7039085</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6757,7 +6757,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129298802</v>
+        <v>129298748</v>
       </c>
       <c r="B63" t="n">
         <v>57736</v>
@@ -6792,10 +6792,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>487302</v>
+        <v>487301</v>
       </c>
       <c r="R63" t="n">
-        <v>7039045</v>
+        <v>7038925</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6859,7 +6859,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129298795</v>
+        <v>129298783</v>
       </c>
       <c r="B64" t="n">
         <v>57736</v>
@@ -6894,10 +6894,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>487100</v>
+        <v>487024</v>
       </c>
       <c r="R64" t="n">
-        <v>7039085</v>
+        <v>7039203</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6961,7 +6961,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129298748</v>
+        <v>129298805</v>
       </c>
       <c r="B65" t="n">
         <v>57736</v>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>487301</v>
+        <v>487346</v>
       </c>
       <c r="R65" t="n">
-        <v>7038925</v>
+        <v>7039012</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7063,7 +7063,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129298783</v>
+        <v>129298809</v>
       </c>
       <c r="B66" t="n">
         <v>57736</v>
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>487024</v>
+        <v>487348</v>
       </c>
       <c r="R66" t="n">
-        <v>7039203</v>
+        <v>7039005</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7777,7 +7777,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129298816</v>
+        <v>129298774</v>
       </c>
       <c r="B73" t="n">
         <v>57736</v>
@@ -7812,10 +7812,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>487389</v>
+        <v>486866</v>
       </c>
       <c r="R73" t="n">
-        <v>7038985</v>
+        <v>7039249</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7852,7 +7852,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7879,7 +7879,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129298813</v>
+        <v>129298773</v>
       </c>
       <c r="B74" t="n">
         <v>57736</v>
@@ -7914,10 +7914,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>487367</v>
+        <v>486807</v>
       </c>
       <c r="R74" t="n">
-        <v>7038998</v>
+        <v>7039220</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7981,7 +7981,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129298820</v>
+        <v>129298816</v>
       </c>
       <c r="B75" t="n">
         <v>57736</v>
@@ -8016,10 +8016,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>487354</v>
+        <v>487389</v>
       </c>
       <c r="R75" t="n">
-        <v>7038894</v>
+        <v>7038985</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8083,7 +8083,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129298774</v>
+        <v>129298813</v>
       </c>
       <c r="B76" t="n">
         <v>57736</v>
@@ -8118,10 +8118,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>486866</v>
+        <v>487367</v>
       </c>
       <c r="R76" t="n">
-        <v>7039249</v>
+        <v>7038998</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8158,7 +8158,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8185,7 +8185,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129298773</v>
+        <v>129298820</v>
       </c>
       <c r="B77" t="n">
         <v>57736</v>
@@ -8220,10 +8220,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>486807</v>
+        <v>487354</v>
       </c>
       <c r="R77" t="n">
-        <v>7039220</v>
+        <v>7038894</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8260,7 +8260,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8593,7 +8593,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129298822</v>
+        <v>129298800</v>
       </c>
       <c r="B81" t="n">
         <v>57736</v>
@@ -8621,17 +8621,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>487373</v>
+        <v>487288</v>
       </c>
       <c r="R81" t="n">
-        <v>7038897</v>
+        <v>7039015</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8668,7 +8684,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Födosökande hane</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8695,7 +8711,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129298817</v>
+        <v>129298822</v>
       </c>
       <c r="B82" t="n">
         <v>57736</v>
@@ -8730,10 +8746,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>487460</v>
+        <v>487373</v>
       </c>
       <c r="R82" t="n">
-        <v>7038984</v>
+        <v>7038897</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8797,7 +8813,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129298800</v>
+        <v>129298817</v>
       </c>
       <c r="B83" t="n">
         <v>57736</v>
@@ -8825,33 +8841,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>487288</v>
+        <v>487460</v>
       </c>
       <c r="R83" t="n">
-        <v>7039015</v>
+        <v>7038984</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Födosökande hane</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9629,61 +9629,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129298847</v>
+        <v>129298789</v>
       </c>
       <c r="B91" t="n">
-        <v>57596</v>
+        <v>57736</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100136</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>486999</v>
+        <v>487041</v>
       </c>
       <c r="R91" t="n">
-        <v>7039199</v>
+        <v>7039167</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9720,7 +9704,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Jagades av en nötskrika</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9747,7 +9731,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129298789</v>
+        <v>129298801</v>
       </c>
       <c r="B92" t="n">
         <v>57736</v>
@@ -9782,10 +9766,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>487041</v>
+        <v>487268</v>
       </c>
       <c r="R92" t="n">
-        <v>7039167</v>
+        <v>7039003</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9849,7 +9833,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129298801</v>
+        <v>129298772</v>
       </c>
       <c r="B93" t="n">
         <v>57736</v>
@@ -9884,10 +9868,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>487268</v>
+        <v>486849</v>
       </c>
       <c r="R93" t="n">
-        <v>7039003</v>
+        <v>7039185</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9951,7 +9935,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129298814</v>
+        <v>129298746</v>
       </c>
       <c r="B94" t="n">
         <v>57736</v>
@@ -9986,10 +9970,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>487366</v>
+        <v>487316</v>
       </c>
       <c r="R94" t="n">
-        <v>7038997</v>
+        <v>7038914</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10026,7 +10010,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10053,45 +10037,61 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129298772</v>
+        <v>129298847</v>
       </c>
       <c r="B95" t="n">
-        <v>57736</v>
+        <v>57596</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>100136</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>486849</v>
+        <v>486999</v>
       </c>
       <c r="R95" t="n">
-        <v>7039185</v>
+        <v>7039199</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10128,7 +10128,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Jagades av en nötskrika</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10155,7 +10155,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129298746</v>
+        <v>129298814</v>
       </c>
       <c r="B96" t="n">
         <v>57736</v>
@@ -10190,10 +10190,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>487316</v>
+        <v>487366</v>
       </c>
       <c r="R96" t="n">
-        <v>7038914</v>
+        <v>7038997</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10230,7 +10230,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10869,7 +10869,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129298806</v>
+        <v>129298815</v>
       </c>
       <c r="B103" t="n">
         <v>57736</v>
@@ -10904,10 +10904,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>487339</v>
+        <v>487375</v>
       </c>
       <c r="R103" t="n">
-        <v>7039009</v>
+        <v>7038981</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10971,7 +10971,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129298782</v>
+        <v>129298806</v>
       </c>
       <c r="B104" t="n">
         <v>57736</v>
@@ -11006,10 +11006,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>486857</v>
+        <v>487339</v>
       </c>
       <c r="R104" t="n">
-        <v>7039276</v>
+        <v>7039009</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11046,7 +11046,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11073,7 +11073,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129298758</v>
+        <v>129298782</v>
       </c>
       <c r="B105" t="n">
         <v>57736</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>487183</v>
+        <v>486857</v>
       </c>
       <c r="R105" t="n">
-        <v>7038993</v>
+        <v>7039276</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11148,7 +11148,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11175,7 +11175,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129298815</v>
+        <v>129298758</v>
       </c>
       <c r="B106" t="n">
         <v>57736</v>
@@ -11210,10 +11210,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>487375</v>
+        <v>487183</v>
       </c>
       <c r="R106" t="n">
-        <v>7038981</v>
+        <v>7038993</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>

--- a/artfynd/A 46357-2025 artfynd.xlsx
+++ b/artfynd/A 46357-2025 artfynd.xlsx
@@ -4404,7 +4404,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129298759</v>
+        <v>129298812</v>
       </c>
       <c r="B40" t="n">
         <v>57736</v>
@@ -4439,10 +4439,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>487171</v>
+        <v>487362</v>
       </c>
       <c r="R40" t="n">
-        <v>7039000</v>
+        <v>7039030</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4506,7 +4506,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129298812</v>
+        <v>129298759</v>
       </c>
       <c r="B41" t="n">
         <v>57736</v>
@@ -4541,10 +4541,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>487362</v>
+        <v>487171</v>
       </c>
       <c r="R41" t="n">
-        <v>7039030</v>
+        <v>7039000</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5118,27 +5118,27 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129298830</v>
+        <v>129298775</v>
       </c>
       <c r="B47" t="n">
-        <v>57577</v>
+        <v>57736</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5146,29 +5146,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>487123</v>
+        <v>486860</v>
       </c>
       <c r="R47" t="n">
-        <v>7039173</v>
+        <v>7039244</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5201,6 +5189,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5227,7 +5220,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129298775</v>
+        <v>129298808</v>
       </c>
       <c r="B48" t="n">
         <v>57736</v>
@@ -5262,10 +5255,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486860</v>
+        <v>487344</v>
       </c>
       <c r="R48" t="n">
-        <v>7039244</v>
+        <v>7039018</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5329,7 +5322,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129298808</v>
+        <v>129298780</v>
       </c>
       <c r="B49" t="n">
         <v>57736</v>
@@ -5364,10 +5357,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>487344</v>
+        <v>486859</v>
       </c>
       <c r="R49" t="n">
-        <v>7039018</v>
+        <v>7039262</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5404,7 +5397,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5431,27 +5424,27 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129298780</v>
+        <v>129298830</v>
       </c>
       <c r="B50" t="n">
-        <v>57736</v>
+        <v>57577</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5459,17 +5452,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486859</v>
+        <v>487123</v>
       </c>
       <c r="R50" t="n">
-        <v>7039262</v>
+        <v>7039173</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5502,11 +5507,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5635,7 +5635,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129298765</v>
+        <v>129298823</v>
       </c>
       <c r="B52" t="n">
         <v>57736</v>
@@ -5670,10 +5670,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>487122</v>
+        <v>487363</v>
       </c>
       <c r="R52" t="n">
-        <v>7039034</v>
+        <v>7038902</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5737,7 +5737,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129298770</v>
+        <v>129298765</v>
       </c>
       <c r="B53" t="n">
         <v>57736</v>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486972</v>
+        <v>487122</v>
       </c>
       <c r="R53" t="n">
-        <v>7039122</v>
+        <v>7039034</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129298778</v>
+        <v>129298770</v>
       </c>
       <c r="B54" t="n">
         <v>57736</v>
@@ -5874,10 +5874,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486871</v>
+        <v>486972</v>
       </c>
       <c r="R54" t="n">
-        <v>7039260</v>
+        <v>7039122</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5941,7 +5941,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129298823</v>
+        <v>129298778</v>
       </c>
       <c r="B55" t="n">
         <v>57736</v>
@@ -5976,10 +5976,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>487363</v>
+        <v>486871</v>
       </c>
       <c r="R55" t="n">
-        <v>7038902</v>
+        <v>7039260</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6553,7 +6553,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129298802</v>
+        <v>129298805</v>
       </c>
       <c r="B61" t="n">
         <v>57736</v>
@@ -6588,10 +6588,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>487302</v>
+        <v>487346</v>
       </c>
       <c r="R61" t="n">
-        <v>7039045</v>
+        <v>7039012</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6655,7 +6655,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129298795</v>
+        <v>129298809</v>
       </c>
       <c r="B62" t="n">
         <v>57736</v>
@@ -6690,10 +6690,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>487100</v>
+        <v>487348</v>
       </c>
       <c r="R62" t="n">
-        <v>7039085</v>
+        <v>7039005</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6757,7 +6757,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129298748</v>
+        <v>129298802</v>
       </c>
       <c r="B63" t="n">
         <v>57736</v>
@@ -6792,10 +6792,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>487301</v>
+        <v>487302</v>
       </c>
       <c r="R63" t="n">
-        <v>7038925</v>
+        <v>7039045</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6859,7 +6859,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129298783</v>
+        <v>129298795</v>
       </c>
       <c r="B64" t="n">
         <v>57736</v>
@@ -6894,10 +6894,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>487024</v>
+        <v>487100</v>
       </c>
       <c r="R64" t="n">
-        <v>7039203</v>
+        <v>7039085</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6961,7 +6961,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129298805</v>
+        <v>129298748</v>
       </c>
       <c r="B65" t="n">
         <v>57736</v>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>487346</v>
+        <v>487301</v>
       </c>
       <c r="R65" t="n">
-        <v>7039012</v>
+        <v>7038925</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7063,7 +7063,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129298809</v>
+        <v>129298783</v>
       </c>
       <c r="B66" t="n">
         <v>57736</v>
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>487348</v>
+        <v>487024</v>
       </c>
       <c r="R66" t="n">
-        <v>7039005</v>
+        <v>7039203</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7777,7 +7777,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129298774</v>
+        <v>129298816</v>
       </c>
       <c r="B73" t="n">
         <v>57736</v>
@@ -7812,10 +7812,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>486866</v>
+        <v>487389</v>
       </c>
       <c r="R73" t="n">
-        <v>7039249</v>
+        <v>7038985</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7852,7 +7852,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7879,7 +7879,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129298773</v>
+        <v>129298813</v>
       </c>
       <c r="B74" t="n">
         <v>57736</v>
@@ -7914,10 +7914,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>486807</v>
+        <v>487367</v>
       </c>
       <c r="R74" t="n">
-        <v>7039220</v>
+        <v>7038998</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7981,7 +7981,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129298816</v>
+        <v>129298820</v>
       </c>
       <c r="B75" t="n">
         <v>57736</v>
@@ -8016,10 +8016,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>487389</v>
+        <v>487354</v>
       </c>
       <c r="R75" t="n">
-        <v>7038985</v>
+        <v>7038894</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8083,7 +8083,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129298813</v>
+        <v>129298774</v>
       </c>
       <c r="B76" t="n">
         <v>57736</v>
@@ -8118,10 +8118,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>487367</v>
+        <v>486866</v>
       </c>
       <c r="R76" t="n">
-        <v>7038998</v>
+        <v>7039249</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8158,7 +8158,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8185,7 +8185,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129298820</v>
+        <v>129298773</v>
       </c>
       <c r="B77" t="n">
         <v>57736</v>
@@ -8220,10 +8220,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>487354</v>
+        <v>486807</v>
       </c>
       <c r="R77" t="n">
-        <v>7038894</v>
+        <v>7039220</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8260,7 +8260,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8593,7 +8593,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129298800</v>
+        <v>129298822</v>
       </c>
       <c r="B81" t="n">
         <v>57736</v>
@@ -8621,33 +8621,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>487288</v>
+        <v>487373</v>
       </c>
       <c r="R81" t="n">
-        <v>7039015</v>
+        <v>7038897</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8684,7 +8668,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Födosökande hane</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8711,7 +8695,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129298822</v>
+        <v>129298817</v>
       </c>
       <c r="B82" t="n">
         <v>57736</v>
@@ -8746,10 +8730,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>487373</v>
+        <v>487460</v>
       </c>
       <c r="R82" t="n">
-        <v>7038897</v>
+        <v>7038984</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8813,7 +8797,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129298817</v>
+        <v>129298800</v>
       </c>
       <c r="B83" t="n">
         <v>57736</v>
@@ -8841,17 +8825,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>487460</v>
+        <v>487288</v>
       </c>
       <c r="R83" t="n">
-        <v>7038984</v>
+        <v>7039015</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Födosökande hane</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9629,45 +9629,61 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129298789</v>
+        <v>129298847</v>
       </c>
       <c r="B91" t="n">
-        <v>57736</v>
+        <v>57596</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>100136</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>487041</v>
+        <v>486999</v>
       </c>
       <c r="R91" t="n">
-        <v>7039167</v>
+        <v>7039199</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9704,7 +9720,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Jagades av en nötskrika</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9731,7 +9747,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129298801</v>
+        <v>129298789</v>
       </c>
       <c r="B92" t="n">
         <v>57736</v>
@@ -9766,10 +9782,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>487268</v>
+        <v>487041</v>
       </c>
       <c r="R92" t="n">
-        <v>7039003</v>
+        <v>7039167</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9833,7 +9849,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129298772</v>
+        <v>129298801</v>
       </c>
       <c r="B93" t="n">
         <v>57736</v>
@@ -9868,10 +9884,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>486849</v>
+        <v>487268</v>
       </c>
       <c r="R93" t="n">
-        <v>7039185</v>
+        <v>7039003</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9935,7 +9951,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129298746</v>
+        <v>129298814</v>
       </c>
       <c r="B94" t="n">
         <v>57736</v>
@@ -9970,10 +9986,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>487316</v>
+        <v>487366</v>
       </c>
       <c r="R94" t="n">
-        <v>7038914</v>
+        <v>7038997</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10010,7 +10026,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10037,61 +10053,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129298847</v>
+        <v>129298772</v>
       </c>
       <c r="B95" t="n">
-        <v>57596</v>
+        <v>57736</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100136</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>486999</v>
+        <v>486849</v>
       </c>
       <c r="R95" t="n">
-        <v>7039199</v>
+        <v>7039185</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10128,7 +10128,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Jagades av en nötskrika</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10155,7 +10155,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129298814</v>
+        <v>129298746</v>
       </c>
       <c r="B96" t="n">
         <v>57736</v>
@@ -10190,10 +10190,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>487366</v>
+        <v>487316</v>
       </c>
       <c r="R96" t="n">
-        <v>7038997</v>
+        <v>7038914</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10230,7 +10230,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10869,7 +10869,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129298815</v>
+        <v>129298806</v>
       </c>
       <c r="B103" t="n">
         <v>57736</v>
@@ -10904,10 +10904,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>487375</v>
+        <v>487339</v>
       </c>
       <c r="R103" t="n">
-        <v>7038981</v>
+        <v>7039009</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10971,7 +10971,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129298806</v>
+        <v>129298782</v>
       </c>
       <c r="B104" t="n">
         <v>57736</v>
@@ -11006,10 +11006,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>487339</v>
+        <v>486857</v>
       </c>
       <c r="R104" t="n">
-        <v>7039009</v>
+        <v>7039276</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11046,7 +11046,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11073,7 +11073,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129298782</v>
+        <v>129298758</v>
       </c>
       <c r="B105" t="n">
         <v>57736</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>486857</v>
+        <v>487183</v>
       </c>
       <c r="R105" t="n">
-        <v>7039276</v>
+        <v>7038993</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11148,7 +11148,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11175,7 +11175,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129298758</v>
+        <v>129298815</v>
       </c>
       <c r="B106" t="n">
         <v>57736</v>
@@ -11210,10 +11210,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>487183</v>
+        <v>487375</v>
       </c>
       <c r="R106" t="n">
-        <v>7038993</v>
+        <v>7038981</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>

--- a/artfynd/A 46357-2025 artfynd.xlsx
+++ b/artfynd/A 46357-2025 artfynd.xlsx
@@ -4098,7 +4098,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129298786</v>
+        <v>129298818</v>
       </c>
       <c r="B37" t="n">
         <v>57736</v>
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>487006</v>
+        <v>487389</v>
       </c>
       <c r="R37" t="n">
-        <v>7039175</v>
+        <v>7038925</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4200,7 +4200,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129298818</v>
+        <v>129298819</v>
       </c>
       <c r="B38" t="n">
         <v>57736</v>
@@ -4235,10 +4235,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>487389</v>
+        <v>487346</v>
       </c>
       <c r="R38" t="n">
-        <v>7038925</v>
+        <v>7038911</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4302,7 +4302,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129298819</v>
+        <v>129298786</v>
       </c>
       <c r="B39" t="n">
         <v>57736</v>
@@ -4337,10 +4337,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>487346</v>
+        <v>487006</v>
       </c>
       <c r="R39" t="n">
-        <v>7038911</v>
+        <v>7039175</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 46357-2025 artfynd.xlsx
+++ b/artfynd/A 46357-2025 artfynd.xlsx
@@ -4098,7 +4098,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129298818</v>
+        <v>129298786</v>
       </c>
       <c r="B37" t="n">
         <v>57736</v>
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>487389</v>
+        <v>487006</v>
       </c>
       <c r="R37" t="n">
-        <v>7038925</v>
+        <v>7039175</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4200,7 +4200,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129298819</v>
+        <v>129298818</v>
       </c>
       <c r="B38" t="n">
         <v>57736</v>
@@ -4235,10 +4235,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>487346</v>
+        <v>487389</v>
       </c>
       <c r="R38" t="n">
-        <v>7038911</v>
+        <v>7038925</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4302,7 +4302,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129298786</v>
+        <v>129298819</v>
       </c>
       <c r="B39" t="n">
         <v>57736</v>
@@ -4337,10 +4337,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>487006</v>
+        <v>487346</v>
       </c>
       <c r="R39" t="n">
-        <v>7039175</v>
+        <v>7038911</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4608,7 +4608,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129298761</v>
+        <v>129298755</v>
       </c>
       <c r="B42" t="n">
         <v>57736</v>
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>487137</v>
+        <v>487206</v>
       </c>
       <c r="R42" t="n">
-        <v>7039024</v>
+        <v>7038982</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4710,7 +4710,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129298755</v>
+        <v>129298799</v>
       </c>
       <c r="B43" t="n">
         <v>57736</v>
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>487206</v>
+        <v>487230</v>
       </c>
       <c r="R43" t="n">
-        <v>7038982</v>
+        <v>7039041</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4812,7 +4812,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129298799</v>
+        <v>129298761</v>
       </c>
       <c r="B44" t="n">
         <v>57736</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>487230</v>
+        <v>487137</v>
       </c>
       <c r="R44" t="n">
-        <v>7039041</v>
+        <v>7039024</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5220,7 +5220,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129298808</v>
+        <v>129298780</v>
       </c>
       <c r="B48" t="n">
         <v>57736</v>
@@ -5255,10 +5255,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>487344</v>
+        <v>486859</v>
       </c>
       <c r="R48" t="n">
-        <v>7039018</v>
+        <v>7039262</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5295,7 +5295,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5322,7 +5322,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129298780</v>
+        <v>129298808</v>
       </c>
       <c r="B49" t="n">
         <v>57736</v>
@@ -5357,10 +5357,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486859</v>
+        <v>487344</v>
       </c>
       <c r="R49" t="n">
-        <v>7039262</v>
+        <v>7039018</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5533,7 +5533,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129298793</v>
+        <v>129298823</v>
       </c>
       <c r="B51" t="n">
         <v>57736</v>
@@ -5568,10 +5568,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>487183</v>
+        <v>487363</v>
       </c>
       <c r="R51" t="n">
-        <v>7039216</v>
+        <v>7038902</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5635,7 +5635,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129298823</v>
+        <v>129298793</v>
       </c>
       <c r="B52" t="n">
         <v>57736</v>
@@ -5670,10 +5670,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>487363</v>
+        <v>487183</v>
       </c>
       <c r="R52" t="n">
-        <v>7038902</v>
+        <v>7039216</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6043,7 +6043,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129298792</v>
+        <v>129298804</v>
       </c>
       <c r="B56" t="n">
         <v>57736</v>
@@ -6078,10 +6078,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>487153</v>
+        <v>487288</v>
       </c>
       <c r="R56" t="n">
-        <v>7039212</v>
+        <v>7039002</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6145,7 +6145,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129298750</v>
+        <v>129298794</v>
       </c>
       <c r="B57" t="n">
         <v>57736</v>
@@ -6180,10 +6180,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>487272</v>
+        <v>487186</v>
       </c>
       <c r="R57" t="n">
-        <v>7038946</v>
+        <v>7039192</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6247,7 +6247,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129298769</v>
+        <v>129298750</v>
       </c>
       <c r="B58" t="n">
         <v>57736</v>
@@ -6282,10 +6282,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>487109</v>
+        <v>487272</v>
       </c>
       <c r="R58" t="n">
-        <v>7039040</v>
+        <v>7038946</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6349,7 +6349,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129298804</v>
+        <v>129298769</v>
       </c>
       <c r="B59" t="n">
         <v>57736</v>
@@ -6384,10 +6384,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>487288</v>
+        <v>487109</v>
       </c>
       <c r="R59" t="n">
-        <v>7039002</v>
+        <v>7039040</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6451,7 +6451,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129298794</v>
+        <v>129298792</v>
       </c>
       <c r="B60" t="n">
         <v>57736</v>
@@ -6486,10 +6486,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>487186</v>
+        <v>487153</v>
       </c>
       <c r="R60" t="n">
-        <v>7039192</v>
+        <v>7039212</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8389,7 +8389,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129298797</v>
+        <v>129298803</v>
       </c>
       <c r="B79" t="n">
         <v>57736</v>
@@ -8424,7 +8424,7 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>487134</v>
+        <v>487303</v>
       </c>
       <c r="R79" t="n">
         <v>7039037</v>
@@ -8491,7 +8491,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129298803</v>
+        <v>129298822</v>
       </c>
       <c r="B80" t="n">
         <v>57736</v>
@@ -8526,10 +8526,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>487303</v>
+        <v>487373</v>
       </c>
       <c r="R80" t="n">
-        <v>7039037</v>
+        <v>7038897</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8593,7 +8593,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129298822</v>
+        <v>129298817</v>
       </c>
       <c r="B81" t="n">
         <v>57736</v>
@@ -8628,10 +8628,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>487373</v>
+        <v>487460</v>
       </c>
       <c r="R81" t="n">
-        <v>7038897</v>
+        <v>7038984</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8695,7 +8695,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129298817</v>
+        <v>129298800</v>
       </c>
       <c r="B82" t="n">
         <v>57736</v>
@@ -8723,17 +8723,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>487460</v>
+        <v>487288</v>
       </c>
       <c r="R82" t="n">
-        <v>7038984</v>
+        <v>7039015</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8770,7 +8786,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Födosökande hane</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8797,7 +8813,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129298800</v>
+        <v>129298821</v>
       </c>
       <c r="B83" t="n">
         <v>57736</v>
@@ -8825,33 +8841,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>487288</v>
+        <v>487368</v>
       </c>
       <c r="R83" t="n">
-        <v>7039015</v>
+        <v>7038892</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Födosökande hane</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8915,7 +8915,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129298821</v>
+        <v>129298797</v>
       </c>
       <c r="B84" t="n">
         <v>57736</v>
@@ -8950,10 +8950,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>487368</v>
+        <v>487134</v>
       </c>
       <c r="R84" t="n">
-        <v>7038892</v>
+        <v>7039037</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9629,61 +9629,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129298847</v>
+        <v>129298789</v>
       </c>
       <c r="B91" t="n">
-        <v>57596</v>
+        <v>57736</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100136</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>486999</v>
+        <v>487041</v>
       </c>
       <c r="R91" t="n">
-        <v>7039199</v>
+        <v>7039167</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9720,7 +9704,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Jagades av en nötskrika</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9747,7 +9731,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129298789</v>
+        <v>129298801</v>
       </c>
       <c r="B92" t="n">
         <v>57736</v>
@@ -9782,10 +9766,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>487041</v>
+        <v>487268</v>
       </c>
       <c r="R92" t="n">
-        <v>7039167</v>
+        <v>7039003</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9849,7 +9833,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129298801</v>
+        <v>129298814</v>
       </c>
       <c r="B93" t="n">
         <v>57736</v>
@@ -9884,10 +9868,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>487268</v>
+        <v>487366</v>
       </c>
       <c r="R93" t="n">
-        <v>7039003</v>
+        <v>7038997</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9924,7 +9908,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9951,7 +9935,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129298814</v>
+        <v>129298772</v>
       </c>
       <c r="B94" t="n">
         <v>57736</v>
@@ -9986,10 +9970,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>487366</v>
+        <v>486849</v>
       </c>
       <c r="R94" t="n">
-        <v>7038997</v>
+        <v>7039185</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10026,7 +10010,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10053,7 +10037,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129298772</v>
+        <v>129298746</v>
       </c>
       <c r="B95" t="n">
         <v>57736</v>
@@ -10088,10 +10072,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>486849</v>
+        <v>487316</v>
       </c>
       <c r="R95" t="n">
-        <v>7039185</v>
+        <v>7038914</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10155,45 +10139,61 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129298746</v>
+        <v>129298847</v>
       </c>
       <c r="B96" t="n">
-        <v>57736</v>
+        <v>57596</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>100136</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>487316</v>
+        <v>486999</v>
       </c>
       <c r="R96" t="n">
-        <v>7038914</v>
+        <v>7039199</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10230,7 +10230,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Jagades av en nötskrika</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10563,7 +10563,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129298791</v>
+        <v>129298754</v>
       </c>
       <c r="B100" t="n">
         <v>57736</v>
@@ -10598,10 +10598,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>487112</v>
+        <v>487222</v>
       </c>
       <c r="R100" t="n">
-        <v>7039182</v>
+        <v>7038974</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10638,7 +10638,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10665,7 +10665,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129298754</v>
+        <v>129298791</v>
       </c>
       <c r="B101" t="n">
         <v>57736</v>
@@ -10700,10 +10700,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>487222</v>
+        <v>487112</v>
       </c>
       <c r="R101" t="n">
-        <v>7038974</v>
+        <v>7039182</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10740,7 +10740,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10869,7 +10869,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129298806</v>
+        <v>129298782</v>
       </c>
       <c r="B103" t="n">
         <v>57736</v>
@@ -10904,10 +10904,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>487339</v>
+        <v>486857</v>
       </c>
       <c r="R103" t="n">
-        <v>7039009</v>
+        <v>7039276</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10944,7 +10944,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10971,7 +10971,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129298782</v>
+        <v>129298758</v>
       </c>
       <c r="B104" t="n">
         <v>57736</v>
@@ -11006,10 +11006,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>486857</v>
+        <v>487183</v>
       </c>
       <c r="R104" t="n">
-        <v>7039276</v>
+        <v>7038993</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11046,7 +11046,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11073,7 +11073,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129298758</v>
+        <v>129298815</v>
       </c>
       <c r="B105" t="n">
         <v>57736</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>487183</v>
+        <v>487375</v>
       </c>
       <c r="R105" t="n">
-        <v>7038993</v>
+        <v>7038981</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11175,7 +11175,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129298815</v>
+        <v>129298788</v>
       </c>
       <c r="B106" t="n">
         <v>57736</v>
@@ -11210,10 +11210,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>487375</v>
+        <v>487039</v>
       </c>
       <c r="R106" t="n">
-        <v>7038981</v>
+        <v>7039164</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11277,7 +11277,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129298788</v>
+        <v>129298806</v>
       </c>
       <c r="B107" t="n">
         <v>57736</v>
@@ -11312,10 +11312,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>487039</v>
+        <v>487339</v>
       </c>
       <c r="R107" t="n">
-        <v>7039164</v>
+        <v>7039009</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11583,7 +11583,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129298760</v>
+        <v>129298790</v>
       </c>
       <c r="B110" t="n">
         <v>57736</v>
@@ -11618,10 +11618,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>487141</v>
+        <v>487044</v>
       </c>
       <c r="R110" t="n">
-        <v>7039023</v>
+        <v>7039168</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11658,7 +11658,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11685,7 +11685,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129298790</v>
+        <v>129298760</v>
       </c>
       <c r="B111" t="n">
         <v>57736</v>
@@ -11720,10 +11720,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>487044</v>
+        <v>487141</v>
       </c>
       <c r="R111" t="n">
-        <v>7039168</v>
+        <v>7039023</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11760,7 +11760,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD111" t="b">

--- a/artfynd/A 46357-2025 artfynd.xlsx
+++ b/artfynd/A 46357-2025 artfynd.xlsx
@@ -4098,7 +4098,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129298786</v>
+        <v>129298818</v>
       </c>
       <c r="B37" t="n">
         <v>57736</v>
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>487006</v>
+        <v>487389</v>
       </c>
       <c r="R37" t="n">
-        <v>7039175</v>
+        <v>7038925</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4200,7 +4200,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129298818</v>
+        <v>129298819</v>
       </c>
       <c r="B38" t="n">
         <v>57736</v>
@@ -4235,10 +4235,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>487389</v>
+        <v>487346</v>
       </c>
       <c r="R38" t="n">
-        <v>7038925</v>
+        <v>7038911</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4302,7 +4302,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129298819</v>
+        <v>129298786</v>
       </c>
       <c r="B39" t="n">
         <v>57736</v>
@@ -4337,10 +4337,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>487346</v>
+        <v>487006</v>
       </c>
       <c r="R39" t="n">
-        <v>7038911</v>
+        <v>7039175</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5118,7 +5118,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129298775</v>
+        <v>129298780</v>
       </c>
       <c r="B47" t="n">
         <v>57736</v>
@@ -5153,10 +5153,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486860</v>
+        <v>486859</v>
       </c>
       <c r="R47" t="n">
-        <v>7039244</v>
+        <v>7039262</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5193,7 +5193,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5220,27 +5220,27 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129298780</v>
+        <v>129298830</v>
       </c>
       <c r="B48" t="n">
-        <v>57736</v>
+        <v>57577</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5248,17 +5248,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486859</v>
+        <v>487123</v>
       </c>
       <c r="R48" t="n">
-        <v>7039262</v>
+        <v>7039173</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5291,11 +5303,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5322,7 +5329,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129298808</v>
+        <v>129298775</v>
       </c>
       <c r="B49" t="n">
         <v>57736</v>
@@ -5357,10 +5364,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>487344</v>
+        <v>486860</v>
       </c>
       <c r="R49" t="n">
-        <v>7039018</v>
+        <v>7039244</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5424,27 +5431,27 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129298830</v>
+        <v>129298808</v>
       </c>
       <c r="B50" t="n">
-        <v>57577</v>
+        <v>57736</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5452,29 +5459,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>487123</v>
+        <v>487344</v>
       </c>
       <c r="R50" t="n">
-        <v>7039173</v>
+        <v>7039018</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5507,6 +5502,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5635,7 +5635,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129298793</v>
+        <v>129298765</v>
       </c>
       <c r="B52" t="n">
         <v>57736</v>
@@ -5670,10 +5670,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>487183</v>
+        <v>487122</v>
       </c>
       <c r="R52" t="n">
-        <v>7039216</v>
+        <v>7039034</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5737,7 +5737,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129298765</v>
+        <v>129298770</v>
       </c>
       <c r="B53" t="n">
         <v>57736</v>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>487122</v>
+        <v>486972</v>
       </c>
       <c r="R53" t="n">
-        <v>7039034</v>
+        <v>7039122</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129298770</v>
+        <v>129298778</v>
       </c>
       <c r="B54" t="n">
         <v>57736</v>
@@ -5874,10 +5874,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486972</v>
+        <v>486871</v>
       </c>
       <c r="R54" t="n">
-        <v>7039122</v>
+        <v>7039260</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5941,7 +5941,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129298778</v>
+        <v>129298793</v>
       </c>
       <c r="B55" t="n">
         <v>57736</v>
@@ -5976,10 +5976,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>486871</v>
+        <v>487183</v>
       </c>
       <c r="R55" t="n">
-        <v>7039260</v>
+        <v>7039216</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6553,7 +6553,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129298805</v>
+        <v>129298802</v>
       </c>
       <c r="B61" t="n">
         <v>57736</v>
@@ -6588,10 +6588,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>487346</v>
+        <v>487302</v>
       </c>
       <c r="R61" t="n">
-        <v>7039012</v>
+        <v>7039045</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6655,7 +6655,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129298809</v>
+        <v>129298795</v>
       </c>
       <c r="B62" t="n">
         <v>57736</v>
@@ -6690,10 +6690,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>487348</v>
+        <v>487100</v>
       </c>
       <c r="R62" t="n">
-        <v>7039005</v>
+        <v>7039085</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6757,7 +6757,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129298802</v>
+        <v>129298748</v>
       </c>
       <c r="B63" t="n">
         <v>57736</v>
@@ -6792,10 +6792,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>487302</v>
+        <v>487301</v>
       </c>
       <c r="R63" t="n">
-        <v>7039045</v>
+        <v>7038925</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6859,7 +6859,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129298795</v>
+        <v>129298783</v>
       </c>
       <c r="B64" t="n">
         <v>57736</v>
@@ -6894,10 +6894,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>487100</v>
+        <v>487024</v>
       </c>
       <c r="R64" t="n">
-        <v>7039085</v>
+        <v>7039203</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6961,7 +6961,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129298748</v>
+        <v>129298805</v>
       </c>
       <c r="B65" t="n">
         <v>57736</v>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>487301</v>
+        <v>487346</v>
       </c>
       <c r="R65" t="n">
-        <v>7038925</v>
+        <v>7039012</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7063,7 +7063,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129298783</v>
+        <v>129298809</v>
       </c>
       <c r="B66" t="n">
         <v>57736</v>
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>487024</v>
+        <v>487348</v>
       </c>
       <c r="R66" t="n">
-        <v>7039203</v>
+        <v>7039005</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -10257,7 +10257,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129298752</v>
+        <v>129298768</v>
       </c>
       <c r="B97" t="n">
         <v>57736</v>
@@ -10292,10 +10292,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>487246</v>
+        <v>487123</v>
       </c>
       <c r="R97" t="n">
-        <v>7038958</v>
+        <v>7039032</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10359,7 +10359,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129298768</v>
+        <v>129298752</v>
       </c>
       <c r="B98" t="n">
         <v>57736</v>
@@ -10394,10 +10394,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>487123</v>
+        <v>487246</v>
       </c>
       <c r="R98" t="n">
-        <v>7039032</v>
+        <v>7038958</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>

--- a/artfynd/A 46357-2025 artfynd.xlsx
+++ b/artfynd/A 46357-2025 artfynd.xlsx
@@ -4098,7 +4098,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129298818</v>
+        <v>129298786</v>
       </c>
       <c r="B37" t="n">
         <v>57736</v>
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>487389</v>
+        <v>487006</v>
       </c>
       <c r="R37" t="n">
-        <v>7038925</v>
+        <v>7039175</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4200,7 +4200,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129298819</v>
+        <v>129298818</v>
       </c>
       <c r="B38" t="n">
         <v>57736</v>
@@ -4235,10 +4235,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>487346</v>
+        <v>487389</v>
       </c>
       <c r="R38" t="n">
-        <v>7038911</v>
+        <v>7038925</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4302,7 +4302,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129298786</v>
+        <v>129298819</v>
       </c>
       <c r="B39" t="n">
         <v>57736</v>
@@ -4337,10 +4337,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>487006</v>
+        <v>487346</v>
       </c>
       <c r="R39" t="n">
-        <v>7039175</v>
+        <v>7038911</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5118,7 +5118,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129298780</v>
+        <v>129298775</v>
       </c>
       <c r="B47" t="n">
         <v>57736</v>
@@ -5153,10 +5153,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486859</v>
+        <v>486860</v>
       </c>
       <c r="R47" t="n">
-        <v>7039262</v>
+        <v>7039244</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5193,7 +5193,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5220,27 +5220,27 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129298830</v>
+        <v>129298780</v>
       </c>
       <c r="B48" t="n">
-        <v>57577</v>
+        <v>57736</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5248,29 +5248,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>487123</v>
+        <v>486859</v>
       </c>
       <c r="R48" t="n">
-        <v>7039173</v>
+        <v>7039262</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5303,6 +5291,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5329,7 +5322,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129298775</v>
+        <v>129298808</v>
       </c>
       <c r="B49" t="n">
         <v>57736</v>
@@ -5364,10 +5357,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486860</v>
+        <v>487344</v>
       </c>
       <c r="R49" t="n">
-        <v>7039244</v>
+        <v>7039018</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5431,27 +5424,27 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129298808</v>
+        <v>129298830</v>
       </c>
       <c r="B50" t="n">
-        <v>57736</v>
+        <v>57577</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5459,17 +5452,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>487344</v>
+        <v>487123</v>
       </c>
       <c r="R50" t="n">
-        <v>7039018</v>
+        <v>7039173</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5502,11 +5507,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6043,7 +6043,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129298804</v>
+        <v>129298792</v>
       </c>
       <c r="B56" t="n">
         <v>57736</v>
@@ -6078,10 +6078,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>487288</v>
+        <v>487153</v>
       </c>
       <c r="R56" t="n">
-        <v>7039002</v>
+        <v>7039212</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6145,7 +6145,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129298794</v>
+        <v>129298804</v>
       </c>
       <c r="B57" t="n">
         <v>57736</v>
@@ -6180,10 +6180,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>487186</v>
+        <v>487288</v>
       </c>
       <c r="R57" t="n">
-        <v>7039192</v>
+        <v>7039002</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6247,7 +6247,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129298750</v>
+        <v>129298794</v>
       </c>
       <c r="B58" t="n">
         <v>57736</v>
@@ -6282,10 +6282,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>487272</v>
+        <v>487186</v>
       </c>
       <c r="R58" t="n">
-        <v>7038946</v>
+        <v>7039192</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6349,7 +6349,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129298769</v>
+        <v>129298750</v>
       </c>
       <c r="B59" t="n">
         <v>57736</v>
@@ -6384,10 +6384,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>487109</v>
+        <v>487272</v>
       </c>
       <c r="R59" t="n">
-        <v>7039040</v>
+        <v>7038946</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6451,7 +6451,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129298792</v>
+        <v>129298769</v>
       </c>
       <c r="B60" t="n">
         <v>57736</v>
@@ -6486,10 +6486,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>487153</v>
+        <v>487109</v>
       </c>
       <c r="R60" t="n">
-        <v>7039212</v>
+        <v>7039040</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7777,7 +7777,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129298816</v>
+        <v>129298774</v>
       </c>
       <c r="B73" t="n">
         <v>57736</v>
@@ -7812,10 +7812,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>487389</v>
+        <v>486866</v>
       </c>
       <c r="R73" t="n">
-        <v>7038985</v>
+        <v>7039249</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7852,7 +7852,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7879,7 +7879,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129298813</v>
+        <v>129298773</v>
       </c>
       <c r="B74" t="n">
         <v>57736</v>
@@ -7914,10 +7914,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>487367</v>
+        <v>486807</v>
       </c>
       <c r="R74" t="n">
-        <v>7038998</v>
+        <v>7039220</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7981,7 +7981,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129298820</v>
+        <v>129298816</v>
       </c>
       <c r="B75" t="n">
         <v>57736</v>
@@ -8016,10 +8016,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>487354</v>
+        <v>487389</v>
       </c>
       <c r="R75" t="n">
-        <v>7038894</v>
+        <v>7038985</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8083,7 +8083,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129298774</v>
+        <v>129298813</v>
       </c>
       <c r="B76" t="n">
         <v>57736</v>
@@ -8118,10 +8118,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>486866</v>
+        <v>487367</v>
       </c>
       <c r="R76" t="n">
-        <v>7039249</v>
+        <v>7038998</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8158,7 +8158,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8185,7 +8185,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129298773</v>
+        <v>129298820</v>
       </c>
       <c r="B77" t="n">
         <v>57736</v>
@@ -8220,10 +8220,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>486807</v>
+        <v>487354</v>
       </c>
       <c r="R77" t="n">
-        <v>7039220</v>
+        <v>7038894</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8260,7 +8260,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">

--- a/artfynd/A 46357-2025 artfynd.xlsx
+++ b/artfynd/A 46357-2025 artfynd.xlsx
@@ -4608,7 +4608,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129298755</v>
+        <v>129298761</v>
       </c>
       <c r="B42" t="n">
         <v>57736</v>
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>487206</v>
+        <v>487137</v>
       </c>
       <c r="R42" t="n">
-        <v>7038982</v>
+        <v>7039024</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4710,7 +4710,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129298799</v>
+        <v>129298755</v>
       </c>
       <c r="B43" t="n">
         <v>57736</v>
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>487230</v>
+        <v>487206</v>
       </c>
       <c r="R43" t="n">
-        <v>7039041</v>
+        <v>7038982</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4812,7 +4812,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129298761</v>
+        <v>129298799</v>
       </c>
       <c r="B44" t="n">
         <v>57736</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>487137</v>
+        <v>487230</v>
       </c>
       <c r="R44" t="n">
-        <v>7039024</v>
+        <v>7039041</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5220,7 +5220,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129298780</v>
+        <v>129298808</v>
       </c>
       <c r="B48" t="n">
         <v>57736</v>
@@ -5255,10 +5255,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486859</v>
+        <v>487344</v>
       </c>
       <c r="R48" t="n">
-        <v>7039262</v>
+        <v>7039018</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5295,7 +5295,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5322,7 +5322,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129298808</v>
+        <v>129298780</v>
       </c>
       <c r="B49" t="n">
         <v>57736</v>
@@ -5357,10 +5357,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>487344</v>
+        <v>486859</v>
       </c>
       <c r="R49" t="n">
-        <v>7039018</v>
+        <v>7039262</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5533,7 +5533,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129298823</v>
+        <v>129298793</v>
       </c>
       <c r="B51" t="n">
         <v>57736</v>
@@ -5568,10 +5568,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>487363</v>
+        <v>487183</v>
       </c>
       <c r="R51" t="n">
-        <v>7038902</v>
+        <v>7039216</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5635,7 +5635,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129298765</v>
+        <v>129298823</v>
       </c>
       <c r="B52" t="n">
         <v>57736</v>
@@ -5670,10 +5670,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>487122</v>
+        <v>487363</v>
       </c>
       <c r="R52" t="n">
-        <v>7039034</v>
+        <v>7038902</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5737,7 +5737,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129298770</v>
+        <v>129298765</v>
       </c>
       <c r="B53" t="n">
         <v>57736</v>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>486972</v>
+        <v>487122</v>
       </c>
       <c r="R53" t="n">
-        <v>7039122</v>
+        <v>7039034</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129298778</v>
+        <v>129298770</v>
       </c>
       <c r="B54" t="n">
         <v>57736</v>
@@ -5874,10 +5874,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>486871</v>
+        <v>486972</v>
       </c>
       <c r="R54" t="n">
-        <v>7039260</v>
+        <v>7039122</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5941,7 +5941,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129298793</v>
+        <v>129298778</v>
       </c>
       <c r="B55" t="n">
         <v>57736</v>
@@ -5976,10 +5976,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>487183</v>
+        <v>486871</v>
       </c>
       <c r="R55" t="n">
-        <v>7039216</v>
+        <v>7039260</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6145,7 +6145,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129298804</v>
+        <v>129298750</v>
       </c>
       <c r="B57" t="n">
         <v>57736</v>
@@ -6180,10 +6180,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>487288</v>
+        <v>487272</v>
       </c>
       <c r="R57" t="n">
-        <v>7039002</v>
+        <v>7038946</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6247,7 +6247,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129298794</v>
+        <v>129298769</v>
       </c>
       <c r="B58" t="n">
         <v>57736</v>
@@ -6282,10 +6282,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>487186</v>
+        <v>487109</v>
       </c>
       <c r="R58" t="n">
-        <v>7039192</v>
+        <v>7039040</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6349,7 +6349,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129298750</v>
+        <v>129298804</v>
       </c>
       <c r="B59" t="n">
         <v>57736</v>
@@ -6384,10 +6384,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>487272</v>
+        <v>487288</v>
       </c>
       <c r="R59" t="n">
-        <v>7038946</v>
+        <v>7039002</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6451,7 +6451,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129298769</v>
+        <v>129298794</v>
       </c>
       <c r="B60" t="n">
         <v>57736</v>
@@ -6486,10 +6486,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>487109</v>
+        <v>487186</v>
       </c>
       <c r="R60" t="n">
-        <v>7039040</v>
+        <v>7039192</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6553,7 +6553,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129298802</v>
+        <v>129298805</v>
       </c>
       <c r="B61" t="n">
         <v>57736</v>
@@ -6588,10 +6588,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>487302</v>
+        <v>487346</v>
       </c>
       <c r="R61" t="n">
-        <v>7039045</v>
+        <v>7039012</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6655,7 +6655,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129298795</v>
+        <v>129298802</v>
       </c>
       <c r="B62" t="n">
         <v>57736</v>
@@ -6690,10 +6690,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>487100</v>
+        <v>487302</v>
       </c>
       <c r="R62" t="n">
-        <v>7039085</v>
+        <v>7039045</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6757,7 +6757,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129298748</v>
+        <v>129298809</v>
       </c>
       <c r="B63" t="n">
         <v>57736</v>
@@ -6792,10 +6792,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>487301</v>
+        <v>487348</v>
       </c>
       <c r="R63" t="n">
-        <v>7038925</v>
+        <v>7039005</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6859,7 +6859,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129298783</v>
+        <v>129298795</v>
       </c>
       <c r="B64" t="n">
         <v>57736</v>
@@ -6894,10 +6894,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>487024</v>
+        <v>487100</v>
       </c>
       <c r="R64" t="n">
-        <v>7039203</v>
+        <v>7039085</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6961,7 +6961,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129298805</v>
+        <v>129298748</v>
       </c>
       <c r="B65" t="n">
         <v>57736</v>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>487346</v>
+        <v>487301</v>
       </c>
       <c r="R65" t="n">
-        <v>7039012</v>
+        <v>7038925</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7063,7 +7063,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129298809</v>
+        <v>129298783</v>
       </c>
       <c r="B66" t="n">
         <v>57736</v>
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>487348</v>
+        <v>487024</v>
       </c>
       <c r="R66" t="n">
-        <v>7039005</v>
+        <v>7039203</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7777,7 +7777,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129298774</v>
+        <v>129298816</v>
       </c>
       <c r="B73" t="n">
         <v>57736</v>
@@ -7812,10 +7812,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>486866</v>
+        <v>487389</v>
       </c>
       <c r="R73" t="n">
-        <v>7039249</v>
+        <v>7038985</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7852,7 +7852,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7879,7 +7879,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129298773</v>
+        <v>129298813</v>
       </c>
       <c r="B74" t="n">
         <v>57736</v>
@@ -7914,10 +7914,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>486807</v>
+        <v>487367</v>
       </c>
       <c r="R74" t="n">
-        <v>7039220</v>
+        <v>7038998</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7981,7 +7981,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129298816</v>
+        <v>129298820</v>
       </c>
       <c r="B75" t="n">
         <v>57736</v>
@@ -8016,10 +8016,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>487389</v>
+        <v>487354</v>
       </c>
       <c r="R75" t="n">
-        <v>7038985</v>
+        <v>7038894</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8083,7 +8083,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129298813</v>
+        <v>129298774</v>
       </c>
       <c r="B76" t="n">
         <v>57736</v>
@@ -8118,10 +8118,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>487367</v>
+        <v>486866</v>
       </c>
       <c r="R76" t="n">
-        <v>7038998</v>
+        <v>7039249</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8158,7 +8158,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8185,7 +8185,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129298820</v>
+        <v>129298773</v>
       </c>
       <c r="B77" t="n">
         <v>57736</v>
@@ -8220,10 +8220,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>487354</v>
+        <v>486807</v>
       </c>
       <c r="R77" t="n">
-        <v>7038894</v>
+        <v>7039220</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8260,7 +8260,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8491,7 +8491,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129298822</v>
+        <v>129298797</v>
       </c>
       <c r="B80" t="n">
         <v>57736</v>
@@ -8526,10 +8526,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>487373</v>
+        <v>487134</v>
       </c>
       <c r="R80" t="n">
-        <v>7038897</v>
+        <v>7039037</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8593,7 +8593,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129298817</v>
+        <v>129298822</v>
       </c>
       <c r="B81" t="n">
         <v>57736</v>
@@ -8628,10 +8628,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>487460</v>
+        <v>487373</v>
       </c>
       <c r="R81" t="n">
-        <v>7038984</v>
+        <v>7038897</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8695,7 +8695,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129298800</v>
+        <v>129298817</v>
       </c>
       <c r="B82" t="n">
         <v>57736</v>
@@ -8723,33 +8723,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>487288</v>
+        <v>487460</v>
       </c>
       <c r="R82" t="n">
-        <v>7039015</v>
+        <v>7038984</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8786,7 +8770,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Födosökande hane</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8813,7 +8797,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129298821</v>
+        <v>129298800</v>
       </c>
       <c r="B83" t="n">
         <v>57736</v>
@@ -8841,17 +8825,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>487368</v>
+        <v>487288</v>
       </c>
       <c r="R83" t="n">
-        <v>7038892</v>
+        <v>7039015</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Födosökande hane</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8915,7 +8915,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129298797</v>
+        <v>129298821</v>
       </c>
       <c r="B84" t="n">
         <v>57736</v>
@@ -8950,10 +8950,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>487134</v>
+        <v>487368</v>
       </c>
       <c r="R84" t="n">
-        <v>7039037</v>
+        <v>7038892</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9527,45 +9527,61 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129298771</v>
+        <v>129298847</v>
       </c>
       <c r="B90" t="n">
-        <v>57736</v>
+        <v>57596</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>100136</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>486885</v>
+        <v>486999</v>
       </c>
       <c r="R90" t="n">
-        <v>7039172</v>
+        <v>7039199</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9602,7 +9618,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Jagades av en nötskrika</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9629,7 +9645,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129298789</v>
+        <v>129298771</v>
       </c>
       <c r="B91" t="n">
         <v>57736</v>
@@ -9664,10 +9680,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>487041</v>
+        <v>486885</v>
       </c>
       <c r="R91" t="n">
-        <v>7039167</v>
+        <v>7039172</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9731,7 +9747,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129298801</v>
+        <v>129298789</v>
       </c>
       <c r="B92" t="n">
         <v>57736</v>
@@ -9766,10 +9782,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>487268</v>
+        <v>487041</v>
       </c>
       <c r="R92" t="n">
-        <v>7039003</v>
+        <v>7039167</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9833,7 +9849,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129298814</v>
+        <v>129298801</v>
       </c>
       <c r="B93" t="n">
         <v>57736</v>
@@ -9868,10 +9884,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>487366</v>
+        <v>487268</v>
       </c>
       <c r="R93" t="n">
-        <v>7038997</v>
+        <v>7039003</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9908,7 +9924,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9935,7 +9951,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129298772</v>
+        <v>129298814</v>
       </c>
       <c r="B94" t="n">
         <v>57736</v>
@@ -9970,10 +9986,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>486849</v>
+        <v>487366</v>
       </c>
       <c r="R94" t="n">
-        <v>7039185</v>
+        <v>7038997</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10010,7 +10026,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10037,7 +10053,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129298746</v>
+        <v>129298772</v>
       </c>
       <c r="B95" t="n">
         <v>57736</v>
@@ -10072,10 +10088,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>487316</v>
+        <v>486849</v>
       </c>
       <c r="R95" t="n">
-        <v>7038914</v>
+        <v>7039185</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10139,61 +10155,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129298847</v>
+        <v>129298746</v>
       </c>
       <c r="B96" t="n">
-        <v>57596</v>
+        <v>57736</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100136</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>486999</v>
+        <v>487316</v>
       </c>
       <c r="R96" t="n">
-        <v>7039199</v>
+        <v>7038914</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10230,7 +10230,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Jagades av en nötskrika</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10257,7 +10257,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129298768</v>
+        <v>129298752</v>
       </c>
       <c r="B97" t="n">
         <v>57736</v>
@@ -10292,10 +10292,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>487123</v>
+        <v>487246</v>
       </c>
       <c r="R97" t="n">
-        <v>7039032</v>
+        <v>7038958</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10359,7 +10359,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129298752</v>
+        <v>129298768</v>
       </c>
       <c r="B98" t="n">
         <v>57736</v>
@@ -10394,10 +10394,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>487246</v>
+        <v>487123</v>
       </c>
       <c r="R98" t="n">
-        <v>7038958</v>
+        <v>7039032</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10563,7 +10563,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129298754</v>
+        <v>129298791</v>
       </c>
       <c r="B100" t="n">
         <v>57736</v>
@@ -10598,10 +10598,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>487222</v>
+        <v>487112</v>
       </c>
       <c r="R100" t="n">
-        <v>7038974</v>
+        <v>7039182</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10638,7 +10638,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10665,7 +10665,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129298791</v>
+        <v>129298754</v>
       </c>
       <c r="B101" t="n">
         <v>57736</v>
@@ -10700,10 +10700,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>487112</v>
+        <v>487222</v>
       </c>
       <c r="R101" t="n">
-        <v>7039182</v>
+        <v>7038974</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10740,7 +10740,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10869,7 +10869,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129298782</v>
+        <v>129298806</v>
       </c>
       <c r="B103" t="n">
         <v>57736</v>
@@ -10904,10 +10904,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>486857</v>
+        <v>487339</v>
       </c>
       <c r="R103" t="n">
-        <v>7039276</v>
+        <v>7039009</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10944,7 +10944,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10971,7 +10971,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129298758</v>
+        <v>129298782</v>
       </c>
       <c r="B104" t="n">
         <v>57736</v>
@@ -11006,10 +11006,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>487183</v>
+        <v>486857</v>
       </c>
       <c r="R104" t="n">
-        <v>7038993</v>
+        <v>7039276</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11046,7 +11046,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11073,7 +11073,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129298815</v>
+        <v>129298758</v>
       </c>
       <c r="B105" t="n">
         <v>57736</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>487375</v>
+        <v>487183</v>
       </c>
       <c r="R105" t="n">
-        <v>7038981</v>
+        <v>7038993</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11175,7 +11175,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129298788</v>
+        <v>129298815</v>
       </c>
       <c r="B106" t="n">
         <v>57736</v>
@@ -11210,10 +11210,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>487039</v>
+        <v>487375</v>
       </c>
       <c r="R106" t="n">
-        <v>7039164</v>
+        <v>7038981</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11277,7 +11277,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129298806</v>
+        <v>129298788</v>
       </c>
       <c r="B107" t="n">
         <v>57736</v>
@@ -11312,10 +11312,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>487339</v>
+        <v>487039</v>
       </c>
       <c r="R107" t="n">
-        <v>7039009</v>
+        <v>7039164</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11583,7 +11583,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129298790</v>
+        <v>129298760</v>
       </c>
       <c r="B110" t="n">
         <v>57736</v>
@@ -11618,10 +11618,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>487044</v>
+        <v>487141</v>
       </c>
       <c r="R110" t="n">
-        <v>7039168</v>
+        <v>7039023</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11658,7 +11658,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11685,7 +11685,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129298760</v>
+        <v>129298790</v>
       </c>
       <c r="B111" t="n">
         <v>57736</v>
@@ -11720,10 +11720,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>487141</v>
+        <v>487044</v>
       </c>
       <c r="R111" t="n">
-        <v>7039023</v>
+        <v>7039168</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11760,7 +11760,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD111" t="b">

--- a/artfynd/A 46357-2025 artfynd.xlsx
+++ b/artfynd/A 46357-2025 artfynd.xlsx
@@ -5118,27 +5118,27 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129298775</v>
+        <v>129298830</v>
       </c>
       <c r="B47" t="n">
-        <v>57736</v>
+        <v>57577</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5146,17 +5146,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>486860</v>
+        <v>487123</v>
       </c>
       <c r="R47" t="n">
-        <v>7039244</v>
+        <v>7039173</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5189,11 +5201,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5220,7 +5227,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129298808</v>
+        <v>129298775</v>
       </c>
       <c r="B48" t="n">
         <v>57736</v>
@@ -5255,10 +5262,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>487344</v>
+        <v>486860</v>
       </c>
       <c r="R48" t="n">
-        <v>7039018</v>
+        <v>7039244</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5322,7 +5329,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129298780</v>
+        <v>129298808</v>
       </c>
       <c r="B49" t="n">
         <v>57736</v>
@@ -5357,10 +5364,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>486859</v>
+        <v>487344</v>
       </c>
       <c r="R49" t="n">
-        <v>7039262</v>
+        <v>7039018</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5397,7 +5404,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5424,27 +5431,27 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129298830</v>
+        <v>129298780</v>
       </c>
       <c r="B50" t="n">
-        <v>57577</v>
+        <v>57736</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5452,29 +5459,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>487123</v>
+        <v>486859</v>
       </c>
       <c r="R50" t="n">
-        <v>7039173</v>
+        <v>7039262</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5507,6 +5502,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -10869,7 +10869,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129298806</v>
+        <v>129298782</v>
       </c>
       <c r="B103" t="n">
         <v>57736</v>
@@ -10904,10 +10904,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>487339</v>
+        <v>486857</v>
       </c>
       <c r="R103" t="n">
-        <v>7039009</v>
+        <v>7039276</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10944,7 +10944,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10971,7 +10971,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129298782</v>
+        <v>129298758</v>
       </c>
       <c r="B104" t="n">
         <v>57736</v>
@@ -11006,10 +11006,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>486857</v>
+        <v>487183</v>
       </c>
       <c r="R104" t="n">
-        <v>7039276</v>
+        <v>7038993</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11046,7 +11046,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11073,7 +11073,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129298758</v>
+        <v>129298815</v>
       </c>
       <c r="B105" t="n">
         <v>57736</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>487183</v>
+        <v>487375</v>
       </c>
       <c r="R105" t="n">
-        <v>7038993</v>
+        <v>7038981</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11175,7 +11175,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129298815</v>
+        <v>129298788</v>
       </c>
       <c r="B106" t="n">
         <v>57736</v>
@@ -11210,10 +11210,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>487375</v>
+        <v>487039</v>
       </c>
       <c r="R106" t="n">
-        <v>7038981</v>
+        <v>7039164</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11277,7 +11277,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129298788</v>
+        <v>129298806</v>
       </c>
       <c r="B107" t="n">
         <v>57736</v>
@@ -11312,10 +11312,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>487039</v>
+        <v>487339</v>
       </c>
       <c r="R107" t="n">
-        <v>7039164</v>
+        <v>7039009</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>

--- a/artfynd/A 46357-2025 artfynd.xlsx
+++ b/artfynd/A 46357-2025 artfynd.xlsx
@@ -5118,27 +5118,27 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129298830</v>
+        <v>129298775</v>
       </c>
       <c r="B47" t="n">
-        <v>57577</v>
+        <v>57736</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5146,29 +5146,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>487123</v>
+        <v>486860</v>
       </c>
       <c r="R47" t="n">
-        <v>7039173</v>
+        <v>7039244</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5201,6 +5189,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5227,7 +5220,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129298775</v>
+        <v>129298808</v>
       </c>
       <c r="B48" t="n">
         <v>57736</v>
@@ -5262,10 +5255,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>486860</v>
+        <v>487344</v>
       </c>
       <c r="R48" t="n">
-        <v>7039244</v>
+        <v>7039018</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5329,7 +5322,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129298808</v>
+        <v>129298780</v>
       </c>
       <c r="B49" t="n">
         <v>57736</v>
@@ -5364,10 +5357,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>487344</v>
+        <v>486859</v>
       </c>
       <c r="R49" t="n">
-        <v>7039018</v>
+        <v>7039262</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5404,7 +5397,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5431,27 +5424,27 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129298780</v>
+        <v>129298830</v>
       </c>
       <c r="B50" t="n">
-        <v>57736</v>
+        <v>57577</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5459,17 +5452,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>486859</v>
+        <v>487123</v>
       </c>
       <c r="R50" t="n">
-        <v>7039262</v>
+        <v>7039173</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5502,11 +5507,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6553,7 +6553,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129298805</v>
+        <v>129298809</v>
       </c>
       <c r="B61" t="n">
         <v>57736</v>
@@ -6588,10 +6588,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>487346</v>
+        <v>487348</v>
       </c>
       <c r="R61" t="n">
-        <v>7039012</v>
+        <v>7039005</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6655,7 +6655,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129298802</v>
+        <v>129298795</v>
       </c>
       <c r="B62" t="n">
         <v>57736</v>
@@ -6690,10 +6690,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>487302</v>
+        <v>487100</v>
       </c>
       <c r="R62" t="n">
-        <v>7039045</v>
+        <v>7039085</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6757,7 +6757,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129298809</v>
+        <v>129298748</v>
       </c>
       <c r="B63" t="n">
         <v>57736</v>
@@ -6792,10 +6792,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>487348</v>
+        <v>487301</v>
       </c>
       <c r="R63" t="n">
-        <v>7039005</v>
+        <v>7038925</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6859,7 +6859,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129298795</v>
+        <v>129298783</v>
       </c>
       <c r="B64" t="n">
         <v>57736</v>
@@ -6894,10 +6894,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>487100</v>
+        <v>487024</v>
       </c>
       <c r="R64" t="n">
-        <v>7039085</v>
+        <v>7039203</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6961,7 +6961,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129298748</v>
+        <v>129298805</v>
       </c>
       <c r="B65" t="n">
         <v>57736</v>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>487301</v>
+        <v>487346</v>
       </c>
       <c r="R65" t="n">
-        <v>7038925</v>
+        <v>7039012</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7063,7 +7063,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129298783</v>
+        <v>129298802</v>
       </c>
       <c r="B66" t="n">
         <v>57736</v>
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>487024</v>
+        <v>487302</v>
       </c>
       <c r="R66" t="n">
-        <v>7039203</v>
+        <v>7039045</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -10869,7 +10869,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129298782</v>
+        <v>129298806</v>
       </c>
       <c r="B103" t="n">
         <v>57736</v>
@@ -10904,10 +10904,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>486857</v>
+        <v>487339</v>
       </c>
       <c r="R103" t="n">
-        <v>7039276</v>
+        <v>7039009</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10944,7 +10944,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10971,7 +10971,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129298758</v>
+        <v>129298782</v>
       </c>
       <c r="B104" t="n">
         <v>57736</v>
@@ -11006,10 +11006,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>487183</v>
+        <v>486857</v>
       </c>
       <c r="R104" t="n">
-        <v>7038993</v>
+        <v>7039276</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11046,7 +11046,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11073,7 +11073,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129298815</v>
+        <v>129298758</v>
       </c>
       <c r="B105" t="n">
         <v>57736</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>487375</v>
+        <v>487183</v>
       </c>
       <c r="R105" t="n">
-        <v>7038981</v>
+        <v>7038993</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11175,7 +11175,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129298788</v>
+        <v>129298815</v>
       </c>
       <c r="B106" t="n">
         <v>57736</v>
@@ -11210,10 +11210,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>487039</v>
+        <v>487375</v>
       </c>
       <c r="R106" t="n">
-        <v>7039164</v>
+        <v>7038981</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11277,7 +11277,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129298806</v>
+        <v>129298788</v>
       </c>
       <c r="B107" t="n">
         <v>57736</v>
@@ -11312,10 +11312,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>487339</v>
+        <v>487039</v>
       </c>
       <c r="R107" t="n">
-        <v>7039009</v>
+        <v>7039164</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>

--- a/artfynd/A 46357-2025 artfynd.xlsx
+++ b/artfynd/A 46357-2025 artfynd.xlsx
@@ -3999,7 +3999,7 @@
         <v>129298751</v>
       </c>
       <c r="B36" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         <v>129298786</v>
       </c>
       <c r="B37" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>129298818</v>
       </c>
       <c r="B38" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>129298819</v>
       </c>
       <c r="B39" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>129298812</v>
       </c>
       <c r="B40" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>129298759</v>
       </c>
       <c r="B41" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>129298761</v>
       </c>
       <c r="B42" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>129298755</v>
       </c>
       <c r="B43" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>129298799</v>
       </c>
       <c r="B44" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>129298777</v>
       </c>
       <c r="B45" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>129298787</v>
       </c>
       <c r="B46" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>129298775</v>
       </c>
       <c r="B47" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>129298808</v>
       </c>
       <c r="B48" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>129298780</v>
       </c>
       <c r="B49" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>129298830</v>
       </c>
       <c r="B50" t="n">
-        <v>57577</v>
+        <v>57578</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>129298793</v>
       </c>
       <c r="B51" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>129298823</v>
       </c>
       <c r="B52" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>129298765</v>
       </c>
       <c r="B53" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>129298770</v>
       </c>
       <c r="B54" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>129298778</v>
       </c>
       <c r="B55" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>129298792</v>
       </c>
       <c r="B56" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>129298750</v>
       </c>
       <c r="B57" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>129298769</v>
       </c>
       <c r="B58" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>129298804</v>
       </c>
       <c r="B59" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>129298794</v>
       </c>
       <c r="B60" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6553,10 +6553,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129298809</v>
+        <v>129298805</v>
       </c>
       <c r="B61" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6588,10 +6588,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>487348</v>
+        <v>487346</v>
       </c>
       <c r="R61" t="n">
-        <v>7039005</v>
+        <v>7039012</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6655,10 +6655,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129298795</v>
+        <v>129298809</v>
       </c>
       <c r="B62" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6690,10 +6690,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>487100</v>
+        <v>487348</v>
       </c>
       <c r="R62" t="n">
-        <v>7039085</v>
+        <v>7039005</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6757,10 +6757,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129298748</v>
+        <v>129298802</v>
       </c>
       <c r="B63" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6792,10 +6792,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>487301</v>
+        <v>487302</v>
       </c>
       <c r="R63" t="n">
-        <v>7038925</v>
+        <v>7039045</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6859,10 +6859,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129298783</v>
+        <v>129298795</v>
       </c>
       <c r="B64" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6894,10 +6894,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>487024</v>
+        <v>487100</v>
       </c>
       <c r="R64" t="n">
-        <v>7039203</v>
+        <v>7039085</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6961,10 +6961,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129298805</v>
+        <v>129298748</v>
       </c>
       <c r="B65" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>487346</v>
+        <v>487301</v>
       </c>
       <c r="R65" t="n">
-        <v>7039012</v>
+        <v>7038925</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7063,10 +7063,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129298802</v>
+        <v>129298783</v>
       </c>
       <c r="B66" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>487302</v>
+        <v>487024</v>
       </c>
       <c r="R66" t="n">
-        <v>7039045</v>
+        <v>7039203</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7168,7 +7168,7 @@
         <v>129298798</v>
       </c>
       <c r="B67" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>129298810</v>
       </c>
       <c r="B68" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>129298779</v>
       </c>
       <c r="B69" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>129298749</v>
       </c>
       <c r="B70" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>129298767</v>
       </c>
       <c r="B71" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>129298776</v>
       </c>
       <c r="B72" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>129298816</v>
       </c>
       <c r="B73" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>129298813</v>
       </c>
       <c r="B74" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>129298820</v>
       </c>
       <c r="B75" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>129298774</v>
       </c>
       <c r="B76" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         <v>129298773</v>
       </c>
       <c r="B77" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>129298811</v>
       </c>
       <c r="B78" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8389,10 +8389,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129298803</v>
+        <v>129298797</v>
       </c>
       <c r="B79" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>487303</v>
+        <v>487134</v>
       </c>
       <c r="R79" t="n">
         <v>7039037</v>
@@ -8491,10 +8491,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129298797</v>
+        <v>129298803</v>
       </c>
       <c r="B80" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>487134</v>
+        <v>487303</v>
       </c>
       <c r="R80" t="n">
         <v>7039037</v>
@@ -8596,7 +8596,7 @@
         <v>129298822</v>
       </c>
       <c r="B81" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>129298817</v>
       </c>
       <c r="B82" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>129298800</v>
       </c>
       <c r="B83" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         <v>129298821</v>
       </c>
       <c r="B84" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>129298781</v>
       </c>
       <c r="B85" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>129298785</v>
       </c>
       <c r="B86" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>129298753</v>
       </c>
       <c r="B87" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9326,7 +9326,7 @@
         <v>129298757</v>
       </c>
       <c r="B88" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>129298784</v>
       </c>
       <c r="B89" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9527,61 +9527,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129298847</v>
+        <v>129298771</v>
       </c>
       <c r="B90" t="n">
-        <v>57596</v>
+        <v>57737</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100136</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>486999</v>
+        <v>486885</v>
       </c>
       <c r="R90" t="n">
-        <v>7039199</v>
+        <v>7039172</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9618,7 +9602,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Jagades av en nötskrika</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9645,45 +9629,61 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129298771</v>
+        <v>129298847</v>
       </c>
       <c r="B91" t="n">
-        <v>57736</v>
+        <v>57597</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>100136</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Tomasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>486885</v>
+        <v>486999</v>
       </c>
       <c r="R91" t="n">
-        <v>7039172</v>
+        <v>7039199</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9720,7 +9720,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Jagades av en nötskrika</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9750,7 +9750,7 @@
         <v>129298789</v>
       </c>
       <c r="B92" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>129298801</v>
       </c>
       <c r="B93" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>129298814</v>
       </c>
       <c r="B94" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10056,7 +10056,7 @@
         <v>129298772</v>
       </c>
       <c r="B95" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>129298746</v>
       </c>
       <c r="B96" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>129298752</v>
       </c>
       <c r="B97" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>129298768</v>
       </c>
       <c r="B98" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
         <v>129298745</v>
       </c>
       <c r="B99" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10566,7 +10566,7 @@
         <v>129298791</v>
       </c>
       <c r="B100" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>129298754</v>
       </c>
       <c r="B101" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>129298807</v>
       </c>
       <c r="B102" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
         <v>129298806</v>
       </c>
       <c r="B103" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>129298782</v>
       </c>
       <c r="B104" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>129298758</v>
       </c>
       <c r="B105" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>129298815</v>
       </c>
       <c r="B106" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>129298788</v>
       </c>
       <c r="B107" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>129298766</v>
       </c>
       <c r="B108" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11484,7 +11484,7 @@
         <v>129298796</v>
       </c>
       <c r="B109" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>129298760</v>
       </c>
       <c r="B110" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>129298790</v>
       </c>
       <c r="B111" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
